--- a/reports/screener_2026-08-11.xlsx
+++ b/reports/screener_2026-08-11.xlsx
@@ -1050,10 +1050,10 @@
         <v>10.27999973297119</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.806939247152598</v>
+        <v>5.806939298270844</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.77187230346807</v>
+        <v>10.77187239829242</v>
       </c>
       <c r="BI2" t="n">
         <v>35.84473591101796</v>
@@ -1062,7 +1062,7 @@
         <v>24.64756109389902</v>
       </c>
       <c r="BK2" t="n">
-        <v>61.97293301439586</v>
+        <v>61.97293320272624</v>
       </c>
       <c r="BL2" t="n">
         <v>17.08511007767805</v>
@@ -1317,10 +1317,10 @@
         <v>4.039999961853027</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.419224480245221</v>
+        <v>3.419461684738401</v>
       </c>
       <c r="BH3" t="n">
-        <v>6.342661410854884</v>
+        <v>6.343101425189735</v>
       </c>
       <c r="BI3" t="n">
         <v>12.47785536003557</v>
@@ -1329,25 +1329,25 @@
         <v>8.411070803097941</v>
       </c>
       <c r="BK3" t="n">
-        <v>24.27141720569131</v>
+        <v>24.27125083123389</v>
       </c>
       <c r="BL3" t="n">
-        <v>11.09300742705852</v>
+        <v>11.09291018546735</v>
       </c>
       <c r="BM3" t="n">
-        <v>10.7582764727997</v>
+        <v>10.75768532124998</v>
       </c>
       <c r="BN3" t="n">
         <v>4.904734709731053</v>
       </c>
       <c r="BO3" t="n">
-        <v>8.997934363929613</v>
+        <v>8.997892967461938</v>
       </c>
       <c r="BP3" t="n">
-        <v>9.584673637948821</v>
+        <v>9.584378062173961</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.62620627415394</v>
+        <v>8.625940255956566</v>
       </c>
       <c r="BR3" t="n">
         <v>6</v>
@@ -1359,10 +1359,10 @@
         <v>7.1</v>
       </c>
       <c r="BU3" t="n">
-        <v>113.5199592971619</v>
+        <v>113.5133746882538</v>
       </c>
       <c r="BV3" t="n">
-        <v>122.7211497250245</v>
+        <v>122.7201250599733</v>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
@@ -1594,10 +1594,10 @@
         <v>23.79999923706055</v>
       </c>
       <c r="BG4" t="n">
-        <v>15.6708491740659</v>
+        <v>15.67084913734821</v>
       </c>
       <c r="BH4" t="n">
-        <v>29.06942521789225</v>
+        <v>29.06942514978093</v>
       </c>
       <c r="BI4" t="n">
         <v>62.32213238953601</v>
@@ -1606,19 +1606,19 @@
         <v>45.62472487613315</v>
       </c>
       <c r="BK4" t="n">
-        <v>103.4137246898866</v>
+        <v>103.4137247113078</v>
       </c>
       <c r="BL4" t="n">
-        <v>20.19414446318722</v>
+        <v>20.19414446787059</v>
       </c>
       <c r="BM4" t="n">
-        <v>50.31447891321876</v>
+        <v>50.31447899054034</v>
       </c>
       <c r="BN4" t="n">
         <v>37.19489833875116</v>
       </c>
       <c r="BO4" t="n">
-        <v>49.73336126980074</v>
+        <v>49.73336127484571</v>
       </c>
       <c r="BP4" t="n">
         <v>45.62472487613315</v>
@@ -1639,7 +1639,7 @@
         <v>72.53047775135681</v>
       </c>
       <c r="BV4" t="n">
-        <v>108.9637095128879</v>
+        <v>108.9637095340853</v>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
@@ -1871,10 +1871,10 @@
         <v>13.63000011444092</v>
       </c>
       <c r="BG5" t="n">
-        <v>15.04788544480291</v>
+        <v>15.04788549860464</v>
       </c>
       <c r="BH5" t="n">
-        <v>27.9138275001094</v>
+        <v>27.91382759991161</v>
       </c>
       <c r="BI5" t="n">
         <v>37.94065157906348</v>
@@ -1883,25 +1883,25 @@
         <v>22.93112736979142</v>
       </c>
       <c r="BK5" t="n">
-        <v>70.78984148599396</v>
+        <v>70.78984138015393</v>
       </c>
       <c r="BL5" t="n">
-        <v>45.29369807452761</v>
+        <v>45.29369803629783</v>
       </c>
       <c r="BM5" t="n">
-        <v>24.32634150128582</v>
+        <v>24.3263413352924</v>
       </c>
       <c r="BN5" t="n">
         <v>8.909513594966207</v>
       </c>
       <c r="BO5" t="n">
-        <v>28.90892191159677</v>
+        <v>28.90892190316023</v>
       </c>
       <c r="BP5" t="n">
-        <v>26.12008450069761</v>
+        <v>26.12008446760201</v>
       </c>
       <c r="BQ5" t="n">
-        <v>23.50807605062785</v>
+        <v>23.50807602084181</v>
       </c>
       <c r="BR5" t="n">
         <v>6</v>
@@ -1913,10 +1913,10 @@
         <v>7.9</v>
       </c>
       <c r="BU5" t="n">
-        <v>72.47304367753568</v>
+        <v>72.47304345900272</v>
       </c>
       <c r="BV5" t="n">
-        <v>112.0977378493776</v>
+        <v>112.0977377874808</v>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
@@ -2148,10 +2148,10 @@
         <v>4.320000171661377</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.922596181840153</v>
+        <v>2.922596170132509</v>
       </c>
       <c r="BH6" t="n">
-        <v>5.421415917313483</v>
+        <v>5.421415895595804</v>
       </c>
       <c r="BI6" t="n">
         <v>12.47058873083077</v>
@@ -2160,7 +2160,7 @@
         <v>8.38874521704944</v>
       </c>
       <c r="BK6" t="n">
-        <v>23.03188434001804</v>
+        <v>23.03188430430845</v>
       </c>
       <c r="BL6" t="n">
         <v>11.34817472758152</v>
@@ -2172,7 +2172,7 @@
         <v>4.921612750118176</v>
       </c>
       <c r="BO6" t="n">
-        <v>10.99580820422241</v>
+        <v>10.99580819601852</v>
       </c>
       <c r="BP6" t="n">
         <v>11.34817472758152</v>
@@ -2193,7 +2193,7 @@
         <v>136.4202974301165</v>
       </c>
       <c r="BV6" t="n">
-        <v>154.5325872057469</v>
+        <v>154.532587015842</v>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>Fundo duplo</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="R7" t="n">
@@ -2425,10 +2425,10 @@
         <v>15.56999969482422</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.370378834709528</v>
+        <v>6.370378843208369</v>
       </c>
       <c r="BH7" t="n">
-        <v>11.81705273838617</v>
+        <v>11.81705275415152</v>
       </c>
       <c r="BI7" t="n">
         <v>25.22035402890231</v>
@@ -2437,19 +2437,19 @@
         <v>18.49208604587491</v>
       </c>
       <c r="BK7" t="n">
-        <v>34.98832838794136</v>
+        <v>34.98832837415703</v>
       </c>
       <c r="BL7" t="n">
-        <v>12.15521321642056</v>
+        <v>12.15521321481462</v>
       </c>
       <c r="BM7" t="n">
-        <v>20.22430271417904</v>
+        <v>20.22430269637158</v>
       </c>
       <c r="BN7" t="n">
         <v>17.52538993234214</v>
       </c>
       <c r="BO7" t="n">
-        <v>20.06038958057807</v>
+        <v>20.06038957808773</v>
       </c>
       <c r="BP7" t="n">
         <v>18.49208604587491</v>
@@ -2470,7 +2470,7 @@
         <v>6.890672880487236</v>
       </c>
       <c r="BV7" t="n">
-        <v>28.84001267672822</v>
+        <v>28.84001266073375</v>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
@@ -2487,16 +2487,8 @@
           <t>última</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>A Mills (MILS3) apresenta-se como uma alternativa robusta no setor de bens industriais, destacando-se por uma eficiência operacional que supera com folga a média de seus pares. A companhia entrega uma rentabilidade excepcional, com ROE de 23,8% e ROIC de 20,6% substancialmente acima das médias setoriais de 15,5% e 12,7%, respectivamente, o que evidencia uma forte geração de valor sobre o capital empregado. Essa alta qualidade operacional convive com múltiplos de preço bastante atrativos, visto que o P/L de 8,18 e o P/VP de 1,95 sugerem que o mercado ainda não precifica totalmente a capacidade de entrega da empresa, uma assimetria reforçada pelo PEG de 0,65. No âmbito financeiro, a excelente rentabilidade é sustentada por uma estrutura de capital muito saudável, com a relação Dívida Líquida/EBITDA em 1,28 vezes, patamar significativamente abaixo da média do setor de 2,29 vezes, e uma liquidez corrente confortável de 2,98. Esse endividamento controlado e a margem líquida robusta de 23,53% conferem sustentabilidade ao dividend yield de 6,78%, mostrando-se coerente com a geração de caixa e a manutenção dos negócios. Por outro lado, o crescimento da receita nos últimos cinco anos, embora expressivo em termos absolutos com um CAGR de 21,3%, ficou muito aquém da média setorial de 117,8%, o que acende um sinal de alerta sobre o ritmo de expansão frente aos concorrentes. No checklist fundamentalista, a empresa atende a 6 dos 8 critérios estipulados, sendo penalizada justamente pelo crescimento inferior aos pares e por movimentações de venda de insiders. Sob a ótica do valuation, as estimativas de preço-teto revelam uma enorme dispersão entre os métodos, variando desde os conservadores R$ 6,37 por Bazin até os otimistas R$ 35,01 por Lynch, resultando em uma média de R$ 20,07 e um preço-teto ajustado com margem de segurança de R$ 16,65, o que confere um upside de 6,9% em relação à cotação atual de R$ 15,58. Em balanço, o ativo traz como pontos positivos a alta rentabilidade, o endividamento sob controle e múltiplos de preço convidativos, enquanto os pontos negativos residem no crescimento histórico abaixo da média do setor e na pressão vendedora por parte de insiders.</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>Fundo duplo</t>
-        </is>
-      </c>
+      <c r="BZ7" t="inlineStr"/>
+      <c r="CA7" t="inlineStr"/>
       <c r="CB7" t="b">
         <v>0</v>
       </c>
@@ -2523,14 +2515,14 @@
         <v>1</v>
       </c>
       <c r="CK7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>Fundo duplo — rompeu pescoço ~R$13.44 (candidato)</t>
+          <t>sem sinal (Em Alta)</t>
         </is>
       </c>
     </row>
@@ -2696,10 +2688,10 @@
         <v>48.38999938964844</v>
       </c>
       <c r="BG8" t="n">
-        <v>18.4311091643195</v>
+        <v>18.43110921108345</v>
       </c>
       <c r="BH8" t="n">
-        <v>34.18970749981268</v>
+        <v>34.18970758655979</v>
       </c>
       <c r="BI8" t="n">
         <v>73.52838210009652</v>
@@ -2708,23 +2700,23 @@
         <v>55.10133168995815</v>
       </c>
       <c r="BK8" t="n">
-        <v>97.40219845085582</v>
+        <v>97.40219837640315</v>
       </c>
       <c r="BL8" t="n">
-        <v>47.18970514406958</v>
+        <v>47.18970513273842</v>
       </c>
       <c r="BM8" t="n">
-        <v>57.44862736282407</v>
+        <v>57.44862726883226</v>
       </c>
       <c r="BN8" t="inlineStr"/>
       <c r="BO8" t="n">
-        <v>43.33472597707457</v>
+        <v>43.33472600761954</v>
       </c>
       <c r="BP8" t="n">
-        <v>40.68970632194113</v>
+        <v>40.68970635964911</v>
       </c>
       <c r="BQ8" t="n">
-        <v>36.62073568974702</v>
+        <v>36.6207357236842</v>
       </c>
       <c r="BR8" t="n">
         <v>4</v>
@@ -2736,10 +2728,10 @@
         <v>4</v>
       </c>
       <c r="BU8" t="n">
-        <v>-24.32168598542923</v>
+        <v>-24.32168591529661</v>
       </c>
       <c r="BV8" t="n">
-        <v>-10.44693836812755</v>
+        <v>-10.44693830500505</v>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
@@ -2957,10 +2949,10 @@
         <v>18.45000076293945</v>
       </c>
       <c r="BG9" t="n">
-        <v>12.68429994841975</v>
+        <v>12.68429990576347</v>
       </c>
       <c r="BH9" t="n">
-        <v>23.52937640431863</v>
+        <v>23.52937632519124</v>
       </c>
       <c r="BI9" t="n">
         <v>19.46357564561686</v>
@@ -2969,7 +2961,7 @@
         <v>12.1658993674517</v>
       </c>
       <c r="BK9" t="n">
-        <v>32.94109944613866</v>
+        <v>32.94109939859185</v>
       </c>
       <c r="BL9" t="n">
         <v>22.27593117185458</v>
@@ -2979,7 +2971,7 @@
       </c>
       <c r="BN9" t="inlineStr"/>
       <c r="BO9" t="n">
-        <v>19.48829579255245</v>
+        <v>19.48829576210654</v>
       </c>
       <c r="BP9" t="n">
         <v>20.86975340873572</v>
@@ -3000,7 +2992,7 @@
         <v>1.80367095480638</v>
       </c>
       <c r="BV9" t="n">
-        <v>5.627615103944184</v>
+        <v>5.627614938925674</v>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
@@ -3223,7 +3215,7 @@
         <v>0.19</v>
       </c>
       <c r="BD10" t="n">
-        <v>128.24</v>
+        <v>128.25</v>
       </c>
       <c r="BE10" t="n">
         <v>35</v>
@@ -3232,10 +3224,10 @@
         <v>31.39999961853027</v>
       </c>
       <c r="BG10" t="n">
-        <v>43.84645055378819</v>
+        <v>43.84701156266345</v>
       </c>
       <c r="BH10" t="n">
-        <v>81.3351657772771</v>
+        <v>81.3362064487407</v>
       </c>
       <c r="BI10" t="n">
         <v>63.4222553270619</v>
@@ -3256,7 +3248,7 @@
         <v>25.86511310728236</v>
       </c>
       <c r="BO10" t="n">
-        <v>67.06903433310754</v>
+        <v>67.06923454314989</v>
       </c>
       <c r="BP10" t="n">
         <v>60.66996877513281</v>
@@ -3277,7 +3269,7 @@
         <v>73.89481707317074</v>
       </c>
       <c r="BV10" t="n">
-        <v>113.5956533372939</v>
+        <v>113.5962909489015</v>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
@@ -3509,10 +3501,10 @@
         <v>31.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>22.10300330650479</v>
+        <v>22.10300332666242</v>
       </c>
       <c r="BH11" t="n">
-        <v>41.00107113356637</v>
+        <v>41.00107117095879</v>
       </c>
       <c r="BI11" t="n">
         <v>45.51526717557251</v>
@@ -3521,25 +3513,25 @@
         <v>19.62721165712462</v>
       </c>
       <c r="BK11" t="n">
-        <v>57.23589733651509</v>
+        <v>57.23589717270841</v>
       </c>
       <c r="BL11" t="n">
-        <v>49.59879613150471</v>
+        <v>49.59879610520782</v>
       </c>
       <c r="BM11" t="n">
-        <v>23.94234276449628</v>
+        <v>23.94234264218778</v>
       </c>
       <c r="BN11" t="n">
         <v>23.78189287402351</v>
       </c>
       <c r="BO11" t="n">
-        <v>35.35068529741349</v>
+        <v>35.35068526555573</v>
       </c>
       <c r="BP11" t="n">
-        <v>32.47170694903133</v>
+        <v>32.47170690657328</v>
       </c>
       <c r="BQ11" t="n">
-        <v>29.2245362541282</v>
+        <v>29.22453621591595</v>
       </c>
       <c r="BR11" t="n">
         <v>8</v>
@@ -3551,10 +3543,10 @@
         <v>2.9</v>
       </c>
       <c r="BU11" t="n">
-        <v>-7.223694431339056</v>
+        <v>-7.223694552647764</v>
       </c>
       <c r="BV11" t="n">
-        <v>12.22439776956663</v>
+        <v>12.22439766843086</v>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
@@ -3786,10 +3778,10 @@
         <v>6.510000228881836</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.939313007595649</v>
+        <v>2.939312997517357</v>
       </c>
       <c r="BH12" t="n">
-        <v>5.452425629089928</v>
+        <v>5.452425610394696</v>
       </c>
       <c r="BI12" t="n">
         <v>21.245690402139</v>
@@ -3798,7 +3790,7 @@
         <v>13.54578759251334</v>
       </c>
       <c r="BK12" t="n">
-        <v>34.18728707871099</v>
+        <v>34.18728704395826</v>
       </c>
       <c r="BL12" t="n">
         <v>11.55192114631721</v>
@@ -4039,10 +4031,10 @@
         <v>13.14000034332275</v>
       </c>
       <c r="BG13" t="n">
-        <v>9.532624397669307</v>
+        <v>9.532624425278916</v>
       </c>
       <c r="BH13" t="n">
-        <v>17.68301825767657</v>
+        <v>17.68301830889239</v>
       </c>
       <c r="BI13" t="n">
         <v>49.32153103371855</v>
@@ -4051,23 +4043,23 @@
         <v>47.39158599337461</v>
       </c>
       <c r="BK13" t="n">
-        <v>71.21193623729023</v>
+        <v>71.21193629271393</v>
       </c>
       <c r="BL13" t="n">
-        <v>31.70486910611248</v>
+        <v>31.70486910188592</v>
       </c>
       <c r="BM13" t="n">
-        <v>30.94181048811404</v>
+        <v>30.9418104541233</v>
       </c>
       <c r="BN13" t="inlineStr"/>
       <c r="BO13" t="n">
-        <v>32.90313946583586</v>
+        <v>32.90313948149895</v>
       </c>
       <c r="BP13" t="n">
-        <v>31.70486910611248</v>
+        <v>31.70486910188592</v>
       </c>
       <c r="BQ13" t="n">
-        <v>28.53438219550123</v>
+        <v>28.53438219169733</v>
       </c>
       <c r="BR13" t="n">
         <v>3</v>
@@ -4079,10 +4071,10 @@
         <v>5.2</v>
       </c>
       <c r="BU13" t="n">
-        <v>117.1566320392169</v>
+        <v>117.1566320102678</v>
       </c>
       <c r="BV13" t="n">
-        <v>150.4044033952859</v>
+        <v>150.4044035144875</v>
       </c>
       <c r="BW13" t="inlineStr">
         <is>
@@ -4314,37 +4306,37 @@
         <v>33.2400016784668</v>
       </c>
       <c r="BG14" t="n">
-        <v>23.90692739356484</v>
+        <v>23.90741365952943</v>
       </c>
       <c r="BH14" t="n">
-        <v>31.38254533312008</v>
+        <v>31.38173465619063</v>
       </c>
       <c r="BI14" t="n">
-        <v>35.57896395648235</v>
+        <v>35.57732123594623</v>
       </c>
       <c r="BJ14" t="n">
         <v>35.59395391834337</v>
       </c>
       <c r="BK14" t="n">
-        <v>49.6423438176403</v>
+        <v>49.64138158167129</v>
       </c>
       <c r="BL14" t="n">
-        <v>48.07460119883368</v>
+        <v>48.074387275934</v>
       </c>
       <c r="BM14" t="n">
-        <v>17.32445864401277</v>
+        <v>17.32336532361797</v>
       </c>
       <c r="BN14" t="n">
         <v>29.12385888600579</v>
       </c>
       <c r="BO14" t="n">
-        <v>33.8284566435004</v>
+        <v>33.82792706715485</v>
       </c>
       <c r="BP14" t="n">
-        <v>33.48075464480122</v>
+        <v>33.47952794606843</v>
       </c>
       <c r="BQ14" t="n">
-        <v>30.13267918032109</v>
+        <v>30.13157515146159</v>
       </c>
       <c r="BR14" t="n">
         <v>8</v>
@@ -4356,10 +4348,10 @@
         <v>2.9</v>
       </c>
       <c r="BU14" t="n">
-        <v>-9.348141820819034</v>
+        <v>-9.351463207111932</v>
       </c>
       <c r="BV14" t="n">
-        <v>1.770321706736899</v>
+        <v>1.768728516848772</v>
       </c>
       <c r="BW14" t="inlineStr">
         <is>
@@ -4396,14 +4388,14 @@
       <c r="CE14" t="inlineStr"/>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="CG14" t="n">
-        <v>33.47999954223633</v>
+        <v>33.70000076293945</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.7168395073206768</v>
+        <v>-1.364982415604354</v>
       </c>
       <c r="CI14" t="n">
         <v>-15.92494252569399</v>
@@ -4599,10 +4591,10 @@
         <v>14.27999973297119</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.387520847375252</v>
+        <v>4.387520843683155</v>
       </c>
       <c r="BH15" t="n">
-        <v>8.138851171881091</v>
+        <v>8.138851165032253</v>
       </c>
       <c r="BI15" t="n">
         <v>23.74027559120054</v>
@@ -4611,25 +4603,25 @@
         <v>19.99443109682345</v>
       </c>
       <c r="BK15" t="n">
-        <v>28.98387347901059</v>
+        <v>28.98387348186536</v>
       </c>
       <c r="BL15" t="n">
-        <v>16.36200631219285</v>
+        <v>16.36200631295526</v>
       </c>
       <c r="BM15" t="n">
-        <v>18.16044427263289</v>
+        <v>18.16044427850392</v>
       </c>
       <c r="BN15" t="n">
         <v>13.94701359457771</v>
       </c>
       <c r="BO15" t="n">
-        <v>18.4752707883313</v>
+        <v>18.47527078870835</v>
       </c>
       <c r="BP15" t="n">
-        <v>18.16044427263289</v>
+        <v>18.16044427850392</v>
       </c>
       <c r="BQ15" t="n">
-        <v>16.3443998453696</v>
+        <v>16.34439985065353</v>
       </c>
       <c r="BR15" t="n">
         <v>7</v>
@@ -4641,10 +4633,10 @@
         <v>6.6</v>
       </c>
       <c r="BU15" t="n">
-        <v>14.45658369048777</v>
+        <v>14.45658372749006</v>
       </c>
       <c r="BV15" t="n">
-        <v>29.37864939642554</v>
+        <v>29.37864939906596</v>
       </c>
       <c r="BW15" t="inlineStr">
         <is>
@@ -4884,10 +4876,10 @@
         <v>16.47999954223633</v>
       </c>
       <c r="BG16" t="n">
-        <v>9.770026172626132</v>
+        <v>9.770026142523131</v>
       </c>
       <c r="BH16" t="n">
-        <v>18.12339855022147</v>
+        <v>18.12339849438041</v>
       </c>
       <c r="BI16" t="n">
         <v>36.09256098093079</v>
@@ -4896,25 +4888,25 @@
         <v>35.53250072181754</v>
       </c>
       <c r="BK16" t="n">
-        <v>40.48255603411169</v>
+        <v>40.48255601999791</v>
       </c>
       <c r="BL16" t="n">
-        <v>32.74874497482649</v>
+        <v>32.74874498109326</v>
       </c>
       <c r="BM16" t="n">
-        <v>18.51211383315473</v>
+        <v>18.5121138680694</v>
       </c>
       <c r="BN16" t="n">
         <v>29.55836540201202</v>
       </c>
       <c r="BO16" t="n">
-        <v>30.15003435672496</v>
+        <v>30.15003435261448</v>
       </c>
       <c r="BP16" t="n">
-        <v>32.74874497482649</v>
+        <v>32.74874498109326</v>
       </c>
       <c r="BQ16" t="n">
-        <v>29.47387047734384</v>
+        <v>29.47387048298393</v>
       </c>
       <c r="BR16" t="n">
         <v>7</v>
@@ -4926,10 +4918,10 @@
         <v>4.1</v>
       </c>
       <c r="BU16" t="n">
-        <v>78.84630640799305</v>
+        <v>78.84630644221696</v>
       </c>
       <c r="BV16" t="n">
-        <v>82.94924268325323</v>
+        <v>82.94924265831096</v>
       </c>
       <c r="BW16" t="inlineStr">
         <is>
@@ -5161,10 +5153,10 @@
         <v>9.220000267028809</v>
       </c>
       <c r="BG17" t="n">
-        <v>9.218246671328879</v>
+        <v>9.218246674682376</v>
       </c>
       <c r="BH17" t="n">
-        <v>17.09984757531507</v>
+        <v>17.0998475815358</v>
       </c>
       <c r="BI17" t="n">
         <v>23.49326991117917</v>
@@ -5173,25 +5165,25 @@
         <v>16.88595648327735</v>
       </c>
       <c r="BK17" t="n">
-        <v>36.83316518982861</v>
+        <v>36.83316518716696</v>
       </c>
       <c r="BL17" t="n">
-        <v>23.3951382436891</v>
+        <v>23.39513824224449</v>
       </c>
       <c r="BM17" t="n">
-        <v>12.28881399952907</v>
+        <v>12.28881399218089</v>
       </c>
       <c r="BN17" t="n">
         <v>9.220000267028809</v>
       </c>
       <c r="BO17" t="n">
-        <v>18.55430479264701</v>
+        <v>18.55430479241198</v>
       </c>
       <c r="BP17" t="n">
-        <v>16.99290202929621</v>
+        <v>16.99290203240658</v>
       </c>
       <c r="BQ17" t="n">
-        <v>15.29361182636659</v>
+        <v>15.29361182916592</v>
       </c>
       <c r="BR17" t="n">
         <v>8</v>
@@ -5203,10 +5195,10 @@
         <v>4</v>
       </c>
       <c r="BU17" t="n">
-        <v>65.8743100155574</v>
+        <v>65.87431004591893</v>
       </c>
       <c r="BV17" t="n">
-        <v>101.2397424650642</v>
+        <v>101.2397424625152</v>
       </c>
       <c r="BW17" t="inlineStr">
         <is>
@@ -5438,10 +5430,10 @@
         <v>12.02999973297119</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.74266549349182</v>
+        <v>3.742665486380992</v>
       </c>
       <c r="BH18" t="n">
-        <v>6.942644490427327</v>
+        <v>6.942644477236739</v>
       </c>
       <c r="BI18" t="n">
         <v>19.51009748615278</v>
@@ -5450,19 +5442,19 @@
         <v>18.37827919410691</v>
       </c>
       <c r="BK18" t="n">
-        <v>20.08107821984336</v>
+        <v>20.08107822200372</v>
       </c>
       <c r="BL18" t="n">
-        <v>15.55766337195318</v>
+        <v>15.55766337334014</v>
       </c>
       <c r="BM18" t="n">
-        <v>12.52469663322948</v>
+        <v>12.52469664224658</v>
       </c>
       <c r="BN18" t="n">
         <v>26.99032004584218</v>
       </c>
       <c r="BO18" t="n">
-        <v>17.14068277736503</v>
+        <v>17.14068277727558</v>
       </c>
       <c r="BP18" t="n">
         <v>18.37827919410691</v>
@@ -5483,7 +5475,7 @@
         <v>37.49336360634341</v>
       </c>
       <c r="BV18" t="n">
-        <v>42.48281926712558</v>
+        <v>42.482819266382</v>
       </c>
       <c r="BW18" t="inlineStr">
         <is>
@@ -5713,10 +5705,10 @@
         <v>3.430000066757202</v>
       </c>
       <c r="BG19" t="n">
-        <v>4.790274321248175</v>
+        <v>4.790274329237143</v>
       </c>
       <c r="BH19" t="n">
-        <v>6.974639411737343</v>
+        <v>6.974639423369282</v>
       </c>
       <c r="BI19" t="n">
         <v>6.618181946989778</v>
@@ -5735,7 +5727,7 @@
         <v>2.330329016381401</v>
       </c>
       <c r="BO19" t="n">
-        <v>5.511348698985302</v>
+        <v>5.511348702255454</v>
       </c>
       <c r="BP19" t="n">
         <v>5.928677058339783</v>
@@ -5756,7 +5748,7 @@
         <v>55.5629518558697</v>
       </c>
       <c r="BV19" t="n">
-        <v>60.68071695974786</v>
+        <v>60.68071705508753</v>
       </c>
       <c r="BW19" t="inlineStr">
         <is>
@@ -5988,10 +5980,10 @@
         <v>20.88999938964844</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.938906069118572</v>
+        <v>2.938906064545861</v>
       </c>
       <c r="BH20" t="n">
-        <v>5.451670758214951</v>
+        <v>5.451670749732572</v>
       </c>
       <c r="BI20" t="n">
         <v>31.74225824688552</v>
@@ -6000,7 +5992,7 @@
         <v>26.44590940575898</v>
       </c>
       <c r="BK20" t="n">
-        <v>40.65305915279662</v>
+        <v>40.65305914545512</v>
       </c>
       <c r="BL20" t="n">
         <v>10.44211857350007</v>
@@ -6241,35 +6233,35 @@
         <v>22.70000076293945</v>
       </c>
       <c r="BG21" t="n">
-        <v>16.28609457236874</v>
+        <v>16.28609454810477</v>
       </c>
       <c r="BH21" t="n">
-        <v>28.49660542318114</v>
+        <v>28.49660542684956</v>
       </c>
       <c r="BI21" t="n">
-        <v>47.12783849970864</v>
+        <v>47.12783857598924</v>
       </c>
       <c r="BJ21" t="n">
         <v>47.60027068070954</v>
       </c>
       <c r="BK21" t="n">
-        <v>58.81912817755629</v>
+        <v>58.81912816885568</v>
       </c>
       <c r="BL21" t="n">
-        <v>30.92711815463805</v>
+        <v>30.92711815834657</v>
       </c>
       <c r="BM21" t="n">
-        <v>23.23843511571345</v>
+        <v>23.2384351457134</v>
       </c>
       <c r="BN21" t="inlineStr"/>
       <c r="BO21" t="n">
-        <v>30.70941416247414</v>
+        <v>30.70941417732254</v>
       </c>
       <c r="BP21" t="n">
-        <v>29.71186178890959</v>
+        <v>29.71186179259806</v>
       </c>
       <c r="BQ21" t="n">
-        <v>26.74067561001863</v>
+        <v>26.74067561333825</v>
       </c>
       <c r="BR21" t="n">
         <v>4</v>
@@ -6281,10 +6273,10 @@
         <v>2.9</v>
       </c>
       <c r="BU21" t="n">
-        <v>17.80032912455263</v>
+        <v>17.80032913917651</v>
       </c>
       <c r="BV21" t="n">
-        <v>35.28375828344043</v>
+        <v>35.28375834885185</v>
       </c>
       <c r="BW21" t="inlineStr">
         <is>
@@ -6514,10 +6506,10 @@
         <v>5.889999866485596</v>
       </c>
       <c r="BG22" t="n">
-        <v>6.967484517143126</v>
+        <v>6.967484522855686</v>
       </c>
       <c r="BH22" t="n">
-        <v>10.14465745696039</v>
+        <v>10.14465746527788</v>
       </c>
       <c r="BI22" t="n">
         <v>8.368305821236365</v>
@@ -6536,7 +6528,7 @@
         <v>5.445300917107223</v>
       </c>
       <c r="BO22" t="n">
-        <v>8.112707691017574</v>
+        <v>8.112707693355913</v>
       </c>
       <c r="BP22" t="n">
         <v>8.595393290251712</v>
@@ -6557,7 +6549,7 @@
         <v>31.33877990802598</v>
       </c>
       <c r="BV22" t="n">
-        <v>37.73697580503017</v>
+        <v>37.73697584473032</v>
       </c>
       <c r="BW22" t="inlineStr">
         <is>
@@ -6789,10 +6781,10 @@
         <v>27.1299991607666</v>
       </c>
       <c r="BG23" t="n">
-        <v>7.182527999327719</v>
+        <v>7.182528062020133</v>
       </c>
       <c r="BH23" t="n">
-        <v>13.32358943875292</v>
+        <v>13.32358955504735</v>
       </c>
       <c r="BI23" t="n">
         <v>34.63126097111343</v>
@@ -6801,19 +6793,19 @@
         <v>27.36859865246639</v>
       </c>
       <c r="BK23" t="n">
-        <v>42.68616600760828</v>
+        <v>42.68616591206175</v>
       </c>
       <c r="BL23" t="n">
-        <v>24.66467732783487</v>
+        <v>24.66467731274425</v>
       </c>
       <c r="BM23" t="n">
-        <v>27.72433021534865</v>
+        <v>27.7243301021412</v>
       </c>
       <c r="BN23" t="n">
         <v>22.34091371576103</v>
       </c>
       <c r="BO23" t="n">
-        <v>27.53421947555508</v>
+        <v>27.53421946019077</v>
       </c>
       <c r="BP23" t="n">
         <v>27.36859865246639</v>
@@ -6834,7 +6826,7 @@
         <v>-9.208479361693655</v>
       </c>
       <c r="BV23" t="n">
-        <v>1.489938545125469</v>
+        <v>1.489938488493281</v>
       </c>
       <c r="BW23" t="inlineStr">
         <is>
@@ -7066,37 +7058,37 @@
         <v>11.01000022888184</v>
       </c>
       <c r="BG24" t="n">
-        <v>9.53170260012339</v>
+        <v>9.531702606440202</v>
       </c>
       <c r="BH24" t="n">
-        <v>17.26678401411701</v>
+        <v>17.26678397502195</v>
       </c>
       <c r="BI24" t="n">
-        <v>20.26492218572863</v>
+        <v>20.26492212641537</v>
       </c>
       <c r="BJ24" t="n">
         <v>11.834803187379</v>
       </c>
       <c r="BK24" t="n">
-        <v>28.09971458761692</v>
+        <v>28.09971456539731</v>
       </c>
       <c r="BL24" t="n">
-        <v>24.03459730002435</v>
+        <v>24.03459729497773</v>
       </c>
       <c r="BM24" t="n">
-        <v>9.914946062520954</v>
+        <v>9.914946040647093</v>
       </c>
       <c r="BN24" t="n">
         <v>8.714817950680764</v>
       </c>
       <c r="BO24" t="n">
-        <v>16.20778598602388</v>
+        <v>16.20778596836993</v>
       </c>
       <c r="BP24" t="n">
-        <v>14.550793600748</v>
+        <v>14.55079358120047</v>
       </c>
       <c r="BQ24" t="n">
-        <v>13.0957142406732</v>
+        <v>13.09571422308043</v>
       </c>
       <c r="BR24" t="n">
         <v>8</v>
@@ -7108,10 +7100,10 @@
         <v>3.2</v>
       </c>
       <c r="BU24" t="n">
-        <v>18.9438144271791</v>
+        <v>18.94381426739002</v>
       </c>
       <c r="BV24" t="n">
-        <v>47.20967891996062</v>
+        <v>47.2096787596159</v>
       </c>
       <c r="BW24" t="inlineStr">
         <is>
@@ -7343,10 +7335,10 @@
         <v>12.86999988555908</v>
       </c>
       <c r="BG25" t="n">
-        <v>8.064609817391995</v>
+        <v>8.0646098175995</v>
       </c>
       <c r="BH25" t="n">
-        <v>14.95985121126215</v>
+        <v>14.95985121164707</v>
       </c>
       <c r="BI25" t="n">
         <v>13.49109956358052</v>
@@ -7367,7 +7359,7 @@
         <v>6.379184203562791</v>
       </c>
       <c r="BO25" t="n">
-        <v>14.53079977236276</v>
+        <v>14.53079977243681</v>
       </c>
       <c r="BP25" t="n">
         <v>12.9056367523308</v>
@@ -7388,7 +7380,7 @@
         <v>-9.750791139240512</v>
       </c>
       <c r="BV25" t="n">
-        <v>12.90442813963961</v>
+        <v>12.90442814021502</v>
       </c>
       <c r="BW25" t="inlineStr">
         <is>
@@ -7425,7 +7417,7 @@
       <c r="CE25" t="inlineStr"/>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="CG25" t="n">
@@ -7614,10 +7606,10 @@
         <v>14.72000026702881</v>
       </c>
       <c r="BG26" t="n">
-        <v>9.143015684258149</v>
+        <v>9.143015750888184</v>
       </c>
       <c r="BH26" t="n">
-        <v>16.96029409429887</v>
+        <v>16.96029421789758</v>
       </c>
       <c r="BI26" t="n">
         <v>30.23876023847003</v>
@@ -7626,23 +7618,23 @@
         <v>28.82030174141344</v>
       </c>
       <c r="BK26" t="n">
-        <v>34.00566208700226</v>
+        <v>34.00566209981805</v>
       </c>
       <c r="BL26" t="n">
-        <v>26.56393125628211</v>
+        <v>26.56393124183635</v>
       </c>
       <c r="BM26" t="n">
-        <v>14.99745135929703</v>
+        <v>14.99745127644658</v>
       </c>
       <c r="BN26" t="inlineStr"/>
       <c r="BO26" t="n">
-        <v>20.72650031832729</v>
+        <v>20.72650036227304</v>
       </c>
       <c r="BP26" t="n">
-        <v>21.76211267529049</v>
+        <v>21.76211272986697</v>
       </c>
       <c r="BQ26" t="n">
-        <v>19.58590140776144</v>
+        <v>19.58590145688027</v>
       </c>
       <c r="BR26" t="n">
         <v>4</v>
@@ -7654,10 +7646,10 @@
         <v>3.3</v>
       </c>
       <c r="BU26" t="n">
-        <v>33.0563930194466</v>
+        <v>33.0563933531343</v>
       </c>
       <c r="BV26" t="n">
-        <v>40.80502678218276</v>
+        <v>40.80502708072724</v>
       </c>
       <c r="BW26" t="inlineStr">
         <is>
@@ -7696,7 +7688,7 @@
         <v>-10.80078673102787</v>
       </c>
       <c r="CI26" t="n">
-        <v>-19.07733209382061</v>
+        <v>-19.07731455987075</v>
       </c>
       <c r="CJ26" t="b">
         <v>1</v>
@@ -7873,10 +7865,10 @@
         <v>37.2599983215332</v>
       </c>
       <c r="BG27" t="n">
-        <v>34.16541003959492</v>
+        <v>34.16540996879814</v>
       </c>
       <c r="BH27" t="n">
-        <v>49.74483701765021</v>
+        <v>49.74483691457011</v>
       </c>
       <c r="BI27" t="n">
         <v>47.95841368118134</v>
@@ -7893,13 +7885,13 @@
       </c>
       <c r="BN27" t="inlineStr"/>
       <c r="BO27" t="n">
-        <v>47.47016038731842</v>
+        <v>47.4701603438492</v>
       </c>
       <c r="BP27" t="n">
-        <v>48.85162534941578</v>
+        <v>48.85162529787573</v>
       </c>
       <c r="BQ27" t="n">
-        <v>43.9664628144742</v>
+        <v>43.96646276808816</v>
       </c>
       <c r="BR27" t="n">
         <v>4</v>
@@ -7911,10 +7903,10 @@
         <v>1.7</v>
       </c>
       <c r="BU27" t="n">
-        <v>17.99910036245283</v>
+        <v>17.99910023795994</v>
       </c>
       <c r="BV27" t="n">
-        <v>27.40247591445699</v>
+        <v>27.40247579779243</v>
       </c>
       <c r="BW27" t="inlineStr">
         <is>
@@ -8144,10 +8136,10 @@
         <v>3.690000057220459</v>
       </c>
       <c r="BG28" t="n">
-        <v>0.8537054792152962</v>
+        <v>0.8537054779550103</v>
       </c>
       <c r="BH28" t="n">
-        <v>1.583623663944375</v>
+        <v>1.583623661606544</v>
       </c>
       <c r="BI28" t="n">
         <v>9.978061379218586</v>
@@ -8156,13 +8148,13 @@
         <v>8.953076401677793</v>
       </c>
       <c r="BK28" t="n">
-        <v>12.46813579753735</v>
+        <v>12.46813579672958</v>
       </c>
       <c r="BL28" t="n">
-        <v>4.490296415879171</v>
+        <v>4.49029641602614</v>
       </c>
       <c r="BM28" t="n">
-        <v>8.31567788178617</v>
+        <v>8.315677883541797</v>
       </c>
       <c r="BN28" t="n">
         <v>8.070693304078278</v>
@@ -8411,37 +8403,37 @@
         <v>15.01000022888184</v>
       </c>
       <c r="BG29" t="n">
-        <v>5.822993551318927</v>
+        <v>5.822993541107746</v>
       </c>
       <c r="BH29" t="n">
-        <v>8.112117347249821</v>
+        <v>8.112117355296171</v>
       </c>
       <c r="BI29" t="n">
-        <v>10.07841818887771</v>
+        <v>10.0784182165479</v>
       </c>
       <c r="BJ29" t="n">
         <v>11.19351621134486</v>
       </c>
       <c r="BK29" t="n">
-        <v>9.136669956599388</v>
+        <v>9.136669973257201</v>
       </c>
       <c r="BL29" t="n">
-        <v>14.61973513446876</v>
+        <v>14.61973513813408</v>
       </c>
       <c r="BM29" t="n">
-        <v>4.991079391254843</v>
+        <v>4.991079407788788</v>
       </c>
       <c r="BN29" t="n">
         <v>10.28842080392437</v>
       </c>
       <c r="BO29" t="n">
-        <v>9.280368823129836</v>
+        <v>9.28036883092514</v>
       </c>
       <c r="BP29" t="n">
-        <v>9.60754407273855</v>
+        <v>9.607544094902551</v>
       </c>
       <c r="BQ29" t="n">
-        <v>8.646789665464695</v>
+        <v>8.646789685412296</v>
       </c>
       <c r="BR29" t="n">
         <v>8</v>
@@ -8453,10 +8445,10 @@
         <v>2.9</v>
       </c>
       <c r="BU29" t="n">
-        <v>-42.39314101523613</v>
+        <v>-42.39314088234071</v>
       </c>
       <c r="BV29" t="n">
-        <v>-38.17209405984684</v>
+        <v>-38.17209400791277</v>
       </c>
       <c r="BW29" t="inlineStr">
         <is>
@@ -8688,10 +8680,10 @@
         <v>30.59000015258789</v>
       </c>
       <c r="BG30" t="n">
-        <v>3.032359191341571</v>
+        <v>3.032359179807987</v>
       </c>
       <c r="BH30" t="n">
-        <v>5.625026299938614</v>
+        <v>5.625026278543815</v>
       </c>
       <c r="BI30" t="n">
         <v>31.32283632316766</v>
@@ -8700,7 +8692,7 @@
         <v>21.94043581226608</v>
       </c>
       <c r="BK30" t="n">
-        <v>38.74057426333852</v>
+        <v>38.74057425086014</v>
       </c>
       <c r="BL30" t="n">
         <v>16.47675213208347</v>
@@ -8770,7 +8762,7 @@
         <v>-5.90586978798332</v>
       </c>
       <c r="CI30" t="n">
-        <v>-35.84819225068575</v>
+        <v>-35.84818696004584</v>
       </c>
       <c r="CJ30" t="b">
         <v>1</v>
@@ -8945,35 +8937,35 @@
         <v>12.63000011444092</v>
       </c>
       <c r="BG31" t="n">
-        <v>8.477710198569117</v>
+        <v>8.477710180027204</v>
       </c>
       <c r="BH31" t="n">
-        <v>13.24330364945143</v>
+        <v>13.24330367008882</v>
       </c>
       <c r="BI31" t="n">
-        <v>17.39835028060029</v>
+        <v>17.39835034576517</v>
       </c>
       <c r="BJ31" t="n">
         <v>16.79972907026644</v>
       </c>
       <c r="BK31" t="n">
-        <v>21.86210625255676</v>
+        <v>21.86210627076501</v>
       </c>
       <c r="BL31" t="n">
-        <v>16.64958769000695</v>
+        <v>16.64958769513608</v>
       </c>
       <c r="BM31" t="n">
-        <v>8.696993311275319</v>
+        <v>8.696993342864806</v>
       </c>
       <c r="BN31" t="inlineStr"/>
       <c r="BO31" t="n">
-        <v>13.94223795465695</v>
+        <v>13.94223797275432</v>
       </c>
       <c r="BP31" t="n">
-        <v>14.94644566972919</v>
+        <v>14.94644568261245</v>
       </c>
       <c r="BQ31" t="n">
-        <v>13.45180110275627</v>
+        <v>13.4518011143512</v>
       </c>
       <c r="BR31" t="n">
         <v>4</v>
@@ -8985,10 +8977,10 @@
         <v>2.1</v>
       </c>
       <c r="BU31" t="n">
-        <v>6.506737774101201</v>
+        <v>6.506737865905876</v>
       </c>
       <c r="BV31" t="n">
-        <v>10.38984820527151</v>
+        <v>10.38984834856027</v>
       </c>
       <c r="BW31" t="inlineStr">
         <is>
@@ -9220,10 +9212,10 @@
         <v>8.350000381469727</v>
       </c>
       <c r="BG32" t="n">
-        <v>2.275170437788945</v>
+        <v>2.275170445514933</v>
       </c>
       <c r="BH32" t="n">
-        <v>4.220441162098493</v>
+        <v>4.220441176430199</v>
       </c>
       <c r="BI32" t="n">
         <v>13.45955049324499</v>
@@ -9232,19 +9224,19 @@
         <v>14.81092624645154</v>
       </c>
       <c r="BK32" t="n">
-        <v>11.28719235011125</v>
+        <v>11.28719235177205</v>
       </c>
       <c r="BL32" t="n">
-        <v>7.403635149027117</v>
+        <v>7.403635148246104</v>
       </c>
       <c r="BM32" t="n">
-        <v>7.372778607655695</v>
+        <v>7.372778600428497</v>
       </c>
       <c r="BN32" t="n">
         <v>9.952965903815388</v>
       </c>
       <c r="BO32" t="n">
-        <v>9.78678427320064</v>
+        <v>9.786784274341255</v>
       </c>
       <c r="BP32" t="n">
         <v>9.952965903815388</v>
@@ -9265,7 +9257,7 @@
         <v>7.277471906620003</v>
       </c>
       <c r="BV32" t="n">
-        <v>17.20699192923889</v>
+        <v>17.20699194289896</v>
       </c>
       <c r="BW32" t="inlineStr">
         <is>
@@ -9495,10 +9487,10 @@
         <v>10.39999961853027</v>
       </c>
       <c r="BG33" t="n">
-        <v>12.94492636538292</v>
+        <v>12.94492644983275</v>
       </c>
       <c r="BH33" t="n">
-        <v>18.84781278799753</v>
+        <v>18.84781291095649</v>
       </c>
       <c r="BI33" t="n">
         <v>17.11392342289792</v>
@@ -9517,7 +9509,7 @@
         <v>15.58796560981411</v>
       </c>
       <c r="BO33" t="n">
-        <v>16.31747703590493</v>
+        <v>16.31747707047306</v>
       </c>
       <c r="BP33" t="n">
         <v>16.35094451635601</v>
@@ -9538,7 +9530,7 @@
         <v>41.49856350475572</v>
       </c>
       <c r="BV33" t="n">
-        <v>56.89882340794652</v>
+        <v>56.89882374033248</v>
       </c>
       <c r="BW33" t="inlineStr">
         <is>
@@ -10021,35 +10013,35 @@
         <v>16.79000091552734</v>
       </c>
       <c r="BG35" t="n">
-        <v>9.983951974598522</v>
+        <v>9.983951960731627</v>
       </c>
       <c r="BH35" t="n">
-        <v>17.31362329693829</v>
+        <v>17.31362329927638</v>
       </c>
       <c r="BI35" t="n">
-        <v>28.29572498979272</v>
+        <v>28.29572503291434</v>
       </c>
       <c r="BJ35" t="n">
         <v>28.80591266774053</v>
       </c>
       <c r="BK35" t="n">
-        <v>31.54471771143841</v>
+        <v>31.54471771245677</v>
       </c>
       <c r="BL35" t="n">
-        <v>29.07473908054563</v>
+        <v>29.07473908385554</v>
       </c>
       <c r="BM35" t="n">
-        <v>13.97702130754151</v>
+        <v>13.97702132478416</v>
       </c>
       <c r="BN35" t="inlineStr"/>
       <c r="BO35" t="n">
-        <v>21.16700983546879</v>
+        <v>21.16700984419447</v>
       </c>
       <c r="BP35" t="n">
-        <v>22.8046741433655</v>
+        <v>22.80467416609536</v>
       </c>
       <c r="BQ35" t="n">
-        <v>20.52420672902895</v>
+        <v>20.52420674948582</v>
       </c>
       <c r="BR35" t="n">
         <v>4</v>
@@ -10061,10 +10053,10 @@
         <v>2.9</v>
       </c>
       <c r="BU35" t="n">
-        <v>22.24065282836423</v>
+        <v>22.24065295020381</v>
       </c>
       <c r="BV35" t="n">
-        <v>26.06914044831052</v>
+        <v>26.06914050028004</v>
       </c>
       <c r="BW35" t="inlineStr">
         <is>
@@ -10103,7 +10095,7 @@
         <v>-11.40119791818688</v>
       </c>
       <c r="CI35" t="n">
-        <v>-20.94721042714066</v>
+        <v>-20.94721767049244</v>
       </c>
       <c r="CJ35" t="b">
         <v>1</v>
@@ -10296,10 +10288,10 @@
         <v>4.25</v>
       </c>
       <c r="BG36" t="n">
-        <v>2.756777599631545</v>
+        <v>2.756777604274725</v>
       </c>
       <c r="BH36" t="n">
-        <v>5.113822447316515</v>
+        <v>5.113822455929615</v>
       </c>
       <c r="BI36" t="n">
         <v>13.83599508599508</v>
@@ -10308,25 +10300,25 @@
         <v>14.73343694068134</v>
       </c>
       <c r="BK36" t="n">
-        <v>16.86864303270065</v>
+        <v>16.86864304137877</v>
       </c>
       <c r="BL36" t="n">
-        <v>8.105886947766782</v>
+        <v>8.105886947238016</v>
       </c>
       <c r="BM36" t="n">
-        <v>7.432122123281853</v>
+        <v>7.432122118697363</v>
       </c>
       <c r="BN36" t="n">
         <v>3.276499576963653</v>
       </c>
       <c r="BO36" t="n">
-        <v>9.909486593529412</v>
+        <v>9.90948659526912</v>
       </c>
       <c r="BP36" t="n">
-        <v>8.105886947766782</v>
+        <v>8.105886947238016</v>
       </c>
       <c r="BQ36" t="n">
-        <v>7.295298252990104</v>
+        <v>7.295298252514215</v>
       </c>
       <c r="BR36" t="n">
         <v>7</v>
@@ -10338,10 +10330,10 @@
         <v>6.1</v>
       </c>
       <c r="BU36" t="n">
-        <v>71.65407654094362</v>
+        <v>71.65407652974622</v>
       </c>
       <c r="BV36" t="n">
-        <v>133.1643904359861</v>
+        <v>133.1643904769205</v>
       </c>
       <c r="BW36" t="inlineStr">
         <is>
@@ -10559,10 +10551,10 @@
         <v>29.52000045776367</v>
       </c>
       <c r="BG37" t="n">
-        <v>15.4318831746634</v>
+        <v>15.43188317097433</v>
       </c>
       <c r="BH37" t="n">
-        <v>28.62614328900059</v>
+        <v>28.62614328215739</v>
       </c>
       <c r="BI37" t="n">
         <v>55.24576356855489</v>
@@ -10571,23 +10563,23 @@
         <v>49.94931085633525</v>
       </c>
       <c r="BK37" t="n">
-        <v>62.03667169361906</v>
+        <v>62.0366716944277</v>
       </c>
       <c r="BL37" t="n">
-        <v>38.72993682063951</v>
+        <v>38.72993681208075</v>
       </c>
       <c r="BM37" t="n">
-        <v>30.95210656982519</v>
+        <v>30.95210657491875</v>
       </c>
       <c r="BN37" t="inlineStr"/>
       <c r="BO37" t="n">
-        <v>34.50843171321459</v>
+        <v>34.50843170844184</v>
       </c>
       <c r="BP37" t="n">
-        <v>33.67804005482005</v>
+        <v>33.67804004711907</v>
       </c>
       <c r="BQ37" t="n">
-        <v>30.31023604933805</v>
+        <v>30.31023604240716</v>
       </c>
       <c r="BR37" t="n">
         <v>4</v>
@@ -10599,10 +10591,10 @@
         <v>3.6</v>
       </c>
       <c r="BU37" t="n">
-        <v>2.676949794445371</v>
+        <v>2.676949770966752</v>
       </c>
       <c r="BV37" t="n">
-        <v>16.89847960059559</v>
+        <v>16.89847958442774</v>
       </c>
       <c r="BW37" t="inlineStr">
         <is>
@@ -10842,37 +10834,37 @@
         <v>10.39999961853027</v>
       </c>
       <c r="BG38" t="n">
-        <v>7.24946442608225</v>
+        <v>7.249464451323488</v>
       </c>
       <c r="BH38" t="n">
-        <v>10.94542260726863</v>
+        <v>10.94542261553002</v>
       </c>
       <c r="BI38" t="n">
-        <v>17.77471065834706</v>
+        <v>17.77471060987495</v>
       </c>
       <c r="BJ38" t="n">
         <v>23.30669690919295</v>
       </c>
       <c r="BK38" t="n">
-        <v>23.21481237219501</v>
+        <v>23.21481238840746</v>
       </c>
       <c r="BL38" t="n">
-        <v>20.50961401757796</v>
+        <v>20.50961401283186</v>
       </c>
       <c r="BM38" t="n">
-        <v>8.884967962904042</v>
+        <v>8.884967937893004</v>
       </c>
       <c r="BN38" t="n">
         <v>9.960670392837367</v>
       </c>
       <c r="BO38" t="n">
-        <v>15.23079491830066</v>
+        <v>15.23079491473639</v>
       </c>
       <c r="BP38" t="n">
-        <v>14.36006663280784</v>
+        <v>14.36006661270249</v>
       </c>
       <c r="BQ38" t="n">
-        <v>12.92405996952706</v>
+        <v>12.92405995143224</v>
       </c>
       <c r="BR38" t="n">
         <v>8</v>
@@ -10884,10 +10876,10 @@
         <v>3.2</v>
       </c>
       <c r="BU38" t="n">
-        <v>24.26981195748819</v>
+        <v>24.26981178349952</v>
       </c>
       <c r="BV38" t="n">
-        <v>46.4499565092587</v>
+        <v>46.44995647498691</v>
       </c>
       <c r="BW38" t="inlineStr">
         <is>
@@ -11105,10 +11097,10 @@
         <v>39</v>
       </c>
       <c r="BG39" t="n">
-        <v>19.93010987979392</v>
+        <v>19.93011005724446</v>
       </c>
       <c r="BH39" t="n">
-        <v>36.97035382701772</v>
+        <v>36.97035415618846</v>
       </c>
       <c r="BI39" t="n">
         <v>54.05334728033472</v>
@@ -11117,23 +11109,23 @@
         <v>40.80446518102817</v>
       </c>
       <c r="BK39" t="n">
-        <v>58.13074606173186</v>
+        <v>58.13074576386963</v>
       </c>
       <c r="BL39" t="n">
-        <v>43.72434341024892</v>
+        <v>43.72434335443165</v>
       </c>
       <c r="BM39" t="n">
-        <v>29.09170552518504</v>
+        <v>29.09170517461377</v>
       </c>
       <c r="BN39" t="inlineStr"/>
       <c r="BO39" t="n">
-        <v>38.66953859934883</v>
+        <v>38.66953871204982</v>
       </c>
       <c r="BP39" t="n">
-        <v>40.34734861863332</v>
+        <v>40.34734875531005</v>
       </c>
       <c r="BQ39" t="n">
-        <v>36.31261375676999</v>
+        <v>36.31261387977905</v>
       </c>
       <c r="BR39" t="n">
         <v>4</v>
@@ -11145,10 +11137,10 @@
         <v>2.7</v>
       </c>
       <c r="BU39" t="n">
-        <v>-6.890733957000017</v>
+        <v>-6.890733641592184</v>
       </c>
       <c r="BV39" t="n">
-        <v>-0.8473369247466001</v>
+        <v>-0.847336635769691</v>
       </c>
       <c r="BW39" t="inlineStr">
         <is>
@@ -11378,10 +11370,10 @@
         <v>5.570000171661377</v>
       </c>
       <c r="BG40" t="n">
-        <v>6.611145437223454</v>
+        <v>6.611145471700185</v>
       </c>
       <c r="BH40" t="n">
-        <v>9.625827756597349</v>
+        <v>9.625827806795471</v>
       </c>
       <c r="BI40" t="n">
         <v>4.355488856035963</v>
@@ -11651,37 +11643,37 @@
         <v>43.65000152587891</v>
       </c>
       <c r="BG41" t="n">
-        <v>31.67320339736693</v>
+        <v>31.67320341920442</v>
       </c>
       <c r="BH41" t="n">
-        <v>38.85442811416343</v>
+        <v>38.85442808626338</v>
       </c>
       <c r="BI41" t="n">
-        <v>43.07167816615766</v>
+        <v>43.07167810553303</v>
       </c>
       <c r="BJ41" t="n">
         <v>47.83302112955008</v>
       </c>
       <c r="BK41" t="n">
-        <v>61.35148243696359</v>
+        <v>61.35148239887413</v>
       </c>
       <c r="BL41" t="n">
-        <v>55.87396020691161</v>
+        <v>55.87396019885573</v>
       </c>
       <c r="BM41" t="n">
-        <v>20.30744564081683</v>
+        <v>20.30744559523414</v>
       </c>
       <c r="BN41" t="n">
         <v>76.39578733574842</v>
       </c>
       <c r="BO41" t="n">
-        <v>46.92012580345982</v>
+        <v>46.92012578365791</v>
       </c>
       <c r="BP41" t="n">
-        <v>45.45234964785386</v>
+        <v>45.45234961754156</v>
       </c>
       <c r="BQ41" t="n">
-        <v>40.90711468306848</v>
+        <v>40.9071146557874</v>
       </c>
       <c r="BR41" t="n">
         <v>8</v>
@@ -11693,10 +11685,10 @@
         <v>3.8</v>
       </c>
       <c r="BU41" t="n">
-        <v>-6.28381843511333</v>
+        <v>-6.283818497612925</v>
       </c>
       <c r="BV41" t="n">
-        <v>7.491693386636289</v>
+        <v>7.491693341271088</v>
       </c>
       <c r="BW41" t="inlineStr">
         <is>
@@ -11928,10 +11920,10 @@
         <v>25.98999977111816</v>
       </c>
       <c r="BG42" t="n">
-        <v>4.764912405572914</v>
+        <v>4.764912401124102</v>
       </c>
       <c r="BH42" t="n">
-        <v>8.838912512337753</v>
+        <v>8.838912504085208</v>
       </c>
       <c r="BI42" t="n">
         <v>32.12383367232422</v>
@@ -11940,13 +11932,13 @@
         <v>25.73909396655281</v>
       </c>
       <c r="BK42" t="n">
-        <v>41.31716359680247</v>
+        <v>41.31716360343043</v>
       </c>
       <c r="BL42" t="n">
-        <v>12.18233647814072</v>
+        <v>12.18233647868668</v>
       </c>
       <c r="BM42" t="n">
-        <v>28.53601231437363</v>
+        <v>28.53601232219179</v>
       </c>
       <c r="BN42" t="n">
         <v>25.98999977111816</v>
@@ -12195,10 +12187,10 @@
         <v>47.36000061035156</v>
       </c>
       <c r="BG43" t="n">
-        <v>7.883046092708915</v>
+        <v>7.883046091816701</v>
       </c>
       <c r="BH43" t="n">
-        <v>14.62305050197503</v>
+        <v>14.62305050031998</v>
       </c>
       <c r="BI43" t="n">
         <v>19.62840187948571</v>
@@ -12207,25 +12199,25 @@
         <v>12.20333989274278</v>
       </c>
       <c r="BK43" t="n">
-        <v>15.97866910688979</v>
+        <v>15.97866911064109</v>
       </c>
       <c r="BL43" t="n">
-        <v>20.76704643507733</v>
+        <v>20.76704643561271</v>
       </c>
       <c r="BM43" t="n">
-        <v>11.83128735882157</v>
+        <v>11.83128736142511</v>
       </c>
       <c r="BN43" t="n">
         <v>12.691038728625</v>
       </c>
       <c r="BO43" t="n">
-        <v>14.45073499954077</v>
+        <v>14.45073500008363</v>
       </c>
       <c r="BP43" t="n">
-        <v>13.65704461530002</v>
+        <v>13.65704461447249</v>
       </c>
       <c r="BQ43" t="n">
-        <v>12.29134015377002</v>
+        <v>12.29134015302524</v>
       </c>
       <c r="BR43" t="n">
         <v>8</v>
@@ -12237,10 +12229,10 @@
         <v>2.6</v>
       </c>
       <c r="BU43" t="n">
-        <v>-74.0470016989749</v>
+        <v>-74.04700170054748</v>
       </c>
       <c r="BV43" t="n">
-        <v>-69.48746872190232</v>
+        <v>-69.48746872075607</v>
       </c>
       <c r="BW43" t="inlineStr">
         <is>
@@ -12291,7 +12283,7 @@
         <v>-3.681101537516229</v>
       </c>
       <c r="CI43" t="n">
-        <v>-12.75737357829422</v>
+        <v>-12.75737983983745</v>
       </c>
       <c r="CJ43" t="b">
         <v>1</v>
@@ -12955,10 +12947,10 @@
         <v>10.27999973297119</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.806939247152598</v>
+        <v>5.806939298270844</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.77187230346807</v>
+        <v>10.77187239829242</v>
       </c>
       <c r="BI2" t="n">
         <v>35.84473591101796</v>
@@ -12967,7 +12959,7 @@
         <v>24.64756109389902</v>
       </c>
       <c r="BK2" t="n">
-        <v>61.97293301439586</v>
+        <v>61.97293320272624</v>
       </c>
       <c r="BL2" t="n">
         <v>17.08511007767805</v>
@@ -13483,10 +13475,10 @@
         <v>4.039999961853027</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.419224480245221</v>
+        <v>3.419461684738401</v>
       </c>
       <c r="BH4" t="n">
-        <v>6.342661410854884</v>
+        <v>6.343101425189735</v>
       </c>
       <c r="BI4" t="n">
         <v>12.47785536003557</v>
@@ -13495,25 +13487,25 @@
         <v>8.411070803097941</v>
       </c>
       <c r="BK4" t="n">
-        <v>24.27141720569131</v>
+        <v>24.27125083123389</v>
       </c>
       <c r="BL4" t="n">
-        <v>11.09300742705852</v>
+        <v>11.09291018546735</v>
       </c>
       <c r="BM4" t="n">
-        <v>10.7582764727997</v>
+        <v>10.75768532124998</v>
       </c>
       <c r="BN4" t="n">
         <v>4.904734709731053</v>
       </c>
       <c r="BO4" t="n">
-        <v>8.997934363929613</v>
+        <v>8.997892967461938</v>
       </c>
       <c r="BP4" t="n">
-        <v>9.584673637948821</v>
+        <v>9.584378062173961</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.62620627415394</v>
+        <v>8.625940255956566</v>
       </c>
       <c r="BR4" t="n">
         <v>6</v>
@@ -13525,10 +13517,10 @@
         <v>7.1</v>
       </c>
       <c r="BU4" t="n">
-        <v>113.5199592971619</v>
+        <v>113.5133746882538</v>
       </c>
       <c r="BV4" t="n">
-        <v>122.7211497250245</v>
+        <v>122.7201250599733</v>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
@@ -13760,10 +13752,10 @@
         <v>23.79999923706055</v>
       </c>
       <c r="BG5" t="n">
-        <v>15.6708491740659</v>
+        <v>15.67084913734821</v>
       </c>
       <c r="BH5" t="n">
-        <v>29.06942521789225</v>
+        <v>29.06942514978093</v>
       </c>
       <c r="BI5" t="n">
         <v>62.32213238953601</v>
@@ -13772,19 +13764,19 @@
         <v>45.62472487613315</v>
       </c>
       <c r="BK5" t="n">
-        <v>103.4137246898866</v>
+        <v>103.4137247113078</v>
       </c>
       <c r="BL5" t="n">
-        <v>20.19414446318722</v>
+        <v>20.19414446787059</v>
       </c>
       <c r="BM5" t="n">
-        <v>50.31447891321876</v>
+        <v>50.31447899054034</v>
       </c>
       <c r="BN5" t="n">
         <v>37.19489833875116</v>
       </c>
       <c r="BO5" t="n">
-        <v>49.73336126980074</v>
+        <v>49.73336127484571</v>
       </c>
       <c r="BP5" t="n">
         <v>45.62472487613315</v>
@@ -13805,7 +13797,7 @@
         <v>72.53047775135681</v>
       </c>
       <c r="BV5" t="n">
-        <v>108.9637095128879</v>
+        <v>108.9637095340853</v>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
@@ -14037,10 +14029,10 @@
         <v>13.63000011444092</v>
       </c>
       <c r="BG6" t="n">
-        <v>15.04788544480291</v>
+        <v>15.04788549860464</v>
       </c>
       <c r="BH6" t="n">
-        <v>27.9138275001094</v>
+        <v>27.91382759991161</v>
       </c>
       <c r="BI6" t="n">
         <v>37.94065157906348</v>
@@ -14049,25 +14041,25 @@
         <v>22.93112736979142</v>
       </c>
       <c r="BK6" t="n">
-        <v>70.78984148599396</v>
+        <v>70.78984138015393</v>
       </c>
       <c r="BL6" t="n">
-        <v>45.29369807452761</v>
+        <v>45.29369803629783</v>
       </c>
       <c r="BM6" t="n">
-        <v>24.32634150128582</v>
+        <v>24.3263413352924</v>
       </c>
       <c r="BN6" t="n">
         <v>8.909513594966207</v>
       </c>
       <c r="BO6" t="n">
-        <v>28.90892191159677</v>
+        <v>28.90892190316023</v>
       </c>
       <c r="BP6" t="n">
-        <v>26.12008450069761</v>
+        <v>26.12008446760201</v>
       </c>
       <c r="BQ6" t="n">
-        <v>23.50807605062785</v>
+        <v>23.50807602084181</v>
       </c>
       <c r="BR6" t="n">
         <v>6</v>
@@ -14079,10 +14071,10 @@
         <v>7.9</v>
       </c>
       <c r="BU6" t="n">
-        <v>72.47304367753568</v>
+        <v>72.47304345900272</v>
       </c>
       <c r="BV6" t="n">
-        <v>112.0977378493776</v>
+        <v>112.0977377874808</v>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
@@ -14497,10 +14489,10 @@
         <v>4.320000171661377</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.922596181840153</v>
+        <v>2.922596170132509</v>
       </c>
       <c r="BH8" t="n">
-        <v>5.421415917313483</v>
+        <v>5.421415895595804</v>
       </c>
       <c r="BI8" t="n">
         <v>12.47058873083077</v>
@@ -14509,7 +14501,7 @@
         <v>8.38874521704944</v>
       </c>
       <c r="BK8" t="n">
-        <v>23.03188434001804</v>
+        <v>23.03188430430845</v>
       </c>
       <c r="BL8" t="n">
         <v>11.34817472758152</v>
@@ -14521,7 +14513,7 @@
         <v>4.921612750118176</v>
       </c>
       <c r="BO8" t="n">
-        <v>10.99580820422241</v>
+        <v>10.99580819601852</v>
       </c>
       <c r="BP8" t="n">
         <v>11.34817472758152</v>
@@ -14542,7 +14534,7 @@
         <v>136.4202974301165</v>
       </c>
       <c r="BV8" t="n">
-        <v>154.5325872057469</v>
+        <v>154.532587015842</v>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
@@ -14651,7 +14643,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>Fundo duplo</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="R9" t="n">
@@ -14774,10 +14766,10 @@
         <v>15.56999969482422</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.370378834709528</v>
+        <v>6.370378843208369</v>
       </c>
       <c r="BH9" t="n">
-        <v>11.81705273838617</v>
+        <v>11.81705275415152</v>
       </c>
       <c r="BI9" t="n">
         <v>25.22035402890231</v>
@@ -14786,19 +14778,19 @@
         <v>18.49208604587491</v>
       </c>
       <c r="BK9" t="n">
-        <v>34.98832838794136</v>
+        <v>34.98832837415703</v>
       </c>
       <c r="BL9" t="n">
-        <v>12.15521321642056</v>
+        <v>12.15521321481462</v>
       </c>
       <c r="BM9" t="n">
-        <v>20.22430271417904</v>
+        <v>20.22430269637158</v>
       </c>
       <c r="BN9" t="n">
         <v>17.52538993234214</v>
       </c>
       <c r="BO9" t="n">
-        <v>20.06038958057807</v>
+        <v>20.06038957808773</v>
       </c>
       <c r="BP9" t="n">
         <v>18.49208604587491</v>
@@ -14819,7 +14811,7 @@
         <v>6.890672880487236</v>
       </c>
       <c r="BV9" t="n">
-        <v>28.84001267672822</v>
+        <v>28.84001266073375</v>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
@@ -14836,16 +14828,8 @@
           <t>última</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>A Mills (MILS3) apresenta-se como uma alternativa robusta no setor de bens industriais, destacando-se por uma eficiência operacional que supera com folga a média de seus pares. A companhia entrega uma rentabilidade excepcional, com ROE de 23,8% e ROIC de 20,6% substancialmente acima das médias setoriais de 15,5% e 12,7%, respectivamente, o que evidencia uma forte geração de valor sobre o capital empregado. Essa alta qualidade operacional convive com múltiplos de preço bastante atrativos, visto que o P/L de 8,18 e o P/VP de 1,95 sugerem que o mercado ainda não precifica totalmente a capacidade de entrega da empresa, uma assimetria reforçada pelo PEG de 0,65. No âmbito financeiro, a excelente rentabilidade é sustentada por uma estrutura de capital muito saudável, com a relação Dívida Líquida/EBITDA em 1,28 vezes, patamar significativamente abaixo da média do setor de 2,29 vezes, e uma liquidez corrente confortável de 2,98. Esse endividamento controlado e a margem líquida robusta de 23,53% conferem sustentabilidade ao dividend yield de 6,78%, mostrando-se coerente com a geração de caixa e a manutenção dos negócios. Por outro lado, o crescimento da receita nos últimos cinco anos, embora expressivo em termos absolutos com um CAGR de 21,3%, ficou muito aquém da média setorial de 117,8%, o que acende um sinal de alerta sobre o ritmo de expansão frente aos concorrentes. No checklist fundamentalista, a empresa atende a 6 dos 8 critérios estipulados, sendo penalizada justamente pelo crescimento inferior aos pares e por movimentações de venda de insiders. Sob a ótica do valuation, as estimativas de preço-teto revelam uma enorme dispersão entre os métodos, variando desde os conservadores R$ 6,37 por Bazin até os otimistas R$ 35,01 por Lynch, resultando em uma média de R$ 20,07 e um preço-teto ajustado com margem de segurança de R$ 16,65, o que confere um upside de 6,9% em relação à cotação atual de R$ 15,58. Em balanço, o ativo traz como pontos positivos a alta rentabilidade, o endividamento sob controle e múltiplos de preço convidativos, enquanto os pontos negativos residem no crescimento histórico abaixo da média do setor e na pressão vendedora por parte de insiders.</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>Fundo duplo</t>
-        </is>
-      </c>
+      <c r="BZ9" t="inlineStr"/>
+      <c r="CA9" t="inlineStr"/>
       <c r="CB9" t="b">
         <v>0</v>
       </c>
@@ -14872,14 +14856,14 @@
         <v>1</v>
       </c>
       <c r="CK9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>Fundo duplo — rompeu pescoço ~R$13.44 (candidato)</t>
+          <t>sem sinal (Em Alta)</t>
         </is>
       </c>
     </row>
@@ -15045,10 +15029,10 @@
         <v>48.38999938964844</v>
       </c>
       <c r="BG10" t="n">
-        <v>18.4311091643195</v>
+        <v>18.43110921108345</v>
       </c>
       <c r="BH10" t="n">
-        <v>34.18970749981268</v>
+        <v>34.18970758655979</v>
       </c>
       <c r="BI10" t="n">
         <v>73.52838210009652</v>
@@ -15057,23 +15041,23 @@
         <v>55.10133168995815</v>
       </c>
       <c r="BK10" t="n">
-        <v>97.40219845085582</v>
+        <v>97.40219837640315</v>
       </c>
       <c r="BL10" t="n">
-        <v>47.18970514406958</v>
+        <v>47.18970513273842</v>
       </c>
       <c r="BM10" t="n">
-        <v>57.44862736282407</v>
+        <v>57.44862726883226</v>
       </c>
       <c r="BN10" t="inlineStr"/>
       <c r="BO10" t="n">
-        <v>43.33472597707457</v>
+        <v>43.33472600761954</v>
       </c>
       <c r="BP10" t="n">
-        <v>40.68970632194113</v>
+        <v>40.68970635964911</v>
       </c>
       <c r="BQ10" t="n">
-        <v>36.62073568974702</v>
+        <v>36.6207357236842</v>
       </c>
       <c r="BR10" t="n">
         <v>4</v>
@@ -15085,10 +15069,10 @@
         <v>4</v>
       </c>
       <c r="BU10" t="n">
-        <v>-24.32168598542923</v>
+        <v>-24.32168591529661</v>
       </c>
       <c r="BV10" t="n">
-        <v>-10.44693836812755</v>
+        <v>-10.44693830500505</v>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
@@ -15306,10 +15290,10 @@
         <v>18.45000076293945</v>
       </c>
       <c r="BG11" t="n">
-        <v>12.68429994841975</v>
+        <v>12.68429990576347</v>
       </c>
       <c r="BH11" t="n">
-        <v>23.52937640431863</v>
+        <v>23.52937632519124</v>
       </c>
       <c r="BI11" t="n">
         <v>19.46357564561686</v>
@@ -15318,7 +15302,7 @@
         <v>12.1658993674517</v>
       </c>
       <c r="BK11" t="n">
-        <v>32.94109944613866</v>
+        <v>32.94109939859185</v>
       </c>
       <c r="BL11" t="n">
         <v>22.27593117185458</v>
@@ -15328,7 +15312,7 @@
       </c>
       <c r="BN11" t="inlineStr"/>
       <c r="BO11" t="n">
-        <v>19.48829579255245</v>
+        <v>19.48829576210654</v>
       </c>
       <c r="BP11" t="n">
         <v>20.86975340873572</v>
@@ -15349,7 +15333,7 @@
         <v>1.80367095480638</v>
       </c>
       <c r="BV11" t="n">
-        <v>5.627615103944184</v>
+        <v>5.627614938925674</v>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
@@ -15572,7 +15556,7 @@
         <v>0.19</v>
       </c>
       <c r="BD12" t="n">
-        <v>128.24</v>
+        <v>128.25</v>
       </c>
       <c r="BE12" t="n">
         <v>35</v>
@@ -15581,10 +15565,10 @@
         <v>31.39999961853027</v>
       </c>
       <c r="BG12" t="n">
-        <v>43.84645055378819</v>
+        <v>43.84701156266345</v>
       </c>
       <c r="BH12" t="n">
-        <v>81.3351657772771</v>
+        <v>81.3362064487407</v>
       </c>
       <c r="BI12" t="n">
         <v>63.4222553270619</v>
@@ -15605,7 +15589,7 @@
         <v>25.86511310728236</v>
       </c>
       <c r="BO12" t="n">
-        <v>67.06903433310754</v>
+        <v>67.06923454314989</v>
       </c>
       <c r="BP12" t="n">
         <v>60.66996877513281</v>
@@ -15626,7 +15610,7 @@
         <v>73.89481707317074</v>
       </c>
       <c r="BV12" t="n">
-        <v>113.5956533372939</v>
+        <v>113.5962909489015</v>
       </c>
       <c r="BW12" t="inlineStr">
         <is>
@@ -15858,10 +15842,10 @@
         <v>31.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>22.10300330650479</v>
+        <v>22.10300332666242</v>
       </c>
       <c r="BH13" t="n">
-        <v>41.00107113356637</v>
+        <v>41.00107117095879</v>
       </c>
       <c r="BI13" t="n">
         <v>45.51526717557251</v>
@@ -15870,25 +15854,25 @@
         <v>19.62721165712462</v>
       </c>
       <c r="BK13" t="n">
-        <v>57.23589733651509</v>
+        <v>57.23589717270841</v>
       </c>
       <c r="BL13" t="n">
-        <v>49.59879613150471</v>
+        <v>49.59879610520782</v>
       </c>
       <c r="BM13" t="n">
-        <v>23.94234276449628</v>
+        <v>23.94234264218778</v>
       </c>
       <c r="BN13" t="n">
         <v>23.78189287402351</v>
       </c>
       <c r="BO13" t="n">
-        <v>35.35068529741349</v>
+        <v>35.35068526555573</v>
       </c>
       <c r="BP13" t="n">
-        <v>32.47170694903133</v>
+        <v>32.47170690657328</v>
       </c>
       <c r="BQ13" t="n">
-        <v>29.2245362541282</v>
+        <v>29.22453621591595</v>
       </c>
       <c r="BR13" t="n">
         <v>8</v>
@@ -15900,10 +15884,10 @@
         <v>2.9</v>
       </c>
       <c r="BU13" t="n">
-        <v>-7.223694431339056</v>
+        <v>-7.223694552647764</v>
       </c>
       <c r="BV13" t="n">
-        <v>12.22439776956663</v>
+        <v>12.22439766843086</v>
       </c>
       <c r="BW13" t="inlineStr">
         <is>
@@ -16135,10 +16119,10 @@
         <v>6.510000228881836</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.939313007595649</v>
+        <v>2.939312997517357</v>
       </c>
       <c r="BH14" t="n">
-        <v>5.452425629089928</v>
+        <v>5.452425610394696</v>
       </c>
       <c r="BI14" t="n">
         <v>21.245690402139</v>
@@ -16147,7 +16131,7 @@
         <v>13.54578759251334</v>
       </c>
       <c r="BK14" t="n">
-        <v>34.18728707871099</v>
+        <v>34.18728704395826</v>
       </c>
       <c r="BL14" t="n">
         <v>11.55192114631721</v>
@@ -16404,10 +16388,10 @@
         <v>41.65999984741211</v>
       </c>
       <c r="BG15" t="n">
-        <v>116.382891403826</v>
+        <v>116.3828918678095</v>
       </c>
       <c r="BH15" t="n">
-        <v>215.8902635540973</v>
+        <v>215.8902644147867</v>
       </c>
       <c r="BI15" t="n">
         <v>135.2928916613261</v>
@@ -16428,7 +16412,7 @@
         <v>63.51616176610359</v>
       </c>
       <c r="BO15" t="n">
-        <v>156.0869281387265</v>
+        <v>156.0869283043106</v>
       </c>
       <c r="BP15" t="n">
         <v>129.4216907024384</v>
@@ -16449,7 +16433,7 @@
         <v>179.5955882352941</v>
       </c>
       <c r="BV15" t="n">
-        <v>274.6685758771612</v>
+        <v>274.6685762746266</v>
       </c>
       <c r="BW15" t="inlineStr">
         <is>
@@ -16677,10 +16661,10 @@
         <v>7.139999866485596</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.680633730912417</v>
+        <v>6.680633775854599</v>
       </c>
       <c r="BH16" t="n">
-        <v>12.39257557084253</v>
+        <v>12.39257565421028</v>
       </c>
       <c r="BI16" t="n">
         <v>39.58368126817327</v>
@@ -16689,7 +16673,7 @@
         <v>26.56660483450646</v>
       </c>
       <c r="BK16" t="n">
-        <v>83.94513398747188</v>
+        <v>83.94513425073151</v>
       </c>
       <c r="BL16" t="n">
         <v>50.65010714487485</v>
@@ -16926,10 +16910,10 @@
         <v>13.14000034332275</v>
       </c>
       <c r="BG17" t="n">
-        <v>9.532624397669307</v>
+        <v>9.532624425278916</v>
       </c>
       <c r="BH17" t="n">
-        <v>17.68301825767657</v>
+        <v>17.68301830889239</v>
       </c>
       <c r="BI17" t="n">
         <v>49.32153103371855</v>
@@ -16938,23 +16922,23 @@
         <v>47.39158599337461</v>
       </c>
       <c r="BK17" t="n">
-        <v>71.21193623729023</v>
+        <v>71.21193629271393</v>
       </c>
       <c r="BL17" t="n">
-        <v>31.70486910611248</v>
+        <v>31.70486910188592</v>
       </c>
       <c r="BM17" t="n">
-        <v>30.94181048811404</v>
+        <v>30.9418104541233</v>
       </c>
       <c r="BN17" t="inlineStr"/>
       <c r="BO17" t="n">
-        <v>32.90313946583586</v>
+        <v>32.90313948149895</v>
       </c>
       <c r="BP17" t="n">
-        <v>31.70486910611248</v>
+        <v>31.70486910188592</v>
       </c>
       <c r="BQ17" t="n">
-        <v>28.53438219550123</v>
+        <v>28.53438219169733</v>
       </c>
       <c r="BR17" t="n">
         <v>3</v>
@@ -16966,10 +16950,10 @@
         <v>5.2</v>
       </c>
       <c r="BU17" t="n">
-        <v>117.1566320392169</v>
+        <v>117.1566320102678</v>
       </c>
       <c r="BV17" t="n">
-        <v>150.4044033952859</v>
+        <v>150.4044035144875</v>
       </c>
       <c r="BW17" t="inlineStr">
         <is>
@@ -17203,10 +17187,10 @@
         <v>46.52999877929688</v>
       </c>
       <c r="BG18" t="n">
-        <v>123.6452420212558</v>
+        <v>123.6452416435381</v>
       </c>
       <c r="BH18" t="n">
-        <v>229.3619239494295</v>
+        <v>229.3619232487632</v>
       </c>
       <c r="BI18" t="n">
         <v>135.2022990845797</v>
@@ -17227,13 +17211,13 @@
         <v>59.74650373916668</v>
       </c>
       <c r="BO18" t="n">
-        <v>158.1040900200363</v>
+        <v>158.1040898852383</v>
       </c>
       <c r="BP18" t="n">
-        <v>129.4237705529177</v>
+        <v>129.4237703640589</v>
       </c>
       <c r="BQ18" t="n">
-        <v>116.481393497626</v>
+        <v>116.481393327653</v>
       </c>
       <c r="BR18" t="n">
         <v>8</v>
@@ -17245,10 +17229,10 @@
         <v>5.1</v>
       </c>
       <c r="BU18" t="n">
-        <v>150.3361198226667</v>
+        <v>150.3361194573692</v>
       </c>
       <c r="BV18" t="n">
-        <v>239.7895855745936</v>
+        <v>239.7895852848923</v>
       </c>
       <c r="BW18" t="inlineStr">
         <is>
@@ -17476,37 +17460,37 @@
         <v>33.2400016784668</v>
       </c>
       <c r="BG19" t="n">
-        <v>23.90692739356484</v>
+        <v>23.90741365952943</v>
       </c>
       <c r="BH19" t="n">
-        <v>31.38254533312008</v>
+        <v>31.38173465619063</v>
       </c>
       <c r="BI19" t="n">
-        <v>35.57896395648235</v>
+        <v>35.57732123594623</v>
       </c>
       <c r="BJ19" t="n">
         <v>35.59395391834337</v>
       </c>
       <c r="BK19" t="n">
-        <v>49.6423438176403</v>
+        <v>49.64138158167129</v>
       </c>
       <c r="BL19" t="n">
-        <v>48.07460119883368</v>
+        <v>48.074387275934</v>
       </c>
       <c r="BM19" t="n">
-        <v>17.32445864401277</v>
+        <v>17.32336532361797</v>
       </c>
       <c r="BN19" t="n">
         <v>29.12385888600579</v>
       </c>
       <c r="BO19" t="n">
-        <v>33.8284566435004</v>
+        <v>33.82792706715485</v>
       </c>
       <c r="BP19" t="n">
-        <v>33.48075464480122</v>
+        <v>33.47952794606843</v>
       </c>
       <c r="BQ19" t="n">
-        <v>30.13267918032109</v>
+        <v>30.13157515146159</v>
       </c>
       <c r="BR19" t="n">
         <v>8</v>
@@ -17518,10 +17502,10 @@
         <v>2.9</v>
       </c>
       <c r="BU19" t="n">
-        <v>-9.348141820819034</v>
+        <v>-9.351463207111932</v>
       </c>
       <c r="BV19" t="n">
-        <v>1.770321706736899</v>
+        <v>1.768728516848772</v>
       </c>
       <c r="BW19" t="inlineStr">
         <is>
@@ -17558,14 +17542,14 @@
       <c r="CE19" t="inlineStr"/>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>Em Alta</t>
+          <t>Lateral</t>
         </is>
       </c>
       <c r="CG19" t="n">
-        <v>33.47999954223633</v>
+        <v>33.70000076293945</v>
       </c>
       <c r="CH19" t="n">
-        <v>-0.7168395073206768</v>
+        <v>-1.364982415604354</v>
       </c>
       <c r="CI19" t="n">
         <v>-15.92494252569399</v>
@@ -17761,10 +17745,10 @@
         <v>14.27999973297119</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.387520847375252</v>
+        <v>4.387520843683155</v>
       </c>
       <c r="BH20" t="n">
-        <v>8.138851171881091</v>
+        <v>8.138851165032253</v>
       </c>
       <c r="BI20" t="n">
         <v>23.74027559120054</v>
@@ -17773,25 +17757,25 @@
         <v>19.99443109682345</v>
       </c>
       <c r="BK20" t="n">
-        <v>28.98387347901059</v>
+        <v>28.98387348186536</v>
       </c>
       <c r="BL20" t="n">
-        <v>16.36200631219285</v>
+        <v>16.36200631295526</v>
       </c>
       <c r="BM20" t="n">
-        <v>18.16044427263289</v>
+        <v>18.16044427850392</v>
       </c>
       <c r="BN20" t="n">
         <v>13.94701359457771</v>
       </c>
       <c r="BO20" t="n">
-        <v>18.4752707883313</v>
+        <v>18.47527078870835</v>
       </c>
       <c r="BP20" t="n">
-        <v>18.16044427263289</v>
+        <v>18.16044427850392</v>
       </c>
       <c r="BQ20" t="n">
-        <v>16.3443998453696</v>
+        <v>16.34439985065353</v>
       </c>
       <c r="BR20" t="n">
         <v>7</v>
@@ -17803,10 +17787,10 @@
         <v>6.6</v>
       </c>
       <c r="BU20" t="n">
-        <v>14.45658369048777</v>
+        <v>14.45658372749006</v>
       </c>
       <c r="BV20" t="n">
-        <v>29.37864939642554</v>
+        <v>29.37864939906596</v>
       </c>
       <c r="BW20" t="inlineStr">
         <is>
@@ -18046,10 +18030,10 @@
         <v>16.47999954223633</v>
       </c>
       <c r="BG21" t="n">
-        <v>9.770026172626132</v>
+        <v>9.770026142523131</v>
       </c>
       <c r="BH21" t="n">
-        <v>18.12339855022147</v>
+        <v>18.12339849438041</v>
       </c>
       <c r="BI21" t="n">
         <v>36.09256098093079</v>
@@ -18058,25 +18042,25 @@
         <v>35.53250072181754</v>
       </c>
       <c r="BK21" t="n">
-        <v>40.48255603411169</v>
+        <v>40.48255601999791</v>
       </c>
       <c r="BL21" t="n">
-        <v>32.74874497482649</v>
+        <v>32.74874498109326</v>
       </c>
       <c r="BM21" t="n">
-        <v>18.51211383315473</v>
+        <v>18.5121138680694</v>
       </c>
       <c r="BN21" t="n">
         <v>29.55836540201202</v>
       </c>
       <c r="BO21" t="n">
-        <v>30.15003435672496</v>
+        <v>30.15003435261448</v>
       </c>
       <c r="BP21" t="n">
-        <v>32.74874497482649</v>
+        <v>32.74874498109326</v>
       </c>
       <c r="BQ21" t="n">
-        <v>29.47387047734384</v>
+        <v>29.47387048298393</v>
       </c>
       <c r="BR21" t="n">
         <v>7</v>
@@ -18088,10 +18072,10 @@
         <v>4.1</v>
       </c>
       <c r="BU21" t="n">
-        <v>78.84630640799305</v>
+        <v>78.84630644221696</v>
       </c>
       <c r="BV21" t="n">
-        <v>82.94924268325323</v>
+        <v>82.94924265831096</v>
       </c>
       <c r="BW21" t="inlineStr">
         <is>
@@ -18323,10 +18307,10 @@
         <v>9.220000267028809</v>
       </c>
       <c r="BG22" t="n">
-        <v>9.218246671328879</v>
+        <v>9.218246674682376</v>
       </c>
       <c r="BH22" t="n">
-        <v>17.09984757531507</v>
+        <v>17.0998475815358</v>
       </c>
       <c r="BI22" t="n">
         <v>23.49326991117917</v>
@@ -18335,25 +18319,25 @@
         <v>16.88595648327735</v>
       </c>
       <c r="BK22" t="n">
-        <v>36.83316518982861</v>
+        <v>36.83316518716696</v>
       </c>
       <c r="BL22" t="n">
-        <v>23.3951382436891</v>
+        <v>23.39513824224449</v>
       </c>
       <c r="BM22" t="n">
-        <v>12.28881399952907</v>
+        <v>12.28881399218089</v>
       </c>
       <c r="BN22" t="n">
         <v>9.220000267028809</v>
       </c>
       <c r="BO22" t="n">
-        <v>18.55430479264701</v>
+        <v>18.55430479241198</v>
       </c>
       <c r="BP22" t="n">
-        <v>16.99290202929621</v>
+        <v>16.99290203240658</v>
       </c>
       <c r="BQ22" t="n">
-        <v>15.29361182636659</v>
+        <v>15.29361182916592</v>
       </c>
       <c r="BR22" t="n">
         <v>8</v>
@@ -18365,10 +18349,10 @@
         <v>4</v>
       </c>
       <c r="BU22" t="n">
-        <v>65.8743100155574</v>
+        <v>65.87431004591893</v>
       </c>
       <c r="BV22" t="n">
-        <v>101.2397424650642</v>
+        <v>101.2397424625152</v>
       </c>
       <c r="BW22" t="inlineStr">
         <is>
@@ -18600,10 +18584,10 @@
         <v>12.02999973297119</v>
       </c>
       <c r="BG23" t="n">
-        <v>3.74266549349182</v>
+        <v>3.742665486380992</v>
       </c>
       <c r="BH23" t="n">
-        <v>6.942644490427327</v>
+        <v>6.942644477236739</v>
       </c>
       <c r="BI23" t="n">
         <v>19.51009748615278</v>
@@ -18612,19 +18596,19 @@
         <v>18.37827919410691</v>
       </c>
       <c r="BK23" t="n">
-        <v>20.08107821984336</v>
+        <v>20.08107822200372</v>
       </c>
       <c r="BL23" t="n">
-        <v>15.55766337195318</v>
+        <v>15.55766337334014</v>
       </c>
       <c r="BM23" t="n">
-        <v>12.52469663322948</v>
+        <v>12.52469664224658</v>
       </c>
       <c r="BN23" t="n">
         <v>26.99032004584218</v>
       </c>
       <c r="BO23" t="n">
-        <v>17.14068277736503</v>
+        <v>17.14068277727558</v>
       </c>
       <c r="BP23" t="n">
         <v>18.37827919410691</v>
@@ -18645,7 +18629,7 @@
         <v>37.49336360634341</v>
       </c>
       <c r="BV23" t="n">
-        <v>42.48281926712558</v>
+        <v>42.482819266382</v>
       </c>
       <c r="BW23" t="inlineStr">
         <is>
@@ -18875,10 +18859,10 @@
         <v>3.430000066757202</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.790274321248175</v>
+        <v>4.790274329237143</v>
       </c>
       <c r="BH24" t="n">
-        <v>6.974639411737343</v>
+        <v>6.974639423369282</v>
       </c>
       <c r="BI24" t="n">
         <v>6.618181946989778</v>
@@ -18897,7 +18881,7 @@
         <v>2.330329016381401</v>
       </c>
       <c r="BO24" t="n">
-        <v>5.511348698985302</v>
+        <v>5.511348702255454</v>
       </c>
       <c r="BP24" t="n">
         <v>5.928677058339783</v>
@@ -18918,7 +18902,7 @@
         <v>55.5629518558697</v>
       </c>
       <c r="BV24" t="n">
-        <v>60.68071695974786</v>
+        <v>60.68071705508753</v>
       </c>
       <c r="BW24" t="inlineStr">
         <is>
@@ -19150,10 +19134,10 @@
         <v>20.88999938964844</v>
       </c>
       <c r="BG25" t="n">
-        <v>2.938906069118572</v>
+        <v>2.938906064545861</v>
       </c>
       <c r="BH25" t="n">
-        <v>5.451670758214951</v>
+        <v>5.451670749732572</v>
       </c>
       <c r="BI25" t="n">
         <v>31.74225824688552</v>
@@ -19162,7 +19146,7 @@
         <v>26.44590940575898</v>
       </c>
       <c r="BK25" t="n">
-        <v>40.65305915279662</v>
+        <v>40.65305914545512</v>
       </c>
       <c r="BL25" t="n">
         <v>10.44211857350007</v>
@@ -19403,35 +19387,35 @@
         <v>22.70000076293945</v>
       </c>
       <c r="BG26" t="n">
-        <v>16.28609457236874</v>
+        <v>16.28609454810477</v>
       </c>
       <c r="BH26" t="n">
-        <v>28.49660542318114</v>
+        <v>28.49660542684956</v>
       </c>
       <c r="BI26" t="n">
-        <v>47.12783849970864</v>
+        <v>47.12783857598924</v>
       </c>
       <c r="BJ26" t="n">
         <v>47.60027068070954</v>
       </c>
       <c r="BK26" t="n">
-        <v>58.81912817755629</v>
+        <v>58.81912816885568</v>
       </c>
       <c r="BL26" t="n">
-        <v>30.92711815463805</v>
+        <v>30.92711815834657</v>
       </c>
       <c r="BM26" t="n">
-        <v>23.23843511571345</v>
+        <v>23.2384351457134</v>
       </c>
       <c r="BN26" t="inlineStr"/>
       <c r="BO26" t="n">
-        <v>30.70941416247414</v>
+        <v>30.70941417732254</v>
       </c>
       <c r="BP26" t="n">
-        <v>29.71186178890959</v>
+        <v>29.71186179259806</v>
       </c>
       <c r="BQ26" t="n">
-        <v>26.74067561001863</v>
+        <v>26.74067561333825</v>
       </c>
       <c r="BR26" t="n">
         <v>4</v>
@@ -19443,10 +19427,10 @@
         <v>2.9</v>
       </c>
       <c r="BU26" t="n">
-        <v>17.80032912455263</v>
+        <v>17.80032913917651</v>
       </c>
       <c r="BV26" t="n">
-        <v>35.28375828344043</v>
+        <v>35.28375834885185</v>
       </c>
       <c r="BW26" t="inlineStr">
         <is>
@@ -19676,10 +19660,10 @@
         <v>5.889999866485596</v>
       </c>
       <c r="BG27" t="n">
-        <v>6.967484517143126</v>
+        <v>6.967484522855686</v>
       </c>
       <c r="BH27" t="n">
-        <v>10.14465745696039</v>
+        <v>10.14465746527788</v>
       </c>
       <c r="BI27" t="n">
         <v>8.368305821236365</v>
@@ -19698,7 +19682,7 @@
         <v>5.445300917107223</v>
       </c>
       <c r="BO27" t="n">
-        <v>8.112707691017574</v>
+        <v>8.112707693355913</v>
       </c>
       <c r="BP27" t="n">
         <v>8.595393290251712</v>
@@ -19719,7 +19703,7 @@
         <v>31.33877990802598</v>
       </c>
       <c r="BV27" t="n">
-        <v>37.73697580503017</v>
+        <v>37.73697584473032</v>
       </c>
       <c r="BW27" t="inlineStr">
         <is>
@@ -19951,10 +19935,10 @@
         <v>27.1299991607666</v>
       </c>
       <c r="BG28" t="n">
-        <v>7.182527999327719</v>
+        <v>7.182528062020133</v>
       </c>
       <c r="BH28" t="n">
-        <v>13.32358943875292</v>
+        <v>13.32358955504735</v>
       </c>
       <c r="BI28" t="n">
         <v>34.63126097111343</v>
@@ -19963,19 +19947,19 @@
         <v>27.36859865246639</v>
       </c>
       <c r="BK28" t="n">
-        <v>42.68616600760828</v>
+        <v>42.68616591206175</v>
       </c>
       <c r="BL28" t="n">
-        <v>24.66467732783487</v>
+        <v>24.66467731274425</v>
       </c>
       <c r="BM28" t="n">
-        <v>27.72433021534865</v>
+        <v>27.7243301021412</v>
       </c>
       <c r="BN28" t="n">
         <v>22.34091371576103</v>
       </c>
       <c r="BO28" t="n">
-        <v>27.53421947555508</v>
+        <v>27.53421946019077</v>
       </c>
       <c r="BP28" t="n">
         <v>27.36859865246639</v>
@@ -19996,7 +19980,7 @@
         <v>-9.208479361693655</v>
       </c>
       <c r="BV28" t="n">
-        <v>1.489938545125469</v>
+        <v>1.489938488493281</v>
       </c>
       <c r="BW28" t="inlineStr">
         <is>
@@ -20228,37 +20212,37 @@
         <v>11.01000022888184</v>
       </c>
       <c r="BG29" t="n">
-        <v>9.53170260012339</v>
+        <v>9.531702606440202</v>
       </c>
       <c r="BH29" t="n">
-        <v>17.26678401411701</v>
+        <v>17.26678397502195</v>
       </c>
       <c r="BI29" t="n">
-        <v>20.26492218572863</v>
+        <v>20.26492212641537</v>
       </c>
       <c r="BJ29" t="n">
         <v>11.834803187379</v>
       </c>
       <c r="BK29" t="n">
-        <v>28.09971458761692</v>
+        <v>28.09971456539731</v>
       </c>
       <c r="BL29" t="n">
-        <v>24.03459730002435</v>
+        <v>24.03459729497773</v>
       </c>
       <c r="BM29" t="n">
-        <v>9.914946062520954</v>
+        <v>9.914946040647093</v>
       </c>
       <c r="BN29" t="n">
         <v>8.714817950680764</v>
       </c>
       <c r="BO29" t="n">
-        <v>16.20778598602388</v>
+        <v>16.20778596836993</v>
       </c>
       <c r="BP29" t="n">
-        <v>14.550793600748</v>
+        <v>14.55079358120047</v>
       </c>
       <c r="BQ29" t="n">
-        <v>13.0957142406732</v>
+        <v>13.09571422308043</v>
       </c>
       <c r="BR29" t="n">
         <v>8</v>
@@ -20270,10 +20254,10 @@
         <v>3.2</v>
       </c>
       <c r="BU29" t="n">
-        <v>18.9438144271791</v>
+        <v>18.94381426739002</v>
       </c>
       <c r="BV29" t="n">
-        <v>47.20967891996062</v>
+        <v>47.2096787596159</v>
       </c>
       <c r="BW29" t="inlineStr">
         <is>
@@ -20505,37 +20489,37 @@
         <v>25.3700008392334</v>
       </c>
       <c r="BG30" t="n">
-        <v>16.13552573611296</v>
+        <v>16.1355255980187</v>
       </c>
       <c r="BH30" t="n">
-        <v>27.68254990019557</v>
+        <v>27.6825498810949</v>
       </c>
       <c r="BI30" t="n">
-        <v>48.1263470993755</v>
+        <v>48.12634747805331</v>
       </c>
       <c r="BJ30" t="n">
         <v>52.28637766046484</v>
       </c>
       <c r="BK30" t="n">
-        <v>56.17235742036772</v>
+        <v>56.17235736681715</v>
       </c>
       <c r="BL30" t="n">
-        <v>39.40869665269115</v>
+        <v>39.40869667608578</v>
       </c>
       <c r="BM30" t="n">
-        <v>23.81940994395484</v>
+        <v>23.81941009841052</v>
       </c>
       <c r="BN30" t="n">
         <v>31.56559010239847</v>
       </c>
       <c r="BO30" t="n">
-        <v>36.89960681444514</v>
+        <v>36.89960685766796</v>
       </c>
       <c r="BP30" t="n">
-        <v>35.48714337754481</v>
+        <v>35.48714338924213</v>
       </c>
       <c r="BQ30" t="n">
-        <v>31.93842903979033</v>
+        <v>31.93842905031791</v>
       </c>
       <c r="BR30" t="n">
         <v>8</v>
@@ -20547,10 +20531,10 @@
         <v>3.5</v>
       </c>
       <c r="BU30" t="n">
-        <v>25.89053205863201</v>
+        <v>25.89053210012819</v>
       </c>
       <c r="BV30" t="n">
-        <v>45.44582417743477</v>
+        <v>45.4458243478046</v>
       </c>
       <c r="BW30" t="inlineStr">
         <is>
@@ -20776,10 +20760,10 @@
         <v>8.670000076293945</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.017238341801162</v>
+        <v>4.017238346199441</v>
       </c>
       <c r="BH31" t="n">
-        <v>7.451977124041156</v>
+        <v>7.451977132199961</v>
       </c>
       <c r="BI31" t="n">
         <v>23.54047151862598</v>
@@ -20788,13 +20772,13 @@
         <v>21.93987763885073</v>
       </c>
       <c r="BK31" t="n">
-        <v>29.483266517664</v>
+        <v>29.48326652117494</v>
       </c>
       <c r="BL31" t="n">
-        <v>10.3210421368999</v>
+        <v>10.32104214771942</v>
       </c>
       <c r="BM31" t="n">
-        <v>16.03430381261787</v>
+        <v>16.03430380689343</v>
       </c>
       <c r="BN31" t="n">
         <v>89.07939849036975</v>
@@ -21039,10 +21023,10 @@
         <v>12.86999988555908</v>
       </c>
       <c r="BG32" t="n">
-        <v>8.064609817391995</v>
+        <v>8.0646098175995</v>
       </c>
       <c r="BH32" t="n">
-        <v>14.95985121126215</v>
+        <v>14.95985121164707</v>
       </c>
       <c r="BI32" t="n">
         <v>13.49109956358052</v>
@@ -21063,7 +21047,7 @@
         <v>6.379184203562791</v>
       </c>
       <c r="BO32" t="n">
-        <v>14.53079977236276</v>
+        <v>14.53079977243681</v>
       </c>
       <c r="BP32" t="n">
         <v>12.9056367523308</v>
@@ -21084,7 +21068,7 @@
         <v>-9.750791139240512</v>
       </c>
       <c r="BV32" t="n">
-        <v>12.90442813963961</v>
+        <v>12.90442814021502</v>
       </c>
       <c r="BW32" t="inlineStr">
         <is>
@@ -21121,7 +21105,7 @@
       <c r="CE32" t="inlineStr"/>
       <c r="CF32" t="inlineStr">
         <is>
-          <t>Lateral</t>
+          <t>Em Alta</t>
         </is>
       </c>
       <c r="CG32" t="n">
@@ -21310,10 +21294,10 @@
         <v>14.72000026702881</v>
       </c>
       <c r="BG33" t="n">
-        <v>9.143015684258149</v>
+        <v>9.143015750888184</v>
       </c>
       <c r="BH33" t="n">
-        <v>16.96029409429887</v>
+        <v>16.96029421789758</v>
       </c>
       <c r="BI33" t="n">
         <v>30.23876023847003</v>
@@ -21322,23 +21306,23 @@
         <v>28.82030174141344</v>
       </c>
       <c r="BK33" t="n">
-        <v>34.00566208700226</v>
+        <v>34.00566209981805</v>
       </c>
       <c r="BL33" t="n">
-        <v>26.56393125628211</v>
+        <v>26.56393124183635</v>
       </c>
       <c r="BM33" t="n">
-        <v>14.99745135929703</v>
+        <v>14.99745127644658</v>
       </c>
       <c r="BN33" t="inlineStr"/>
       <c r="BO33" t="n">
-        <v>20.72650031832729</v>
+        <v>20.72650036227304</v>
       </c>
       <c r="BP33" t="n">
-        <v>21.76211267529049</v>
+        <v>21.76211272986697</v>
       </c>
       <c r="BQ33" t="n">
-        <v>19.58590140776144</v>
+        <v>19.58590145688027</v>
       </c>
       <c r="BR33" t="n">
         <v>4</v>
@@ -21350,10 +21334,10 @@
         <v>3.3</v>
       </c>
       <c r="BU33" t="n">
-        <v>33.0563930194466</v>
+        <v>33.0563933531343</v>
       </c>
       <c r="BV33" t="n">
-        <v>40.80502678218276</v>
+        <v>40.80502708072724</v>
       </c>
       <c r="BW33" t="inlineStr">
         <is>
@@ -21392,7 +21376,7 @@
         <v>-10.80078673102787</v>
       </c>
       <c r="CI33" t="n">
-        <v>-19.07733209382061</v>
+        <v>-19.07731455987075</v>
       </c>
       <c r="CJ33" t="b">
         <v>1</v>
@@ -21569,10 +21553,10 @@
         <v>37.2599983215332</v>
       </c>
       <c r="BG34" t="n">
-        <v>34.16541003959492</v>
+        <v>34.16540996879814</v>
       </c>
       <c r="BH34" t="n">
-        <v>49.74483701765021</v>
+        <v>49.74483691457011</v>
       </c>
       <c r="BI34" t="n">
         <v>47.95841368118134</v>
@@ -21589,13 +21573,13 @@
       </c>
       <c r="BN34" t="inlineStr"/>
       <c r="BO34" t="n">
-        <v>47.47016038731842</v>
+        <v>47.4701603438492</v>
       </c>
       <c r="BP34" t="n">
-        <v>48.85162534941578</v>
+        <v>48.85162529787573</v>
       </c>
       <c r="BQ34" t="n">
-        <v>43.9664628144742</v>
+        <v>43.96646276808816</v>
       </c>
       <c r="BR34" t="n">
         <v>4</v>
@@ -21607,10 +21591,10 @@
         <v>1.7</v>
       </c>
       <c r="BU34" t="n">
-        <v>17.99910036245283</v>
+        <v>17.99910023795994</v>
       </c>
       <c r="BV34" t="n">
-        <v>27.40247591445699</v>
+        <v>27.40247579779243</v>
       </c>
       <c r="BW34" t="inlineStr">
         <is>
@@ -21840,10 +21824,10 @@
         <v>3.690000057220459</v>
       </c>
       <c r="BG35" t="n">
-        <v>0.8537054792152962</v>
+        <v>0.8537054779550103</v>
       </c>
       <c r="BH35" t="n">
-        <v>1.583623663944375</v>
+        <v>1.583623661606544</v>
       </c>
       <c r="BI35" t="n">
         <v>9.978061379218586</v>
@@ -21852,13 +21836,13 @@
         <v>8.953076401677793</v>
       </c>
       <c r="BK35" t="n">
-        <v>12.46813579753735</v>
+        <v>12.46813579672958</v>
       </c>
       <c r="BL35" t="n">
-        <v>4.490296415879171</v>
+        <v>4.49029641602614</v>
       </c>
       <c r="BM35" t="n">
-        <v>8.31567788178617</v>
+        <v>8.315677883541797</v>
       </c>
       <c r="BN35" t="n">
         <v>8.070693304078278</v>
@@ -22107,37 +22091,37 @@
         <v>15.01000022888184</v>
       </c>
       <c r="BG36" t="n">
-        <v>5.822993551318927</v>
+        <v>5.822993541107746</v>
       </c>
       <c r="BH36" t="n">
-        <v>8.112117347249821</v>
+        <v>8.112117355296171</v>
       </c>
       <c r="BI36" t="n">
-        <v>10.07841818887771</v>
+        <v>10.0784182165479</v>
       </c>
       <c r="BJ36" t="n">
         <v>11.19351621134486</v>
       </c>
       <c r="BK36" t="n">
-        <v>9.136669956599388</v>
+        <v>9.136669973257201</v>
       </c>
       <c r="BL36" t="n">
-        <v>14.61973513446876</v>
+        <v>14.61973513813408</v>
       </c>
       <c r="BM36" t="n">
-        <v>4.991079391254843</v>
+        <v>4.991079407788788</v>
       </c>
       <c r="BN36" t="n">
         <v>10.28842080392437</v>
       </c>
       <c r="BO36" t="n">
-        <v>9.280368823129836</v>
+        <v>9.28036883092514</v>
       </c>
       <c r="BP36" t="n">
-        <v>9.60754407273855</v>
+        <v>9.607544094902551</v>
       </c>
       <c r="BQ36" t="n">
-        <v>8.646789665464695</v>
+        <v>8.646789685412296</v>
       </c>
       <c r="BR36" t="n">
         <v>8</v>
@@ -22149,10 +22133,10 @@
         <v>2.9</v>
       </c>
       <c r="BU36" t="n">
-        <v>-42.39314101523613</v>
+        <v>-42.39314088234071</v>
       </c>
       <c r="BV36" t="n">
-        <v>-38.17209405984684</v>
+        <v>-38.17209400791277</v>
       </c>
       <c r="BW36" t="inlineStr">
         <is>
@@ -22384,10 +22368,10 @@
         <v>30.59000015258789</v>
       </c>
       <c r="BG37" t="n">
-        <v>3.032359191341571</v>
+        <v>3.032359179807987</v>
       </c>
       <c r="BH37" t="n">
-        <v>5.625026299938614</v>
+        <v>5.625026278543815</v>
       </c>
       <c r="BI37" t="n">
         <v>31.32283632316766</v>
@@ -22396,7 +22380,7 @@
         <v>21.94043581226608</v>
       </c>
       <c r="BK37" t="n">
-        <v>38.74057426333852</v>
+        <v>38.74057425086014</v>
       </c>
       <c r="BL37" t="n">
         <v>16.47675213208347</v>
@@ -22466,7 +22450,7 @@
         <v>-5.90586978798332</v>
       </c>
       <c r="CI37" t="n">
-        <v>-35.84819225068575</v>
+        <v>-35.84818696004584</v>
       </c>
       <c r="CJ37" t="b">
         <v>1</v>
@@ -22641,35 +22625,35 @@
         <v>12.63000011444092</v>
       </c>
       <c r="BG38" t="n">
-        <v>8.477710198569117</v>
+        <v>8.477710180027204</v>
       </c>
       <c r="BH38" t="n">
-        <v>13.24330364945143</v>
+        <v>13.24330367008882</v>
       </c>
       <c r="BI38" t="n">
-        <v>17.39835028060029</v>
+        <v>17.39835034576517</v>
       </c>
       <c r="BJ38" t="n">
         <v>16.79972907026644</v>
       </c>
       <c r="BK38" t="n">
-        <v>21.86210625255676</v>
+        <v>21.86210627076501</v>
       </c>
       <c r="BL38" t="n">
-        <v>16.64958769000695</v>
+        <v>16.64958769513608</v>
       </c>
       <c r="BM38" t="n">
-        <v>8.696993311275319</v>
+        <v>8.696993342864806</v>
       </c>
       <c r="BN38" t="inlineStr"/>
       <c r="BO38" t="n">
-        <v>13.94223795465695</v>
+        <v>13.94223797275432</v>
       </c>
       <c r="BP38" t="n">
-        <v>14.94644566972919</v>
+        <v>14.94644568261245</v>
       </c>
       <c r="BQ38" t="n">
-        <v>13.45180110275627</v>
+        <v>13.4518011143512</v>
       </c>
       <c r="BR38" t="n">
         <v>4</v>
@@ -22681,10 +22665,10 @@
         <v>2.1</v>
       </c>
       <c r="BU38" t="n">
-        <v>6.506737774101201</v>
+        <v>6.506737865905876</v>
       </c>
       <c r="BV38" t="n">
-        <v>10.38984820527151</v>
+        <v>10.38984834856027</v>
       </c>
       <c r="BW38" t="inlineStr">
         <is>
@@ -22916,10 +22900,10 @@
         <v>8.350000381469727</v>
       </c>
       <c r="BG39" t="n">
-        <v>2.275170437788945</v>
+        <v>2.275170445514933</v>
       </c>
       <c r="BH39" t="n">
-        <v>4.220441162098493</v>
+        <v>4.220441176430199</v>
       </c>
       <c r="BI39" t="n">
         <v>13.45955049324499</v>
@@ -22928,19 +22912,19 @@
         <v>14.81092624645154</v>
       </c>
       <c r="BK39" t="n">
-        <v>11.28719235011125</v>
+        <v>11.28719235177205</v>
       </c>
       <c r="BL39" t="n">
-        <v>7.403635149027117</v>
+        <v>7.403635148246104</v>
       </c>
       <c r="BM39" t="n">
-        <v>7.372778607655695</v>
+        <v>7.372778600428497</v>
       </c>
       <c r="BN39" t="n">
         <v>9.952965903815388</v>
       </c>
       <c r="BO39" t="n">
-        <v>9.78678427320064</v>
+        <v>9.786784274341255</v>
       </c>
       <c r="BP39" t="n">
         <v>9.952965903815388</v>
@@ -22961,7 +22945,7 @@
         <v>7.277471906620003</v>
       </c>
       <c r="BV39" t="n">
-        <v>17.20699192923889</v>
+        <v>17.20699194289896</v>
       </c>
       <c r="BW39" t="inlineStr">
         <is>
@@ -23191,10 +23175,10 @@
         <v>10.39999961853027</v>
       </c>
       <c r="BG40" t="n">
-        <v>12.94492636538292</v>
+        <v>12.94492644983275</v>
       </c>
       <c r="BH40" t="n">
-        <v>18.84781278799753</v>
+        <v>18.84781291095649</v>
       </c>
       <c r="BI40" t="n">
         <v>17.11392342289792</v>
@@ -23213,7 +23197,7 @@
         <v>15.58796560981411</v>
       </c>
       <c r="BO40" t="n">
-        <v>16.31747703590493</v>
+        <v>16.31747707047306</v>
       </c>
       <c r="BP40" t="n">
         <v>16.35094451635601</v>
@@ -23234,7 +23218,7 @@
         <v>41.49856350475572</v>
       </c>
       <c r="BV40" t="n">
-        <v>56.89882340794652</v>
+        <v>56.89882374033248</v>
       </c>
       <c r="BW40" t="inlineStr">
         <is>
@@ -23466,10 +23450,10 @@
         <v>20.54000091552734</v>
       </c>
       <c r="BG41" t="n">
-        <v>10.65665904615412</v>
+        <v>10.65665906559777</v>
       </c>
       <c r="BH41" t="n">
-        <v>19.76810253061589</v>
+        <v>19.76810256668387</v>
       </c>
       <c r="BI41" t="n">
         <v>55.31605937616612</v>
@@ -23478,13 +23462,13 @@
         <v>45.79470361759502</v>
       </c>
       <c r="BK41" t="n">
-        <v>80.22510937124684</v>
+        <v>80.22510937594305</v>
       </c>
       <c r="BL41" t="n">
-        <v>27.74194761639551</v>
+        <v>27.74194761339023</v>
       </c>
       <c r="BM41" t="n">
-        <v>42.51919243745702</v>
+        <v>42.51919240563165</v>
       </c>
       <c r="BN41" t="n">
         <v>4.320378356765164</v>
@@ -23980,35 +23964,35 @@
         <v>16.79000091552734</v>
       </c>
       <c r="BG43" t="n">
-        <v>9.983951974598522</v>
+        <v>9.983951960731627</v>
       </c>
       <c r="BH43" t="n">
-        <v>17.31362329693829</v>
+        <v>17.31362329927638</v>
       </c>
       <c r="BI43" t="n">
-        <v>28.29572498979272</v>
+        <v>28.29572503291434</v>
       </c>
       <c r="BJ43" t="n">
         <v>28.80591266774053</v>
       </c>
       <c r="BK43" t="n">
-        <v>31.54471771143841</v>
+        <v>31.54471771245677</v>
       </c>
       <c r="BL43" t="n">
-        <v>29.07473908054563</v>
+        <v>29.07473908385554</v>
       </c>
       <c r="BM43" t="n">
-        <v>13.97702130754151</v>
+        <v>13.97702132478416</v>
       </c>
       <c r="BN43" t="inlineStr"/>
       <c r="BO43" t="n">
-        <v>21.16700983546879</v>
+        <v>21.16700984419447</v>
       </c>
       <c r="BP43" t="n">
-        <v>22.8046741433655</v>
+        <v>22.80467416609536</v>
       </c>
       <c r="BQ43" t="n">
-        <v>20.52420672902895</v>
+        <v>20.52420674948582</v>
       </c>
       <c r="BR43" t="n">
         <v>4</v>
@@ -24020,10 +24004,10 @@
         <v>2.9</v>
       </c>
       <c r="BU43" t="n">
-        <v>22.24065282836423</v>
+        <v>22.24065295020381</v>
       </c>
       <c r="BV43" t="n">
-        <v>26.06914044831052</v>
+        <v>26.06914050028004</v>
       </c>
       <c r="BW43" t="inlineStr">
         <is>
@@ -24062,7 +24046,7 @@
         <v>-11.40119791818688</v>
       </c>
       <c r="CI43" t="n">
-        <v>-20.94721042714066</v>
+        <v>-20.94721767049244</v>
       </c>
       <c r="CJ43" t="b">
         <v>1</v>
@@ -24255,10 +24239,10 @@
         <v>4.25</v>
       </c>
       <c r="BG44" t="n">
-        <v>2.756777599631545</v>
+        <v>2.756777604274725</v>
       </c>
       <c r="BH44" t="n">
-        <v>5.113822447316515</v>
+        <v>5.113822455929615</v>
       </c>
       <c r="BI44" t="n">
         <v>13.83599508599508</v>
@@ -24267,25 +24251,25 @@
         <v>14.73343694068134</v>
       </c>
       <c r="BK44" t="n">
-        <v>16.86864303270065</v>
+        <v>16.86864304137877</v>
       </c>
       <c r="BL44" t="n">
-        <v>8.105886947766782</v>
+        <v>8.105886947238016</v>
       </c>
       <c r="BM44" t="n">
-        <v>7.432122123281853</v>
+        <v>7.432122118697363</v>
       </c>
       <c r="BN44" t="n">
         <v>3.276499576963653</v>
       </c>
       <c r="BO44" t="n">
-        <v>9.909486593529412</v>
+        <v>9.90948659526912</v>
       </c>
       <c r="BP44" t="n">
-        <v>8.105886947766782</v>
+        <v>8.105886947238016</v>
       </c>
       <c r="BQ44" t="n">
-        <v>7.295298252990104</v>
+        <v>7.295298252514215</v>
       </c>
       <c r="BR44" t="n">
         <v>7</v>
@@ -24297,10 +24281,10 @@
         <v>6.1</v>
       </c>
       <c r="BU44" t="n">
-        <v>71.65407654094362</v>
+        <v>71.65407652974622</v>
       </c>
       <c r="BV44" t="n">
-        <v>133.1643904359861</v>
+        <v>133.1643904769205</v>
       </c>
       <c r="BW44" t="inlineStr">
         <is>
@@ -24518,10 +24502,10 @@
         <v>29.52000045776367</v>
       </c>
       <c r="BG45" t="n">
-        <v>15.4318831746634</v>
+        <v>15.43188317097433</v>
       </c>
       <c r="BH45" t="n">
-        <v>28.62614328900059</v>
+        <v>28.62614328215739</v>
       </c>
       <c r="BI45" t="n">
         <v>55.24576356855489</v>
@@ -24530,23 +24514,23 @@
         <v>49.94931085633525</v>
       </c>
       <c r="BK45" t="n">
-        <v>62.03667169361906</v>
+        <v>62.0366716944277</v>
       </c>
       <c r="BL45" t="n">
-        <v>38.72993682063951</v>
+        <v>38.72993681208075</v>
       </c>
       <c r="BM45" t="n">
-        <v>30.95210656982519</v>
+        <v>30.95210657491875</v>
       </c>
       <c r="BN45" t="inlineStr"/>
       <c r="BO45" t="n">
-        <v>34.50843171321459</v>
+        <v>34.50843170844184</v>
       </c>
       <c r="BP45" t="n">
-        <v>33.67804005482005</v>
+        <v>33.67804004711907</v>
       </c>
       <c r="BQ45" t="n">
-        <v>30.31023604933805</v>
+        <v>30.31023604240716</v>
       </c>
       <c r="BR45" t="n">
         <v>4</v>
@@ -24558,10 +24542,10 @@
         <v>3.6</v>
       </c>
       <c r="BU45" t="n">
-        <v>2.676949794445371</v>
+        <v>2.676949770966752</v>
       </c>
       <c r="BV45" t="n">
-        <v>16.89847960059559</v>
+        <v>16.89847958442774</v>
       </c>
       <c r="BW45" t="inlineStr">
         <is>
@@ -24801,37 +24785,37 @@
         <v>10.39999961853027</v>
       </c>
       <c r="BG46" t="n">
-        <v>7.24946442608225</v>
+        <v>7.249464451323488</v>
       </c>
       <c r="BH46" t="n">
-        <v>10.94542260726863</v>
+        <v>10.94542261553002</v>
       </c>
       <c r="BI46" t="n">
-        <v>17.77471065834706</v>
+        <v>17.77471060987495</v>
       </c>
       <c r="BJ46" t="n">
         <v>23.30669690919295</v>
       </c>
       <c r="BK46" t="n">
-        <v>23.21481237219501</v>
+        <v>23.21481238840746</v>
       </c>
       <c r="BL46" t="n">
-        <v>20.50961401757796</v>
+        <v>20.50961401283186</v>
       </c>
       <c r="BM46" t="n">
-        <v>8.884967962904042</v>
+        <v>8.884967937893004</v>
       </c>
       <c r="BN46" t="n">
         <v>9.960670392837367</v>
       </c>
       <c r="BO46" t="n">
-        <v>15.23079491830066</v>
+        <v>15.23079491473639</v>
       </c>
       <c r="BP46" t="n">
-        <v>14.36006663280784</v>
+        <v>14.36006661270249</v>
       </c>
       <c r="BQ46" t="n">
-        <v>12.92405996952706</v>
+        <v>12.92405995143224</v>
       </c>
       <c r="BR46" t="n">
         <v>8</v>
@@ -24843,10 +24827,10 @@
         <v>3.2</v>
       </c>
       <c r="BU46" t="n">
-        <v>24.26981195748819</v>
+        <v>24.26981178349952</v>
       </c>
       <c r="BV46" t="n">
-        <v>46.4499565092587</v>
+        <v>46.44995647498691</v>
       </c>
       <c r="BW46" t="inlineStr">
         <is>
@@ -25064,10 +25048,10 @@
         <v>39</v>
       </c>
       <c r="BG47" t="n">
-        <v>19.93010987979392</v>
+        <v>19.93011005724446</v>
       </c>
       <c r="BH47" t="n">
-        <v>36.97035382701772</v>
+        <v>36.97035415618846</v>
       </c>
       <c r="BI47" t="n">
         <v>54.05334728033472</v>
@@ -25076,23 +25060,23 @@
         <v>40.80446518102817</v>
       </c>
       <c r="BK47" t="n">
-        <v>58.13074606173186</v>
+        <v>58.13074576386963</v>
       </c>
       <c r="BL47" t="n">
-        <v>43.72434341024892</v>
+        <v>43.72434335443165</v>
       </c>
       <c r="BM47" t="n">
-        <v>29.09170552518504</v>
+        <v>29.09170517461377</v>
       </c>
       <c r="BN47" t="inlineStr"/>
       <c r="BO47" t="n">
-        <v>38.66953859934883</v>
+        <v>38.66953871204982</v>
       </c>
       <c r="BP47" t="n">
-        <v>40.34734861863332</v>
+        <v>40.34734875531005</v>
       </c>
       <c r="BQ47" t="n">
-        <v>36.31261375676999</v>
+        <v>36.31261387977905</v>
       </c>
       <c r="BR47" t="n">
         <v>4</v>
@@ -25104,10 +25088,10 @@
         <v>2.7</v>
       </c>
       <c r="BU47" t="n">
-        <v>-6.890733957000017</v>
+        <v>-6.890733641592184</v>
       </c>
       <c r="BV47" t="n">
-        <v>-0.8473369247466001</v>
+        <v>-0.847336635769691</v>
       </c>
       <c r="BW47" t="inlineStr">
         <is>
@@ -25339,10 +25323,10 @@
         <v>13.94999980926514</v>
       </c>
       <c r="BG48" t="n">
-        <v>1.715333660835079</v>
+        <v>1.715333667460783</v>
       </c>
       <c r="BH48" t="n">
-        <v>3.181943940849071</v>
+        <v>3.181943953139752</v>
       </c>
       <c r="BI48" t="n">
         <v>12.01023375391573</v>
@@ -25351,10 +25335,10 @@
         <v>8.698657440543561</v>
       </c>
       <c r="BK48" t="n">
-        <v>15.15689853090761</v>
+        <v>15.15689853693489</v>
       </c>
       <c r="BL48" t="n">
-        <v>4.602811989907461</v>
+        <v>4.602812007686433</v>
       </c>
       <c r="BM48" t="n">
         <v>10.96783610734946</v>
@@ -25600,10 +25584,10 @@
         <v>5.570000171661377</v>
       </c>
       <c r="BG49" t="n">
-        <v>6.611145437223454</v>
+        <v>6.611145471700185</v>
       </c>
       <c r="BH49" t="n">
-        <v>9.625827756597349</v>
+        <v>9.625827806795471</v>
       </c>
       <c r="BI49" t="n">
         <v>4.355488856035963</v>
@@ -25873,37 +25857,37 @@
         <v>43.65000152587891</v>
       </c>
       <c r="BG50" t="n">
-        <v>31.67320339736693</v>
+        <v>31.67320341920442</v>
       </c>
       <c r="BH50" t="n">
-        <v>38.85442811416343</v>
+        <v>38.85442808626338</v>
       </c>
       <c r="BI50" t="n">
-        <v>43.07167816615766</v>
+        <v>43.07167810553303</v>
       </c>
       <c r="BJ50" t="n">
         <v>47.83302112955008</v>
       </c>
       <c r="BK50" t="n">
-        <v>61.35148243696359</v>
+        <v>61.35148239887413</v>
       </c>
       <c r="BL50" t="n">
-        <v>55.87396020691161</v>
+        <v>55.87396019885573</v>
       </c>
       <c r="BM50" t="n">
-        <v>20.30744564081683</v>
+        <v>20.30744559523414</v>
       </c>
       <c r="BN50" t="n">
         <v>76.39578733574842</v>
       </c>
       <c r="BO50" t="n">
-        <v>46.92012580345982</v>
+        <v>46.92012578365791</v>
       </c>
       <c r="BP50" t="n">
-        <v>45.45234964785386</v>
+        <v>45.45234961754156</v>
       </c>
       <c r="BQ50" t="n">
-        <v>40.90711468306848</v>
+        <v>40.9071146557874</v>
       </c>
       <c r="BR50" t="n">
         <v>8</v>
@@ -25915,10 +25899,10 @@
         <v>3.8</v>
       </c>
       <c r="BU50" t="n">
-        <v>-6.28381843511333</v>
+        <v>-6.283818497612925</v>
       </c>
       <c r="BV50" t="n">
-        <v>7.491693386636289</v>
+        <v>7.491693341271088</v>
       </c>
       <c r="BW50" t="inlineStr">
         <is>
@@ -26150,10 +26134,10 @@
         <v>10.3100004196167</v>
       </c>
       <c r="BG51" t="n">
-        <v>4.048541586805194</v>
+        <v>4.048541575118946</v>
       </c>
       <c r="BH51" t="n">
-        <v>7.510044643523633</v>
+        <v>7.510044621845643</v>
       </c>
       <c r="BI51" t="n">
         <v>24.39419742141451</v>
@@ -26162,25 +26146,25 @@
         <v>27.3727543950329</v>
       </c>
       <c r="BK51" t="n">
-        <v>23.05525213271807</v>
+        <v>23.05525212010862</v>
       </c>
       <c r="BL51" t="n">
-        <v>15.96194444652864</v>
+        <v>15.96194444787387</v>
       </c>
       <c r="BM51" t="n">
-        <v>13.04816986351545</v>
+        <v>13.04816987395361</v>
       </c>
       <c r="BN51" t="n">
         <v>4.783281030861835</v>
       </c>
       <c r="BO51" t="n">
-        <v>18.55706048378887</v>
+        <v>18.55706048003819</v>
       </c>
       <c r="BP51" t="n">
-        <v>19.50859828962335</v>
+        <v>19.50859828399124</v>
       </c>
       <c r="BQ51" t="n">
-        <v>17.55773846066102</v>
+        <v>17.55773845559212</v>
       </c>
       <c r="BR51" t="n">
         <v>6</v>
@@ -26192,10 +26176,10 @@
         <v>6.8</v>
       </c>
       <c r="BU51" t="n">
-        <v>70.29813526732885</v>
+        <v>70.29813521816396</v>
       </c>
       <c r="BV51" t="n">
-        <v>79.99088000501533</v>
+        <v>79.99087996863629</v>
       </c>
       <c r="BW51" t="inlineStr">
         <is>
@@ -26423,10 +26407,10 @@
         <v>30.82999992370605</v>
       </c>
       <c r="BG52" t="n">
-        <v>10.12943439046499</v>
+        <v>10.12943438892123</v>
       </c>
       <c r="BH52" t="n">
-        <v>18.79010079431256</v>
+        <v>18.79010079144888</v>
       </c>
       <c r="BI52" t="n">
         <v>54.9794749648863</v>
@@ -26435,19 +26419,19 @@
         <v>51.86549020659677</v>
       </c>
       <c r="BK52" t="n">
-        <v>58.36213067561426</v>
+        <v>58.36213067581333</v>
       </c>
       <c r="BL52" t="n">
-        <v>25.87252909353287</v>
+        <v>25.87252908976683</v>
       </c>
       <c r="BM52" t="n">
-        <v>35.77240177211769</v>
+        <v>35.77240177407123</v>
       </c>
       <c r="BN52" t="n">
         <v>59.1977960724276</v>
       </c>
       <c r="BO52" t="n">
-        <v>43.54856051135544</v>
+        <v>43.54856051071584</v>
       </c>
       <c r="BP52" t="n">
         <v>51.86549020659677</v>
@@ -26468,7 +26452,7 @@
         <v>51.40752935923412</v>
       </c>
       <c r="BV52" t="n">
-        <v>41.25384566695936</v>
+        <v>41.25384566488477</v>
       </c>
       <c r="BW52" t="inlineStr">
         <is>
@@ -26696,37 +26680,37 @@
         <v>31.54999923706055</v>
       </c>
       <c r="BG53" t="n">
-        <v>14.28761664540396</v>
+        <v>14.28761666067266</v>
       </c>
       <c r="BH53" t="n">
-        <v>22.268400434313</v>
+        <v>22.26840044420988</v>
       </c>
       <c r="BI53" t="n">
-        <v>42.62587812954437</v>
+        <v>42.62587810293599</v>
       </c>
       <c r="BJ53" t="n">
         <v>58.65613740495224</v>
       </c>
       <c r="BK53" t="n">
-        <v>41.90294540071708</v>
+        <v>41.9029454060524</v>
       </c>
       <c r="BL53" t="n">
-        <v>34.87261615893475</v>
+        <v>34.87261619440774</v>
       </c>
       <c r="BM53" t="n">
-        <v>21.30896305174318</v>
+        <v>21.30896303879043</v>
       </c>
       <c r="BN53" t="n">
         <v>76.55851215726285</v>
       </c>
       <c r="BO53" t="n">
-        <v>42.59906467678106</v>
+        <v>42.59906467837308</v>
       </c>
       <c r="BP53" t="n">
-        <v>41.90294540071708</v>
+        <v>41.9029454060524</v>
       </c>
       <c r="BQ53" t="n">
-        <v>37.71265086064538</v>
+        <v>37.71265086544716</v>
       </c>
       <c r="BR53" t="n">
         <v>7</v>
@@ -26738,10 +26722,10 @@
         <v>5.4</v>
       </c>
       <c r="BU53" t="n">
-        <v>19.53296916833458</v>
+        <v>19.53296918355416</v>
       </c>
       <c r="BV53" t="n">
-        <v>35.02081048148366</v>
+        <v>35.02081048652965</v>
       </c>
       <c r="BW53" t="inlineStr">
         <is>
@@ -26969,10 +26953,10 @@
         <v>25.98999977111816</v>
       </c>
       <c r="BG54" t="n">
-        <v>4.764912405572914</v>
+        <v>4.764912401124102</v>
       </c>
       <c r="BH54" t="n">
-        <v>8.838912512337753</v>
+        <v>8.838912504085208</v>
       </c>
       <c r="BI54" t="n">
         <v>32.12383367232422</v>
@@ -26981,13 +26965,13 @@
         <v>25.73909396655281</v>
       </c>
       <c r="BK54" t="n">
-        <v>41.31716359680247</v>
+        <v>41.31716360343043</v>
       </c>
       <c r="BL54" t="n">
-        <v>12.18233647814072</v>
+        <v>12.18233647868668</v>
       </c>
       <c r="BM54" t="n">
-        <v>28.53601231437363</v>
+        <v>28.53601232219179</v>
       </c>
       <c r="BN54" t="n">
         <v>25.98999977111816</v>
@@ -27236,37 +27220,37 @@
         <v>22.70000076293945</v>
       </c>
       <c r="BG55" t="n">
-        <v>9.685713095419844</v>
+        <v>9.685744921201403</v>
       </c>
       <c r="BH55" t="n">
-        <v>14.38739452482768</v>
+        <v>14.3873774777648</v>
       </c>
       <c r="BI55" t="n">
-        <v>19.31443173504305</v>
+        <v>19.31434538612159</v>
       </c>
       <c r="BJ55" t="n">
         <v>21.34857150335456</v>
       </c>
       <c r="BK55" t="n">
-        <v>18.48510626296217</v>
+        <v>18.48506896615266</v>
       </c>
       <c r="BL55" t="n">
-        <v>22.55168604255184</v>
+        <v>22.55167735860742</v>
       </c>
       <c r="BM55" t="n">
-        <v>9.647048894779628</v>
+        <v>9.647002991818368</v>
       </c>
       <c r="BN55" t="n">
         <v>17.92914232069673</v>
       </c>
       <c r="BO55" t="n">
-        <v>16.66863679745444</v>
+        <v>16.66861636571469</v>
       </c>
       <c r="BP55" t="n">
-        <v>18.20712429182945</v>
+        <v>18.2071056434247</v>
       </c>
       <c r="BQ55" t="n">
-        <v>16.38641186264651</v>
+        <v>16.38639507908223</v>
       </c>
       <c r="BR55" t="n">
         <v>8</v>
@@ -27278,10 +27262,10 @@
         <v>2.3</v>
       </c>
       <c r="BU55" t="n">
-        <v>-27.81316602685166</v>
+        <v>-27.81323996325571</v>
       </c>
       <c r="BV55" t="n">
-        <v>-26.56988441750169</v>
+        <v>-26.56997442516275</v>
       </c>
       <c r="BW55" t="inlineStr">
         <is>
@@ -27509,10 +27493,10 @@
         <v>47.36000061035156</v>
       </c>
       <c r="BG56" t="n">
-        <v>7.883046092708915</v>
+        <v>7.883046091816701</v>
       </c>
       <c r="BH56" t="n">
-        <v>14.62305050197503</v>
+        <v>14.62305050031998</v>
       </c>
       <c r="BI56" t="n">
         <v>19.62840187948571</v>
@@ -27521,25 +27505,25 @@
         <v>12.20333989274278</v>
       </c>
       <c r="BK56" t="n">
-        <v>15.97866910688979</v>
+        <v>15.97866911064109</v>
       </c>
       <c r="BL56" t="n">
-        <v>20.76704643507733</v>
+        <v>20.76704643561271</v>
       </c>
       <c r="BM56" t="n">
-        <v>11.83128735882157</v>
+        <v>11.83128736142511</v>
       </c>
       <c r="BN56" t="n">
         <v>12.691038728625</v>
       </c>
       <c r="BO56" t="n">
-        <v>14.45073499954077</v>
+        <v>14.45073500008363</v>
       </c>
       <c r="BP56" t="n">
-        <v>13.65704461530002</v>
+        <v>13.65704461447249</v>
       </c>
       <c r="BQ56" t="n">
-        <v>12.29134015377002</v>
+        <v>12.29134015302524</v>
       </c>
       <c r="BR56" t="n">
         <v>8</v>
@@ -27551,10 +27535,10 @@
         <v>2.6</v>
       </c>
       <c r="BU56" t="n">
-        <v>-74.0470016989749</v>
+        <v>-74.04700170054748</v>
       </c>
       <c r="BV56" t="n">
-        <v>-69.48746872190232</v>
+        <v>-69.48746872075607</v>
       </c>
       <c r="BW56" t="inlineStr">
         <is>
@@ -27605,7 +27589,7 @@
         <v>-3.681101537516229</v>
       </c>
       <c r="CI56" t="n">
-        <v>-12.75737357829422</v>
+        <v>-12.75737983983745</v>
       </c>
       <c r="CJ56" t="b">
         <v>1</v>
@@ -27784,10 +27768,10 @@
         <v>50.13000106811523</v>
       </c>
       <c r="BG57" t="n">
-        <v>9.795829238123236</v>
+        <v>9.795809275281858</v>
       </c>
       <c r="BH57" t="n">
-        <v>18.17126323671861</v>
+        <v>18.17122620564785</v>
       </c>
       <c r="BI57" t="n">
         <v>57.70829836251319</v>
@@ -27796,23 +27780,23 @@
         <v>43.21887290828121</v>
       </c>
       <c r="BK57" t="n">
-        <v>77.24514555651207</v>
+        <v>77.24512127503689</v>
       </c>
       <c r="BL57" t="n">
-        <v>26.28547512229735</v>
+        <v>26.28542155533965</v>
       </c>
       <c r="BM57" t="n">
         <v>52.69965359897433</v>
       </c>
       <c r="BN57" t="inlineStr"/>
       <c r="BO57" t="n">
-        <v>18.0841891990464</v>
+        <v>18.08415234542312</v>
       </c>
       <c r="BP57" t="n">
-        <v>18.17126323671861</v>
+        <v>18.17122620564785</v>
       </c>
       <c r="BQ57" t="n">
-        <v>16.35413691304674</v>
+        <v>16.35410358508306</v>
       </c>
       <c r="BR57" t="n">
         <v>3</v>
@@ -27824,10 +27808,10 @@
         <v>5.9</v>
       </c>
       <c r="BU57" t="n">
-        <v>-67.37654784641795</v>
+        <v>-67.37661432948792</v>
       </c>
       <c r="BV57" t="n">
-        <v>-63.92541629018896</v>
+        <v>-63.92548980629208</v>
       </c>
       <c r="BW57" t="inlineStr">
         <is>
@@ -28055,10 +28039,10 @@
         <v>11.22000026702881</v>
       </c>
       <c r="BG58" t="n">
-        <v>1.930034012265158</v>
+        <v>1.93003401310115</v>
       </c>
       <c r="BH58" t="n">
-        <v>3.580213092751869</v>
+        <v>3.580213094302634</v>
       </c>
       <c r="BI58" t="n">
         <v>24.09481418770368</v>
@@ -28067,13 +28051,13 @@
         <v>20.71331717707942</v>
       </c>
       <c r="BK58" t="n">
-        <v>31.31926061743706</v>
+        <v>31.31926061729749</v>
       </c>
       <c r="BL58" t="n">
-        <v>5.170573449730828</v>
+        <v>5.170573451920021</v>
       </c>
       <c r="BM58" t="n">
-        <v>21.79159983977973</v>
+        <v>21.79159983849966</v>
       </c>
       <c r="BN58" t="n">
         <v>35.73116610615543</v>
@@ -28318,10 +28302,10 @@
         <v>21.15999984741211</v>
       </c>
       <c r="BG59" t="n">
-        <v>5.849808892583543</v>
+        <v>5.849808909790182</v>
       </c>
       <c r="BH59" t="n">
-        <v>10.85139549574247</v>
+        <v>10.85139552766079</v>
       </c>
       <c r="BI59" t="n">
         <v>32.11569278100921</v>
@@ -28330,25 +28314,25 @@
         <v>32.99490367325112</v>
       </c>
       <c r="BK59" t="n">
-        <v>28.79985359276257</v>
+        <v>28.79985359120823</v>
       </c>
       <c r="BL59" t="n">
-        <v>23.13732278310927</v>
+        <v>23.13732278053323</v>
       </c>
       <c r="BM59" t="n">
-        <v>18.68112822072748</v>
+        <v>18.68112820240585</v>
       </c>
       <c r="BN59" t="n">
         <v>14.31401835039106</v>
       </c>
       <c r="BO59" t="n">
-        <v>22.98490212814188</v>
+        <v>22.98490212949421</v>
       </c>
       <c r="BP59" t="n">
-        <v>23.13732278310927</v>
+        <v>23.13732278053323</v>
       </c>
       <c r="BQ59" t="n">
-        <v>20.82359050479834</v>
+        <v>20.82359050247991</v>
       </c>
       <c r="BR59" t="n">
         <v>7</v>
@@ -28360,10 +28344,10 @@
         <v>5.6</v>
       </c>
       <c r="BU59" t="n">
-        <v>-1.589836224195029</v>
+        <v>-1.589836235151687</v>
       </c>
       <c r="BV59" t="n">
-        <v>8.624301955999103</v>
+        <v>8.62430196239008</v>
       </c>
       <c r="BW59" t="inlineStr">
         <is>
@@ -28591,37 +28575,37 @@
         <v>38.29999923706055</v>
       </c>
       <c r="BG60" t="n">
-        <v>29.22536354194774</v>
+        <v>29.2253634967025</v>
       </c>
       <c r="BH60" t="n">
-        <v>34.44313633825139</v>
+        <v>34.44313637267875</v>
       </c>
       <c r="BI60" t="n">
-        <v>38.11036736629421</v>
+        <v>38.11036746338768</v>
       </c>
       <c r="BJ60" t="n">
         <v>48.33331772630119</v>
       </c>
       <c r="BK60" t="n">
-        <v>56.94551053775743</v>
+        <v>56.94551058766987</v>
       </c>
       <c r="BL60" t="n">
-        <v>69.48521588404623</v>
+        <v>69.48521579526914</v>
       </c>
       <c r="BM60" t="n">
-        <v>17.48847139153215</v>
+        <v>17.48847146996929</v>
       </c>
       <c r="BN60" t="n">
         <v>27.33708824000841</v>
       </c>
       <c r="BO60" t="n">
-        <v>40.17105887826735</v>
+        <v>40.17105889399835</v>
       </c>
       <c r="BP60" t="n">
-        <v>36.2767518522728</v>
+        <v>36.27675191803321</v>
       </c>
       <c r="BQ60" t="n">
-        <v>32.64907666704552</v>
+        <v>32.64907672622989</v>
       </c>
       <c r="BR60" t="n">
         <v>8</v>
@@ -28633,10 +28617,10 @@
         <v>4</v>
       </c>
       <c r="BU60" t="n">
-        <v>-14.75436731744626</v>
+        <v>-14.75436716291786</v>
       </c>
       <c r="BV60" t="n">
-        <v>4.885273311954252</v>
+        <v>4.885273353027375</v>
       </c>
       <c r="BW60" t="inlineStr">
         <is>
@@ -28864,35 +28848,35 @@
         <v>23.48999977111816</v>
       </c>
       <c r="BG61" t="n">
-        <v>22.18042716658769</v>
+        <v>22.17988071297886</v>
       </c>
       <c r="BH61" t="n">
-        <v>27.69809049157537</v>
+        <v>27.69794445206331</v>
       </c>
       <c r="BI61" t="n">
-        <v>36.24992082951945</v>
+        <v>36.25062279755324</v>
       </c>
       <c r="BJ61" t="n">
         <v>59.33971209695032</v>
       </c>
       <c r="BK61" t="n">
-        <v>63.91577304833363</v>
+        <v>63.91526269053831</v>
       </c>
       <c r="BL61" t="n">
-        <v>39.66505233956753</v>
+        <v>39.6651297698297</v>
       </c>
       <c r="BM61" t="n">
-        <v>17.26284286760575</v>
+        <v>17.2633540421696</v>
       </c>
       <c r="BN61" t="inlineStr"/>
       <c r="BO61" t="n">
-        <v>38.04454554859139</v>
+        <v>38.04455808029763</v>
       </c>
       <c r="BP61" t="n">
-        <v>36.24992082951945</v>
+        <v>36.25062279755324</v>
       </c>
       <c r="BQ61" t="n">
-        <v>32.62492874656751</v>
+        <v>32.62556051779791</v>
       </c>
       <c r="BR61" t="n">
         <v>7</v>
@@ -28904,10 +28888,10 @@
         <v>3.7</v>
       </c>
       <c r="BU61" t="n">
-        <v>38.88858690701687</v>
+        <v>38.89127643973956</v>
       </c>
       <c r="BV61" t="n">
-        <v>61.96060416896463</v>
+        <v>61.96065751807642</v>
       </c>
       <c r="BW61" t="inlineStr">
         <is>
@@ -29135,10 +29119,10 @@
         <v>17</v>
       </c>
       <c r="BG62" t="n">
-        <v>3.911558454033365</v>
+        <v>3.911866897278518</v>
       </c>
       <c r="BH62" t="n">
-        <v>7.255940932231892</v>
+        <v>7.25651309445165</v>
       </c>
       <c r="BI62" t="n">
         <v>26.9115890083632</v>
@@ -29147,13 +29131,13 @@
         <v>33.31412657095888</v>
       </c>
       <c r="BK62" t="n">
-        <v>18.89972862606365</v>
+        <v>18.89988483417865</v>
       </c>
       <c r="BL62" t="n">
-        <v>21.61171348807137</v>
+        <v>21.61167740828704</v>
       </c>
       <c r="BM62" t="n">
-        <v>13.19315932876288</v>
+        <v>13.19293322752645</v>
       </c>
       <c r="BN62" t="n">
         <v>22.22798951537628</v>
@@ -29398,10 +29382,10 @@
         <v>16.31999969482422</v>
       </c>
       <c r="BG63" t="n">
-        <v>4.116375330767659</v>
+        <v>4.116375317010836</v>
       </c>
       <c r="BH63" t="n">
-        <v>7.635876238574009</v>
+        <v>7.635876213055101</v>
       </c>
       <c r="BI63" t="n">
         <v>51.98076825875502</v>
@@ -29410,13 +29394,13 @@
         <v>57.88026518876954</v>
       </c>
       <c r="BK63" t="n">
-        <v>48.62627512174297</v>
+        <v>48.62627509545664</v>
       </c>
       <c r="BL63" t="n">
-        <v>40.34459323360636</v>
+        <v>40.3445932354967</v>
       </c>
       <c r="BM63" t="n">
-        <v>32.33758975777158</v>
+        <v>32.33758977034972</v>
       </c>
       <c r="BN63" t="n">
         <v>33.29124944271519</v>
@@ -29657,10 +29641,10 @@
         <v>23.60000038146973</v>
       </c>
       <c r="BG64" t="n">
-        <v>4.133363631674825</v>
+        <v>4.133363624298475</v>
       </c>
       <c r="BH64" t="n">
-        <v>7.667389536756801</v>
+        <v>7.667389523073671</v>
       </c>
       <c r="BI64" t="n">
         <v>27.31004410956103</v>
@@ -29669,25 +29653,25 @@
         <v>27.193785526638</v>
       </c>
       <c r="BK64" t="n">
-        <v>24.22216033087246</v>
+        <v>24.22216033520601</v>
       </c>
       <c r="BL64" t="n">
-        <v>10.54144132318475</v>
+        <v>10.54144130499742</v>
       </c>
       <c r="BM64" t="n">
-        <v>17.55480031056356</v>
+        <v>17.55480031895667</v>
       </c>
       <c r="BN64" t="n">
         <v>16.32128907814843</v>
       </c>
       <c r="BO64" t="n">
-        <v>18.68727288796072</v>
+        <v>18.68727288522589</v>
       </c>
       <c r="BP64" t="n">
-        <v>17.55480031056356</v>
+        <v>17.55480031895667</v>
       </c>
       <c r="BQ64" t="n">
-        <v>15.7993202795072</v>
+        <v>15.799320287061</v>
       </c>
       <c r="BR64" t="n">
         <v>7</v>
@@ -29699,10 +29683,10 @@
         <v>6.6</v>
       </c>
       <c r="BU64" t="n">
-        <v>-33.05372871132438</v>
+        <v>-33.05372867931676</v>
       </c>
       <c r="BV64" t="n">
-        <v>-20.81664158516873</v>
+        <v>-20.81664159675699</v>
       </c>
       <c r="BW64" t="inlineStr">
         <is>
@@ -29930,37 +29914,37 @@
         <v>30.13999938964844</v>
       </c>
       <c r="BG65" t="n">
-        <v>13.85397102195946</v>
+        <v>13.85397097498956</v>
       </c>
       <c r="BH65" t="n">
-        <v>14.30392292862422</v>
+        <v>14.30392291921939</v>
       </c>
       <c r="BI65" t="n">
-        <v>14.87803214006896</v>
+        <v>14.87803218072849</v>
       </c>
       <c r="BJ65" t="n">
         <v>30.20046083334148</v>
       </c>
       <c r="BK65" t="n">
-        <v>13.7646641223975</v>
+        <v>13.76466414446952</v>
       </c>
       <c r="BL65" t="n">
-        <v>29.79376866222914</v>
+        <v>29.79376867195135</v>
       </c>
       <c r="BM65" t="n">
-        <v>5.881118133329942</v>
+        <v>5.881118174870117</v>
       </c>
       <c r="BN65" t="n">
         <v>38.90017075407383</v>
       </c>
       <c r="BO65" t="n">
-        <v>17.52513397742153</v>
+        <v>17.52513398565284</v>
       </c>
       <c r="BP65" t="n">
-        <v>14.30392292862422</v>
+        <v>14.30392291921939</v>
       </c>
       <c r="BQ65" t="n">
-        <v>12.8735306357618</v>
+        <v>12.87353062729745</v>
       </c>
       <c r="BR65" t="n">
         <v>7</v>
@@ -29972,10 +29956,10 @@
         <v>6.6</v>
       </c>
       <c r="BU65" t="n">
-        <v>-57.2875550880628</v>
+        <v>-57.28755511614623</v>
       </c>
       <c r="BV65" t="n">
-        <v>-41.85423247407057</v>
+        <v>-41.85423244676031</v>
       </c>
       <c r="BW65" t="inlineStr">
         <is>
@@ -30203,10 +30187,10 @@
         <v>13.9399995803833</v>
       </c>
       <c r="BG66" t="n">
-        <v>9.123776648767207</v>
+        <v>9.123776624073715</v>
       </c>
       <c r="BH66" t="n">
-        <v>16.92460568346317</v>
+        <v>16.92460563765674</v>
       </c>
       <c r="BI66" t="n">
         <v>13.57127071565604</v>
@@ -30227,7 +30211,7 @@
         <v>12.4245083187292</v>
       </c>
       <c r="BO66" t="n">
-        <v>14.60394186676404</v>
+        <v>14.60394185795155</v>
       </c>
       <c r="BP66" t="n">
         <v>12.94835109589414</v>
@@ -30248,7 +30232,7 @@
         <v>-16.40232182859006</v>
       </c>
       <c r="BV66" t="n">
-        <v>4.762857291007783</v>
+        <v>4.762857227790507</v>
       </c>
       <c r="BW66" t="inlineStr">
         <is>
@@ -30476,10 +30460,10 @@
         <v>8.720000267028809</v>
       </c>
       <c r="BG67" t="n">
-        <v>1.668744295765918</v>
+        <v>1.668744296359276</v>
       </c>
       <c r="BH67" t="n">
-        <v>3.095520668645777</v>
+        <v>3.095520669746457</v>
       </c>
       <c r="BI67" t="n">
         <v>22.97017962984726</v>
@@ -30488,13 +30472,13 @@
         <v>22.70135587940091</v>
       </c>
       <c r="BK67" t="n">
-        <v>24.24927992434498</v>
+        <v>24.24927992491074</v>
       </c>
       <c r="BL67" t="n">
-        <v>6.453369682185873</v>
+        <v>6.453369682149564</v>
       </c>
       <c r="BM67" t="n">
-        <v>16.95411586651125</v>
+        <v>16.95411586582879</v>
       </c>
       <c r="BN67" t="n">
         <v>26.03006316116035</v>
@@ -30721,35 +30705,35 @@
         <v>12.30000019073486</v>
       </c>
       <c r="BG68" t="n">
-        <v>10.05632369233228</v>
+        <v>10.05632367065691</v>
       </c>
       <c r="BH68" t="n">
-        <v>10.75470860586766</v>
+        <v>10.75470862022576</v>
       </c>
       <c r="BI68" t="n">
-        <v>11.2122421284478</v>
+        <v>11.21224216758357</v>
       </c>
       <c r="BJ68" t="n">
         <v>15.69034148938449</v>
       </c>
       <c r="BK68" t="n">
-        <v>17.98047494272045</v>
+        <v>17.98047496628928</v>
       </c>
       <c r="BL68" t="n">
-        <v>23.65338612574274</v>
+        <v>23.65338608431716</v>
       </c>
       <c r="BM68" t="n">
-        <v>4.662743542568388</v>
+        <v>4.662743580144818</v>
       </c>
       <c r="BN68" t="inlineStr"/>
       <c r="BO68" t="n">
-        <v>13.91916513809762</v>
+        <v>13.91916513569585</v>
       </c>
       <c r="BP68" t="n">
-        <v>10.98347536715773</v>
+        <v>10.98347539390467</v>
       </c>
       <c r="BQ68" t="n">
-        <v>9.885127830441958</v>
+        <v>9.885127854514199</v>
       </c>
       <c r="BR68" t="n">
         <v>4</v>
@@ -30761,10 +30745,10 @@
         <v>2.4</v>
       </c>
       <c r="BU68" t="n">
-        <v>-19.63310831581889</v>
+        <v>-19.63310812010961</v>
       </c>
       <c r="BV68" t="n">
-        <v>13.1639424573539</v>
+        <v>13.1639424378273</v>
       </c>
       <c r="BW68" t="inlineStr">
         <is>
@@ -30992,10 +30976,10 @@
         <v>3.269999980926514</v>
       </c>
       <c r="BG69" t="n">
-        <v>0.7957444707102643</v>
+        <v>0.7957444748394055</v>
       </c>
       <c r="BH69" t="n">
-        <v>1.47610599316754</v>
+        <v>1.476106000827097</v>
       </c>
       <c r="BI69" t="n">
         <v>9.337823221395755</v>
@@ -31004,7 +30988,7 @@
         <v>4.448661621270232</v>
       </c>
       <c r="BK69" t="n">
-        <v>12.97207377237961</v>
+        <v>12.97207378483823</v>
       </c>
       <c r="BL69" t="n">
         <v>6.795306578521528</v>
@@ -31255,10 +31239,10 @@
         <v>15.01000022888184</v>
       </c>
       <c r="BG70" t="n">
-        <v>3.646640791511056</v>
+        <v>3.646640790366459</v>
       </c>
       <c r="BH70" t="n">
-        <v>6.76451866825301</v>
+        <v>6.764518666129782</v>
       </c>
       <c r="BI70" t="n">
         <v>32.49714101841246</v>
@@ -31267,13 +31251,13 @@
         <v>35.16080790586962</v>
       </c>
       <c r="BK70" t="n">
-        <v>29.70492050114732</v>
+        <v>29.70492050029164</v>
       </c>
       <c r="BL70" t="n">
-        <v>11.20055468585323</v>
+        <v>11.20055468592728</v>
       </c>
       <c r="BM70" t="n">
-        <v>19.9801127632564</v>
+        <v>19.98011276436437</v>
       </c>
       <c r="BN70" t="n">
         <v>43.92869987016114</v>
@@ -31518,10 +31502,10 @@
         <v>29.09000015258789</v>
       </c>
       <c r="BG71" t="n">
-        <v>12.61857461616302</v>
+        <v>12.61857467376289</v>
       </c>
       <c r="BH71" t="n">
-        <v>23.4074559129824</v>
+        <v>23.40745601983015</v>
       </c>
       <c r="BI71" t="n">
         <v>36.84918757378484</v>
@@ -31530,19 +31514,19 @@
         <v>25.68115779228379</v>
       </c>
       <c r="BK71" t="n">
-        <v>43.64068778558902</v>
+        <v>43.64068765003535</v>
       </c>
       <c r="BL71" t="n">
-        <v>34.41130752972894</v>
+        <v>34.41130750572611</v>
       </c>
       <c r="BM71" t="n">
-        <v>24.24471211611172</v>
+        <v>24.24471198244778</v>
       </c>
       <c r="BN71" t="n">
         <v>26.21217804663085</v>
       </c>
       <c r="BO71" t="n">
-        <v>28.38315767165932</v>
+        <v>28.38315765556272</v>
       </c>
       <c r="BP71" t="n">
         <v>25.94666791945733</v>
@@ -31563,7 +31547,7 @@
         <v>-19.72498795111156</v>
       </c>
       <c r="BV71" t="n">
-        <v>-2.429846948164027</v>
+        <v>-2.42984700349782</v>
       </c>
       <c r="BW71" t="inlineStr">
         <is>
@@ -31799,37 +31783,37 @@
         <v>18.59000015258789</v>
       </c>
       <c r="BG72" t="n">
-        <v>8.03751357900051</v>
+        <v>8.037513554231637</v>
       </c>
       <c r="BH72" t="n">
-        <v>9.133497109814961</v>
+        <v>9.133497110754361</v>
       </c>
       <c r="BI72" t="n">
-        <v>10.32094256056929</v>
+        <v>10.32094259343644</v>
       </c>
       <c r="BJ72" t="n">
         <v>16.7309332137301</v>
       </c>
       <c r="BK72" t="n">
-        <v>9.598482611092516</v>
+        <v>9.598482632453381</v>
       </c>
       <c r="BL72" t="n">
-        <v>19.39667777957719</v>
+        <v>19.39667778635243</v>
       </c>
       <c r="BM72" t="n">
-        <v>4.59227433841432</v>
+        <v>4.59227436674991</v>
       </c>
       <c r="BN72" t="n">
         <v>17.43118727772496</v>
       </c>
       <c r="BO72" t="n">
-        <v>11.90518855874048</v>
+        <v>11.90518856692915</v>
       </c>
       <c r="BP72" t="n">
-        <v>9.959712585830903</v>
+        <v>9.959712612944911</v>
       </c>
       <c r="BQ72" t="n">
-        <v>8.963741327247813</v>
+        <v>8.96374135165042</v>
       </c>
       <c r="BR72" t="n">
         <v>8</v>
@@ -31841,10 +31825,10 @@
         <v>4.2</v>
       </c>
       <c r="BU72" t="n">
-        <v>-51.78191902273879</v>
+        <v>-51.7819188914714</v>
       </c>
       <c r="BV72" t="n">
-        <v>-35.95917987615953</v>
+        <v>-35.95917983211072</v>
       </c>
       <c r="BW72" t="inlineStr">
         <is>
@@ -31896,7 +31880,7 @@
       </c>
       <c r="CM72" t="inlineStr">
         <is>
-          <t>Fundo duplo — rompeu pescoço ~R$16.83 (candidato)</t>
+          <t>Fundo duplo — rompeu pescoço ~R$17.68 (candidato)</t>
         </is>
       </c>
     </row>
@@ -32076,10 +32060,10 @@
         <v>14.02999973297119</v>
       </c>
       <c r="BG73" t="n">
-        <v>2.263579252097877</v>
+        <v>2.263579260668935</v>
       </c>
       <c r="BH73" t="n">
-        <v>4.198939512641562</v>
+        <v>4.198939528540873</v>
       </c>
       <c r="BI73" t="n">
         <v>24.81942542882086</v>
@@ -32088,7 +32072,7 @@
         <v>18.98830018964925</v>
       </c>
       <c r="BK73" t="n">
-        <v>32.32845200586624</v>
+        <v>32.32845202188691</v>
       </c>
       <c r="BL73" t="n">
         <v>11.58009282301775</v>
@@ -32216,7 +32200,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>Fundo duplo</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="R74" t="n">
@@ -32339,10 +32323,10 @@
         <v>10.68000030517578</v>
       </c>
       <c r="BG74" t="n">
-        <v>6.305613051408286</v>
+        <v>6.305613014172991</v>
       </c>
       <c r="BH74" t="n">
-        <v>11.69691221036237</v>
+        <v>11.6969121412909</v>
       </c>
       <c r="BI74" t="n">
         <v>7.624461424761804</v>
@@ -32363,7 +32347,7 @@
         <v>35.54000257500483</v>
       </c>
       <c r="BO74" t="n">
-        <v>9.873483628855436</v>
+        <v>9.873483613668753</v>
       </c>
       <c r="BP74" t="n">
         <v>7.624461424761804</v>
@@ -32384,7 +32368,7 @@
         <v>-35.74892241379312</v>
       </c>
       <c r="BV74" t="n">
-        <v>-7.551654056877588</v>
+        <v>-7.551654199074987</v>
       </c>
       <c r="BW74" t="inlineStr">
         <is>
@@ -32398,11 +32382,7 @@
       </c>
       <c r="BY74" t="inlineStr"/>
       <c r="BZ74" t="inlineStr"/>
-      <c r="CA74" t="inlineStr">
-        <is>
-          <t>Fundo duplo</t>
-        </is>
-      </c>
+      <c r="CA74" t="inlineStr"/>
       <c r="CB74" t="b">
         <v>0</v>
       </c>
@@ -32429,14 +32409,14 @@
         <v>0</v>
       </c>
       <c r="CK74" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL74" t="b">
         <v>0</v>
       </c>
       <c r="CM74" t="inlineStr">
         <is>
-          <t>Fundo duplo — rompeu pescoço ~R$10.57 (candidato)</t>
+          <t>sem sinal (Em Alta)</t>
         </is>
       </c>
     </row>
@@ -32616,10 +32596,10 @@
         <v>33.16999816894531</v>
       </c>
       <c r="BG75" t="n">
-        <v>9.494426941659437</v>
+        <v>9.494426963569666</v>
       </c>
       <c r="BH75" t="n">
-        <v>17.61216197677826</v>
+        <v>17.61216201742173</v>
       </c>
       <c r="BI75" t="n">
         <v>26.65266681252428</v>
@@ -32628,25 +32608,25 @@
         <v>19.74676755649356</v>
       </c>
       <c r="BK75" t="n">
-        <v>23.99252029424684</v>
+        <v>23.99252024122408</v>
       </c>
       <c r="BL75" t="n">
-        <v>20.91381301062647</v>
+        <v>20.91381300372618</v>
       </c>
       <c r="BM75" t="n">
-        <v>15.38788502661726</v>
+        <v>15.38788498159612</v>
       </c>
       <c r="BN75" t="n">
         <v>26.56395252902917</v>
       </c>
       <c r="BO75" t="n">
-        <v>20.04552426849691</v>
+        <v>20.0455242631981</v>
       </c>
       <c r="BP75" t="n">
-        <v>20.33029028356001</v>
+        <v>20.33029028010987</v>
       </c>
       <c r="BQ75" t="n">
-        <v>18.29726125520401</v>
+        <v>18.29726125209888</v>
       </c>
       <c r="BR75" t="n">
         <v>8</v>
@@ -32658,10 +32638,10 @@
         <v>2.8</v>
       </c>
       <c r="BU75" t="n">
-        <v>-44.83791900738051</v>
+        <v>-44.83791901674176</v>
       </c>
       <c r="BV75" t="n">
-        <v>-39.56730366278978</v>
+        <v>-39.5673036787645</v>
       </c>
       <c r="BW75" t="inlineStr">
         <is>
@@ -32696,7 +32676,7 @@
         <v>-4.243652559481303</v>
       </c>
       <c r="CI75" t="n">
-        <v>-26.21017695879399</v>
+        <v>-26.21018326098841</v>
       </c>
       <c r="CJ75" t="b">
         <v>0</v>
@@ -32889,10 +32869,10 @@
         <v>40.38000106811523</v>
       </c>
       <c r="BG76" t="n">
-        <v>8.834643303924864</v>
+        <v>8.834643325311742</v>
       </c>
       <c r="BH76" t="n">
-        <v>16.38826332878062</v>
+        <v>16.38826336845328</v>
       </c>
       <c r="BI76" t="n">
         <v>116.5653625604633</v>
@@ -32901,7 +32881,7 @@
         <v>85.63237581561071</v>
       </c>
       <c r="BK76" t="n">
-        <v>158.9074122607139</v>
+        <v>158.9074123259462</v>
       </c>
       <c r="BL76" t="n">
         <v>21.83399299607427</v>
@@ -33150,35 +33130,35 @@
         <v>3.289999961853027</v>
       </c>
       <c r="BG77" t="n">
-        <v>2.525405067940134</v>
+        <v>2.52540508489531</v>
       </c>
       <c r="BH77" t="n">
-        <v>3.007784118568462</v>
+        <v>3.007784124456961</v>
       </c>
       <c r="BI77" t="n">
-        <v>3.80281901755897</v>
+        <v>3.802818999472418</v>
       </c>
       <c r="BJ77" t="n">
         <v>6.826829719365466</v>
       </c>
       <c r="BK77" t="n">
-        <v>5.701854068409848</v>
+        <v>5.701854077850046</v>
       </c>
       <c r="BL77" t="n">
-        <v>7.599863477754468</v>
+        <v>7.599863473952553</v>
       </c>
       <c r="BM77" t="n">
-        <v>1.758674092642156</v>
+        <v>1.758674078303502</v>
       </c>
       <c r="BN77" t="inlineStr"/>
       <c r="BO77" t="n">
-        <v>4.460461366034215</v>
+        <v>4.460461365470894</v>
       </c>
       <c r="BP77" t="n">
-        <v>3.80281901755897</v>
+        <v>3.802818999472418</v>
       </c>
       <c r="BQ77" t="n">
-        <v>3.422537115803073</v>
+        <v>3.422537099525176</v>
       </c>
       <c r="BR77" t="n">
         <v>7</v>
@@ -33190,10 +33170,10 @@
         <v>4.3</v>
       </c>
       <c r="BU77" t="n">
-        <v>4.028484969203361</v>
+        <v>4.028484474434446</v>
       </c>
       <c r="BV77" t="n">
-        <v>35.57633488609368</v>
+        <v>35.57633486897147</v>
       </c>
       <c r="BW77" t="inlineStr">
         <is>
@@ -33419,10 +33399,10 @@
         <v>57.90000152587891</v>
       </c>
       <c r="BG78" t="n">
-        <v>42.10777109378977</v>
+        <v>42.10777087521996</v>
       </c>
       <c r="BH78" t="n">
-        <v>61.30891471255791</v>
+        <v>61.30891439432025</v>
       </c>
       <c r="BI78" t="n">
         <v>35.44202565445207</v>
@@ -33441,13 +33421,13 @@
         <v>47.85923110896672</v>
       </c>
       <c r="BO78" t="n">
-        <v>43.597433275089</v>
+        <v>43.59743318562109</v>
       </c>
       <c r="BP78" t="n">
-        <v>41.59695218296385</v>
+        <v>41.59695207367895</v>
       </c>
       <c r="BQ78" t="n">
-        <v>37.43725696466747</v>
+        <v>37.43725686631105</v>
       </c>
       <c r="BR78" t="n">
         <v>6</v>
@@ -33459,10 +33439,10 @@
         <v>6.7</v>
       </c>
       <c r="BU78" t="n">
-        <v>-35.34152680819091</v>
+        <v>-35.34152697806381</v>
       </c>
       <c r="BV78" t="n">
-        <v>-24.70218976487807</v>
+        <v>-24.7021899193995</v>
       </c>
       <c r="BW78" t="inlineStr">
         <is>
@@ -33567,7 +33547,7 @@
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="R79" t="n">
@@ -33737,11 +33717,7 @@
       </c>
       <c r="BY79" t="inlineStr"/>
       <c r="BZ79" t="inlineStr"/>
-      <c r="CA79" t="inlineStr">
-        <is>
-          <t>Pivô de alta</t>
-        </is>
-      </c>
+      <c r="CA79" t="inlineStr"/>
       <c r="CB79" t="b">
         <v>0</v>
       </c>
@@ -33756,10 +33732,10 @@
         </is>
       </c>
       <c r="CG79" t="n">
-        <v>60.54000091552734</v>
+        <v>61.2400016784668</v>
       </c>
       <c r="CH79" t="n">
-        <v>-2.130824076675031</v>
+        <v>-3.249512775840635</v>
       </c>
       <c r="CI79" t="n">
         <v>-18.81337726141548</v>
@@ -33768,14 +33744,14 @@
         <v>0</v>
       </c>
       <c r="CK79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL79" t="b">
         <v>0</v>
       </c>
       <c r="CM79" t="inlineStr">
         <is>
-          <t>Pivô de alta</t>
+          <t>sem sinal (Em Alta)</t>
         </is>
       </c>
     </row>
@@ -33955,10 +33931,10 @@
         <v>30.98999977111816</v>
       </c>
       <c r="BG80" t="n">
-        <v>9.784912707436973</v>
+        <v>9.784912701202215</v>
       </c>
       <c r="BH80" t="n">
-        <v>18.15101307229558</v>
+        <v>18.15101306073011</v>
       </c>
       <c r="BI80" t="n">
         <v>35.58210545643983</v>
@@ -33967,25 +33943,25 @@
         <v>29.86072035143237</v>
       </c>
       <c r="BK80" t="n">
-        <v>35.8007078279028</v>
+        <v>35.8007078362164</v>
       </c>
       <c r="BL80" t="n">
-        <v>19.53056351449733</v>
+        <v>19.53056351555757</v>
       </c>
       <c r="BM80" t="n">
-        <v>22.21563646461234</v>
+        <v>22.21563647459244</v>
       </c>
       <c r="BN80" t="n">
         <v>16.06212703391342</v>
       </c>
       <c r="BO80" t="n">
-        <v>23.37347330356633</v>
+        <v>23.37347330376054</v>
       </c>
       <c r="BP80" t="n">
-        <v>20.87309998955483</v>
+        <v>20.87309999507501</v>
       </c>
       <c r="BQ80" t="n">
-        <v>18.78578999059935</v>
+        <v>18.78578999556751</v>
       </c>
       <c r="BR80" t="n">
         <v>8</v>
@@ -33997,10 +33973,10 @@
         <v>3.7</v>
       </c>
       <c r="BU80" t="n">
-        <v>-39.38112252550838</v>
+        <v>-39.38112250947691</v>
       </c>
       <c r="BV80" t="n">
-        <v>-24.57736858278466</v>
+        <v>-24.57736858215798</v>
       </c>
       <c r="BW80" t="inlineStr">
         <is>
@@ -34228,10 +34204,10 @@
         <v>24.15999984741211</v>
       </c>
       <c r="BG81" t="n">
-        <v>11.69546839580993</v>
+        <v>11.6954683894059</v>
       </c>
       <c r="BH81" t="n">
-        <v>21.69509387422742</v>
+        <v>21.69509386234794</v>
       </c>
       <c r="BI81" t="n">
         <v>14.33587093498479</v>
@@ -34252,7 +34228,7 @@
         <v>20.88570664769529</v>
       </c>
       <c r="BO81" t="n">
-        <v>18.81177711215338</v>
+        <v>18.81177710986794</v>
       </c>
       <c r="BP81" t="n">
         <v>17.61078879134004</v>
@@ -34273,7 +34249,7 @@
         <v>-34.39689564441875</v>
       </c>
       <c r="BV81" t="n">
-        <v>-22.13668364667479</v>
+        <v>-22.13668365613439</v>
       </c>
       <c r="BW81" t="inlineStr">
         <is>
@@ -34501,10 +34477,10 @@
         <v>6.010000228881836</v>
       </c>
       <c r="BG82" t="n">
-        <v>1.077283896123123</v>
+        <v>1.077283895273072</v>
       </c>
       <c r="BH82" t="n">
-        <v>1.998361627308394</v>
+        <v>1.998361625731548</v>
       </c>
       <c r="BI82" t="n">
         <v>10.00408329556336</v>
@@ -34513,13 +34489,13 @@
         <v>9.814231118279432</v>
       </c>
       <c r="BK82" t="n">
-        <v>9.918568250839762</v>
+        <v>9.918568250925112</v>
       </c>
       <c r="BL82" t="n">
-        <v>1.795623135730037</v>
+        <v>1.795623135764012</v>
       </c>
       <c r="BM82" t="n">
-        <v>7.060557263035136</v>
+        <v>7.06055726402854</v>
       </c>
       <c r="BN82" t="n">
         <v>9.241541426150913</v>
@@ -34764,25 +34740,25 @@
         <v>26.04999923706055</v>
       </c>
       <c r="BG83" t="n">
-        <v>11.33091891434538</v>
+        <v>11.33091889978696</v>
       </c>
       <c r="BH83" t="n">
-        <v>12.12045521070685</v>
+        <v>12.1204552037617</v>
       </c>
       <c r="BI83" t="n">
-        <v>13.63266060603447</v>
+        <v>13.6326606157386</v>
       </c>
       <c r="BJ83" t="n">
         <v>31.41012129143711</v>
       </c>
       <c r="BK83" t="n">
-        <v>12.30412766420294</v>
+        <v>12.30412766506037</v>
       </c>
       <c r="BL83" t="n">
-        <v>23.32462261564971</v>
+        <v>23.32462261757124</v>
       </c>
       <c r="BM83" t="n">
-        <v>5.670915281387018</v>
+        <v>5.670915290700914</v>
       </c>
       <c r="BN83" t="n">
         <v>51.82639978137158</v>
@@ -34834,7 +34810,7 @@
         <v>-5.513240749324433</v>
       </c>
       <c r="CI83" t="n">
-        <v>-20.56481296180598</v>
+        <v>-20.5648036205231</v>
       </c>
       <c r="CJ83" t="b">
         <v>0</v>
@@ -35025,25 +35001,25 @@
         <v>2.029999971389771</v>
       </c>
       <c r="BG84" t="n">
-        <v>0.5820059035673154</v>
+        <v>0.5820059056963254</v>
       </c>
       <c r="BH84" t="n">
-        <v>0.8154021957189567</v>
+        <v>0.8154021982909477</v>
       </c>
       <c r="BI84" t="n">
-        <v>3.106238043843287</v>
+        <v>3.106238042278378</v>
       </c>
       <c r="BJ84" t="n">
         <v>6.656155012762671</v>
       </c>
       <c r="BK84" t="n">
-        <v>2.37673280709405</v>
+        <v>2.37673281017914</v>
       </c>
       <c r="BL84" t="n">
-        <v>1.407489294170764</v>
+        <v>1.407489299255019</v>
       </c>
       <c r="BM84" t="n">
-        <v>1.540024007474453</v>
+        <v>1.54002400654893</v>
       </c>
       <c r="BN84" t="n">
         <v>9.281107245550819</v>
@@ -35286,10 +35262,10 @@
         <v>5.090000152587891</v>
       </c>
       <c r="BG85" t="n">
-        <v>3.01038566796279</v>
+        <v>3.010385652776415</v>
       </c>
       <c r="BH85" t="n">
-        <v>4.383121532553822</v>
+        <v>4.383121510442461</v>
       </c>
       <c r="BI85" t="n">
         <v>3.927003085082646</v>
@@ -35547,37 +35523,37 @@
         <v>49.43000030517578</v>
       </c>
       <c r="BG86" t="n">
-        <v>15.09930991115325</v>
+        <v>15.09930991600853</v>
       </c>
       <c r="BH86" t="n">
-        <v>23.31094171644006</v>
+        <v>23.31094171933127</v>
       </c>
       <c r="BI86" t="n">
-        <v>43.05579288150041</v>
+        <v>43.05579287299565</v>
       </c>
       <c r="BJ86" t="n">
         <v>58.9399838960196</v>
       </c>
       <c r="BK86" t="n">
-        <v>34.35202648214948</v>
+        <v>34.35202648081643</v>
       </c>
       <c r="BL86" t="n">
-        <v>20.00393888384049</v>
+        <v>20.00393888351196</v>
       </c>
       <c r="BM86" t="n">
-        <v>21.52751972851954</v>
+        <v>21.52751972430671</v>
       </c>
       <c r="BN86" t="n">
         <v>21.42321827789122</v>
       </c>
       <c r="BO86" t="n">
-        <v>25.53896398307064</v>
+        <v>25.53896398212311</v>
       </c>
       <c r="BP86" t="n">
-        <v>21.52751972851954</v>
+        <v>21.52751972430671</v>
       </c>
       <c r="BQ86" t="n">
-        <v>19.37476775566759</v>
+        <v>19.37476775187604</v>
       </c>
       <c r="BR86" t="n">
         <v>7</v>
@@ -35589,10 +35565,10 @@
         <v>3.9</v>
       </c>
       <c r="BU86" t="n">
-        <v>-60.80362606504197</v>
+        <v>-60.80362607271253</v>
       </c>
       <c r="BV86" t="n">
-        <v>-48.33306933968101</v>
+        <v>-48.33306934159792</v>
       </c>
       <c r="BW86" t="inlineStr">
         <is>
@@ -35830,10 +35806,10 @@
         <v>74.40000152587891</v>
       </c>
       <c r="BG87" t="n">
-        <v>67.74477291079374</v>
+        <v>67.74477312265029</v>
       </c>
       <c r="BH87" t="n">
-        <v>98.63638935811569</v>
+        <v>98.63638966657882</v>
       </c>
       <c r="BI87" t="n">
         <v>23.80067720298803</v>
@@ -36091,10 +36067,10 @@
         <v>34.70999908447266</v>
       </c>
       <c r="BG88" t="n">
-        <v>8.573258019316874</v>
+        <v>8.573258018821953</v>
       </c>
       <c r="BH88" t="n">
-        <v>15.9033936258328</v>
+        <v>15.90339362491472</v>
       </c>
       <c r="BI88" t="n">
         <v>38.58284294205224</v>
@@ -36103,19 +36079,19 @@
         <v>38.8078211315257</v>
       </c>
       <c r="BK88" t="n">
-        <v>31.68748502824105</v>
+        <v>31.68748502853488</v>
       </c>
       <c r="BL88" t="n">
-        <v>46.1948250489849</v>
+        <v>46.19482504911414</v>
       </c>
       <c r="BM88" t="n">
-        <v>21.36756356245093</v>
+        <v>21.36756356300101</v>
       </c>
       <c r="BN88" t="n">
         <v>38.23996334747979</v>
       </c>
       <c r="BO88" t="n">
-        <v>32.96912781236677</v>
+        <v>32.96912781237464</v>
       </c>
       <c r="BP88" t="n">
         <v>38.23996334747979</v>
@@ -36136,7 +36112,7 @@
         <v>-0.8471105718708571</v>
       </c>
       <c r="BV88" t="n">
-        <v>-5.015474843053669</v>
+        <v>-5.015474843030987</v>
       </c>
       <c r="BW88" t="inlineStr">
         <is>
@@ -36372,10 +36348,10 @@
         <v>11</v>
       </c>
       <c r="BG89" t="n">
-        <v>1.815788323009038</v>
+        <v>1.815788319374932</v>
       </c>
       <c r="BH89" t="n">
-        <v>3.368287339181765</v>
+        <v>3.368287332440499</v>
       </c>
       <c r="BI89" t="n">
         <v>11.4763779527559</v>
@@ -36384,19 +36360,19 @@
         <v>10.25101809243598</v>
       </c>
       <c r="BK89" t="n">
-        <v>11.81091623307214</v>
+        <v>11.8109162372217</v>
       </c>
       <c r="BL89" t="n">
-        <v>6.252286168183502</v>
+        <v>6.252286168712332</v>
       </c>
       <c r="BM89" t="n">
-        <v>8.479656225047405</v>
+        <v>8.47965623017382</v>
       </c>
       <c r="BN89" t="n">
         <v>9.119823240596812</v>
       </c>
       <c r="BO89" t="n">
-        <v>9.565012985348623</v>
+        <v>9.565012986982758</v>
       </c>
       <c r="BP89" t="n">
         <v>9.685420666516395</v>
@@ -36417,7 +36393,7 @@
         <v>-20.75564909213859</v>
       </c>
       <c r="BV89" t="n">
-        <v>-13.04533649683069</v>
+        <v>-13.04533648197492</v>
       </c>
       <c r="BW89" t="inlineStr">
         <is>
@@ -36645,10 +36621,10 @@
         <v>18.28000068664551</v>
       </c>
       <c r="BG90" t="n">
-        <v>1.883948390768156</v>
+        <v>1.883948388053788</v>
       </c>
       <c r="BH90" t="n">
-        <v>3.494724264874929</v>
+        <v>3.494724259839777</v>
       </c>
       <c r="BI90" t="n">
         <v>9.5735181461681</v>
@@ -36657,19 +36633,19 @@
         <v>7.985723111152071</v>
       </c>
       <c r="BK90" t="n">
-        <v>9.488583754072808</v>
+        <v>9.488583759566801</v>
       </c>
       <c r="BL90" t="n">
-        <v>6.41177924057098</v>
+        <v>6.411779241126835</v>
       </c>
       <c r="BM90" t="n">
-        <v>7.239152656534939</v>
+        <v>7.239152660932433</v>
       </c>
       <c r="BN90" t="n">
         <v>12.36591560593228</v>
       </c>
       <c r="BO90" t="n">
-        <v>8.079913825615158</v>
+        <v>8.079913826388328</v>
       </c>
       <c r="BP90" t="n">
         <v>7.985723111152071</v>
@@ -36690,7 +36666,7 @@
         <v>-60.68298397117976</v>
       </c>
       <c r="BV90" t="n">
-        <v>-55.79916016350067</v>
+        <v>-55.79916015927108</v>
       </c>
       <c r="BW90" t="inlineStr">
         <is>
@@ -36916,35 +36892,35 @@
         <v>1.990000009536743</v>
       </c>
       <c r="BG91" t="n">
-        <v>0.9124357707552146</v>
+        <v>0.9124357713583469</v>
       </c>
       <c r="BH91" t="n">
-        <v>1.241127160929692</v>
+        <v>1.241127161558012</v>
       </c>
       <c r="BI91" t="n">
-        <v>3.088621474106118</v>
+        <v>3.08862147362811</v>
       </c>
       <c r="BJ91" t="n">
         <v>6.377098847417107</v>
       </c>
       <c r="BK91" t="n">
-        <v>3.109236245501028</v>
+        <v>3.109236246375341</v>
       </c>
       <c r="BL91" t="n">
-        <v>2.200587261527998</v>
+        <v>2.200587262950834</v>
       </c>
       <c r="BM91" t="n">
-        <v>1.520943857733824</v>
+        <v>1.520943857435539</v>
       </c>
       <c r="BN91" t="inlineStr"/>
       <c r="BO91" t="n">
-        <v>2.012158628425646</v>
+        <v>2.012158628884364</v>
       </c>
       <c r="BP91" t="n">
-        <v>1.860765559630911</v>
+        <v>1.860765560193186</v>
       </c>
       <c r="BQ91" t="n">
-        <v>1.67468900366782</v>
+        <v>1.674689004173868</v>
       </c>
       <c r="BR91" t="n">
         <v>6</v>
@@ -36956,10 +36932,10 @@
         <v>7</v>
       </c>
       <c r="BU91" t="n">
-        <v>-15.84477408833407</v>
+        <v>-15.84477406290452</v>
       </c>
       <c r="BV91" t="n">
-        <v>1.113498431292004</v>
+        <v>1.113498454343165</v>
       </c>
       <c r="BW91" t="inlineStr">
         <is>
@@ -37173,35 +37149,35 @@
         <v>19.28000068664551</v>
       </c>
       <c r="BG92" t="n">
-        <v>11.48823754145262</v>
+        <v>11.48823748727932</v>
       </c>
       <c r="BH92" t="n">
-        <v>14.44345302880337</v>
+        <v>14.44345299470607</v>
       </c>
       <c r="BI92" t="n">
-        <v>21.69670302252312</v>
+        <v>21.69670307361452</v>
       </c>
       <c r="BJ92" t="n">
         <v>41.11506807497437</v>
       </c>
       <c r="BK92" t="n">
-        <v>26.38206893840436</v>
+        <v>26.38206890183815</v>
       </c>
       <c r="BL92" t="n">
-        <v>17.69598463945069</v>
+        <v>17.69598464362598</v>
       </c>
       <c r="BM92" t="n">
-        <v>10.3685604162557</v>
+        <v>10.3685604530112</v>
       </c>
       <c r="BN92" t="inlineStr"/>
       <c r="BO92" t="n">
-        <v>16.33109455805745</v>
+        <v>16.33109454980647</v>
       </c>
       <c r="BP92" t="n">
-        <v>16.06971883412703</v>
+        <v>16.06971881916602</v>
       </c>
       <c r="BQ92" t="n">
-        <v>14.46274695071433</v>
+        <v>14.46274693724942</v>
       </c>
       <c r="BR92" t="n">
         <v>4</v>
@@ -37213,10 +37189,10 @@
         <v>1.9</v>
       </c>
       <c r="BU92" t="n">
-        <v>-24.98575500190672</v>
+        <v>-24.98575507174546</v>
       </c>
       <c r="BV92" t="n">
-        <v>-15.29515572388256</v>
+        <v>-15.29515576667809</v>
       </c>
       <c r="BW92" t="inlineStr">
         <is>
@@ -37454,10 +37430,10 @@
         <v>8.079999923706055</v>
       </c>
       <c r="BG93" t="n">
-        <v>0.4798846686063476</v>
+        <v>0.479884668303645</v>
       </c>
       <c r="BH93" t="n">
-        <v>0.8901860602647746</v>
+        <v>0.8901860597032614</v>
       </c>
       <c r="BI93" t="n">
         <v>9.465959238647676</v>
@@ -37466,13 +37442,13 @@
         <v>8.689746150922641</v>
       </c>
       <c r="BK93" t="n">
-        <v>10.43836207473843</v>
+        <v>10.43836207500831</v>
       </c>
       <c r="BL93" t="n">
-        <v>1.421542439208229</v>
+        <v>1.421542439219501</v>
       </c>
       <c r="BM93" t="n">
-        <v>8.096371773076108</v>
+        <v>8.09637177348127</v>
       </c>
       <c r="BN93" t="inlineStr"/>
       <c r="BO93" t="inlineStr"/>
@@ -37715,10 +37691,10 @@
         <v>6.860000133514404</v>
       </c>
       <c r="BG94" t="n">
-        <v>2.853139461799771</v>
+        <v>2.853139461461771</v>
       </c>
       <c r="BH94" t="n">
-        <v>5.292573701638576</v>
+        <v>5.292573701011584</v>
       </c>
       <c r="BI94" t="n">
         <v>13.11616187143807</v>
@@ -37727,13 +37703,13 @@
         <v>14.08650985127578</v>
       </c>
       <c r="BK94" t="n">
-        <v>12.30620919305192</v>
+        <v>12.3062091928934</v>
       </c>
       <c r="BL94" t="n">
-        <v>12.24172365447213</v>
+        <v>12.24172365453295</v>
       </c>
       <c r="BM94" t="n">
-        <v>6.756741751482018</v>
+        <v>6.756741751811584</v>
       </c>
       <c r="BN94" t="n">
         <v>69.89589803243278</v>
@@ -37978,10 +37954,10 @@
         <v>6.619999885559082</v>
       </c>
       <c r="BG95" t="n">
-        <v>2.937502850885992</v>
+        <v>2.937502865592459</v>
       </c>
       <c r="BH95" t="n">
-        <v>5.449067788393515</v>
+        <v>5.449067815674011</v>
       </c>
       <c r="BI95" t="inlineStr"/>
       <c r="BJ95" t="inlineStr"/>
@@ -37992,13 +37968,13 @@
         <v>8.770765162555669</v>
       </c>
       <c r="BO95" t="n">
-        <v>5.719111933945059</v>
+        <v>5.719111947940713</v>
       </c>
       <c r="BP95" t="n">
-        <v>5.449067788393515</v>
+        <v>5.449067815674011</v>
       </c>
       <c r="BQ95" t="n">
-        <v>4.904161009554164</v>
+        <v>4.90416103410661</v>
       </c>
       <c r="BR95" t="n">
         <v>3</v>
@@ -38010,10 +37986,10 @@
         <v>3</v>
       </c>
       <c r="BU95" t="n">
-        <v>-25.9190167019166</v>
+        <v>-25.91901633103372</v>
       </c>
       <c r="BV95" t="n">
-        <v>-13.6085795647705</v>
+        <v>-13.60857935335576</v>
       </c>
       <c r="BW95" t="inlineStr">
         <is>
@@ -38239,10 +38215,10 @@
         <v>7.900000095367432</v>
       </c>
       <c r="BG96" t="n">
-        <v>5.082618186934732</v>
+        <v>5.082618184350363</v>
       </c>
       <c r="BH96" t="n">
-        <v>7.400292080176969</v>
+        <v>7.400292076414129</v>
       </c>
       <c r="BI96" t="n">
         <v>5.753501470015497</v>
@@ -38261,7 +38237,7 @@
         <v>6.990639790663585</v>
       </c>
       <c r="BO96" t="n">
-        <v>6.453555792599161</v>
+        <v>6.453555791541294</v>
       </c>
       <c r="BP96" t="n">
         <v>6.372070630339541</v>
@@ -38282,7 +38258,7 @@
         <v>-27.40679116360369</v>
       </c>
       <c r="BV96" t="n">
-        <v>-18.30942133300058</v>
+        <v>-18.30942134639131</v>
       </c>
       <c r="BW96" t="inlineStr">
         <is>
@@ -38490,10 +38466,10 @@
         <v>49.04999923706055</v>
       </c>
       <c r="BG97" t="n">
-        <v>10.25848670506038</v>
+        <v>10.25848666210822</v>
       </c>
       <c r="BH97" t="n">
-        <v>14.93635664256792</v>
+        <v>14.93635658002957</v>
       </c>
       <c r="BI97" t="inlineStr"/>
       <c r="BJ97" t="inlineStr"/>
@@ -38502,13 +38478,13 @@
       <c r="BM97" t="inlineStr"/>
       <c r="BN97" t="inlineStr"/>
       <c r="BO97" t="n">
-        <v>12.59742167381415</v>
+        <v>12.59742162106889</v>
       </c>
       <c r="BP97" t="n">
-        <v>12.59742167381415</v>
+        <v>12.59742162106889</v>
       </c>
       <c r="BQ97" t="n">
-        <v>11.33767950643274</v>
+        <v>11.337679458962</v>
       </c>
       <c r="BR97" t="n">
         <v>2</v>
@@ -38520,10 +38496,10 @@
         <v>1.5</v>
       </c>
       <c r="BU97" t="n">
-        <v>-76.88546445915871</v>
+        <v>-76.88546455593901</v>
       </c>
       <c r="BV97" t="n">
-        <v>-74.31718273239858</v>
+        <v>-74.31718283993224</v>
       </c>
       <c r="BW97" t="inlineStr">
         <is>
@@ -38765,10 +38741,10 @@
         <v>3.769999980926514</v>
       </c>
       <c r="BG98" t="n">
-        <v>34.95537526754106</v>
+        <v>34.95537504562256</v>
       </c>
       <c r="BH98" t="n">
-        <v>64.84222112128866</v>
+        <v>64.84222070962984</v>
       </c>
       <c r="BI98" t="n">
         <v>5.406114691263668</v>
@@ -39024,10 +39000,10 @@
         <v>21.04999923706055</v>
       </c>
       <c r="BG99" t="n">
-        <v>36.28933542909621</v>
+        <v>36.28933528297076</v>
       </c>
       <c r="BH99" t="n">
-        <v>67.31671722097346</v>
+        <v>67.31671694991077</v>
       </c>
       <c r="BI99" t="n">
         <v>25.63533914439818</v>
@@ -39046,7 +39022,7 @@
       </c>
       <c r="BN99" t="inlineStr"/>
       <c r="BO99" t="n">
-        <v>36.47880910543785</v>
+        <v>36.47880904583955</v>
       </c>
       <c r="BP99" t="n">
         <v>28.99450153171436</v>
@@ -39067,7 +39043,7 @@
         <v>23.966994414898</v>
       </c>
       <c r="BV99" t="n">
-        <v>73.29601153245366</v>
+        <v>73.2960112493263</v>
       </c>
       <c r="BW99" t="inlineStr">
         <is>
@@ -39295,10 +39271,10 @@
         <v>2.799999952316284</v>
       </c>
       <c r="BG100" t="n">
-        <v>0.5849893564132463</v>
+        <v>0.5849893599441209</v>
       </c>
       <c r="BH100" t="n">
-        <v>1.085155256146572</v>
+        <v>1.085155262696344</v>
       </c>
       <c r="BI100" t="n">
         <v>3.209342505898855</v>
@@ -39307,13 +39283,13 @@
         <v>3.337413992024261</v>
       </c>
       <c r="BK100" t="n">
-        <v>2.601796801102944</v>
+        <v>2.601796799541142</v>
       </c>
       <c r="BL100" t="n">
-        <v>2.312237281138035</v>
+        <v>2.312237280621134</v>
       </c>
       <c r="BM100" t="n">
-        <v>1.837153327293113</v>
+        <v>1.837153323623546</v>
       </c>
       <c r="BN100" t="n">
         <v>7.034023413406607</v>
@@ -39558,10 +39534,10 @@
         <v>10.88000011444092</v>
       </c>
       <c r="BG101" t="n">
-        <v>0.7363540693746117</v>
+        <v>0.7363540686999448</v>
       </c>
       <c r="BH101" t="n">
-        <v>1.365936798689905</v>
+        <v>1.365936797438398</v>
       </c>
       <c r="BI101" t="n">
         <v>18.22503179726196</v>
@@ -39570,13 +39546,13 @@
         <v>16.89238276609682</v>
       </c>
       <c r="BK101" t="n">
-        <v>20.29998254465431</v>
+        <v>20.2999825448704</v>
       </c>
       <c r="BL101" t="n">
-        <v>2.020442028320307</v>
+        <v>2.020442028338507</v>
       </c>
       <c r="BM101" t="n">
-        <v>15.61526429385439</v>
+        <v>15.6152642947408</v>
       </c>
       <c r="BN101" t="n">
         <v>2.743300088818764</v>
@@ -39819,10 +39795,10 @@
         <v>58.16999816894531</v>
       </c>
       <c r="BG102" t="n">
-        <v>71.06675241843992</v>
+        <v>71.06675256319065</v>
       </c>
       <c r="BH102" t="n">
-        <v>103.4731915212485</v>
+        <v>103.4731917320056</v>
       </c>
       <c r="BI102" t="n">
         <v>24.27640373021794</v>
@@ -40080,10 +40056,10 @@
         <v>11.38000011444092</v>
       </c>
       <c r="BG103" t="n">
-        <v>2.021214158423594</v>
+        <v>2.02121416234779</v>
       </c>
       <c r="BH103" t="n">
-        <v>3.749352263875767</v>
+        <v>3.749352271155151</v>
       </c>
       <c r="BI103" t="n">
         <v>11.51909866435005</v>
@@ -40092,25 +40068,25 @@
         <v>12.74686594914816</v>
       </c>
       <c r="BK103" t="n">
-        <v>8.289564099812065</v>
+        <v>8.289564098267967</v>
       </c>
       <c r="BL103" t="n">
-        <v>5.481051627056617</v>
+        <v>5.481051626718494</v>
       </c>
       <c r="BM103" t="n">
-        <v>6.174232717166075</v>
+        <v>6.174232713557385</v>
       </c>
       <c r="BN103" t="n">
         <v>10.87624860734963</v>
       </c>
       <c r="BO103" t="n">
-        <v>8.405201989822624</v>
+        <v>8.405201990078121</v>
       </c>
       <c r="BP103" t="n">
-        <v>8.289564099812065</v>
+        <v>8.289564098267967</v>
       </c>
       <c r="BQ103" t="n">
-        <v>7.460607689830859</v>
+        <v>7.46060768844117</v>
       </c>
       <c r="BR103" t="n">
         <v>7</v>
@@ -40122,10 +40098,10 @@
         <v>6.3</v>
       </c>
       <c r="BU103" t="n">
-        <v>-34.44105786639189</v>
+        <v>-34.44105787860355</v>
       </c>
       <c r="BV103" t="n">
-        <v>-26.14058079703667</v>
+        <v>-26.14058079479154</v>
       </c>
       <c r="BW103" t="inlineStr">
         <is>
@@ -40164,7 +40140,7 @@
         <v>-8.520896315896199</v>
       </c>
       <c r="CI103" t="n">
-        <v>-30.16381761208197</v>
+        <v>-30.1638259014074</v>
       </c>
       <c r="CJ103" t="b">
         <v>0</v>
@@ -40234,7 +40210,7 @@
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>Fundo duplo</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="R104" t="n">
@@ -40357,37 +40333,37 @@
         <v>33.22999954223633</v>
       </c>
       <c r="BG104" t="n">
-        <v>14.40022172396017</v>
+        <v>14.40022172862921</v>
       </c>
       <c r="BH104" t="n">
-        <v>18.22494523100412</v>
+        <v>18.22494523044871</v>
       </c>
       <c r="BI104" t="n">
-        <v>22.53560402277081</v>
+        <v>22.53560401477721</v>
       </c>
       <c r="BJ104" t="n">
         <v>31.82713953449119</v>
       </c>
       <c r="BK104" t="n">
-        <v>21.71874064589809</v>
+        <v>21.71874064176161</v>
       </c>
       <c r="BL104" t="n">
-        <v>20.85105073315407</v>
+        <v>20.85105073241741</v>
       </c>
       <c r="BM104" t="n">
-        <v>10.80478951459744</v>
+        <v>10.80478950891503</v>
       </c>
       <c r="BN104" t="n">
         <v>9.730162667946294</v>
       </c>
       <c r="BO104" t="n">
-        <v>18.76158175922777</v>
+        <v>18.76158175742333</v>
       </c>
       <c r="BP104" t="n">
-        <v>19.53799798207909</v>
+        <v>19.53799798143306</v>
       </c>
       <c r="BQ104" t="n">
-        <v>17.58419818387118</v>
+        <v>17.58419818328975</v>
       </c>
       <c r="BR104" t="n">
         <v>8</v>
@@ -40399,10 +40375,10 @@
         <v>3.3</v>
       </c>
       <c r="BU104" t="n">
-        <v>-47.0833631474441</v>
+        <v>-47.08336314919382</v>
       </c>
       <c r="BV104" t="n">
-        <v>-43.54022865579267</v>
+        <v>-43.54022866122283</v>
       </c>
       <c r="BW104" t="inlineStr">
         <is>
@@ -40416,11 +40392,7 @@
       </c>
       <c r="BY104" t="inlineStr"/>
       <c r="BZ104" t="inlineStr"/>
-      <c r="CA104" t="inlineStr">
-        <is>
-          <t>Fundo duplo</t>
-        </is>
-      </c>
+      <c r="CA104" t="inlineStr"/>
       <c r="CB104" t="b">
         <v>0</v>
       </c>
@@ -40447,14 +40419,14 @@
         <v>0</v>
       </c>
       <c r="CK104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL104" t="b">
         <v>0</v>
       </c>
       <c r="CM104" t="inlineStr">
         <is>
-          <t>Fundo duplo — rompeu pescoço ~R$30.82 (candidato)</t>
+          <t>sem sinal (Em Alta)</t>
         </is>
       </c>
     </row>
@@ -40630,10 +40602,10 @@
         <v>13.69999980926514</v>
       </c>
       <c r="BG105" t="n">
-        <v>5.914353193404778</v>
+        <v>5.914353201453679</v>
       </c>
       <c r="BH105" t="n">
-        <v>10.97112517376586</v>
+        <v>10.97112518869657</v>
       </c>
       <c r="BI105" t="n">
         <v>4.690568410148916</v>
@@ -40654,13 +40626,13 @@
         <v>7.282189293389739</v>
       </c>
       <c r="BO105" t="n">
-        <v>7.008328769527365</v>
+        <v>7.008328772399818</v>
       </c>
       <c r="BP105" t="n">
-        <v>6.494690009404375</v>
+        <v>6.494690013428826</v>
       </c>
       <c r="BQ105" t="n">
-        <v>5.845221008463938</v>
+        <v>5.845221012085944</v>
       </c>
       <c r="BR105" t="n">
         <v>8</v>
@@ -40672,10 +40644,10 @@
         <v>2.6</v>
       </c>
       <c r="BU105" t="n">
-        <v>-57.33415262888626</v>
+        <v>-57.33415260244825</v>
       </c>
       <c r="BV105" t="n">
-        <v>-48.84431483869276</v>
+        <v>-48.84431481772595</v>
       </c>
       <c r="BW105" t="inlineStr">
         <is>
@@ -40903,37 +40875,37 @@
         <v>20.64999961853027</v>
       </c>
       <c r="BG106" t="n">
-        <v>4.523447164449627</v>
+        <v>4.523447136263847</v>
       </c>
       <c r="BH106" t="n">
-        <v>6.059080987072282</v>
+        <v>6.059080977604651</v>
       </c>
       <c r="BI106" t="n">
-        <v>8.71905349441113</v>
+        <v>8.719053535115924</v>
       </c>
       <c r="BJ106" t="n">
         <v>13.33806641923568</v>
       </c>
       <c r="BK106" t="n">
-        <v>5.722211872666971</v>
+        <v>5.722211896804462</v>
       </c>
       <c r="BL106" t="n">
-        <v>7.646329529034534</v>
+        <v>7.646329532412437</v>
       </c>
       <c r="BM106" t="n">
-        <v>4.27460635537011</v>
+        <v>4.274606381488181</v>
       </c>
       <c r="BN106" t="n">
         <v>9.542354752362813</v>
       </c>
       <c r="BO106" t="n">
-        <v>7.478143821825393</v>
+        <v>7.478143828911</v>
       </c>
       <c r="BP106" t="n">
-        <v>6.852705258053408</v>
+        <v>6.852705255008544</v>
       </c>
       <c r="BQ106" t="n">
-        <v>6.167434732248068</v>
+        <v>6.16743472950769</v>
       </c>
       <c r="BR106" t="n">
         <v>8</v>
@@ -40945,10 +40917,10 @@
         <v>3.1</v>
       </c>
       <c r="BU106" t="n">
-        <v>-70.13348742770087</v>
+        <v>-70.13348744097145</v>
       </c>
       <c r="BV106" t="n">
-        <v>-63.78622779675559</v>
+        <v>-63.78622776244273</v>
       </c>
       <c r="BW106" t="inlineStr">
         <is>
@@ -41180,10 +41152,10 @@
         <v>11.10000038146973</v>
       </c>
       <c r="BG107" t="n">
-        <v>2.412775871327606</v>
+        <v>2.412775872012713</v>
       </c>
       <c r="BH107" t="n">
-        <v>4.475699241312709</v>
+        <v>4.475699242583583</v>
       </c>
       <c r="BI107" t="n">
         <v>12.17508319987366</v>
@@ -41192,19 +41164,19 @@
         <v>12.66813745138942</v>
       </c>
       <c r="BK107" t="n">
-        <v>9.658884147835673</v>
+        <v>9.658884147496916</v>
       </c>
       <c r="BL107" t="n">
-        <v>6.050273288521856</v>
+        <v>6.050273290170428</v>
       </c>
       <c r="BM107" t="n">
-        <v>6.768354111701337</v>
+        <v>6.768354110989319</v>
       </c>
       <c r="BN107" t="n">
         <v>6.969597281386505</v>
       </c>
       <c r="BO107" t="n">
-        <v>8.395146960288736</v>
+        <v>8.395146960555691</v>
       </c>
       <c r="BP107" t="n">
         <v>6.969597281386505</v>
@@ -41225,7 +41197,7 @@
         <v>-43.48975371460926</v>
       </c>
       <c r="BV107" t="n">
-        <v>-24.36804800202041</v>
+        <v>-24.36804799961541</v>
       </c>
       <c r="BW107" t="inlineStr">
         <is>
@@ -41453,10 +41425,10 @@
         <v>3.279999971389771</v>
       </c>
       <c r="BG108" t="n">
-        <v>1.613230662694517</v>
+        <v>1.61323065843806</v>
       </c>
       <c r="BH108" t="n">
-        <v>2.249836301127046</v>
+        <v>2.249836295190926</v>
       </c>
       <c r="BI108" t="n">
         <v>0.6472631907457261</v>
@@ -41465,7 +41437,7 @@
         <v>3.871064759123143</v>
       </c>
       <c r="BK108" t="n">
-        <v>0.6813238743012365</v>
+        <v>0.6813238731207611</v>
       </c>
       <c r="BL108" t="n">
         <v>0.4994766813694884</v>
@@ -41593,7 +41565,7 @@
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>Fundo duplo</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="R109" t="n">
@@ -41714,10 +41686,10 @@
         <v>92.48000335693359</v>
       </c>
       <c r="BG109" t="n">
-        <v>4.73484274643576</v>
+        <v>4.734842769816722</v>
       </c>
       <c r="BH109" t="n">
-        <v>8.783133294638334</v>
+        <v>8.783133338010019</v>
       </c>
       <c r="BI109" t="n">
         <v>40.72316532001894</v>
@@ -41726,13 +41698,13 @@
         <v>40.44265171170704</v>
       </c>
       <c r="BK109" t="n">
-        <v>33.56447992492561</v>
+        <v>33.56447989321801</v>
       </c>
       <c r="BL109" t="n">
-        <v>12.17530263076958</v>
+        <v>12.1753026893612</v>
       </c>
       <c r="BM109" t="n">
-        <v>27.92343271962525</v>
+        <v>27.92343269285686</v>
       </c>
       <c r="BN109" t="n">
         <v>40.83466718250591</v>
@@ -41763,11 +41735,7 @@
       </c>
       <c r="BY109" t="inlineStr"/>
       <c r="BZ109" t="inlineStr"/>
-      <c r="CA109" t="inlineStr">
-        <is>
-          <t>Fundo duplo</t>
-        </is>
-      </c>
+      <c r="CA109" t="inlineStr"/>
       <c r="CB109" t="b">
         <v>0</v>
       </c>
@@ -41794,14 +41762,14 @@
         <v>0</v>
       </c>
       <c r="CK109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL109" t="b">
         <v>0</v>
       </c>
       <c r="CM109" t="inlineStr">
         <is>
-          <t>Fundo duplo — rompeu pescoço ~R$86.70 (candidato)</t>
+          <t>sem sinal (Em Alta)</t>
         </is>
       </c>
     </row>
@@ -41981,25 +41949,25 @@
         <v>45.63999938964844</v>
       </c>
       <c r="BG110" t="n">
-        <v>17.92408489050545</v>
+        <v>17.92408475806052</v>
       </c>
       <c r="BH110" t="n">
-        <v>19.84158814985145</v>
+        <v>19.84158808813151</v>
       </c>
       <c r="BI110" t="n">
-        <v>23.46392692666285</v>
+        <v>23.46392702705516</v>
       </c>
       <c r="BJ110" t="n">
         <v>50.39275454877635</v>
       </c>
       <c r="BK110" t="n">
-        <v>19.87997254470887</v>
+        <v>19.87997256840683</v>
       </c>
       <c r="BL110" t="n">
-        <v>42.32518621560163</v>
+        <v>42.32518592318311</v>
       </c>
       <c r="BM110" t="n">
-        <v>10.16776761449776</v>
+        <v>10.16776770517486</v>
       </c>
       <c r="BN110" t="n">
         <v>125.2323153640256</v>
@@ -42242,25 +42210,25 @@
         <v>1.490000009536743</v>
       </c>
       <c r="BG111" t="n">
-        <v>0.1327367703555731</v>
+        <v>0.1327367701444729</v>
       </c>
       <c r="BH111" t="n">
-        <v>0.1412162777626765</v>
+        <v>0.1412162775462785</v>
       </c>
       <c r="BI111" t="n">
-        <v>0.3868379085021857</v>
+        <v>0.3868379085246146</v>
       </c>
       <c r="BJ111" t="n">
         <v>2.240405914537407</v>
       </c>
       <c r="BK111" t="n">
-        <v>0.1013057114173975</v>
+        <v>0.1013057113510053</v>
       </c>
       <c r="BL111" t="n">
-        <v>0.3907382805498145</v>
+        <v>0.390738280552449</v>
       </c>
       <c r="BM111" t="n">
-        <v>0.1597607256891873</v>
+        <v>0.1597607257109221</v>
       </c>
       <c r="BN111" t="inlineStr"/>
       <c r="BO111" t="inlineStr"/>
@@ -42503,10 +42471,10 @@
         <v>18.72999954223633</v>
       </c>
       <c r="BG112" t="n">
-        <v>11.97114008340181</v>
+        <v>11.97114010651761</v>
       </c>
       <c r="BH112" t="n">
-        <v>14.93790088667965</v>
+        <v>14.93790091552414</v>
       </c>
       <c r="BI112" t="inlineStr"/>
       <c r="BJ112" t="inlineStr"/>
@@ -43005,10 +42973,10 @@
         <v>13.30000019073486</v>
       </c>
       <c r="BG114" t="n">
-        <v>6.697030029040647</v>
+        <v>6.697030028737272</v>
       </c>
       <c r="BH114" t="n">
-        <v>9.750875722283183</v>
+        <v>9.750875721841469</v>
       </c>
       <c r="BI114" t="n">
         <v>6.721088531761059</v>
@@ -43027,7 +42995,7 @@
         <v>8.072404896288001</v>
       </c>
       <c r="BO114" t="n">
-        <v>8.644470933864456</v>
+        <v>8.644470933740275</v>
       </c>
       <c r="BP114" t="n">
         <v>8.129705699135654</v>
@@ -43048,7 +43016,7 @@
         <v>-44.98695470456367</v>
       </c>
       <c r="BV114" t="n">
-        <v>-35.00397887297455</v>
+        <v>-35.00397887390825</v>
       </c>
       <c r="BW114" t="inlineStr">
         <is>
@@ -43274,10 +43242,10 @@
         <v>4.78000020980835</v>
       </c>
       <c r="BG115" t="n">
-        <v>4.731783412021332</v>
+        <v>4.731783420054365</v>
       </c>
       <c r="BH115" t="n">
-        <v>5.792188207433291</v>
+        <v>5.792188217266546</v>
       </c>
       <c r="BI115" t="inlineStr"/>
       <c r="BJ115" t="inlineStr"/>
@@ -43286,13 +43254,13 @@
       <c r="BM115" t="inlineStr"/>
       <c r="BN115" t="inlineStr"/>
       <c r="BO115" t="n">
-        <v>5.261985809727312</v>
+        <v>5.261985818660456</v>
       </c>
       <c r="BP115" t="n">
-        <v>5.261985809727312</v>
+        <v>5.261985818660456</v>
       </c>
       <c r="BQ115" t="n">
-        <v>4.735787228754581</v>
+        <v>4.735787236794411</v>
       </c>
       <c r="BR115" t="n">
         <v>2</v>
@@ -43304,10 +43272,10 @@
         <v>1.2</v>
       </c>
       <c r="BU115" t="n">
-        <v>-0.924957722032016</v>
+        <v>-0.9249575538347377</v>
       </c>
       <c r="BV115" t="n">
-        <v>10.08338030885332</v>
+        <v>10.08338049573916</v>
       </c>
       <c r="BW115" t="inlineStr">
         <is>
@@ -43535,25 +43503,25 @@
         <v>8.840000152587891</v>
       </c>
       <c r="BG116" t="n">
-        <v>3.431346817249354</v>
+        <v>3.431346814622071</v>
       </c>
       <c r="BH116" t="n">
-        <v>3.53641204926751</v>
+        <v>3.536412046980224</v>
       </c>
       <c r="BI116" t="n">
-        <v>4.231225264548861</v>
+        <v>4.23122526505191</v>
       </c>
       <c r="BJ116" t="n">
         <v>18.33689952444415</v>
       </c>
       <c r="BK116" t="n">
-        <v>3.333938711025489</v>
+        <v>3.333938709454183</v>
       </c>
       <c r="BL116" t="n">
-        <v>7.293756886670397</v>
+        <v>7.293756886774103</v>
       </c>
       <c r="BM116" t="n">
-        <v>1.667762765775128</v>
+        <v>1.667762766290706</v>
       </c>
       <c r="BN116" t="n">
         <v>20.33122852208574</v>
@@ -43605,7 +43573,7 @@
         <v>-8.959834007633127</v>
       </c>
       <c r="CI116" t="n">
-        <v>-38.06040172867179</v>
+        <v>-37.7634313974045</v>
       </c>
       <c r="CJ116" t="b">
         <v>0</v>
@@ -43798,10 +43766,10 @@
         <v>3.180000066757202</v>
       </c>
       <c r="BG117" t="n">
-        <v>1.082154258362903</v>
+        <v>1.082154257086523</v>
       </c>
       <c r="BH117" t="n">
-        <v>1.350340313696318</v>
+        <v>1.350340312103617</v>
       </c>
       <c r="BI117" t="n">
         <v>1.231789606948257</v>
@@ -43810,7 +43778,7 @@
         <v>3.296396031779571</v>
       </c>
       <c r="BK117" t="n">
-        <v>1.003918287004504</v>
+        <v>1.003918286227915</v>
       </c>
       <c r="BL117" t="n">
         <v>1.804822955819676</v>
@@ -43822,13 +43790,13 @@
         <v>3.992690653062959</v>
       </c>
       <c r="BO117" t="n">
-        <v>1.176565268389638</v>
+        <v>1.176565267782027</v>
       </c>
       <c r="BP117" t="n">
-        <v>1.15697193265558</v>
+        <v>1.15697193201739</v>
       </c>
       <c r="BQ117" t="n">
-        <v>1.041274739390022</v>
+        <v>1.041274738815651</v>
       </c>
       <c r="BR117" t="n">
         <v>6</v>
@@ -43840,10 +43808,10 @@
         <v>6.8</v>
       </c>
       <c r="BU117" t="n">
-        <v>-67.25551202733591</v>
+        <v>-67.25551204539789</v>
       </c>
       <c r="BV117" t="n">
-        <v>-63.00109296571689</v>
+        <v>-63.00109298482417</v>
       </c>
       <c r="BW117" t="inlineStr">
         <is>
@@ -44071,25 +44039,25 @@
         <v>12.96000003814697</v>
       </c>
       <c r="BG118" t="n">
-        <v>1.212265416707701</v>
+        <v>1.2122654132083</v>
       </c>
       <c r="BH118" t="n">
-        <v>2.022224111547668</v>
+        <v>2.022224107370945</v>
       </c>
       <c r="BI118" t="n">
-        <v>6.537755011621071</v>
+        <v>6.537755016990216</v>
       </c>
       <c r="BJ118" t="n">
         <v>9.507573293362324</v>
       </c>
       <c r="BK118" t="n">
-        <v>3.557019843889104</v>
+        <v>3.557019845484418</v>
       </c>
       <c r="BL118" t="n">
-        <v>6.343693811520882</v>
+        <v>6.343693811924265</v>
       </c>
       <c r="BM118" t="n">
-        <v>3.24997223527193</v>
+        <v>3.249972237578455</v>
       </c>
       <c r="BN118" t="n">
         <v>11.90042122154035</v>
@@ -44334,10 +44302,10 @@
         <v>4.980000019073486</v>
       </c>
       <c r="BG119" t="n">
-        <v>1.366636232510593</v>
+        <v>1.366636234952888</v>
       </c>
       <c r="BH119" t="n">
-        <v>2.535110211307149</v>
+        <v>2.535110215837607</v>
       </c>
       <c r="BI119" t="n">
         <v>2.179881078715681</v>
@@ -44396,10 +44364,10 @@
         </is>
       </c>
       <c r="CG119" t="n">
-        <v>5.960000038146973</v>
+        <v>5.920000076293945</v>
       </c>
       <c r="CH119" t="n">
-        <v>-16.44295323491607</v>
+        <v>-15.87837914030772</v>
       </c>
       <c r="CI119" t="n">
         <v>-52.37080697051134</v>
@@ -44415,7 +44383,7 @@
       </c>
       <c r="CM119" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-16.4%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-15.9%))</t>
         </is>
       </c>
     </row>
@@ -44593,10 +44561,10 @@
         <v>17.54000091552734</v>
       </c>
       <c r="BG120" t="n">
-        <v>3.291278857595421</v>
+        <v>3.291278834642578</v>
       </c>
       <c r="BH120" t="n">
-        <v>6.105322280839506</v>
+        <v>6.105322238261983</v>
       </c>
       <c r="BI120" t="n">
         <v>14.45304801808068</v>
@@ -44605,23 +44573,23 @@
         <v>15.37949780888101</v>
       </c>
       <c r="BK120" t="n">
-        <v>9.984733809460344</v>
+        <v>9.984733825787924</v>
       </c>
       <c r="BL120" t="n">
-        <v>12.88735513984486</v>
+        <v>12.88735514387208</v>
       </c>
       <c r="BM120" t="n">
-        <v>7.388904815026846</v>
+        <v>7.388904837851153</v>
       </c>
       <c r="BN120" t="inlineStr"/>
       <c r="BO120" t="n">
-        <v>11.03314364535554</v>
+        <v>11.0331436454558</v>
       </c>
       <c r="BP120" t="n">
-        <v>11.4360444746526</v>
+        <v>11.43604448483</v>
       </c>
       <c r="BQ120" t="n">
-        <v>10.29244002718734</v>
+        <v>10.292440036347</v>
       </c>
       <c r="BR120" t="n">
         <v>6</v>
@@ -44633,10 +44601,10 @@
         <v>4.7</v>
       </c>
       <c r="BU120" t="n">
-        <v>-41.32018534801828</v>
+        <v>-41.32018529579675</v>
       </c>
       <c r="BV120" t="n">
-        <v>-37.09724589815493</v>
+        <v>-37.0972458975833</v>
       </c>
       <c r="BW120" t="inlineStr">
         <is>
@@ -44996,7 +44964,7 @@
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>Fundo duplo</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="R122" t="n">
@@ -45119,25 +45087,25 @@
         <v>18.60000038146973</v>
       </c>
       <c r="BG122" t="n">
-        <v>0.5796472207106205</v>
+        <v>0.5796472205434684</v>
       </c>
       <c r="BH122" t="n">
-        <v>0.8145998495636376</v>
+        <v>0.8145998493454358</v>
       </c>
       <c r="BI122" t="n">
-        <v>5.293708529670349</v>
+        <v>5.293708529778896</v>
       </c>
       <c r="BJ122" t="n">
         <v>12.01035285796767</v>
       </c>
       <c r="BK122" t="n">
-        <v>2.16663432560372</v>
+        <v>2.166634325638933</v>
       </c>
       <c r="BL122" t="n">
-        <v>0.7437994164795726</v>
+        <v>0.7437994164809544</v>
       </c>
       <c r="BM122" t="n">
-        <v>2.626065802825144</v>
+        <v>2.626065802888983</v>
       </c>
       <c r="BN122" t="n">
         <v>18.60000038146973</v>
@@ -45168,11 +45136,7 @@
       </c>
       <c r="BY122" t="inlineStr"/>
       <c r="BZ122" t="inlineStr"/>
-      <c r="CA122" t="inlineStr">
-        <is>
-          <t>Fundo duplo</t>
-        </is>
-      </c>
+      <c r="CA122" t="inlineStr"/>
       <c r="CB122" t="b">
         <v>0</v>
       </c>
@@ -45199,14 +45163,14 @@
         <v>0</v>
       </c>
       <c r="CK122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL122" t="b">
         <v>0</v>
       </c>
       <c r="CM122" t="inlineStr">
         <is>
-          <t>Fundo duplo — rompeu pescoço ~R$14.95 (candidato)</t>
+          <t>sem sinal (Em Alta)</t>
         </is>
       </c>
     </row>
@@ -45428,10 +45392,10 @@
         </is>
       </c>
       <c r="CG123" t="n">
-        <v>1.049999952316284</v>
+        <v>0.9100000262260437</v>
       </c>
       <c r="CH123" t="n">
-        <v>-37.14285179060308</v>
+        <v>-27.47252668077397</v>
       </c>
       <c r="CI123" t="n">
         <v>-87.9562039429038</v>
@@ -45447,7 +45411,7 @@
       </c>
       <c r="CM123" t="inlineStr">
         <is>
-          <t>sem sinal (Em Baixa; sem novo topo (-37.1%))</t>
+          <t>sem sinal (Em Baixa; sem novo topo (-27.5%))</t>
         </is>
       </c>
     </row>
@@ -45627,10 +45591,10 @@
         <v>4.670000076293945</v>
       </c>
       <c r="BG124" t="n">
-        <v>1.435643399777155</v>
+        <v>1.435643396591055</v>
       </c>
       <c r="BH124" t="n">
-        <v>2.090296790075537</v>
+        <v>2.090296785436576</v>
       </c>
       <c r="BI124" t="inlineStr"/>
       <c r="BJ124" t="inlineStr"/>
@@ -45641,13 +45605,13 @@
         <v>8.935570481567899</v>
       </c>
       <c r="BO124" t="n">
-        <v>1.762970094926346</v>
+        <v>1.762970091013816</v>
       </c>
       <c r="BP124" t="n">
-        <v>1.762970094926346</v>
+        <v>1.762970091013816</v>
       </c>
       <c r="BQ124" t="n">
-        <v>1.586673085433711</v>
+        <v>1.586673081912434</v>
       </c>
       <c r="BR124" t="n">
         <v>2</v>
@@ -45659,10 +45623,10 @@
         <v>6.2</v>
       </c>
       <c r="BU124" t="n">
-        <v>-66.02413148796187</v>
+        <v>-66.02413156336395</v>
       </c>
       <c r="BV124" t="n">
-        <v>-62.2490349866243</v>
+        <v>-62.24903507040438</v>
       </c>
       <c r="BW124" t="inlineStr">
         <is>
@@ -45771,7 +45735,7 @@
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>Fundo duplo</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="R125" t="n">
@@ -45890,10 +45854,10 @@
         <v>5.110000133514404</v>
       </c>
       <c r="BG125" t="n">
-        <v>1.246509808831512</v>
+        <v>1.246509807626005</v>
       </c>
       <c r="BH125" t="n">
-        <v>1.814918281658681</v>
+        <v>1.814918279903464</v>
       </c>
       <c r="BI125" t="inlineStr"/>
       <c r="BJ125" t="inlineStr"/>
@@ -45904,13 +45868,13 @@
         <v>5.110000133514404</v>
       </c>
       <c r="BO125" t="n">
-        <v>1.530714045245096</v>
+        <v>1.530714043764735</v>
       </c>
       <c r="BP125" t="n">
-        <v>1.530714045245096</v>
+        <v>1.530714043764735</v>
       </c>
       <c r="BQ125" t="n">
-        <v>1.377642640720587</v>
+        <v>1.377642639388261</v>
       </c>
       <c r="BR125" t="n">
         <v>2</v>
@@ -45922,10 +45886,10 @@
         <v>4.1</v>
       </c>
       <c r="BU125" t="n">
-        <v>-73.04026213844514</v>
+        <v>-73.04026216451804</v>
       </c>
       <c r="BV125" t="n">
-        <v>-70.0447357093835</v>
+        <v>-70.0447357383534</v>
       </c>
       <c r="BW125" t="inlineStr">
         <is>
@@ -45939,11 +45903,7 @@
       </c>
       <c r="BY125" t="inlineStr"/>
       <c r="BZ125" t="inlineStr"/>
-      <c r="CA125" t="inlineStr">
-        <is>
-          <t>Fundo duplo</t>
-        </is>
-      </c>
+      <c r="CA125" t="inlineStr"/>
       <c r="CB125" t="b">
         <v>0</v>
       </c>
@@ -45970,14 +45930,14 @@
         <v>0</v>
       </c>
       <c r="CK125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL125" t="b">
         <v>0</v>
       </c>
       <c r="CM125" t="inlineStr">
         <is>
-          <t>Fundo duplo — rompeu pescoço ~R$4.99 (candidato)</t>
+          <t>sem sinal (Em Alta)</t>
         </is>
       </c>
     </row>
@@ -46155,10 +46115,10 @@
         <v>4.28000020980835</v>
       </c>
       <c r="BG126" t="n">
-        <v>0.8142138771205825</v>
+        <v>0.8142138751323587</v>
       </c>
       <c r="BH126" t="n">
-        <v>1.510366742058681</v>
+        <v>1.510366738370525</v>
       </c>
       <c r="BI126" t="inlineStr"/>
       <c r="BJ126" t="inlineStr"/>
@@ -46169,13 +46129,13 @@
         <v>2.641155783568356</v>
       </c>
       <c r="BO126" t="n">
-        <v>1.65524546758254</v>
+        <v>1.655245465690413</v>
       </c>
       <c r="BP126" t="n">
-        <v>1.510366742058681</v>
+        <v>1.510366738370525</v>
       </c>
       <c r="BQ126" t="n">
-        <v>1.359330067852813</v>
+        <v>1.359330064533473</v>
       </c>
       <c r="BR126" t="n">
         <v>3</v>
@@ -46187,10 +46147,10 @@
         <v>3.2</v>
       </c>
       <c r="BU126" t="n">
-        <v>-68.23995324257984</v>
+        <v>-68.2399533201345</v>
       </c>
       <c r="BV126" t="n">
-        <v>-61.32604237286572</v>
+        <v>-61.32604241707427</v>
       </c>
       <c r="BW126" t="inlineStr">
         <is>
@@ -46418,10 +46378,10 @@
         <v>6.150000095367432</v>
       </c>
       <c r="BG127" t="n">
-        <v>0.9823296683800564</v>
+        <v>0.9823296693730859</v>
       </c>
       <c r="BH127" t="n">
-        <v>1.822221534845005</v>
+        <v>1.822221536687074</v>
       </c>
       <c r="BI127" t="inlineStr"/>
       <c r="BJ127" t="inlineStr"/>
@@ -46667,10 +46627,10 @@
         <v>1.029999971389771</v>
       </c>
       <c r="BG128" t="n">
-        <v>0.3006580853748933</v>
+        <v>0.3006580848837518</v>
       </c>
       <c r="BH128" t="n">
-        <v>0.4237819498517185</v>
+        <v>0.4237819491594474</v>
       </c>
       <c r="BI128" t="inlineStr"/>
       <c r="BJ128" t="inlineStr"/>
@@ -46679,13 +46639,13 @@
       <c r="BM128" t="inlineStr"/>
       <c r="BN128" t="inlineStr"/>
       <c r="BO128" t="n">
-        <v>0.3622200176133059</v>
+        <v>0.3622200170215996</v>
       </c>
       <c r="BP128" t="n">
-        <v>0.3622200176133059</v>
+        <v>0.3622200170215996</v>
       </c>
       <c r="BQ128" t="n">
-        <v>0.3259980158519754</v>
+        <v>0.3259980153194397</v>
       </c>
       <c r="BR128" t="n">
         <v>2</v>
@@ -46697,10 +46657,10 @@
         <v>1.4</v>
       </c>
       <c r="BU128" t="n">
-        <v>-68.34970631968962</v>
+        <v>-68.3497063713921</v>
       </c>
       <c r="BV128" t="n">
-        <v>-64.83300702187735</v>
+        <v>-64.83300707932456</v>
       </c>
       <c r="BW128" t="inlineStr">
         <is>
@@ -46928,25 +46888,25 @@
         <v>7.519999980926514</v>
       </c>
       <c r="BG129" t="n">
-        <v>1.933891672437335</v>
+        <v>1.933891675977965</v>
       </c>
       <c r="BH129" t="n">
-        <v>2.193509933481675</v>
+        <v>2.193509936602485</v>
       </c>
       <c r="BI129" t="n">
-        <v>3.495424121314159</v>
+        <v>3.495424119887732</v>
       </c>
       <c r="BJ129" t="n">
         <v>10.2857475189034</v>
       </c>
       <c r="BK129" t="n">
-        <v>2.189679678750924</v>
+        <v>2.189679679631879</v>
       </c>
       <c r="BL129" t="n">
-        <v>6.10204935035525</v>
+        <v>6.102049350081661</v>
       </c>
       <c r="BM129" t="n">
-        <v>1.552554598344003</v>
+        <v>1.552554597110164</v>
       </c>
       <c r="BN129" t="n">
         <v>17.47579512860355</v>
@@ -47181,10 +47141,10 @@
         <v>3.319999933242798</v>
       </c>
       <c r="BG130" t="n">
-        <v>0.2180486325326315</v>
+        <v>0.2179622010041239</v>
       </c>
       <c r="BH130" t="n">
-        <v>0.3174788089675115</v>
+        <v>0.3173529646620045</v>
       </c>
       <c r="BI130" t="inlineStr"/>
       <c r="BJ130" t="inlineStr"/>
@@ -47193,13 +47153,13 @@
       <c r="BM130" t="inlineStr"/>
       <c r="BN130" t="inlineStr"/>
       <c r="BO130" t="n">
-        <v>0.2677637207500715</v>
+        <v>0.2676575828330642</v>
       </c>
       <c r="BP130" t="n">
-        <v>0.2677637207500715</v>
+        <v>0.2676575828330642</v>
       </c>
       <c r="BQ130" t="n">
-        <v>0.2409873486750644</v>
+        <v>0.2408918245497578</v>
       </c>
       <c r="BR130" t="n">
         <v>2</v>
@@ -47211,10 +47171,10 @@
         <v>1.5</v>
       </c>
       <c r="BU130" t="n">
-        <v>-92.7413447734717</v>
+        <v>-92.74422200621952</v>
       </c>
       <c r="BV130" t="n">
-        <v>-91.93482752607966</v>
+        <v>-91.93802445135502</v>
       </c>
       <c r="BW130" t="inlineStr">
         <is>
@@ -47436,10 +47396,10 @@
         <v>3.599999904632568</v>
       </c>
       <c r="BG131" t="n">
-        <v>0.6792706431514036</v>
+        <v>0.6792706437604058</v>
       </c>
       <c r="BH131" t="n">
-        <v>1.260047043045853</v>
+        <v>1.260047044175553</v>
       </c>
       <c r="BI131" t="inlineStr"/>
       <c r="BJ131" t="inlineStr"/>
@@ -47448,13 +47408,13 @@
       <c r="BM131" t="inlineStr"/>
       <c r="BN131" t="inlineStr"/>
       <c r="BO131" t="n">
-        <v>0.9696588430986286</v>
+        <v>0.9696588439679792</v>
       </c>
       <c r="BP131" t="n">
-        <v>0.9696588430986286</v>
+        <v>0.9696588439679792</v>
       </c>
       <c r="BQ131" t="n">
-        <v>0.8726929587887657</v>
+        <v>0.8726929595711813</v>
       </c>
       <c r="BR131" t="n">
         <v>2</v>
@@ -47466,10 +47426,10 @@
         <v>1.9</v>
       </c>
       <c r="BU131" t="n">
-        <v>-75.75852828035458</v>
+        <v>-75.75852825862083</v>
       </c>
       <c r="BV131" t="n">
-        <v>-73.06503142261622</v>
+        <v>-73.06503139846758</v>
       </c>
       <c r="BW131" t="inlineStr">
         <is>
@@ -47695,10 +47655,10 @@
         <v>4.28000020980835</v>
       </c>
       <c r="BG132" t="n">
-        <v>4.711356972185492</v>
+        <v>4.711357005392489</v>
       </c>
       <c r="BH132" t="n">
-        <v>6.859735751502078</v>
+        <v>6.859735799851464</v>
       </c>
       <c r="BI132" t="inlineStr"/>
       <c r="BJ132" t="inlineStr"/>
@@ -47707,13 +47667,13 @@
       <c r="BM132" t="inlineStr"/>
       <c r="BN132" t="inlineStr"/>
       <c r="BO132" t="n">
-        <v>5.785546361843785</v>
+        <v>5.785546402621977</v>
       </c>
       <c r="BP132" t="n">
-        <v>5.785546361843785</v>
+        <v>5.785546402621977</v>
       </c>
       <c r="BQ132" t="n">
-        <v>5.206991725659407</v>
+        <v>5.206991762359779</v>
       </c>
       <c r="BR132" t="n">
         <v>2</v>
@@ -47725,10 +47685,10 @@
         <v>1.5</v>
       </c>
       <c r="BU132" t="n">
-        <v>21.65867921517148</v>
+        <v>21.65868007265679</v>
       </c>
       <c r="BV132" t="n">
-        <v>35.17631023907943</v>
+        <v>35.17631119184086</v>
       </c>
       <c r="BW132" t="inlineStr">
         <is>
@@ -47956,25 +47916,25 @@
         <v>35.81000137329102</v>
       </c>
       <c r="BG133" t="n">
-        <v>8.065634742825267</v>
+        <v>8.06563477187346</v>
       </c>
       <c r="BH133" t="n">
-        <v>8.292129790220599</v>
+        <v>8.29212980597074</v>
       </c>
       <c r="BI133" t="n">
-        <v>8.783185321950423</v>
+        <v>8.783185307000842</v>
       </c>
       <c r="BJ133" t="n">
         <v>23.1384064783354</v>
       </c>
       <c r="BK133" t="n">
-        <v>4.174063087737034</v>
+        <v>4.174063076838205</v>
       </c>
       <c r="BL133" t="n">
-        <v>13.43033403033554</v>
+        <v>13.43033402759574</v>
       </c>
       <c r="BM133" t="n">
-        <v>3.448221683598776</v>
+        <v>3.448221668210203</v>
       </c>
       <c r="BN133" t="n">
         <v>47.75065260804188</v>
@@ -48478,10 +48438,10 @@
         <v>1.899999976158142</v>
       </c>
       <c r="BG135" t="n">
-        <v>0.5330663182090856</v>
+        <v>0.5330663181333803</v>
       </c>
       <c r="BH135" t="n">
-        <v>0.7761445593124285</v>
+        <v>0.7761445592022017</v>
       </c>
       <c r="BI135" t="n">
         <v>0.4389160318090776</v>
@@ -48733,10 +48693,10 @@
         <v>18.64999961853027</v>
       </c>
       <c r="BG136" t="n">
-        <v>1.435796758328224</v>
+        <v>1.435796758626157</v>
       </c>
       <c r="BH136" t="n">
-        <v>2.090520080125894</v>
+        <v>2.090520080559684</v>
       </c>
       <c r="BI136" t="inlineStr"/>
       <c r="BJ136" t="inlineStr"/>
@@ -48867,7 +48827,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>Fundo duplo</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="R137" t="n">
@@ -49009,11 +48969,7 @@
       </c>
       <c r="BY137" t="inlineStr"/>
       <c r="BZ137" t="inlineStr"/>
-      <c r="CA137" t="inlineStr">
-        <is>
-          <t>Fundo duplo</t>
-        </is>
-      </c>
+      <c r="CA137" t="inlineStr"/>
       <c r="CB137" t="b">
         <v>0</v>
       </c>
@@ -49040,14 +48996,14 @@
         <v>0</v>
       </c>
       <c r="CK137" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL137" t="b">
         <v>0</v>
       </c>
       <c r="CM137" t="inlineStr">
         <is>
-          <t>Fundo duplo — rompeu pescoço ~R$4.90 (candidato)</t>
+          <t>sem sinal (Lateral)</t>
         </is>
       </c>
     </row>
@@ -49452,37 +49408,37 @@
         <v>17.29999923706055</v>
       </c>
       <c r="BG139" t="n">
-        <v>2.082354464818384</v>
+        <v>2.082354460518884</v>
       </c>
       <c r="BH139" t="n">
-        <v>3.272847465967874</v>
+        <v>3.272847461818208</v>
       </c>
       <c r="BI139" t="n">
-        <v>7.904674632956166</v>
+        <v>7.904674639254793</v>
       </c>
       <c r="BJ139" t="n">
         <v>11.82515192553242</v>
       </c>
       <c r="BK139" t="n">
-        <v>4.478923523496296</v>
+        <v>4.478923525849839</v>
       </c>
       <c r="BL139" t="n">
-        <v>5.046513525898138</v>
+        <v>5.046513526227029</v>
       </c>
       <c r="BM139" t="n">
-        <v>3.950487906147784</v>
+        <v>3.950487909167065</v>
       </c>
       <c r="BN139" t="n">
         <v>12.81759973415833</v>
       </c>
       <c r="BO139" t="n">
-        <v>5.508707634973867</v>
+        <v>5.508707635481178</v>
       </c>
       <c r="BP139" t="n">
-        <v>4.478923523496296</v>
+        <v>4.478923525849839</v>
       </c>
       <c r="BQ139" t="n">
-        <v>4.031031171146666</v>
+        <v>4.031031173264855</v>
       </c>
       <c r="BR139" t="n">
         <v>7</v>
@@ -49494,10 +49450,10 @@
         <v>6.2</v>
       </c>
       <c r="BU139" t="n">
-        <v>-76.69924075770317</v>
+        <v>-76.69924074545931</v>
       </c>
       <c r="BV139" t="n">
-        <v>-68.15775793115091</v>
+        <v>-68.15775792821846</v>
       </c>
       <c r="BW139" t="inlineStr">
         <is>
@@ -49725,25 +49681,25 @@
         <v>4.460000038146973</v>
       </c>
       <c r="BG140" t="n">
-        <v>1.382638831589418</v>
+        <v>1.382638833159787</v>
       </c>
       <c r="BH140" t="n">
-        <v>1.558197248910166</v>
+        <v>1.55819725031872</v>
       </c>
       <c r="BI140" t="n">
-        <v>2.514156469147515</v>
+        <v>2.5141564685647</v>
       </c>
       <c r="BJ140" t="n">
         <v>7.689960038519025</v>
       </c>
       <c r="BK140" t="n">
-        <v>1.793736047318987</v>
+        <v>1.793736048047312</v>
       </c>
       <c r="BL140" t="n">
-        <v>1.859346784792415</v>
+        <v>1.859346784744788</v>
       </c>
       <c r="BM140" t="n">
-        <v>1.109798639581701</v>
+        <v>1.10979863907177</v>
       </c>
       <c r="BN140" t="n">
         <v>0.03409797823786088</v>
@@ -50731,10 +50687,10 @@
         <v>5.639999866485596</v>
       </c>
       <c r="BG144" t="n">
-        <v>3.947371420385105</v>
+        <v>3.947371396441933</v>
       </c>
       <c r="BH144" t="n">
-        <v>7.32237398481437</v>
+        <v>7.322373940399785</v>
       </c>
       <c r="BI144" t="inlineStr"/>
       <c r="BJ144" t="inlineStr"/>
@@ -50743,13 +50699,13 @@
       <c r="BM144" t="inlineStr"/>
       <c r="BN144" t="inlineStr"/>
       <c r="BO144" t="n">
-        <v>5.634872702599738</v>
+        <v>5.634872668420859</v>
       </c>
       <c r="BP144" t="n">
-        <v>5.634872702599738</v>
+        <v>5.634872668420859</v>
       </c>
       <c r="BQ144" t="n">
-        <v>5.071385432339764</v>
+        <v>5.071385401578773</v>
       </c>
       <c r="BR144" t="n">
         <v>2</v>
@@ -50761,10 +50717,10 @@
         <v>1.9</v>
       </c>
       <c r="BU144" t="n">
-        <v>-10.08181644692391</v>
+        <v>-10.08181699233157</v>
       </c>
       <c r="BV144" t="n">
-        <v>-0.09090716324878789</v>
+        <v>-0.09090776925729793</v>
       </c>
       <c r="BW144" t="inlineStr">
         <is>
@@ -50992,10 +50948,10 @@
         <v>3.279999971389771</v>
       </c>
       <c r="BG145" t="n">
-        <v>0.5928288464451491</v>
+        <v>0.5928288471040746</v>
       </c>
       <c r="BH145" t="n">
-        <v>1.099697510155752</v>
+        <v>1.099697511378058</v>
       </c>
       <c r="BI145" t="inlineStr"/>
       <c r="BJ145" t="inlineStr"/>
@@ -51006,13 +50962,13 @@
         <v>3.043030546037059</v>
       </c>
       <c r="BO145" t="n">
-        <v>0.8462631783004504</v>
+        <v>0.8462631792410664</v>
       </c>
       <c r="BP145" t="n">
-        <v>0.8462631783004504</v>
+        <v>0.8462631792410664</v>
       </c>
       <c r="BQ145" t="n">
-        <v>0.7616368604704054</v>
+        <v>0.7616368613169598</v>
       </c>
       <c r="BR145" t="n">
         <v>2</v>
@@ -51024,10 +50980,10 @@
         <v>5.1</v>
       </c>
       <c r="BU145" t="n">
-        <v>-76.77936380750357</v>
+        <v>-76.77936378169399</v>
       </c>
       <c r="BV145" t="n">
-        <v>-74.19929311944841</v>
+        <v>-74.19929309077111</v>
       </c>
       <c r="BW145" t="inlineStr">
         <is>
@@ -51516,10 +51472,10 @@
         <v>17.54999923706055</v>
       </c>
       <c r="BG147" t="n">
-        <v>8.893768152026635</v>
+        <v>8.893768123540744</v>
       </c>
       <c r="BH147" t="n">
-        <v>12.94932642935078</v>
+        <v>12.94932638787532</v>
       </c>
       <c r="BI147" t="n">
         <v>4.596323144432881</v>
@@ -52291,10 +52247,10 @@
         <v>10.53999996185303</v>
       </c>
       <c r="BG150" t="n">
-        <v>5.631539577496492</v>
+        <v>5.631539553863648</v>
       </c>
       <c r="BH150" t="n">
-        <v>10.30780318221765</v>
+        <v>10.3078031389608</v>
       </c>
       <c r="BI150" t="inlineStr"/>
       <c r="BJ150" t="inlineStr"/>
@@ -52305,13 +52261,13 @@
         <v>3.619100702685365</v>
       </c>
       <c r="BO150" t="n">
-        <v>6.519481154133171</v>
+        <v>6.519481131836603</v>
       </c>
       <c r="BP150" t="n">
-        <v>5.631539577496492</v>
+        <v>5.631539553863648</v>
       </c>
       <c r="BQ150" t="n">
-        <v>5.068385619746843</v>
+        <v>5.068385598477284</v>
       </c>
       <c r="BR150" t="n">
         <v>3</v>
@@ -52323,10 +52279,10 @@
         <v>2.8</v>
       </c>
       <c r="BU150" t="n">
-        <v>-51.91284973348543</v>
+        <v>-51.91284993528391</v>
       </c>
       <c r="BV150" t="n">
-        <v>-38.14533986974524</v>
+        <v>-38.14534008128764</v>
       </c>
       <c r="BW150" t="inlineStr">
         <is>
@@ -52554,10 +52510,10 @@
         <v>14.69999980926514</v>
       </c>
       <c r="BG151" t="n">
-        <v>3.918118763866213</v>
+        <v>3.91811876728182</v>
       </c>
       <c r="BH151" t="n">
-        <v>5.704780920189207</v>
+        <v>5.70478092516233</v>
       </c>
       <c r="BI151" t="inlineStr"/>
       <c r="BJ151" t="inlineStr"/>
@@ -52568,7 +52524,7 @@
         <v>4.70041613027538</v>
       </c>
       <c r="BO151" t="n">
-        <v>4.774438604776933</v>
+        <v>4.774438607573177</v>
       </c>
       <c r="BP151" t="n">
         <v>4.70041613027538</v>
@@ -52589,7 +52545,7 @@
         <v>-71.22194168613856</v>
       </c>
       <c r="BV151" t="n">
-        <v>-67.52082539642149</v>
+        <v>-67.5208253773994</v>
       </c>
       <c r="BW151" t="inlineStr">
         <is>
@@ -52819,10 +52775,10 @@
         <v>16.15999984741211</v>
       </c>
       <c r="BG152" t="n">
-        <v>24.72829511458395</v>
+        <v>24.72829508050393</v>
       </c>
       <c r="BH152" t="n">
-        <v>33.56088953093385</v>
+        <v>33.56088948468092</v>
       </c>
       <c r="BI152" t="n">
         <v>2.716455865750314</v>
@@ -52831,7 +52787,7 @@
         <v>7.265725417124772</v>
       </c>
       <c r="BK152" t="n">
-        <v>6.938972274918187</v>
+        <v>6.938972266644902</v>
       </c>
       <c r="BL152" t="n">
         <v>3.053166357475611</v>

--- a/reports/screener_2026-08-11.xlsx
+++ b/reports/screener_2026-08-11.xlsx
@@ -1106,10 +1106,10 @@
         <v>10.27999973297119</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.806939245491056</v>
+        <v>5.806939284342563</v>
       </c>
       <c r="BO2" t="n">
-        <v>10.77187230038591</v>
+        <v>10.77187237245545</v>
       </c>
       <c r="BP2" t="n">
         <v>35.84473591101796</v>
@@ -1118,7 +1118,7 @@
         <v>24.64756109389902</v>
       </c>
       <c r="BR2" t="n">
-        <v>61.97293300827438</v>
+        <v>61.97293315141151</v>
       </c>
       <c r="BS2" t="n">
         <v>17.08511007767805</v>
@@ -1394,10 +1394,10 @@
         <v>4.039999961853027</v>
       </c>
       <c r="BN3" t="n">
-        <v>3.419461678271012</v>
+        <v>3.419461662610363</v>
       </c>
       <c r="BO3" t="n">
-        <v>6.343101413192727</v>
+        <v>6.343101384142222</v>
       </c>
       <c r="BP3" t="n">
         <v>12.47785536003557</v>
@@ -1406,25 +1406,25 @@
         <v>8.411070803097941</v>
       </c>
       <c r="BR3" t="n">
-        <v>24.27125083577009</v>
+        <v>24.27125084675442</v>
       </c>
       <c r="BS3" t="n">
-        <v>11.09291018811865</v>
+        <v>11.09291019453871</v>
       </c>
       <c r="BT3" t="n">
-        <v>10.75768533736775</v>
+        <v>10.75768537639659</v>
       </c>
       <c r="BU3" t="n">
         <v>4.904734709731053</v>
       </c>
       <c r="BV3" t="n">
-        <v>8.997892968590614</v>
+        <v>8.997892971323681</v>
       </c>
       <c r="BW3" t="n">
-        <v>9.584378070232844</v>
+        <v>9.584378089747268</v>
       </c>
       <c r="BX3" t="n">
-        <v>8.625940263209561</v>
+        <v>8.625940280772541</v>
       </c>
       <c r="BY3" t="n">
         <v>6</v>
@@ -1436,10 +1436,10 @@
         <v>7.1</v>
       </c>
       <c r="CB3" t="n">
-        <v>113.5133748677834</v>
+        <v>113.5133753025106</v>
       </c>
       <c r="CC3" t="n">
-        <v>122.7201250879109</v>
+        <v>122.720125155561</v>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
@@ -1692,10 +1692,10 @@
         <v>23.79999923706055</v>
       </c>
       <c r="BN4" t="n">
-        <v>15.67084916591658</v>
+        <v>15.67084917279736</v>
       </c>
       <c r="BO4" t="n">
-        <v>29.06942520277526</v>
+        <v>29.06942521553909</v>
       </c>
       <c r="BP4" t="n">
         <v>62.32213238953601</v>
@@ -1704,19 +1704,19 @@
         <v>45.62472487613315</v>
       </c>
       <c r="BR4" t="n">
-        <v>103.4137246946409</v>
+        <v>103.4137246906267</v>
       </c>
       <c r="BS4" t="n">
-        <v>20.19414446422667</v>
+        <v>20.19414446334902</v>
       </c>
       <c r="BT4" t="n">
-        <v>50.31447893037993</v>
+        <v>50.31447891589011</v>
       </c>
       <c r="BU4" t="n">
         <v>37.19489833875116</v>
       </c>
       <c r="BV4" t="n">
-        <v>49.73336127092045</v>
+        <v>49.73336126997503</v>
       </c>
       <c r="BW4" t="n">
         <v>45.62472487613315</v>
@@ -1737,7 +1737,7 @@
         <v>72.53047775135681</v>
       </c>
       <c r="CC4" t="n">
-        <v>108.9637095175925</v>
+        <v>108.9637095136202</v>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
@@ -1990,10 +1990,10 @@
         <v>13.63000011444092</v>
       </c>
       <c r="BN5" t="n">
-        <v>15.04788536135715</v>
+        <v>15.04788548267626</v>
       </c>
       <c r="BO5" t="n">
-        <v>27.91382734531751</v>
+        <v>27.91382757036445</v>
       </c>
       <c r="BP5" t="n">
         <v>37.94065157906348</v>
@@ -2002,25 +2002,25 @@
         <v>22.93112736979142</v>
       </c>
       <c r="BR5" t="n">
-        <v>70.78984165015041</v>
+        <v>70.78984141148864</v>
       </c>
       <c r="BS5" t="n">
-        <v>45.2936981338215</v>
+        <v>45.29369804761603</v>
       </c>
       <c r="BT5" t="n">
-        <v>24.32634175873935</v>
+        <v>24.32634138443595</v>
       </c>
       <c r="BU5" t="n">
         <v>8.909513594966207</v>
       </c>
       <c r="BV5" t="n">
-        <v>28.90892192468174</v>
+        <v>28.90892190565793</v>
       </c>
       <c r="BW5" t="n">
-        <v>26.12008455202843</v>
+        <v>26.1200844774002</v>
       </c>
       <c r="BX5" t="n">
-        <v>23.50807609682559</v>
+        <v>23.50807602966018</v>
       </c>
       <c r="BY5" t="n">
         <v>6</v>
@@ -2032,10 +2032,10 @@
         <v>7.9</v>
       </c>
       <c r="CB5" t="n">
-        <v>72.47304401647727</v>
+        <v>72.47304352370101</v>
       </c>
       <c r="CC5" t="n">
-        <v>112.0977379453788</v>
+        <v>112.0977378058058</v>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
@@ -2288,10 +2288,10 @@
         <v>4.320000171661377</v>
       </c>
       <c r="BN6" t="n">
-        <v>2.922596179279397</v>
+        <v>2.92259619629234</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.421415912563281</v>
+        <v>5.421415944122291</v>
       </c>
       <c r="BP6" t="n">
         <v>12.47058873083077</v>
@@ -2300,7 +2300,7 @@
         <v>8.38874521704944</v>
       </c>
       <c r="BR6" t="n">
-        <v>23.03188433220745</v>
+        <v>23.03188438409878</v>
       </c>
       <c r="BS6" t="n">
         <v>11.34817472758152</v>
@@ -2312,7 +2312,7 @@
         <v>4.921612750118176</v>
       </c>
       <c r="BV6" t="n">
-        <v>10.99580820242801</v>
+        <v>10.99580821434949</v>
       </c>
       <c r="BW6" t="n">
         <v>11.34817472758152</v>
@@ -2333,7 +2333,7 @@
         <v>136.4202974301165</v>
       </c>
       <c r="CC6" t="n">
-        <v>154.53258716421</v>
+        <v>154.5325874401701</v>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
@@ -2586,10 +2586,10 @@
         <v>15.56999969482422</v>
       </c>
       <c r="BN7" t="n">
-        <v>6.370378857060131</v>
+        <v>6.37037883656561</v>
       </c>
       <c r="BO7" t="n">
-        <v>11.81705277984654</v>
+        <v>11.81705274182921</v>
       </c>
       <c r="BP7" t="n">
         <v>25.22035402890231</v>
@@ -2598,19 +2598,19 @@
         <v>18.49208604587491</v>
       </c>
       <c r="BR7" t="n">
-        <v>34.98832835169073</v>
+        <v>34.98832838493097</v>
       </c>
       <c r="BS7" t="n">
-        <v>12.44970856183109</v>
+        <v>12.44970856579755</v>
       </c>
       <c r="BT7" t="n">
-        <v>20.22430266734827</v>
+        <v>20.22430271029003</v>
       </c>
       <c r="BU7" t="n">
         <v>17.52538993234214</v>
       </c>
       <c r="BV7" t="n">
-        <v>20.10246033826229</v>
+        <v>20.10246034428101</v>
       </c>
       <c r="BW7" t="n">
         <v>18.49208604587491</v>
@@ -2631,7 +2631,7 @@
         <v>6.890672880487236</v>
       </c>
       <c r="CC7" t="n">
-        <v>29.11021664916762</v>
+        <v>29.11021668782354</v>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
@@ -2870,10 +2870,10 @@
         <v>48.38999938964844</v>
       </c>
       <c r="BN8" t="n">
-        <v>18.43110919828188</v>
+        <v>18.43110925157252</v>
       </c>
       <c r="BO8" t="n">
-        <v>34.18970756281288</v>
+        <v>34.18970766166702</v>
       </c>
       <c r="BP8" t="n">
         <v>73.52838210009652</v>
@@ -2882,23 +2882,23 @@
         <v>55.10133168995815</v>
       </c>
       <c r="BR8" t="n">
-        <v>97.40219839678448</v>
+        <v>97.40219831194068</v>
       </c>
       <c r="BS8" t="n">
-        <v>47.18970513584031</v>
+        <v>47.18970512292769</v>
       </c>
       <c r="BT8" t="n">
-        <v>57.4486272945624</v>
+        <v>57.44862718745247</v>
       </c>
       <c r="BU8" t="inlineStr"/>
       <c r="BV8" t="n">
-        <v>43.3347259992579</v>
+        <v>43.33472603406594</v>
       </c>
       <c r="BW8" t="n">
-        <v>40.6897063493266</v>
+        <v>40.68970639229735</v>
       </c>
       <c r="BX8" t="n">
-        <v>36.62073571439394</v>
+        <v>36.62073575306762</v>
       </c>
       <c r="BY8" t="n">
         <v>4</v>
@@ -2910,10 +2910,10 @@
         <v>4</v>
       </c>
       <c r="CB8" t="n">
-        <v>-24.32168593449533</v>
+        <v>-24.32168585457451</v>
       </c>
       <c r="CC8" t="n">
-        <v>-10.44693832228475</v>
+        <v>-10.44693825035246</v>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
@@ -3152,10 +3152,10 @@
         <v>18.45000076293945</v>
       </c>
       <c r="BN9" t="n">
-        <v>12.68429995798505</v>
+        <v>12.68429994572237</v>
       </c>
       <c r="BO9" t="n">
-        <v>23.52937642206226</v>
+        <v>23.529376399315</v>
       </c>
       <c r="BP9" t="n">
         <v>19.46357564561686</v>
@@ -3164,7 +3164,7 @@
         <v>12.1658993674517</v>
       </c>
       <c r="BR9" t="n">
-        <v>32.94109945680061</v>
+        <v>32.94109944313202</v>
       </c>
       <c r="BS9" t="n">
         <v>22.27593117185458</v>
@@ -3174,7 +3174,7 @@
       </c>
       <c r="BU9" t="inlineStr"/>
       <c r="BV9" t="n">
-        <v>19.48829579937969</v>
+        <v>19.4882957906272</v>
       </c>
       <c r="BW9" t="n">
         <v>20.86975340873572</v>
@@ -3195,7 +3195,7 @@
         <v>1.80367095480638</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.627615140948161</v>
+        <v>5.62761509350922</v>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
@@ -3448,10 +3448,10 @@
         <v>31.39999961853027</v>
       </c>
       <c r="BN10" t="n">
-        <v>43.84701151402275</v>
+        <v>43.84701139465804</v>
       </c>
       <c r="BO10" t="n">
-        <v>81.33620635851219</v>
+        <v>81.33620613709066</v>
       </c>
       <c r="BP10" t="n">
         <v>63.4222553270619</v>
@@ -3472,7 +3472,7 @@
         <v>25.86511310728236</v>
       </c>
       <c r="BV10" t="n">
-        <v>67.06923452579125</v>
+        <v>67.06923448319296</v>
       </c>
       <c r="BW10" t="n">
         <v>60.66996877513281</v>
@@ -3493,7 +3493,7 @@
         <v>73.89481707317074</v>
       </c>
       <c r="CC10" t="n">
-        <v>113.5962908936192</v>
+        <v>113.5962907579559</v>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
@@ -3746,10 +3746,10 @@
         <v>31.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>22.1030031867634</v>
+        <v>22.10300327913806</v>
       </c>
       <c r="BO11" t="n">
-        <v>41.00107091144611</v>
+        <v>41.0010710828011</v>
       </c>
       <c r="BP11" t="n">
         <v>45.51526717557251</v>
@@ -3758,25 +3758,25 @@
         <v>19.62721165712462</v>
       </c>
       <c r="BR11" t="n">
-        <v>57.2358983095674</v>
+        <v>57.23589755890481</v>
       </c>
       <c r="BS11" t="n">
-        <v>49.59879628771473</v>
+        <v>49.59879616720629</v>
       </c>
       <c r="BT11" t="n">
-        <v>23.9423434910391</v>
+        <v>23.94234293054661</v>
       </c>
       <c r="BU11" t="n">
         <v>23.78189287402351</v>
       </c>
       <c r="BV11" t="n">
-        <v>35.35068548665642</v>
+        <v>35.35068534066469</v>
       </c>
       <c r="BW11" t="n">
-        <v>32.47170720124261</v>
+        <v>32.47170700667385</v>
       </c>
       <c r="BX11" t="n">
-        <v>29.22453648111835</v>
+        <v>29.22453630600647</v>
       </c>
       <c r="BY11" t="n">
         <v>8</v>
@@ -3788,10 +3788,10 @@
         <v>2.9</v>
       </c>
       <c r="CB11" t="n">
-        <v>-7.223693710735402</v>
+        <v>-7.223694266646142</v>
       </c>
       <c r="CC11" t="n">
-        <v>12.22439837033786</v>
+        <v>12.22439790687202</v>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
@@ -4044,10 +4044,10 @@
         <v>6.510000228881836</v>
       </c>
       <c r="BN12" t="n">
-        <v>2.939313004811351</v>
+        <v>2.93931301034954</v>
       </c>
       <c r="BO12" t="n">
-        <v>5.452425623925055</v>
+        <v>5.452425634198397</v>
       </c>
       <c r="BP12" t="n">
         <v>21.245690402139</v>
@@ -4056,7 +4056,7 @@
         <v>13.54578759251334</v>
       </c>
       <c r="BR12" t="n">
-        <v>34.18728706910997</v>
+        <v>34.18728708820717</v>
       </c>
       <c r="BS12" t="n">
         <v>11.55192114631721</v>
@@ -4318,10 +4318,10 @@
         <v>13.14000034332275</v>
       </c>
       <c r="BN13" t="n">
-        <v>9.532624410650243</v>
+        <v>9.532624430413199</v>
       </c>
       <c r="BO13" t="n">
-        <v>17.6830182817562</v>
+        <v>17.68301831841648</v>
       </c>
       <c r="BP13" t="n">
         <v>49.32153103371855</v>
@@ -4330,23 +4330,23 @@
         <v>47.39158599337461</v>
       </c>
       <c r="BR13" t="n">
-        <v>71.21193626334824</v>
+        <v>71.21193630302051</v>
       </c>
       <c r="BS13" t="n">
-        <v>31.70486910412532</v>
+        <v>31.70486910109994</v>
       </c>
       <c r="BT13" t="n">
-        <v>30.94181047213296</v>
+        <v>30.94181044780239</v>
       </c>
       <c r="BU13" t="inlineStr"/>
       <c r="BV13" t="n">
-        <v>32.90313947320002</v>
+        <v>32.90313948441166</v>
       </c>
       <c r="BW13" t="n">
-        <v>31.70486910412532</v>
+        <v>31.70486910109994</v>
       </c>
       <c r="BX13" t="n">
-        <v>28.53438219371279</v>
+        <v>28.53438219098994</v>
       </c>
       <c r="BY13" t="n">
         <v>3</v>
@@ -4358,10 +4358,10 @@
         <v>5.2</v>
       </c>
       <c r="CB13" t="n">
-        <v>117.1566320256062</v>
+        <v>117.1566320048844</v>
       </c>
       <c r="CC13" t="n">
-        <v>150.4044034513298</v>
+        <v>150.4044035366543</v>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
@@ -4614,37 +4614,37 @@
         <v>33.2400016784668</v>
       </c>
       <c r="BN14" t="n">
-        <v>23.90741373264288</v>
+        <v>23.90741379607601</v>
       </c>
       <c r="BO14" t="n">
-        <v>31.38173453430443</v>
+        <v>31.3817344285561</v>
       </c>
       <c r="BP14" t="n">
-        <v>35.57732098896218</v>
+        <v>35.57732077467912</v>
       </c>
       <c r="BQ14" t="n">
         <v>35.59395391834337</v>
       </c>
       <c r="BR14" t="n">
-        <v>49.64138143699247</v>
+        <v>49.64138131146932</v>
       </c>
       <c r="BS14" t="n">
-        <v>48.07438724376921</v>
+        <v>48.07438721586309</v>
       </c>
       <c r="BT14" t="n">
-        <v>17.32336515922971</v>
+        <v>17.32336501660665</v>
       </c>
       <c r="BU14" t="n">
         <v>29.12385888600579</v>
       </c>
       <c r="BV14" t="n">
-        <v>33.82792698753126</v>
+        <v>33.82792691844993</v>
       </c>
       <c r="BW14" t="n">
-        <v>33.47952776163331</v>
+        <v>33.4795276016176</v>
       </c>
       <c r="BX14" t="n">
-        <v>30.13157498546998</v>
+        <v>30.13157484145584</v>
       </c>
       <c r="BY14" t="n">
         <v>8</v>
@@ -4656,10 +4656,10 @@
         <v>2.9</v>
       </c>
       <c r="CB14" t="n">
-        <v>-9.351463706484974</v>
+        <v>-9.351464139740473</v>
       </c>
       <c r="CC14" t="n">
-        <v>1.768728277307297</v>
+        <v>1.768728069481407</v>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
@@ -4920,10 +4920,10 @@
         <v>14.27999973297119</v>
       </c>
       <c r="BN15" t="n">
-        <v>4.387520844480649</v>
+        <v>4.387520843971235</v>
       </c>
       <c r="BO15" t="n">
-        <v>8.138851166511603</v>
+        <v>8.13885116556664</v>
       </c>
       <c r="BP15" t="n">
         <v>23.74027559120054</v>
@@ -4932,25 +4932,25 @@
         <v>19.99443109682345</v>
       </c>
       <c r="BR15" t="n">
-        <v>28.98387348124873</v>
+        <v>28.98387348164261</v>
       </c>
       <c r="BS15" t="n">
-        <v>16.36200631279058</v>
+        <v>16.36200631289578</v>
       </c>
       <c r="BT15" t="n">
-        <v>18.16044427723578</v>
+        <v>18.16044427804582</v>
       </c>
       <c r="BU15" t="n">
         <v>13.94701359457771</v>
       </c>
       <c r="BV15" t="n">
-        <v>18.47527078862691</v>
+        <v>18.47527078867894</v>
       </c>
       <c r="BW15" t="n">
-        <v>18.16044427723578</v>
+        <v>18.16044427804582</v>
       </c>
       <c r="BX15" t="n">
-        <v>16.3443998495122</v>
+        <v>16.34439985024124</v>
       </c>
       <c r="BY15" t="n">
         <v>7</v>
@@ -4962,10 +4962,10 @@
         <v>6.6</v>
       </c>
       <c r="CB15" t="n">
-        <v>14.45658371949756</v>
+        <v>14.4565837246029</v>
       </c>
       <c r="CC15" t="n">
-        <v>29.37864939849566</v>
+        <v>29.37864939885997</v>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
@@ -5226,10 +5226,10 @@
         <v>16.47999954223633</v>
       </c>
       <c r="BN16" t="n">
-        <v>9.770026178296948</v>
+        <v>9.770026175461824</v>
       </c>
       <c r="BO16" t="n">
-        <v>18.12339856074084</v>
+        <v>18.12339855548168</v>
       </c>
       <c r="BP16" t="n">
         <v>36.09256098093079</v>
@@ -5238,25 +5238,25 @@
         <v>35.53250072181754</v>
       </c>
       <c r="BR16" t="n">
-        <v>40.48255603677045</v>
+        <v>40.48255603544121</v>
       </c>
       <c r="BS16" t="n">
-        <v>32.74874497364594</v>
+        <v>32.74874497423615</v>
       </c>
       <c r="BT16" t="n">
-        <v>18.51211382657749</v>
+        <v>18.51211382986578</v>
       </c>
       <c r="BU16" t="n">
         <v>29.55836540201202</v>
       </c>
       <c r="BV16" t="n">
-        <v>30.1500343574993</v>
+        <v>30.15003435711217</v>
       </c>
       <c r="BW16" t="n">
-        <v>32.74874497364594</v>
+        <v>32.74874497423615</v>
       </c>
       <c r="BX16" t="n">
-        <v>29.47387047628135</v>
+        <v>29.47387047681254</v>
       </c>
       <c r="BY16" t="n">
         <v>7</v>
@@ -5268,10 +5268,10 @@
         <v>4.1</v>
       </c>
       <c r="CB16" t="n">
-        <v>78.84630640154593</v>
+        <v>78.84630640476917</v>
       </c>
       <c r="CC16" t="n">
-        <v>82.94924268795188</v>
+        <v>82.94924268560277</v>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
@@ -5524,10 +5524,10 @@
         <v>9.220000267028809</v>
       </c>
       <c r="BN17" t="n">
-        <v>9.218246638132781</v>
+        <v>9.218246727545807</v>
       </c>
       <c r="BO17" t="n">
-        <v>17.09984751373631</v>
+        <v>17.09984767959747</v>
       </c>
       <c r="BP17" t="n">
         <v>23.49326991117917</v>
@@ -5536,25 +5536,25 @@
         <v>16.88595648327735</v>
       </c>
       <c r="BR17" t="n">
-        <v>36.8331652161761</v>
+        <v>36.83316514520967</v>
       </c>
       <c r="BS17" t="n">
-        <v>23.39513825798915</v>
+        <v>23.39513821947223</v>
       </c>
       <c r="BT17" t="n">
-        <v>12.28881407226837</v>
+        <v>12.28881387634654</v>
       </c>
       <c r="BU17" t="n">
         <v>9.220000267028809</v>
       </c>
       <c r="BV17" t="n">
-        <v>18.5543047949735</v>
+        <v>18.55430478870713</v>
       </c>
       <c r="BW17" t="n">
-        <v>16.99290199850683</v>
+        <v>16.99290208143741</v>
       </c>
       <c r="BX17" t="n">
-        <v>15.29361179865614</v>
+        <v>15.29361187329367</v>
       </c>
       <c r="BY17" t="n">
         <v>8</v>
@@ -5566,10 +5566,10 @@
         <v>4</v>
       </c>
       <c r="CB17" t="n">
-        <v>65.87430971501031</v>
+        <v>65.8743105245279</v>
       </c>
       <c r="CC17" t="n">
-        <v>101.2397424902974</v>
+        <v>101.2397424223324</v>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
@@ -5822,10 +5822,10 @@
         <v>12.02999973297119</v>
       </c>
       <c r="BN18" t="n">
-        <v>3.742665490763264</v>
+        <v>3.742665502032937</v>
       </c>
       <c r="BO18" t="n">
-        <v>6.942644485365855</v>
+        <v>6.942644506271098</v>
       </c>
       <c r="BP18" t="n">
         <v>19.51009748615278</v>
@@ -5834,19 +5834,19 @@
         <v>18.37827919410691</v>
       </c>
       <c r="BR18" t="n">
-        <v>20.08107822067232</v>
+        <v>20.08107821724845</v>
       </c>
       <c r="BS18" t="n">
-        <v>15.55766337248538</v>
+        <v>15.55766337028725</v>
       </c>
       <c r="BT18" t="n">
-        <v>12.52469663668951</v>
+        <v>12.52469662239866</v>
       </c>
       <c r="BU18" t="n">
         <v>26.99032004584218</v>
       </c>
       <c r="BV18" t="n">
-        <v>17.14068277733071</v>
+        <v>17.14068277747247</v>
       </c>
       <c r="BW18" t="n">
         <v>18.37827919410691</v>
@@ -5867,7 +5867,7 @@
         <v>37.49336360634341</v>
       </c>
       <c r="CC18" t="n">
-        <v>42.48281926684023</v>
+        <v>42.48281926801869</v>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>-13.45323695596481</v>
       </c>
       <c r="CP18" t="n">
-        <v>-27.76080595405424</v>
+        <v>-27.7608147027258</v>
       </c>
       <c r="CQ18" t="b">
         <v>1</v>
@@ -6118,10 +6118,10 @@
         <v>3.430000066757202</v>
       </c>
       <c r="BN19" t="n">
-        <v>4.79027427163927</v>
+        <v>4.79027430247879</v>
       </c>
       <c r="BO19" t="n">
-        <v>6.974639339506778</v>
+        <v>6.974639384409119</v>
       </c>
       <c r="BP19" t="n">
         <v>6.618181946989778</v>
@@ -6140,7 +6140,7 @@
         <v>2.330329016381401</v>
       </c>
       <c r="BV19" t="n">
-        <v>5.511348678678725</v>
+        <v>5.511348691302367</v>
       </c>
       <c r="BW19" t="n">
         <v>5.928677058339783</v>
@@ -6161,7 +6161,7 @@
         <v>55.5629518558697</v>
       </c>
       <c r="CC19" t="n">
-        <v>60.68071636771937</v>
+        <v>60.68071673575557</v>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
@@ -6414,10 +6414,10 @@
         <v>20.88999938964844</v>
       </c>
       <c r="BN20" t="n">
-        <v>2.938906067098677</v>
+        <v>2.938906070377924</v>
       </c>
       <c r="BO20" t="n">
-        <v>5.451670754468045</v>
+        <v>5.451670760551048</v>
       </c>
       <c r="BP20" t="n">
         <v>31.74225824688552</v>
@@ -6426,7 +6426,7 @@
         <v>26.44590940575898</v>
       </c>
       <c r="BR20" t="n">
-        <v>40.65305914955367</v>
+        <v>40.65305915481851</v>
       </c>
       <c r="BS20" t="n">
         <v>10.44211857350007</v>
@@ -6688,35 +6688,35 @@
         <v>22.70000076293945</v>
       </c>
       <c r="BN21" t="n">
-        <v>16.28609448199667</v>
+        <v>16.28609456572976</v>
       </c>
       <c r="BO21" t="n">
-        <v>28.49660543684429</v>
+        <v>28.49660542418487</v>
       </c>
       <c r="BP21" t="n">
-        <v>47.12783878381875</v>
+        <v>47.12783852058014</v>
       </c>
       <c r="BQ21" t="n">
         <v>47.60027068070954</v>
       </c>
       <c r="BR21" t="n">
-        <v>58.81912814515054</v>
+        <v>58.81912817517568</v>
       </c>
       <c r="BS21" t="n">
-        <v>30.92711816845054</v>
+        <v>30.92711815565275</v>
       </c>
       <c r="BT21" t="n">
-        <v>23.23843522744946</v>
+        <v>23.23843512392188</v>
       </c>
       <c r="BU21" t="inlineStr"/>
       <c r="BV21" t="n">
-        <v>30.70941421777756</v>
+        <v>30.70941416653688</v>
       </c>
       <c r="BW21" t="n">
-        <v>29.71186180264742</v>
+        <v>29.71186178991881</v>
       </c>
       <c r="BX21" t="n">
-        <v>26.74067562238268</v>
+        <v>26.74067561092693</v>
       </c>
       <c r="BY21" t="n">
         <v>4</v>
@@ -6728,10 +6728,10 @@
         <v>2.9</v>
       </c>
       <c r="CB21" t="n">
-        <v>17.80032917901979</v>
+        <v>17.80032912855394</v>
       </c>
       <c r="CC21" t="n">
-        <v>35.28375852706782</v>
+        <v>35.28375830133794</v>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
@@ -6982,10 +6982,10 @@
         <v>5.889999866485596</v>
       </c>
       <c r="BN22" t="n">
-        <v>6.967484579308371</v>
+        <v>6.96748449039864</v>
       </c>
       <c r="BO22" t="n">
-        <v>10.14465754747299</v>
+        <v>10.14465741802042</v>
       </c>
       <c r="BP22" t="n">
         <v>8.368305821236365</v>
@@ -7004,7 +7004,7 @@
         <v>5.445300917107223</v>
       </c>
       <c r="BV22" t="n">
-        <v>8.112707716463881</v>
+        <v>8.112707680070164</v>
       </c>
       <c r="BW22" t="n">
         <v>8.595393290251712</v>
@@ -7025,7 +7025,7 @@
         <v>31.33877990802598</v>
       </c>
       <c r="CC22" t="n">
-        <v>37.73697623705576</v>
+        <v>37.73697561916583</v>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
@@ -7278,10 +7278,10 @@
         <v>27.1299991607666</v>
       </c>
       <c r="BN23" t="n">
-        <v>7.18252804582947</v>
+        <v>7.182528011456576</v>
       </c>
       <c r="BO23" t="n">
-        <v>13.32358952501367</v>
+        <v>13.32358946125195</v>
       </c>
       <c r="BP23" t="n">
         <v>34.63126097111343</v>
@@ -7290,19 +7290,19 @@
         <v>27.36859865246639</v>
       </c>
       <c r="BR23" t="n">
-        <v>42.68616593673717</v>
+        <v>42.68616598912325</v>
       </c>
       <c r="BS23" t="n">
-        <v>24.66467731664149</v>
+        <v>24.66467732491535</v>
       </c>
       <c r="BT23" t="n">
-        <v>27.72433013137766</v>
+        <v>27.72433019344685</v>
       </c>
       <c r="BU23" t="n">
         <v>22.34091371576103</v>
       </c>
       <c r="BV23" t="n">
-        <v>27.53421946415869</v>
+        <v>27.53421947258261</v>
       </c>
       <c r="BW23" t="n">
         <v>27.36859865246639</v>
@@ -7323,7 +7323,7 @@
         <v>-9.208479361693655</v>
       </c>
       <c r="CC23" t="n">
-        <v>1.489938503118871</v>
+        <v>1.489938534169055</v>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>-6.673548518829275</v>
       </c>
       <c r="CP23" t="n">
-        <v>-23.09690478621134</v>
+        <v>-23.09691313905869</v>
       </c>
       <c r="CQ23" t="b">
         <v>1</v>
@@ -7576,37 +7576,37 @@
         <v>11.01000022888184</v>
       </c>
       <c r="BN24" t="n">
-        <v>9.531702580833194</v>
+        <v>9.531702597764133</v>
       </c>
       <c r="BO24" t="n">
-        <v>17.26678413350498</v>
+        <v>17.26678402871858</v>
       </c>
       <c r="BP24" t="n">
-        <v>20.26492236685869</v>
+        <v>20.26492220788147</v>
       </c>
       <c r="BQ24" t="n">
         <v>11.834803187379</v>
       </c>
       <c r="BR24" t="n">
-        <v>28.09971465547086</v>
+        <v>28.0997145959157</v>
       </c>
       <c r="BS24" t="n">
-        <v>24.03459731543566</v>
+        <v>24.03459730190921</v>
       </c>
       <c r="BT24" t="n">
-        <v>9.914946129319048</v>
+        <v>9.914946070690592</v>
       </c>
       <c r="BU24" t="n">
         <v>8.714817950680764</v>
       </c>
       <c r="BV24" t="n">
-        <v>16.20778603993527</v>
+        <v>16.20778599261743</v>
       </c>
       <c r="BW24" t="n">
-        <v>14.55079366044199</v>
+        <v>14.55079360804879</v>
       </c>
       <c r="BX24" t="n">
-        <v>13.09571429439779</v>
+        <v>13.09571424724391</v>
       </c>
       <c r="BY24" t="n">
         <v>8</v>
@@ -7618,10 +7618,10 @@
         <v>3.2</v>
       </c>
       <c r="CB24" t="n">
-        <v>18.94381491514083</v>
+        <v>18.94381448685854</v>
       </c>
       <c r="CC24" t="n">
-        <v>47.20967940961902</v>
+        <v>47.20967897984756</v>
       </c>
       <c r="CD24" t="inlineStr">
         <is>
@@ -7874,10 +7874,10 @@
         <v>12.86999988555908</v>
       </c>
       <c r="BN25" t="n">
-        <v>8.064609801892797</v>
+        <v>8.064609824522909</v>
       </c>
       <c r="BO25" t="n">
-        <v>14.95985118251114</v>
+        <v>14.95985122449</v>
       </c>
       <c r="BP25" t="n">
         <v>13.49109956358052</v>
@@ -7898,7 +7898,7 @@
         <v>6.379184203562791</v>
       </c>
       <c r="BV25" t="n">
-        <v>14.53079976683148</v>
+        <v>14.5307997749076</v>
       </c>
       <c r="BW25" t="n">
         <v>12.9056367523308</v>
@@ -7919,7 +7919,7 @@
         <v>-9.750791139240512</v>
       </c>
       <c r="CC25" t="n">
-        <v>12.90442809666155</v>
+        <v>12.90442815941308</v>
       </c>
       <c r="CD25" t="inlineStr">
         <is>
@@ -8166,10 +8166,10 @@
         <v>14.72000026702881</v>
       </c>
       <c r="BN26" t="n">
-        <v>9.143015732646591</v>
+        <v>9.143015713300365</v>
       </c>
       <c r="BO26" t="n">
-        <v>16.96029418405942</v>
+        <v>16.96029414817217</v>
       </c>
       <c r="BP26" t="n">
         <v>30.23876023847003</v>
@@ -8178,23 +8178,23 @@
         <v>28.82030174141344</v>
       </c>
       <c r="BR26" t="n">
-        <v>34.00566209630941</v>
+        <v>34.00566209258832</v>
       </c>
       <c r="BS26" t="n">
-        <v>26.56393124579123</v>
+        <v>26.5639312499856</v>
       </c>
       <c r="BT26" t="n">
-        <v>14.99745129912891</v>
+        <v>14.99745132318477</v>
       </c>
       <c r="BU26" t="inlineStr"/>
       <c r="BV26" t="n">
-        <v>20.72650035024182</v>
+        <v>20.72650033748204</v>
       </c>
       <c r="BW26" t="n">
-        <v>21.76211271492533</v>
+        <v>21.76211269907889</v>
       </c>
       <c r="BX26" t="n">
-        <v>19.58590144343279</v>
+        <v>19.585901429171</v>
       </c>
       <c r="BY26" t="n">
         <v>4</v>
@@ -8206,10 +8206,10 @@
         <v>3.3</v>
       </c>
       <c r="CB26" t="n">
-        <v>33.05639326177916</v>
+        <v>33.05639316489199</v>
       </c>
       <c r="CC26" t="n">
-        <v>40.80502699899342</v>
+        <v>40.80502691231016</v>
       </c>
       <c r="CD26" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
         <v>-10.80078673102787</v>
       </c>
       <c r="CP26" t="n">
-        <v>-19.07733209382061</v>
+        <v>-19.07732332684662</v>
       </c>
       <c r="CQ26" t="b">
         <v>1</v>
@@ -8446,10 +8446,10 @@
         <v>37.2599983215332</v>
       </c>
       <c r="BN27" t="n">
-        <v>34.16540997415938</v>
+        <v>34.16540993615371</v>
       </c>
       <c r="BO27" t="n">
-        <v>49.74483692237606</v>
+        <v>49.74483686703981</v>
       </c>
       <c r="BP27" t="n">
         <v>47.95841368118134</v>
@@ -8466,13 +8466,13 @@
       </c>
       <c r="BU27" t="inlineStr"/>
       <c r="BV27" t="n">
-        <v>47.47016034714099</v>
+        <v>47.47016032380552</v>
       </c>
       <c r="BW27" t="n">
-        <v>48.8516253017787</v>
+        <v>48.85162527411057</v>
       </c>
       <c r="BX27" t="n">
-        <v>43.96646277160083</v>
+        <v>43.96646274669952</v>
       </c>
       <c r="BY27" t="n">
         <v>4</v>
@@ -8484,10 +8484,10 @@
         <v>1.7</v>
       </c>
       <c r="CB27" t="n">
-        <v>17.9991002473874</v>
+        <v>17.99910018055619</v>
       </c>
       <c r="CC27" t="n">
-        <v>27.40247580662707</v>
+        <v>27.4024757439983</v>
       </c>
       <c r="CD27" t="inlineStr">
         <is>
@@ -8738,10 +8738,10 @@
         <v>3.690000057220459</v>
       </c>
       <c r="BN28" t="n">
-        <v>0.8537054734197488</v>
+        <v>0.8537054775691739</v>
       </c>
       <c r="BO28" t="n">
-        <v>1.583623653193634</v>
+        <v>1.583623660890817</v>
       </c>
       <c r="BP28" t="n">
         <v>9.978061379218586</v>
@@ -8750,13 +8750,13 @@
         <v>8.953076401677793</v>
       </c>
       <c r="BR28" t="n">
-        <v>12.46813579382274</v>
+        <v>12.46813579648228</v>
       </c>
       <c r="BS28" t="n">
-        <v>4.490296416555022</v>
+        <v>4.490296416071136</v>
       </c>
       <c r="BT28" t="n">
-        <v>8.315677889859598</v>
+        <v>8.315677884079284</v>
       </c>
       <c r="BU28" t="n">
         <v>8.070693304078278</v>
@@ -9026,37 +9026,37 @@
         <v>15.01000022888184</v>
       </c>
       <c r="BN29" t="n">
-        <v>5.822993539681077</v>
+        <v>5.822993549709619</v>
       </c>
       <c r="BO29" t="n">
-        <v>8.112117356420375</v>
+        <v>8.112117348517947</v>
       </c>
       <c r="BP29" t="n">
-        <v>10.07841822041387</v>
+        <v>10.07841819323861</v>
       </c>
       <c r="BQ29" t="n">
         <v>11.19351621134486</v>
       </c>
       <c r="BR29" t="n">
-        <v>9.136669975584569</v>
+        <v>9.136669959224704</v>
       </c>
       <c r="BS29" t="n">
-        <v>14.61973513864618</v>
+        <v>14.61973513504642</v>
       </c>
       <c r="BT29" t="n">
-        <v>4.991079410098848</v>
+        <v>4.991079393860636</v>
       </c>
       <c r="BU29" t="n">
         <v>10.28842080392437</v>
       </c>
       <c r="BV29" t="n">
-        <v>9.28036883201427</v>
+        <v>9.280368824358396</v>
       </c>
       <c r="BW29" t="n">
-        <v>9.607544097999222</v>
+        <v>9.607544076231655</v>
       </c>
       <c r="BX29" t="n">
-        <v>8.6467896881993</v>
+        <v>8.64678966860849</v>
       </c>
       <c r="BY29" t="n">
         <v>8</v>
@@ -9068,10 +9068,10 @@
         <v>2.9</v>
       </c>
       <c r="CB29" t="n">
-        <v>-42.39314086377306</v>
+        <v>-42.39314099429146</v>
       </c>
       <c r="CC29" t="n">
-        <v>-38.17209400065674</v>
+        <v>-38.1720940516619</v>
       </c>
       <c r="CD29" t="inlineStr">
         <is>
@@ -9324,10 +9324,10 @@
         <v>30.59000015258789</v>
       </c>
       <c r="BN30" t="n">
-        <v>3.032359189618023</v>
+        <v>3.03235917937138</v>
       </c>
       <c r="BO30" t="n">
-        <v>5.625026296741432</v>
+        <v>5.625026277733911</v>
       </c>
       <c r="BP30" t="n">
         <v>31.32283632316766</v>
@@ -9336,7 +9336,7 @@
         <v>21.94043581226608</v>
       </c>
       <c r="BR30" t="n">
-        <v>38.74057426147379</v>
+        <v>38.74057425038777</v>
       </c>
       <c r="BS30" t="n">
         <v>16.47675213208347</v>
@@ -9602,35 +9602,35 @@
         <v>12.63000011444092</v>
       </c>
       <c r="BN31" t="n">
-        <v>8.477710191261535</v>
+        <v>8.477710171212845</v>
       </c>
       <c r="BO31" t="n">
-        <v>13.24330365758486</v>
+        <v>13.24330367989931</v>
       </c>
       <c r="BP31" t="n">
-        <v>17.39835030628252</v>
+        <v>17.3983503767429</v>
       </c>
       <c r="BQ31" t="n">
         <v>16.79972907026644</v>
       </c>
       <c r="BR31" t="n">
-        <v>21.86210625973284</v>
+        <v>21.86210627942075</v>
       </c>
       <c r="BS31" t="n">
-        <v>16.6495876920284</v>
+        <v>16.64958769757434</v>
       </c>
       <c r="BT31" t="n">
-        <v>8.696993323725099</v>
+        <v>8.696993357881651</v>
       </c>
       <c r="BU31" t="inlineStr"/>
       <c r="BV31" t="n">
-        <v>13.94223796178933</v>
+        <v>13.94223798135735</v>
       </c>
       <c r="BW31" t="n">
-        <v>14.94644567480663</v>
+        <v>14.94644568873682</v>
       </c>
       <c r="BX31" t="n">
-        <v>13.45180110732597</v>
+        <v>13.45180111986314</v>
       </c>
       <c r="BY31" t="n">
         <v>4</v>
@@ -9642,10 +9642,10 @@
         <v>2.1</v>
       </c>
       <c r="CB31" t="n">
-        <v>6.506737810282504</v>
+        <v>6.506737909547522</v>
       </c>
       <c r="CC31" t="n">
-        <v>10.38984826174325</v>
+        <v>10.3898484166761</v>
       </c>
       <c r="CD31" t="inlineStr">
         <is>
@@ -9898,10 +9898,10 @@
         <v>8.350000381469727</v>
       </c>
       <c r="BN32" t="n">
-        <v>2.27517043785061</v>
+        <v>2.275170444003772</v>
       </c>
       <c r="BO32" t="n">
-        <v>4.220441162212881</v>
+        <v>4.220441173626996</v>
       </c>
       <c r="BP32" t="n">
         <v>13.45955049324499</v>
@@ -9910,19 +9910,19 @@
         <v>14.81092624645154</v>
       </c>
       <c r="BR32" t="n">
-        <v>11.28719235012451</v>
+        <v>11.28719235144721</v>
       </c>
       <c r="BS32" t="n">
-        <v>7.403635149020883</v>
+        <v>7.403635148398864</v>
       </c>
       <c r="BT32" t="n">
-        <v>7.37277860759801</v>
+        <v>7.372778601842098</v>
       </c>
       <c r="BU32" t="n">
         <v>9.952965903815388</v>
       </c>
       <c r="BV32" t="n">
-        <v>9.786784273209744</v>
+        <v>9.786784274118157</v>
       </c>
       <c r="BW32" t="n">
         <v>9.952965903815388</v>
@@ -9943,7 +9943,7 @@
         <v>7.277471906620003</v>
       </c>
       <c r="CC32" t="n">
-        <v>17.20699192934794</v>
+        <v>17.20699194022712</v>
       </c>
       <c r="CD32" t="inlineStr">
         <is>
@@ -10194,10 +10194,10 @@
         <v>10.39999961853027</v>
       </c>
       <c r="BN33" t="n">
-        <v>12.94492616447744</v>
+        <v>12.94492638520225</v>
       </c>
       <c r="BO33" t="n">
-        <v>18.84781249547915</v>
+        <v>18.84781281685448</v>
       </c>
       <c r="BP33" t="n">
         <v>17.11392342289792</v>
@@ -10216,7 +10216,7 @@
         <v>15.58796560981411</v>
       </c>
       <c r="BV33" t="n">
-        <v>16.31747695366762</v>
+        <v>16.31747704401764</v>
       </c>
       <c r="BW33" t="n">
         <v>16.35094451635601</v>
@@ -10237,7 +10237,7 @@
         <v>41.49856350475572</v>
       </c>
       <c r="CC33" t="n">
-        <v>56.89882261720316</v>
+        <v>56.89882348595343</v>
       </c>
       <c r="CD33" t="inlineStr">
         <is>
@@ -10488,10 +10488,10 @@
         <v>32.40000152587891</v>
       </c>
       <c r="BN34" t="n">
-        <v>8.926844974578826</v>
+        <v>8.926845001173641</v>
       </c>
       <c r="BO34" t="n">
-        <v>16.55929742784372</v>
+        <v>16.5592974771771</v>
       </c>
       <c r="BP34" t="n">
         <v>61.76978708171158</v>
@@ -10500,7 +10500,7 @@
         <v>36.01581457783751</v>
       </c>
       <c r="BR34" t="n">
-        <v>87.91019460896219</v>
+        <v>87.91019466253447</v>
       </c>
       <c r="BS34" t="n">
         <v>22.23751954027694</v>
@@ -10762,35 +10762,35 @@
         <v>16.79000091552734</v>
       </c>
       <c r="BN35" t="n">
-        <v>9.983952032237859</v>
+        <v>9.983951970710299</v>
       </c>
       <c r="BO35" t="n">
-        <v>17.31362328721972</v>
+        <v>17.31362329759388</v>
       </c>
       <c r="BP35" t="n">
-        <v>28.29572481055279</v>
+        <v>28.29572500188385</v>
       </c>
       <c r="BQ35" t="n">
         <v>28.80591266774053</v>
       </c>
       <c r="BR35" t="n">
-        <v>31.54471770720549</v>
+        <v>31.54471771172395</v>
       </c>
       <c r="BS35" t="n">
-        <v>29.07473906678766</v>
+        <v>29.07473908147372</v>
       </c>
       <c r="BT35" t="n">
-        <v>13.97702123587045</v>
+        <v>13.97702131237628</v>
       </c>
       <c r="BU35" t="inlineStr"/>
       <c r="BV35" t="n">
-        <v>21.16700979919951</v>
+        <v>21.16700983791544</v>
       </c>
       <c r="BW35" t="n">
-        <v>22.80467404888626</v>
+        <v>22.80467414973887</v>
       </c>
       <c r="BX35" t="n">
-        <v>20.52420664399763</v>
+        <v>20.52420673476498</v>
       </c>
       <c r="BY35" t="n">
         <v>4</v>
@@ -10802,10 +10802,10 @@
         <v>2.9</v>
       </c>
       <c r="CB35" t="n">
-        <v>22.24065232192398</v>
+        <v>22.24065286252756</v>
       </c>
       <c r="CC35" t="n">
-        <v>26.06914023229336</v>
+        <v>26.06914046288258</v>
       </c>
       <c r="CD35" t="inlineStr">
         <is>
@@ -11058,10 +11058,10 @@
         <v>4.25</v>
       </c>
       <c r="BN36" t="n">
-        <v>2.756777606664025</v>
+        <v>2.756777600458519</v>
       </c>
       <c r="BO36" t="n">
-        <v>5.113822460361766</v>
+        <v>5.113822448850553</v>
       </c>
       <c r="BP36" t="n">
         <v>13.83599508599508</v>
@@ -11070,25 +11070,25 @@
         <v>14.73343694068134</v>
       </c>
       <c r="BR36" t="n">
-        <v>16.86864304584438</v>
+        <v>16.86864303424626</v>
       </c>
       <c r="BS36" t="n">
-        <v>8.105886946965924</v>
+        <v>8.105886947672605</v>
       </c>
       <c r="BT36" t="n">
-        <v>7.432122116338263</v>
+        <v>7.432122122465331</v>
       </c>
       <c r="BU36" t="n">
         <v>3.276499576963653</v>
       </c>
       <c r="BV36" t="n">
-        <v>9.909486596164346</v>
+        <v>9.909486593839262</v>
       </c>
       <c r="BW36" t="n">
-        <v>8.105886946965924</v>
+        <v>8.105886947672605</v>
       </c>
       <c r="BX36" t="n">
-        <v>7.295298252269332</v>
+        <v>7.295298252905345</v>
       </c>
       <c r="BY36" t="n">
         <v>7</v>
@@ -11100,10 +11100,10 @@
         <v>6.1</v>
       </c>
       <c r="CB36" t="n">
-        <v>71.6540765239843</v>
+        <v>71.65407653894928</v>
       </c>
       <c r="CC36" t="n">
-        <v>133.1643904979846</v>
+        <v>133.1643904432767</v>
       </c>
       <c r="CD36" t="inlineStr">
         <is>
@@ -11342,10 +11342,10 @@
         <v>29.52000045776367</v>
       </c>
       <c r="BN37" t="n">
-        <v>15.43188315690255</v>
+        <v>15.43188318623062</v>
       </c>
       <c r="BO37" t="n">
-        <v>28.62614325605423</v>
+        <v>28.6261433104578</v>
       </c>
       <c r="BP37" t="n">
         <v>55.24576356855489</v>
@@ -11354,23 +11354,23 @@
         <v>49.94931085633525</v>
       </c>
       <c r="BR37" t="n">
-        <v>62.03667169751222</v>
+        <v>62.03667169108353</v>
       </c>
       <c r="BS37" t="n">
-        <v>38.72993677943371</v>
+        <v>38.72993684747589</v>
       </c>
       <c r="BT37" t="n">
-        <v>30.95210659434795</v>
+        <v>30.95210655385409</v>
       </c>
       <c r="BU37" t="inlineStr"/>
       <c r="BV37" t="n">
-        <v>34.50843169023634</v>
+        <v>34.5084317281798</v>
       </c>
       <c r="BW37" t="n">
-        <v>33.67804001774397</v>
+        <v>33.67804007896684</v>
       </c>
       <c r="BX37" t="n">
-        <v>30.31023601596957</v>
+        <v>30.31023607107016</v>
       </c>
       <c r="BY37" t="n">
         <v>4</v>
@@ -11382,10 +11382,10 @@
         <v>3.6</v>
       </c>
       <c r="CB37" t="n">
-        <v>2.676949681408525</v>
+        <v>2.676949868063638</v>
       </c>
       <c r="CC37" t="n">
-        <v>16.89847952275601</v>
+        <v>16.89847965129074</v>
       </c>
       <c r="CD37" t="inlineStr">
         <is>
@@ -11646,37 +11646,37 @@
         <v>10.39999961853027</v>
       </c>
       <c r="BN38" t="n">
-        <v>7.249464452720715</v>
+        <v>7.24946445445088</v>
       </c>
       <c r="BO38" t="n">
-        <v>10.94542261598734</v>
+        <v>10.94542261655361</v>
       </c>
       <c r="BP38" t="n">
-        <v>17.77471060719179</v>
+        <v>17.77471060386925</v>
       </c>
       <c r="BQ38" t="n">
         <v>23.30669690919295</v>
       </c>
       <c r="BR38" t="n">
-        <v>23.2148123893049</v>
+        <v>23.21481239041619</v>
       </c>
       <c r="BS38" t="n">
-        <v>20.50961401256914</v>
+        <v>20.50961401224382</v>
       </c>
       <c r="BT38" t="n">
-        <v>8.88496793650852</v>
+        <v>8.884967934794133</v>
       </c>
       <c r="BU38" t="n">
         <v>9.960670392837367</v>
       </c>
       <c r="BV38" t="n">
-        <v>15.23079491453909</v>
+        <v>15.23079491429477</v>
       </c>
       <c r="BW38" t="n">
-        <v>14.36006661158956</v>
+        <v>14.36006661021143</v>
       </c>
       <c r="BX38" t="n">
-        <v>12.92405995043061</v>
+        <v>12.92405994919029</v>
       </c>
       <c r="BY38" t="n">
         <v>8</v>
@@ -11688,10 +11688,10 @@
         <v>3.2</v>
       </c>
       <c r="CB38" t="n">
-        <v>24.26981177386842</v>
+        <v>24.26981176194229</v>
       </c>
       <c r="CC38" t="n">
-        <v>46.44995647308978</v>
+        <v>46.4499564707406</v>
       </c>
       <c r="CD38" t="inlineStr">
         <is>
@@ -11930,10 +11930,10 @@
         <v>39</v>
       </c>
       <c r="BN39" t="n">
-        <v>19.93010989560153</v>
+        <v>19.93010991987252</v>
       </c>
       <c r="BO39" t="n">
-        <v>36.97035385634084</v>
+        <v>36.97035390136352</v>
       </c>
       <c r="BP39" t="n">
         <v>54.05334728033472</v>
@@ -11942,23 +11942,23 @@
         <v>40.80446518102817</v>
       </c>
       <c r="BR39" t="n">
-        <v>58.13074603519775</v>
+        <v>58.13074599445734</v>
       </c>
       <c r="BS39" t="n">
-        <v>43.72434340527661</v>
+        <v>43.72434339764214</v>
       </c>
       <c r="BT39" t="n">
-        <v>29.09170549395553</v>
+        <v>29.09170544600577</v>
       </c>
       <c r="BU39" t="inlineStr"/>
       <c r="BV39" t="n">
-        <v>38.66953860938843</v>
+        <v>38.66953862480322</v>
       </c>
       <c r="BW39" t="n">
-        <v>40.34734863080872</v>
+        <v>40.34734864950283</v>
       </c>
       <c r="BX39" t="n">
-        <v>36.31261376772785</v>
+        <v>36.31261378455255</v>
       </c>
       <c r="BY39" t="n">
         <v>4</v>
@@ -11970,10 +11970,10 @@
         <v>2.7</v>
       </c>
       <c r="CB39" t="n">
-        <v>-6.890733928902937</v>
+        <v>-6.890733885762678</v>
       </c>
       <c r="CC39" t="n">
-        <v>-0.8473368990040364</v>
+        <v>-0.8473368594789088</v>
       </c>
       <c r="CD39" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>-9.659481922204559</v>
       </c>
       <c r="CP39" t="n">
-        <v>-19.91624499385604</v>
+        <v>-19.91623237135492</v>
       </c>
       <c r="CQ39" t="b">
         <v>1</v>
@@ -12224,10 +12224,10 @@
         <v>5.570000171661377</v>
       </c>
       <c r="BN40" t="n">
-        <v>6.611145498583777</v>
+        <v>6.611145418783511</v>
       </c>
       <c r="BO40" t="n">
-        <v>9.625827845937978</v>
+        <v>9.625827729748794</v>
       </c>
       <c r="BP40" t="n">
         <v>4.355488856035963</v>
@@ -12518,37 +12518,37 @@
         <v>43.65000152587891</v>
       </c>
       <c r="BN41" t="n">
-        <v>31.67320334287897</v>
+        <v>31.67320332508118</v>
       </c>
       <c r="BO41" t="n">
-        <v>38.85442818377845</v>
+        <v>38.85442820651731</v>
       </c>
       <c r="BP41" t="n">
-        <v>43.07167831742562</v>
+        <v>43.07167836683539</v>
       </c>
       <c r="BQ41" t="n">
         <v>47.83302112955008</v>
       </c>
       <c r="BR41" t="n">
-        <v>61.35148253200276</v>
+        <v>61.3514825630461</v>
       </c>
       <c r="BS41" t="n">
-        <v>55.87396022701227</v>
+        <v>55.87396023357789</v>
       </c>
       <c r="BT41" t="n">
-        <v>20.30744575455281</v>
+        <v>20.30744579170323</v>
       </c>
       <c r="BU41" t="n">
         <v>76.39578733574842</v>
       </c>
       <c r="BV41" t="n">
-        <v>46.92012585286868</v>
+        <v>46.92012586900745</v>
       </c>
       <c r="BW41" t="n">
-        <v>45.45234972348785</v>
+        <v>45.45234974819273</v>
       </c>
       <c r="BX41" t="n">
-        <v>40.90711475113906</v>
+        <v>40.90711477337346</v>
       </c>
       <c r="BY41" t="n">
         <v>8</v>
@@ -12560,10 +12560,10 @@
         <v>3.8</v>
       </c>
       <c r="CB41" t="n">
-        <v>-6.283818279166975</v>
+        <v>-6.283818228229077</v>
       </c>
       <c r="CC41" t="n">
-        <v>7.491693499829566</v>
+        <v>7.491693536802679</v>
       </c>
       <c r="CD41" t="inlineStr">
         <is>
@@ -12816,10 +12816,10 @@
         <v>25.98999977111816</v>
       </c>
       <c r="BN42" t="n">
-        <v>4.764912414817951</v>
+        <v>4.764912412684581</v>
       </c>
       <c r="BO42" t="n">
-        <v>8.838912529487299</v>
+        <v>8.838912525529899</v>
       </c>
       <c r="BP42" t="n">
         <v>32.12383367232422</v>
@@ -12828,13 +12828,13 @@
         <v>25.73909396655281</v>
       </c>
       <c r="BR42" t="n">
-        <v>41.31716358302893</v>
+        <v>41.31716358620729</v>
       </c>
       <c r="BS42" t="n">
-        <v>12.18233647700617</v>
+        <v>12.18233647726798</v>
       </c>
       <c r="BT42" t="n">
-        <v>28.53601229812676</v>
+        <v>28.53601230187587</v>
       </c>
       <c r="BU42" t="n">
         <v>25.98999977111816</v>
@@ -13104,10 +13104,10 @@
         <v>47.36000061035156</v>
       </c>
       <c r="BN43" t="n">
-        <v>7.883046079194521</v>
+        <v>7.883046070219398</v>
       </c>
       <c r="BO43" t="n">
-        <v>14.62305047690583</v>
+        <v>14.62305046025698</v>
       </c>
       <c r="BP43" t="n">
         <v>19.62840187948571</v>
@@ -13116,25 +13116,25 @@
         <v>12.20333989274278</v>
       </c>
       <c r="BR43" t="n">
-        <v>15.97866916371092</v>
+        <v>15.97866920144672</v>
       </c>
       <c r="BS43" t="n">
-        <v>20.76704644318677</v>
+        <v>20.76704644857238</v>
       </c>
       <c r="BT43" t="n">
-        <v>11.83128739825765</v>
+        <v>11.83128742444777</v>
       </c>
       <c r="BU43" t="n">
         <v>12.691038728625</v>
       </c>
       <c r="BV43" t="n">
-        <v>14.45073500776365</v>
+        <v>14.45073501322459</v>
       </c>
       <c r="BW43" t="n">
-        <v>13.65704460276542</v>
+        <v>13.65704459444099</v>
       </c>
       <c r="BX43" t="n">
-        <v>12.29134014248888</v>
+        <v>12.29134013499689</v>
       </c>
       <c r="BY43" t="n">
         <v>8</v>
@@ -13146,10 +13146,10 @@
         <v>2.6</v>
       </c>
       <c r="CB43" t="n">
-        <v>-74.04700172279487</v>
+        <v>-74.0470017386141</v>
       </c>
       <c r="CC43" t="n">
-        <v>-69.48746870453984</v>
+        <v>-69.48746869300912</v>
       </c>
       <c r="CD43" t="inlineStr">
         <is>
@@ -13200,7 +13200,7 @@
         <v>-3.681101537516229</v>
       </c>
       <c r="CP43" t="n">
-        <v>-12.75737983983745</v>
+        <v>-12.75737357829422</v>
       </c>
       <c r="CQ43" t="b">
         <v>1</v>
@@ -13920,10 +13920,10 @@
         <v>10.27999973297119</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.806939245491056</v>
+        <v>5.806939284342563</v>
       </c>
       <c r="BO2" t="n">
-        <v>10.77187230038591</v>
+        <v>10.77187237245545</v>
       </c>
       <c r="BP2" t="n">
         <v>35.84473591101796</v>
@@ -13932,7 +13932,7 @@
         <v>24.64756109389902</v>
       </c>
       <c r="BR2" t="n">
-        <v>61.97293300827438</v>
+        <v>61.97293315141151</v>
       </c>
       <c r="BS2" t="n">
         <v>17.08511007767805</v>
@@ -14206,10 +14206,10 @@
         <v>12.30000019073486</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.1808424152165332</v>
+        <v>0.1808424152373775</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.3354626802266691</v>
+        <v>0.3354626802653352</v>
       </c>
       <c r="BP3" t="n">
         <v>95.30701902177597</v>
@@ -14221,7 +14221,7 @@
         <v>215.7894770304362</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.4852604808310308</v>
+        <v>0.4852604808869629</v>
       </c>
       <c r="BT3" t="n">
         <v>87.03508906894261</v>
@@ -14490,10 +14490,10 @@
         <v>4.039999961853027</v>
       </c>
       <c r="BN4" t="n">
-        <v>3.419461678271012</v>
+        <v>3.419461662610363</v>
       </c>
       <c r="BO4" t="n">
-        <v>6.343101413192727</v>
+        <v>6.343101384142222</v>
       </c>
       <c r="BP4" t="n">
         <v>12.47785536003557</v>
@@ -14502,25 +14502,25 @@
         <v>8.411070803097941</v>
       </c>
       <c r="BR4" t="n">
-        <v>24.27125083577009</v>
+        <v>24.27125084675442</v>
       </c>
       <c r="BS4" t="n">
-        <v>11.09291018811865</v>
+        <v>11.09291019453871</v>
       </c>
       <c r="BT4" t="n">
-        <v>10.75768533736775</v>
+        <v>10.75768537639659</v>
       </c>
       <c r="BU4" t="n">
         <v>4.904734709731053</v>
       </c>
       <c r="BV4" t="n">
-        <v>8.997892968590614</v>
+        <v>8.997892971323681</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.584378070232844</v>
+        <v>9.584378089747268</v>
       </c>
       <c r="BX4" t="n">
-        <v>8.625940263209561</v>
+        <v>8.625940280772541</v>
       </c>
       <c r="BY4" t="n">
         <v>6</v>
@@ -14532,10 +14532,10 @@
         <v>7.1</v>
       </c>
       <c r="CB4" t="n">
-        <v>113.5133748677834</v>
+        <v>113.5133753025106</v>
       </c>
       <c r="CC4" t="n">
-        <v>122.7201250879109</v>
+        <v>122.720125155561</v>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
@@ -14788,10 +14788,10 @@
         <v>23.79999923706055</v>
       </c>
       <c r="BN5" t="n">
-        <v>15.67084916591658</v>
+        <v>15.67084917279736</v>
       </c>
       <c r="BO5" t="n">
-        <v>29.06942520277526</v>
+        <v>29.06942521553909</v>
       </c>
       <c r="BP5" t="n">
         <v>62.32213238953601</v>
@@ -14800,19 +14800,19 @@
         <v>45.62472487613315</v>
       </c>
       <c r="BR5" t="n">
-        <v>103.4137246946409</v>
+        <v>103.4137246906267</v>
       </c>
       <c r="BS5" t="n">
-        <v>20.19414446422667</v>
+        <v>20.19414446334902</v>
       </c>
       <c r="BT5" t="n">
-        <v>50.31447893037993</v>
+        <v>50.31447891589011</v>
       </c>
       <c r="BU5" t="n">
         <v>37.19489833875116</v>
       </c>
       <c r="BV5" t="n">
-        <v>49.73336127092045</v>
+        <v>49.73336126997503</v>
       </c>
       <c r="BW5" t="n">
         <v>45.62472487613315</v>
@@ -14833,7 +14833,7 @@
         <v>72.53047775135681</v>
       </c>
       <c r="CC5" t="n">
-        <v>108.9637095175925</v>
+        <v>108.9637095136202</v>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
@@ -15086,10 +15086,10 @@
         <v>13.63000011444092</v>
       </c>
       <c r="BN6" t="n">
-        <v>15.04788536135715</v>
+        <v>15.04788548267626</v>
       </c>
       <c r="BO6" t="n">
-        <v>27.91382734531751</v>
+        <v>27.91382757036445</v>
       </c>
       <c r="BP6" t="n">
         <v>37.94065157906348</v>
@@ -15098,25 +15098,25 @@
         <v>22.93112736979142</v>
       </c>
       <c r="BR6" t="n">
-        <v>70.78984165015041</v>
+        <v>70.78984141148864</v>
       </c>
       <c r="BS6" t="n">
-        <v>45.2936981338215</v>
+        <v>45.29369804761603</v>
       </c>
       <c r="BT6" t="n">
-        <v>24.32634175873935</v>
+        <v>24.32634138443595</v>
       </c>
       <c r="BU6" t="n">
         <v>8.909513594966207</v>
       </c>
       <c r="BV6" t="n">
-        <v>28.90892192468174</v>
+        <v>28.90892190565793</v>
       </c>
       <c r="BW6" t="n">
-        <v>26.12008455202843</v>
+        <v>26.1200844774002</v>
       </c>
       <c r="BX6" t="n">
-        <v>23.50807609682559</v>
+        <v>23.50807602966018</v>
       </c>
       <c r="BY6" t="n">
         <v>6</v>
@@ -15128,10 +15128,10 @@
         <v>7.9</v>
       </c>
       <c r="CB6" t="n">
-        <v>72.47304401647727</v>
+        <v>72.47304352370101</v>
       </c>
       <c r="CC6" t="n">
-        <v>112.0977379453788</v>
+        <v>112.0977378058058</v>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
@@ -15574,10 +15574,10 @@
         <v>4.320000171661377</v>
       </c>
       <c r="BN8" t="n">
-        <v>2.922596179279397</v>
+        <v>2.92259619629234</v>
       </c>
       <c r="BO8" t="n">
-        <v>5.421415912563281</v>
+        <v>5.421415944122291</v>
       </c>
       <c r="BP8" t="n">
         <v>12.47058873083077</v>
@@ -15586,7 +15586,7 @@
         <v>8.38874521704944</v>
       </c>
       <c r="BR8" t="n">
-        <v>23.03188433220745</v>
+        <v>23.03188438409878</v>
       </c>
       <c r="BS8" t="n">
         <v>11.34817472758152</v>
@@ -15598,7 +15598,7 @@
         <v>4.921612750118176</v>
       </c>
       <c r="BV8" t="n">
-        <v>10.99580820242801</v>
+        <v>10.99580821434949</v>
       </c>
       <c r="BW8" t="n">
         <v>11.34817472758152</v>
@@ -15619,7 +15619,7 @@
         <v>136.4202974301165</v>
       </c>
       <c r="CC8" t="n">
-        <v>154.53258716421</v>
+        <v>154.5325874401701</v>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
@@ -15872,10 +15872,10 @@
         <v>15.56999969482422</v>
       </c>
       <c r="BN9" t="n">
-        <v>6.370378857060131</v>
+        <v>6.37037883656561</v>
       </c>
       <c r="BO9" t="n">
-        <v>11.81705277984654</v>
+        <v>11.81705274182921</v>
       </c>
       <c r="BP9" t="n">
         <v>25.22035402890231</v>
@@ -15884,19 +15884,19 @@
         <v>18.49208604587491</v>
       </c>
       <c r="BR9" t="n">
-        <v>34.98832835169073</v>
+        <v>34.98832838493097</v>
       </c>
       <c r="BS9" t="n">
-        <v>12.44970856183109</v>
+        <v>12.44970856579755</v>
       </c>
       <c r="BT9" t="n">
-        <v>20.22430266734827</v>
+        <v>20.22430271029003</v>
       </c>
       <c r="BU9" t="n">
         <v>17.52538993234214</v>
       </c>
       <c r="BV9" t="n">
-        <v>20.10246033826229</v>
+        <v>20.10246034428101</v>
       </c>
       <c r="BW9" t="n">
         <v>18.49208604587491</v>
@@ -15917,7 +15917,7 @@
         <v>6.890672880487236</v>
       </c>
       <c r="CC9" t="n">
-        <v>29.11021664916762</v>
+        <v>29.11021668782354</v>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
@@ -16156,10 +16156,10 @@
         <v>48.38999938964844</v>
       </c>
       <c r="BN10" t="n">
-        <v>18.43110919828188</v>
+        <v>18.43110925157252</v>
       </c>
       <c r="BO10" t="n">
-        <v>34.18970756281288</v>
+        <v>34.18970766166702</v>
       </c>
       <c r="BP10" t="n">
         <v>73.52838210009652</v>
@@ -16168,23 +16168,23 @@
         <v>55.10133168995815</v>
       </c>
       <c r="BR10" t="n">
-        <v>97.40219839678448</v>
+        <v>97.40219831194068</v>
       </c>
       <c r="BS10" t="n">
-        <v>47.18970513584031</v>
+        <v>47.18970512292769</v>
       </c>
       <c r="BT10" t="n">
-        <v>57.4486272945624</v>
+        <v>57.44862718745247</v>
       </c>
       <c r="BU10" t="inlineStr"/>
       <c r="BV10" t="n">
-        <v>43.3347259992579</v>
+        <v>43.33472603406594</v>
       </c>
       <c r="BW10" t="n">
-        <v>40.6897063493266</v>
+        <v>40.68970639229735</v>
       </c>
       <c r="BX10" t="n">
-        <v>36.62073571439394</v>
+        <v>36.62073575306762</v>
       </c>
       <c r="BY10" t="n">
         <v>4</v>
@@ -16196,10 +16196,10 @@
         <v>4</v>
       </c>
       <c r="CB10" t="n">
-        <v>-24.32168593449533</v>
+        <v>-24.32168585457451</v>
       </c>
       <c r="CC10" t="n">
-        <v>-10.44693832228475</v>
+        <v>-10.44693825035246</v>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
@@ -16438,10 +16438,10 @@
         <v>18.45000076293945</v>
       </c>
       <c r="BN11" t="n">
-        <v>12.68429995798505</v>
+        <v>12.68429994572237</v>
       </c>
       <c r="BO11" t="n">
-        <v>23.52937642206226</v>
+        <v>23.529376399315</v>
       </c>
       <c r="BP11" t="n">
         <v>19.46357564561686</v>
@@ -16450,7 +16450,7 @@
         <v>12.1658993674517</v>
       </c>
       <c r="BR11" t="n">
-        <v>32.94109945680061</v>
+        <v>32.94109944313202</v>
       </c>
       <c r="BS11" t="n">
         <v>22.27593117185458</v>
@@ -16460,7 +16460,7 @@
       </c>
       <c r="BU11" t="inlineStr"/>
       <c r="BV11" t="n">
-        <v>19.48829579937969</v>
+        <v>19.4882957906272</v>
       </c>
       <c r="BW11" t="n">
         <v>20.86975340873572</v>
@@ -16481,7 +16481,7 @@
         <v>1.80367095480638</v>
       </c>
       <c r="CC11" t="n">
-        <v>5.627615140948161</v>
+        <v>5.62761509350922</v>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
@@ -16734,10 +16734,10 @@
         <v>31.39999961853027</v>
       </c>
       <c r="BN12" t="n">
-        <v>43.84701151402275</v>
+        <v>43.84701139465804</v>
       </c>
       <c r="BO12" t="n">
-        <v>81.33620635851219</v>
+        <v>81.33620613709066</v>
       </c>
       <c r="BP12" t="n">
         <v>63.4222553270619</v>
@@ -16758,7 +16758,7 @@
         <v>25.86511310728236</v>
       </c>
       <c r="BV12" t="n">
-        <v>67.06923452579125</v>
+        <v>67.06923448319296</v>
       </c>
       <c r="BW12" t="n">
         <v>60.66996877513281</v>
@@ -16779,7 +16779,7 @@
         <v>73.89481707317074</v>
       </c>
       <c r="CC12" t="n">
-        <v>113.5962908936192</v>
+        <v>113.5962907579559</v>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
@@ -17032,10 +17032,10 @@
         <v>31.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>22.1030031867634</v>
+        <v>22.10300327913806</v>
       </c>
       <c r="BO13" t="n">
-        <v>41.00107091144611</v>
+        <v>41.0010710828011</v>
       </c>
       <c r="BP13" t="n">
         <v>45.51526717557251</v>
@@ -17044,25 +17044,25 @@
         <v>19.62721165712462</v>
       </c>
       <c r="BR13" t="n">
-        <v>57.2358983095674</v>
+        <v>57.23589755890481</v>
       </c>
       <c r="BS13" t="n">
-        <v>49.59879628771473</v>
+        <v>49.59879616720629</v>
       </c>
       <c r="BT13" t="n">
-        <v>23.9423434910391</v>
+        <v>23.94234293054661</v>
       </c>
       <c r="BU13" t="n">
         <v>23.78189287402351</v>
       </c>
       <c r="BV13" t="n">
-        <v>35.35068548665642</v>
+        <v>35.35068534066469</v>
       </c>
       <c r="BW13" t="n">
-        <v>32.47170720124261</v>
+        <v>32.47170700667385</v>
       </c>
       <c r="BX13" t="n">
-        <v>29.22453648111835</v>
+        <v>29.22453630600647</v>
       </c>
       <c r="BY13" t="n">
         <v>8</v>
@@ -17074,10 +17074,10 @@
         <v>2.9</v>
       </c>
       <c r="CB13" t="n">
-        <v>-7.223693710735402</v>
+        <v>-7.223694266646142</v>
       </c>
       <c r="CC13" t="n">
-        <v>12.22439837033786</v>
+        <v>12.22439790687202</v>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
@@ -17330,10 +17330,10 @@
         <v>6.510000228881836</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.939313004811351</v>
+        <v>2.93931301034954</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.452425623925055</v>
+        <v>5.452425634198397</v>
       </c>
       <c r="BP14" t="n">
         <v>21.245690402139</v>
@@ -17342,7 +17342,7 @@
         <v>13.54578759251334</v>
       </c>
       <c r="BR14" t="n">
-        <v>34.18728706910997</v>
+        <v>34.18728708820717</v>
       </c>
       <c r="BS14" t="n">
         <v>11.55192114631721</v>
@@ -17620,10 +17620,10 @@
         <v>41.65999984741211</v>
       </c>
       <c r="BN15" t="n">
-        <v>116.382891782211</v>
+        <v>116.3828916007254</v>
       </c>
       <c r="BO15" t="n">
-        <v>215.8902642560014</v>
+        <v>215.8902639193455</v>
       </c>
       <c r="BP15" t="n">
         <v>135.2928916613261</v>
@@ -17644,7 +17644,7 @@
         <v>63.51616176610359</v>
       </c>
       <c r="BV15" t="n">
-        <v>156.0869282737626</v>
+        <v>156.0869282089949</v>
       </c>
       <c r="BW15" t="n">
         <v>129.4216907024384</v>
@@ -17665,7 +17665,7 @@
         <v>179.5955882352941</v>
       </c>
       <c r="CC15" t="n">
-        <v>274.6685762012999</v>
+        <v>274.6685760458325</v>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
@@ -17914,10 +17914,10 @@
         <v>7.139999866485596</v>
       </c>
       <c r="BN16" t="n">
-        <v>6.680633730099554</v>
+        <v>6.680633769287853</v>
       </c>
       <c r="BO16" t="n">
-        <v>12.39257556933467</v>
+        <v>12.39257564202897</v>
       </c>
       <c r="BP16" t="n">
         <v>39.58368126817327</v>
@@ -17926,7 +17926,7 @@
         <v>26.56660483450646</v>
       </c>
       <c r="BR16" t="n">
-        <v>83.94513398271033</v>
+        <v>83.94513421226523</v>
       </c>
       <c r="BS16" t="n">
         <v>50.65010714487485</v>
@@ -18184,10 +18184,10 @@
         <v>13.14000034332275</v>
       </c>
       <c r="BN17" t="n">
-        <v>9.532624410650243</v>
+        <v>9.532624430413199</v>
       </c>
       <c r="BO17" t="n">
-        <v>17.6830182817562</v>
+        <v>17.68301831841648</v>
       </c>
       <c r="BP17" t="n">
         <v>49.32153103371855</v>
@@ -18196,23 +18196,23 @@
         <v>47.39158599337461</v>
       </c>
       <c r="BR17" t="n">
-        <v>71.21193626334824</v>
+        <v>71.21193630302051</v>
       </c>
       <c r="BS17" t="n">
-        <v>31.70486910412532</v>
+        <v>31.70486910109994</v>
       </c>
       <c r="BT17" t="n">
-        <v>30.94181047213296</v>
+        <v>30.94181044780239</v>
       </c>
       <c r="BU17" t="inlineStr"/>
       <c r="BV17" t="n">
-        <v>32.90313947320002</v>
+        <v>32.90313948441166</v>
       </c>
       <c r="BW17" t="n">
-        <v>31.70486910412532</v>
+        <v>31.70486910109994</v>
       </c>
       <c r="BX17" t="n">
-        <v>28.53438219371279</v>
+        <v>28.53438219098994</v>
       </c>
       <c r="BY17" t="n">
         <v>3</v>
@@ -18224,10 +18224,10 @@
         <v>5.2</v>
       </c>
       <c r="CB17" t="n">
-        <v>117.1566320256062</v>
+        <v>117.1566320048844</v>
       </c>
       <c r="CC17" t="n">
-        <v>150.4044034513298</v>
+        <v>150.4044035366543</v>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
@@ -18482,10 +18482,10 @@
         <v>46.52999877929688</v>
       </c>
       <c r="BN18" t="n">
-        <v>123.6452424291906</v>
+        <v>123.6452412140183</v>
       </c>
       <c r="BO18" t="n">
-        <v>229.3619247061486</v>
+        <v>229.3619224520039</v>
       </c>
       <c r="BP18" t="n">
         <v>135.2022990845797</v>
@@ -18506,13 +18506,13 @@
         <v>59.74650373916668</v>
       </c>
       <c r="BV18" t="n">
-        <v>158.1040901656181</v>
+        <v>158.1040897319534</v>
       </c>
       <c r="BW18" t="n">
-        <v>129.4237707568852</v>
+        <v>129.423770149299</v>
       </c>
       <c r="BX18" t="n">
-        <v>116.4813936811967</v>
+        <v>116.4813931343691</v>
       </c>
       <c r="BY18" t="n">
         <v>8</v>
@@ -18524,10 +18524,10 @@
         <v>5.1</v>
       </c>
       <c r="CB18" t="n">
-        <v>150.3361202171878</v>
+        <v>150.3361190419728</v>
       </c>
       <c r="CC18" t="n">
-        <v>239.7895858874708</v>
+        <v>239.7895849554599</v>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
@@ -18776,37 +18776,37 @@
         <v>33.2400016784668</v>
       </c>
       <c r="BN19" t="n">
-        <v>23.90741373264288</v>
+        <v>23.90741379607601</v>
       </c>
       <c r="BO19" t="n">
-        <v>31.38173453430443</v>
+        <v>31.3817344285561</v>
       </c>
       <c r="BP19" t="n">
-        <v>35.57732098896218</v>
+        <v>35.57732077467912</v>
       </c>
       <c r="BQ19" t="n">
         <v>35.59395391834337</v>
       </c>
       <c r="BR19" t="n">
-        <v>49.64138143699247</v>
+        <v>49.64138131146932</v>
       </c>
       <c r="BS19" t="n">
-        <v>48.07438724376921</v>
+        <v>48.07438721586309</v>
       </c>
       <c r="BT19" t="n">
-        <v>17.32336515922971</v>
+        <v>17.32336501660665</v>
       </c>
       <c r="BU19" t="n">
         <v>29.12385888600579</v>
       </c>
       <c r="BV19" t="n">
-        <v>33.82792698753126</v>
+        <v>33.82792691844993</v>
       </c>
       <c r="BW19" t="n">
-        <v>33.47952776163331</v>
+        <v>33.4795276016176</v>
       </c>
       <c r="BX19" t="n">
-        <v>30.13157498546998</v>
+        <v>30.13157484145584</v>
       </c>
       <c r="BY19" t="n">
         <v>8</v>
@@ -18818,10 +18818,10 @@
         <v>2.9</v>
       </c>
       <c r="CB19" t="n">
-        <v>-9.351463706484974</v>
+        <v>-9.351464139740473</v>
       </c>
       <c r="CC19" t="n">
-        <v>1.768728277307297</v>
+        <v>1.768728069481407</v>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
@@ -19082,10 +19082,10 @@
         <v>14.27999973297119</v>
       </c>
       <c r="BN20" t="n">
-        <v>4.387520844480649</v>
+        <v>4.387520843971235</v>
       </c>
       <c r="BO20" t="n">
-        <v>8.138851166511603</v>
+        <v>8.13885116556664</v>
       </c>
       <c r="BP20" t="n">
         <v>23.74027559120054</v>
@@ -19094,25 +19094,25 @@
         <v>19.99443109682345</v>
       </c>
       <c r="BR20" t="n">
-        <v>28.98387348124873</v>
+        <v>28.98387348164261</v>
       </c>
       <c r="BS20" t="n">
-        <v>16.36200631279058</v>
+        <v>16.36200631289578</v>
       </c>
       <c r="BT20" t="n">
-        <v>18.16044427723578</v>
+        <v>18.16044427804582</v>
       </c>
       <c r="BU20" t="n">
         <v>13.94701359457771</v>
       </c>
       <c r="BV20" t="n">
-        <v>18.47527078862691</v>
+        <v>18.47527078867894</v>
       </c>
       <c r="BW20" t="n">
-        <v>18.16044427723578</v>
+        <v>18.16044427804582</v>
       </c>
       <c r="BX20" t="n">
-        <v>16.3443998495122</v>
+        <v>16.34439985024124</v>
       </c>
       <c r="BY20" t="n">
         <v>7</v>
@@ -19124,10 +19124,10 @@
         <v>6.6</v>
       </c>
       <c r="CB20" t="n">
-        <v>14.45658371949756</v>
+        <v>14.4565837246029</v>
       </c>
       <c r="CC20" t="n">
-        <v>29.37864939849566</v>
+        <v>29.37864939885997</v>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
@@ -19388,10 +19388,10 @@
         <v>16.47999954223633</v>
       </c>
       <c r="BN21" t="n">
-        <v>9.770026178296948</v>
+        <v>9.770026175461824</v>
       </c>
       <c r="BO21" t="n">
-        <v>18.12339856074084</v>
+        <v>18.12339855548168</v>
       </c>
       <c r="BP21" t="n">
         <v>36.09256098093079</v>
@@ -19400,25 +19400,25 @@
         <v>35.53250072181754</v>
       </c>
       <c r="BR21" t="n">
-        <v>40.48255603677045</v>
+        <v>40.48255603544121</v>
       </c>
       <c r="BS21" t="n">
-        <v>32.74874497364594</v>
+        <v>32.74874497423615</v>
       </c>
       <c r="BT21" t="n">
-        <v>18.51211382657749</v>
+        <v>18.51211382986578</v>
       </c>
       <c r="BU21" t="n">
         <v>29.55836540201202</v>
       </c>
       <c r="BV21" t="n">
-        <v>30.1500343574993</v>
+        <v>30.15003435711217</v>
       </c>
       <c r="BW21" t="n">
-        <v>32.74874497364594</v>
+        <v>32.74874497423615</v>
       </c>
       <c r="BX21" t="n">
-        <v>29.47387047628135</v>
+        <v>29.47387047681254</v>
       </c>
       <c r="BY21" t="n">
         <v>7</v>
@@ -19430,10 +19430,10 @@
         <v>4.1</v>
       </c>
       <c r="CB21" t="n">
-        <v>78.84630640154593</v>
+        <v>78.84630640476917</v>
       </c>
       <c r="CC21" t="n">
-        <v>82.94924268795188</v>
+        <v>82.94924268560277</v>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
@@ -19686,10 +19686,10 @@
         <v>9.220000267028809</v>
       </c>
       <c r="BN22" t="n">
-        <v>9.218246638132781</v>
+        <v>9.218246727545807</v>
       </c>
       <c r="BO22" t="n">
-        <v>17.09984751373631</v>
+        <v>17.09984767959747</v>
       </c>
       <c r="BP22" t="n">
         <v>23.49326991117917</v>
@@ -19698,25 +19698,25 @@
         <v>16.88595648327735</v>
       </c>
       <c r="BR22" t="n">
-        <v>36.8331652161761</v>
+        <v>36.83316514520967</v>
       </c>
       <c r="BS22" t="n">
-        <v>23.39513825798915</v>
+        <v>23.39513821947223</v>
       </c>
       <c r="BT22" t="n">
-        <v>12.28881407226837</v>
+        <v>12.28881387634654</v>
       </c>
       <c r="BU22" t="n">
         <v>9.220000267028809</v>
       </c>
       <c r="BV22" t="n">
-        <v>18.5543047949735</v>
+        <v>18.55430478870713</v>
       </c>
       <c r="BW22" t="n">
-        <v>16.99290199850683</v>
+        <v>16.99290208143741</v>
       </c>
       <c r="BX22" t="n">
-        <v>15.29361179865614</v>
+        <v>15.29361187329367</v>
       </c>
       <c r="BY22" t="n">
         <v>8</v>
@@ -19728,10 +19728,10 @@
         <v>4</v>
       </c>
       <c r="CB22" t="n">
-        <v>65.87430971501031</v>
+        <v>65.8743105245279</v>
       </c>
       <c r="CC22" t="n">
-        <v>101.2397424902974</v>
+        <v>101.2397424223324</v>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
@@ -19984,10 +19984,10 @@
         <v>12.02999973297119</v>
       </c>
       <c r="BN23" t="n">
-        <v>3.742665490763264</v>
+        <v>3.742665502032937</v>
       </c>
       <c r="BO23" t="n">
-        <v>6.942644485365855</v>
+        <v>6.942644506271098</v>
       </c>
       <c r="BP23" t="n">
         <v>19.51009748615278</v>
@@ -19996,19 +19996,19 @@
         <v>18.37827919410691</v>
       </c>
       <c r="BR23" t="n">
-        <v>20.08107822067232</v>
+        <v>20.08107821724845</v>
       </c>
       <c r="BS23" t="n">
-        <v>15.55766337248538</v>
+        <v>15.55766337028725</v>
       </c>
       <c r="BT23" t="n">
-        <v>12.52469663668951</v>
+        <v>12.52469662239866</v>
       </c>
       <c r="BU23" t="n">
         <v>26.99032004584218</v>
       </c>
       <c r="BV23" t="n">
-        <v>17.14068277733071</v>
+        <v>17.14068277747247</v>
       </c>
       <c r="BW23" t="n">
         <v>18.37827919410691</v>
@@ -20029,7 +20029,7 @@
         <v>37.49336360634341</v>
       </c>
       <c r="CC23" t="n">
-        <v>42.48281926684023</v>
+        <v>42.48281926801869</v>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
@@ -20068,7 +20068,7 @@
         <v>-13.45323695596481</v>
       </c>
       <c r="CP23" t="n">
-        <v>-27.76080595405424</v>
+        <v>-27.7608147027258</v>
       </c>
       <c r="CQ23" t="b">
         <v>1</v>
@@ -20280,10 +20280,10 @@
         <v>3.430000066757202</v>
       </c>
       <c r="BN24" t="n">
-        <v>4.79027427163927</v>
+        <v>4.79027430247879</v>
       </c>
       <c r="BO24" t="n">
-        <v>6.974639339506778</v>
+        <v>6.974639384409119</v>
       </c>
       <c r="BP24" t="n">
         <v>6.618181946989778</v>
@@ -20302,7 +20302,7 @@
         <v>2.330329016381401</v>
       </c>
       <c r="BV24" t="n">
-        <v>5.511348678678725</v>
+        <v>5.511348691302367</v>
       </c>
       <c r="BW24" t="n">
         <v>5.928677058339783</v>
@@ -20323,7 +20323,7 @@
         <v>55.5629518558697</v>
       </c>
       <c r="CC24" t="n">
-        <v>60.68071636771937</v>
+        <v>60.68071673575557</v>
       </c>
       <c r="CD24" t="inlineStr">
         <is>
@@ -20576,10 +20576,10 @@
         <v>20.88999938964844</v>
       </c>
       <c r="BN25" t="n">
-        <v>2.938906067098677</v>
+        <v>2.938906070377924</v>
       </c>
       <c r="BO25" t="n">
-        <v>5.451670754468045</v>
+        <v>5.451670760551048</v>
       </c>
       <c r="BP25" t="n">
         <v>31.74225824688552</v>
@@ -20588,7 +20588,7 @@
         <v>26.44590940575898</v>
       </c>
       <c r="BR25" t="n">
-        <v>40.65305914955367</v>
+        <v>40.65305915481851</v>
       </c>
       <c r="BS25" t="n">
         <v>10.44211857350007</v>
@@ -20850,35 +20850,35 @@
         <v>22.70000076293945</v>
       </c>
       <c r="BN26" t="n">
-        <v>16.28609448199667</v>
+        <v>16.28609456572976</v>
       </c>
       <c r="BO26" t="n">
-        <v>28.49660543684429</v>
+        <v>28.49660542418487</v>
       </c>
       <c r="BP26" t="n">
-        <v>47.12783878381875</v>
+        <v>47.12783852058014</v>
       </c>
       <c r="BQ26" t="n">
         <v>47.60027068070954</v>
       </c>
       <c r="BR26" t="n">
-        <v>58.81912814515054</v>
+        <v>58.81912817517568</v>
       </c>
       <c r="BS26" t="n">
-        <v>30.92711816845054</v>
+        <v>30.92711815565275</v>
       </c>
       <c r="BT26" t="n">
-        <v>23.23843522744946</v>
+        <v>23.23843512392188</v>
       </c>
       <c r="BU26" t="inlineStr"/>
       <c r="BV26" t="n">
-        <v>30.70941421777756</v>
+        <v>30.70941416653688</v>
       </c>
       <c r="BW26" t="n">
-        <v>29.71186180264742</v>
+        <v>29.71186178991881</v>
       </c>
       <c r="BX26" t="n">
-        <v>26.74067562238268</v>
+        <v>26.74067561092693</v>
       </c>
       <c r="BY26" t="n">
         <v>4</v>
@@ -20890,10 +20890,10 @@
         <v>2.9</v>
       </c>
       <c r="CB26" t="n">
-        <v>17.80032917901979</v>
+        <v>17.80032912855394</v>
       </c>
       <c r="CC26" t="n">
-        <v>35.28375852706782</v>
+        <v>35.28375830133794</v>
       </c>
       <c r="CD26" t="inlineStr">
         <is>
@@ -21144,10 +21144,10 @@
         <v>5.889999866485596</v>
       </c>
       <c r="BN27" t="n">
-        <v>6.967484579308371</v>
+        <v>6.96748449039864</v>
       </c>
       <c r="BO27" t="n">
-        <v>10.14465754747299</v>
+        <v>10.14465741802042</v>
       </c>
       <c r="BP27" t="n">
         <v>8.368305821236365</v>
@@ -21166,7 +21166,7 @@
         <v>5.445300917107223</v>
       </c>
       <c r="BV27" t="n">
-        <v>8.112707716463881</v>
+        <v>8.112707680070164</v>
       </c>
       <c r="BW27" t="n">
         <v>8.595393290251712</v>
@@ -21187,7 +21187,7 @@
         <v>31.33877990802598</v>
       </c>
       <c r="CC27" t="n">
-        <v>37.73697623705576</v>
+        <v>37.73697561916583</v>
       </c>
       <c r="CD27" t="inlineStr">
         <is>
@@ -21440,10 +21440,10 @@
         <v>27.1299991607666</v>
       </c>
       <c r="BN28" t="n">
-        <v>7.18252804582947</v>
+        <v>7.182528011456576</v>
       </c>
       <c r="BO28" t="n">
-        <v>13.32358952501367</v>
+        <v>13.32358946125195</v>
       </c>
       <c r="BP28" t="n">
         <v>34.63126097111343</v>
@@ -21452,19 +21452,19 @@
         <v>27.36859865246639</v>
       </c>
       <c r="BR28" t="n">
-        <v>42.68616593673717</v>
+        <v>42.68616598912325</v>
       </c>
       <c r="BS28" t="n">
-        <v>24.66467731664149</v>
+        <v>24.66467732491535</v>
       </c>
       <c r="BT28" t="n">
-        <v>27.72433013137766</v>
+        <v>27.72433019344685</v>
       </c>
       <c r="BU28" t="n">
         <v>22.34091371576103</v>
       </c>
       <c r="BV28" t="n">
-        <v>27.53421946415869</v>
+        <v>27.53421947258261</v>
       </c>
       <c r="BW28" t="n">
         <v>27.36859865246639</v>
@@ -21485,7 +21485,7 @@
         <v>-9.208479361693655</v>
       </c>
       <c r="CC28" t="n">
-        <v>1.489938503118871</v>
+        <v>1.489938534169055</v>
       </c>
       <c r="CD28" t="inlineStr">
         <is>
@@ -21524,7 +21524,7 @@
         <v>-6.673548518829275</v>
       </c>
       <c r="CP28" t="n">
-        <v>-23.09690478621134</v>
+        <v>-23.09691313905869</v>
       </c>
       <c r="CQ28" t="b">
         <v>1</v>
@@ -21738,37 +21738,37 @@
         <v>11.01000022888184</v>
       </c>
       <c r="BN29" t="n">
-        <v>9.531702580833194</v>
+        <v>9.531702597764133</v>
       </c>
       <c r="BO29" t="n">
-        <v>17.26678413350498</v>
+        <v>17.26678402871858</v>
       </c>
       <c r="BP29" t="n">
-        <v>20.26492236685869</v>
+        <v>20.26492220788147</v>
       </c>
       <c r="BQ29" t="n">
         <v>11.834803187379</v>
       </c>
       <c r="BR29" t="n">
-        <v>28.09971465547086</v>
+        <v>28.0997145959157</v>
       </c>
       <c r="BS29" t="n">
-        <v>24.03459731543566</v>
+        <v>24.03459730190921</v>
       </c>
       <c r="BT29" t="n">
-        <v>9.914946129319048</v>
+        <v>9.914946070690592</v>
       </c>
       <c r="BU29" t="n">
         <v>8.714817950680764</v>
       </c>
       <c r="BV29" t="n">
-        <v>16.20778603993527</v>
+        <v>16.20778599261743</v>
       </c>
       <c r="BW29" t="n">
-        <v>14.55079366044199</v>
+        <v>14.55079360804879</v>
       </c>
       <c r="BX29" t="n">
-        <v>13.09571429439779</v>
+        <v>13.09571424724391</v>
       </c>
       <c r="BY29" t="n">
         <v>8</v>
@@ -21780,10 +21780,10 @@
         <v>3.2</v>
       </c>
       <c r="CB29" t="n">
-        <v>18.94381491514083</v>
+        <v>18.94381448685854</v>
       </c>
       <c r="CC29" t="n">
-        <v>47.20967940961902</v>
+        <v>47.20967897984756</v>
       </c>
       <c r="CD29" t="inlineStr">
         <is>
@@ -22036,37 +22036,37 @@
         <v>25.3700008392334</v>
       </c>
       <c r="BN30" t="n">
-        <v>16.13552566273303</v>
+        <v>16.13552567032167</v>
       </c>
       <c r="BO30" t="n">
-        <v>27.68254989004594</v>
+        <v>27.68254989109558</v>
       </c>
       <c r="BP30" t="n">
-        <v>48.12634730059568</v>
+        <v>48.12634727978634</v>
       </c>
       <c r="BQ30" t="n">
         <v>52.28637766046484</v>
       </c>
       <c r="BR30" t="n">
-        <v>56.17235739191225</v>
+        <v>56.17235739485499</v>
       </c>
       <c r="BS30" t="n">
-        <v>39.40869666512248</v>
+        <v>39.40869666383689</v>
       </c>
       <c r="BT30" t="n">
-        <v>23.81941002602883</v>
+        <v>23.81941001754109</v>
       </c>
       <c r="BU30" t="n">
         <v>31.56559010239847</v>
       </c>
       <c r="BV30" t="n">
-        <v>36.89960683741269</v>
+        <v>36.89960683503749</v>
       </c>
       <c r="BW30" t="n">
-        <v>35.48714338376048</v>
+        <v>35.48714338311768</v>
       </c>
       <c r="BX30" t="n">
-        <v>31.93842904538443</v>
+        <v>31.93842904480591</v>
       </c>
       <c r="BY30" t="n">
         <v>8</v>
@@ -22078,10 +22078,10 @@
         <v>3.5</v>
       </c>
       <c r="CB30" t="n">
-        <v>25.89053208068206</v>
+        <v>25.89053207840175</v>
       </c>
       <c r="CC30" t="n">
-        <v>45.44582426796515</v>
+        <v>45.44582425860288</v>
       </c>
       <c r="CD30" t="inlineStr">
         <is>
@@ -22328,10 +22328,10 @@
         <v>8.670000076293945</v>
       </c>
       <c r="BN31" t="n">
-        <v>4.017238346199441</v>
+        <v>4.017238341801162</v>
       </c>
       <c r="BO31" t="n">
-        <v>7.451977132199961</v>
+        <v>7.451977124041156</v>
       </c>
       <c r="BP31" t="n">
         <v>23.54047151862598</v>
@@ -22340,13 +22340,13 @@
         <v>21.93987763885073</v>
       </c>
       <c r="BR31" t="n">
-        <v>29.48326652117494</v>
+        <v>29.483266517664</v>
       </c>
       <c r="BS31" t="n">
-        <v>10.32104214771942</v>
+        <v>10.3210421368999</v>
       </c>
       <c r="BT31" t="n">
-        <v>16.03430380689343</v>
+        <v>16.03430381261787</v>
       </c>
       <c r="BU31" t="n">
         <v>89.07939849036975</v>
@@ -22612,10 +22612,10 @@
         <v>12.86999988555908</v>
       </c>
       <c r="BN32" t="n">
-        <v>8.064609801892797</v>
+        <v>8.064609824522909</v>
       </c>
       <c r="BO32" t="n">
-        <v>14.95985118251114</v>
+        <v>14.95985122449</v>
       </c>
       <c r="BP32" t="n">
         <v>13.49109956358052</v>
@@ -22636,7 +22636,7 @@
         <v>6.379184203562791</v>
       </c>
       <c r="BV32" t="n">
-        <v>14.53079976683148</v>
+        <v>14.5307997749076</v>
       </c>
       <c r="BW32" t="n">
         <v>12.9056367523308</v>
@@ -22657,7 +22657,7 @@
         <v>-9.750791139240512</v>
       </c>
       <c r="CC32" t="n">
-        <v>12.90442809666155</v>
+        <v>12.90442815941308</v>
       </c>
       <c r="CD32" t="inlineStr">
         <is>
@@ -22904,10 +22904,10 @@
         <v>14.72000026702881</v>
       </c>
       <c r="BN33" t="n">
-        <v>9.143015732646591</v>
+        <v>9.143015713300365</v>
       </c>
       <c r="BO33" t="n">
-        <v>16.96029418405942</v>
+        <v>16.96029414817217</v>
       </c>
       <c r="BP33" t="n">
         <v>30.23876023847003</v>
@@ -22916,23 +22916,23 @@
         <v>28.82030174141344</v>
       </c>
       <c r="BR33" t="n">
-        <v>34.00566209630941</v>
+        <v>34.00566209258832</v>
       </c>
       <c r="BS33" t="n">
-        <v>26.56393124579123</v>
+        <v>26.5639312499856</v>
       </c>
       <c r="BT33" t="n">
-        <v>14.99745129912891</v>
+        <v>14.99745132318477</v>
       </c>
       <c r="BU33" t="inlineStr"/>
       <c r="BV33" t="n">
-        <v>20.72650035024182</v>
+        <v>20.72650033748204</v>
       </c>
       <c r="BW33" t="n">
-        <v>21.76211271492533</v>
+        <v>21.76211269907889</v>
       </c>
       <c r="BX33" t="n">
-        <v>19.58590144343279</v>
+        <v>19.585901429171</v>
       </c>
       <c r="BY33" t="n">
         <v>4</v>
@@ -22944,10 +22944,10 @@
         <v>3.3</v>
       </c>
       <c r="CB33" t="n">
-        <v>33.05639326177916</v>
+        <v>33.05639316489199</v>
       </c>
       <c r="CC33" t="n">
-        <v>40.80502699899342</v>
+        <v>40.80502691231016</v>
       </c>
       <c r="CD33" t="inlineStr">
         <is>
@@ -22986,7 +22986,7 @@
         <v>-10.80078673102787</v>
       </c>
       <c r="CP33" t="n">
-        <v>-19.07733209382061</v>
+        <v>-19.07732332684662</v>
       </c>
       <c r="CQ33" t="b">
         <v>1</v>
@@ -23184,10 +23184,10 @@
         <v>37.2599983215332</v>
       </c>
       <c r="BN34" t="n">
-        <v>34.16540997415938</v>
+        <v>34.16540993615371</v>
       </c>
       <c r="BO34" t="n">
-        <v>49.74483692237606</v>
+        <v>49.74483686703981</v>
       </c>
       <c r="BP34" t="n">
         <v>47.95841368118134</v>
@@ -23204,13 +23204,13 @@
       </c>
       <c r="BU34" t="inlineStr"/>
       <c r="BV34" t="n">
-        <v>47.47016034714099</v>
+        <v>47.47016032380552</v>
       </c>
       <c r="BW34" t="n">
-        <v>48.8516253017787</v>
+        <v>48.85162527411057</v>
       </c>
       <c r="BX34" t="n">
-        <v>43.96646277160083</v>
+        <v>43.96646274669952</v>
       </c>
       <c r="BY34" t="n">
         <v>4</v>
@@ -23222,10 +23222,10 @@
         <v>1.7</v>
       </c>
       <c r="CB34" t="n">
-        <v>17.9991002473874</v>
+        <v>17.99910018055619</v>
       </c>
       <c r="CC34" t="n">
-        <v>27.40247580662707</v>
+        <v>27.4024757439983</v>
       </c>
       <c r="CD34" t="inlineStr">
         <is>
@@ -23476,10 +23476,10 @@
         <v>3.690000057220459</v>
       </c>
       <c r="BN35" t="n">
-        <v>0.8537054734197488</v>
+        <v>0.8537054775691739</v>
       </c>
       <c r="BO35" t="n">
-        <v>1.583623653193634</v>
+        <v>1.583623660890817</v>
       </c>
       <c r="BP35" t="n">
         <v>9.978061379218586</v>
@@ -23488,13 +23488,13 @@
         <v>8.953076401677793</v>
       </c>
       <c r="BR35" t="n">
-        <v>12.46813579382274</v>
+        <v>12.46813579648228</v>
       </c>
       <c r="BS35" t="n">
-        <v>4.490296416555022</v>
+        <v>4.490296416071136</v>
       </c>
       <c r="BT35" t="n">
-        <v>8.315677889859598</v>
+        <v>8.315677884079284</v>
       </c>
       <c r="BU35" t="n">
         <v>8.070693304078278</v>
@@ -23764,37 +23764,37 @@
         <v>15.01000022888184</v>
       </c>
       <c r="BN36" t="n">
-        <v>5.822993539681077</v>
+        <v>5.822993549709619</v>
       </c>
       <c r="BO36" t="n">
-        <v>8.112117356420375</v>
+        <v>8.112117348517947</v>
       </c>
       <c r="BP36" t="n">
-        <v>10.07841822041387</v>
+        <v>10.07841819323861</v>
       </c>
       <c r="BQ36" t="n">
         <v>11.19351621134486</v>
       </c>
       <c r="BR36" t="n">
-        <v>9.136669975584569</v>
+        <v>9.136669959224704</v>
       </c>
       <c r="BS36" t="n">
-        <v>14.61973513864618</v>
+        <v>14.61973513504642</v>
       </c>
       <c r="BT36" t="n">
-        <v>4.991079410098848</v>
+        <v>4.991079393860636</v>
       </c>
       <c r="BU36" t="n">
         <v>10.28842080392437</v>
       </c>
       <c r="BV36" t="n">
-        <v>9.28036883201427</v>
+        <v>9.280368824358396</v>
       </c>
       <c r="BW36" t="n">
-        <v>9.607544097999222</v>
+        <v>9.607544076231655</v>
       </c>
       <c r="BX36" t="n">
-        <v>8.6467896881993</v>
+        <v>8.64678966860849</v>
       </c>
       <c r="BY36" t="n">
         <v>8</v>
@@ -23806,10 +23806,10 @@
         <v>2.9</v>
       </c>
       <c r="CB36" t="n">
-        <v>-42.39314086377306</v>
+        <v>-42.39314099429146</v>
       </c>
       <c r="CC36" t="n">
-        <v>-38.17209400065674</v>
+        <v>-38.1720940516619</v>
       </c>
       <c r="CD36" t="inlineStr">
         <is>
@@ -24062,10 +24062,10 @@
         <v>30.59000015258789</v>
       </c>
       <c r="BN37" t="n">
-        <v>3.032359189618023</v>
+        <v>3.03235917937138</v>
       </c>
       <c r="BO37" t="n">
-        <v>5.625026296741432</v>
+        <v>5.625026277733911</v>
       </c>
       <c r="BP37" t="n">
         <v>31.32283632316766</v>
@@ -24074,7 +24074,7 @@
         <v>21.94043581226608</v>
       </c>
       <c r="BR37" t="n">
-        <v>38.74057426147379</v>
+        <v>38.74057425038777</v>
       </c>
       <c r="BS37" t="n">
         <v>16.47675213208347</v>
@@ -24340,35 +24340,35 @@
         <v>12.63000011444092</v>
       </c>
       <c r="BN38" t="n">
-        <v>8.477710191261535</v>
+        <v>8.477710171212845</v>
       </c>
       <c r="BO38" t="n">
-        <v>13.24330365758486</v>
+        <v>13.24330367989931</v>
       </c>
       <c r="BP38" t="n">
-        <v>17.39835030628252</v>
+        <v>17.3983503767429</v>
       </c>
       <c r="BQ38" t="n">
         <v>16.79972907026644</v>
       </c>
       <c r="BR38" t="n">
-        <v>21.86210625973284</v>
+        <v>21.86210627942075</v>
       </c>
       <c r="BS38" t="n">
-        <v>16.6495876920284</v>
+        <v>16.64958769757434</v>
       </c>
       <c r="BT38" t="n">
-        <v>8.696993323725099</v>
+        <v>8.696993357881651</v>
       </c>
       <c r="BU38" t="inlineStr"/>
       <c r="BV38" t="n">
-        <v>13.94223796178933</v>
+        <v>13.94223798135735</v>
       </c>
       <c r="BW38" t="n">
-        <v>14.94644567480663</v>
+        <v>14.94644568873682</v>
       </c>
       <c r="BX38" t="n">
-        <v>13.45180110732597</v>
+        <v>13.45180111986314</v>
       </c>
       <c r="BY38" t="n">
         <v>4</v>
@@ -24380,10 +24380,10 @@
         <v>2.1</v>
       </c>
       <c r="CB38" t="n">
-        <v>6.506737810282504</v>
+        <v>6.506737909547522</v>
       </c>
       <c r="CC38" t="n">
-        <v>10.38984826174325</v>
+        <v>10.3898484166761</v>
       </c>
       <c r="CD38" t="inlineStr">
         <is>
@@ -24636,10 +24636,10 @@
         <v>8.350000381469727</v>
       </c>
       <c r="BN39" t="n">
-        <v>2.27517043785061</v>
+        <v>2.275170444003772</v>
       </c>
       <c r="BO39" t="n">
-        <v>4.220441162212881</v>
+        <v>4.220441173626996</v>
       </c>
       <c r="BP39" t="n">
         <v>13.45955049324499</v>
@@ -24648,19 +24648,19 @@
         <v>14.81092624645154</v>
       </c>
       <c r="BR39" t="n">
-        <v>11.28719235012451</v>
+        <v>11.28719235144721</v>
       </c>
       <c r="BS39" t="n">
-        <v>7.403635149020883</v>
+        <v>7.403635148398864</v>
       </c>
       <c r="BT39" t="n">
-        <v>7.37277860759801</v>
+        <v>7.372778601842098</v>
       </c>
       <c r="BU39" t="n">
         <v>9.952965903815388</v>
       </c>
       <c r="BV39" t="n">
-        <v>9.786784273209744</v>
+        <v>9.786784274118157</v>
       </c>
       <c r="BW39" t="n">
         <v>9.952965903815388</v>
@@ -24681,7 +24681,7 @@
         <v>7.277471906620003</v>
       </c>
       <c r="CC39" t="n">
-        <v>17.20699192934794</v>
+        <v>17.20699194022712</v>
       </c>
       <c r="CD39" t="inlineStr">
         <is>
@@ -24932,10 +24932,10 @@
         <v>10.39999961853027</v>
       </c>
       <c r="BN40" t="n">
-        <v>12.94492616447744</v>
+        <v>12.94492638520225</v>
       </c>
       <c r="BO40" t="n">
-        <v>18.84781249547915</v>
+        <v>18.84781281685448</v>
       </c>
       <c r="BP40" t="n">
         <v>17.11392342289792</v>
@@ -24954,7 +24954,7 @@
         <v>15.58796560981411</v>
       </c>
       <c r="BV40" t="n">
-        <v>16.31747695366762</v>
+        <v>16.31747704401764</v>
       </c>
       <c r="BW40" t="n">
         <v>16.35094451635601</v>
@@ -24975,7 +24975,7 @@
         <v>41.49856350475572</v>
       </c>
       <c r="CC40" t="n">
-        <v>56.89882261720316</v>
+        <v>56.89882348595343</v>
       </c>
       <c r="CD40" t="inlineStr">
         <is>
@@ -25228,10 +25228,10 @@
         <v>20.54000091552734</v>
       </c>
       <c r="BN41" t="n">
-        <v>10.65665905345763</v>
+        <v>10.65665905890321</v>
       </c>
       <c r="BO41" t="n">
-        <v>19.7681025441639</v>
+        <v>19.76810255426544</v>
       </c>
       <c r="BP41" t="n">
         <v>55.31605937616612</v>
@@ -25240,13 +25240,13 @@
         <v>45.79470361759502</v>
       </c>
       <c r="BR41" t="n">
-        <v>80.22510937301085</v>
+        <v>80.22510937432611</v>
       </c>
       <c r="BS41" t="n">
-        <v>27.74194761526666</v>
+        <v>27.74194761442497</v>
       </c>
       <c r="BT41" t="n">
-        <v>42.51919242550263</v>
+        <v>42.51919241658931</v>
       </c>
       <c r="BU41" t="n">
         <v>4.320378356765164</v>
@@ -25510,10 +25510,10 @@
         <v>32.40000152587891</v>
       </c>
       <c r="BN42" t="n">
-        <v>8.926844974578826</v>
+        <v>8.926845001173641</v>
       </c>
       <c r="BO42" t="n">
-        <v>16.55929742784372</v>
+        <v>16.5592974771771</v>
       </c>
       <c r="BP42" t="n">
         <v>61.76978708171158</v>
@@ -25522,7 +25522,7 @@
         <v>36.01581457783751</v>
       </c>
       <c r="BR42" t="n">
-        <v>87.91019460896219</v>
+        <v>87.91019466253447</v>
       </c>
       <c r="BS42" t="n">
         <v>22.23751954027694</v>
@@ -25784,35 +25784,35 @@
         <v>16.79000091552734</v>
       </c>
       <c r="BN43" t="n">
-        <v>9.983952032237859</v>
+        <v>9.983951970710299</v>
       </c>
       <c r="BO43" t="n">
-        <v>17.31362328721972</v>
+        <v>17.31362329759388</v>
       </c>
       <c r="BP43" t="n">
-        <v>28.29572481055279</v>
+        <v>28.29572500188385</v>
       </c>
       <c r="BQ43" t="n">
         <v>28.80591266774053</v>
       </c>
       <c r="BR43" t="n">
-        <v>31.54471770720549</v>
+        <v>31.54471771172395</v>
       </c>
       <c r="BS43" t="n">
-        <v>29.07473906678766</v>
+        <v>29.07473908147372</v>
       </c>
       <c r="BT43" t="n">
-        <v>13.97702123587045</v>
+        <v>13.97702131237628</v>
       </c>
       <c r="BU43" t="inlineStr"/>
       <c r="BV43" t="n">
-        <v>21.16700979919951</v>
+        <v>21.16700983791544</v>
       </c>
       <c r="BW43" t="n">
-        <v>22.80467404888626</v>
+        <v>22.80467414973887</v>
       </c>
       <c r="BX43" t="n">
-        <v>20.52420664399763</v>
+        <v>20.52420673476498</v>
       </c>
       <c r="BY43" t="n">
         <v>4</v>
@@ -25824,10 +25824,10 @@
         <v>2.9</v>
       </c>
       <c r="CB43" t="n">
-        <v>22.24065232192398</v>
+        <v>22.24065286252756</v>
       </c>
       <c r="CC43" t="n">
-        <v>26.06914023229336</v>
+        <v>26.06914046288258</v>
       </c>
       <c r="CD43" t="inlineStr">
         <is>
@@ -26080,10 +26080,10 @@
         <v>4.25</v>
       </c>
       <c r="BN44" t="n">
-        <v>2.756777606664025</v>
+        <v>2.756777600458519</v>
       </c>
       <c r="BO44" t="n">
-        <v>5.113822460361766</v>
+        <v>5.113822448850553</v>
       </c>
       <c r="BP44" t="n">
         <v>13.83599508599508</v>
@@ -26092,25 +26092,25 @@
         <v>14.73343694068134</v>
       </c>
       <c r="BR44" t="n">
-        <v>16.86864304584438</v>
+        <v>16.86864303424626</v>
       </c>
       <c r="BS44" t="n">
-        <v>8.105886946965924</v>
+        <v>8.105886947672605</v>
       </c>
       <c r="BT44" t="n">
-        <v>7.432122116338263</v>
+        <v>7.432122122465331</v>
       </c>
       <c r="BU44" t="n">
         <v>3.276499576963653</v>
       </c>
       <c r="BV44" t="n">
-        <v>9.909486596164346</v>
+        <v>9.909486593839262</v>
       </c>
       <c r="BW44" t="n">
-        <v>8.105886946965924</v>
+        <v>8.105886947672605</v>
       </c>
       <c r="BX44" t="n">
-        <v>7.295298252269332</v>
+        <v>7.295298252905345</v>
       </c>
       <c r="BY44" t="n">
         <v>7</v>
@@ -26122,10 +26122,10 @@
         <v>6.1</v>
       </c>
       <c r="CB44" t="n">
-        <v>71.6540765239843</v>
+        <v>71.65407653894928</v>
       </c>
       <c r="CC44" t="n">
-        <v>133.1643904979846</v>
+        <v>133.1643904432767</v>
       </c>
       <c r="CD44" t="inlineStr">
         <is>
@@ -26364,10 +26364,10 @@
         <v>29.52000045776367</v>
       </c>
       <c r="BN45" t="n">
-        <v>15.43188315690255</v>
+        <v>15.43188318623062</v>
       </c>
       <c r="BO45" t="n">
-        <v>28.62614325605423</v>
+        <v>28.6261433104578</v>
       </c>
       <c r="BP45" t="n">
         <v>55.24576356855489</v>
@@ -26376,23 +26376,23 @@
         <v>49.94931085633525</v>
       </c>
       <c r="BR45" t="n">
-        <v>62.03667169751222</v>
+        <v>62.03667169108353</v>
       </c>
       <c r="BS45" t="n">
-        <v>38.72993677943371</v>
+        <v>38.72993684747589</v>
       </c>
       <c r="BT45" t="n">
-        <v>30.95210659434795</v>
+        <v>30.95210655385409</v>
       </c>
       <c r="BU45" t="inlineStr"/>
       <c r="BV45" t="n">
-        <v>34.50843169023634</v>
+        <v>34.5084317281798</v>
       </c>
       <c r="BW45" t="n">
-        <v>33.67804001774397</v>
+        <v>33.67804007896684</v>
       </c>
       <c r="BX45" t="n">
-        <v>30.31023601596957</v>
+        <v>30.31023607107016</v>
       </c>
       <c r="BY45" t="n">
         <v>4</v>
@@ -26404,10 +26404,10 @@
         <v>3.6</v>
       </c>
       <c r="CB45" t="n">
-        <v>2.676949681408525</v>
+        <v>2.676949868063638</v>
       </c>
       <c r="CC45" t="n">
-        <v>16.89847952275601</v>
+        <v>16.89847965129074</v>
       </c>
       <c r="CD45" t="inlineStr">
         <is>
@@ -26668,37 +26668,37 @@
         <v>10.39999961853027</v>
       </c>
       <c r="BN46" t="n">
-        <v>7.249464452720715</v>
+        <v>7.24946445445088</v>
       </c>
       <c r="BO46" t="n">
-        <v>10.94542261598734</v>
+        <v>10.94542261655361</v>
       </c>
       <c r="BP46" t="n">
-        <v>17.77471060719179</v>
+        <v>17.77471060386925</v>
       </c>
       <c r="BQ46" t="n">
         <v>23.30669690919295</v>
       </c>
       <c r="BR46" t="n">
-        <v>23.2148123893049</v>
+        <v>23.21481239041619</v>
       </c>
       <c r="BS46" t="n">
-        <v>20.50961401256914</v>
+        <v>20.50961401224382</v>
       </c>
       <c r="BT46" t="n">
-        <v>8.88496793650852</v>
+        <v>8.884967934794133</v>
       </c>
       <c r="BU46" t="n">
         <v>9.960670392837367</v>
       </c>
       <c r="BV46" t="n">
-        <v>15.23079491453909</v>
+        <v>15.23079491429477</v>
       </c>
       <c r="BW46" t="n">
-        <v>14.36006661158956</v>
+        <v>14.36006661021143</v>
       </c>
       <c r="BX46" t="n">
-        <v>12.92405995043061</v>
+        <v>12.92405994919029</v>
       </c>
       <c r="BY46" t="n">
         <v>8</v>
@@ -26710,10 +26710,10 @@
         <v>3.2</v>
       </c>
       <c r="CB46" t="n">
-        <v>24.26981177386842</v>
+        <v>24.26981176194229</v>
       </c>
       <c r="CC46" t="n">
-        <v>46.44995647308978</v>
+        <v>46.4499564707406</v>
       </c>
       <c r="CD46" t="inlineStr">
         <is>
@@ -26952,10 +26952,10 @@
         <v>39</v>
       </c>
       <c r="BN47" t="n">
-        <v>19.93010989560153</v>
+        <v>19.93010991987252</v>
       </c>
       <c r="BO47" t="n">
-        <v>36.97035385634084</v>
+        <v>36.97035390136352</v>
       </c>
       <c r="BP47" t="n">
         <v>54.05334728033472</v>
@@ -26964,23 +26964,23 @@
         <v>40.80446518102817</v>
       </c>
       <c r="BR47" t="n">
-        <v>58.13074603519775</v>
+        <v>58.13074599445734</v>
       </c>
       <c r="BS47" t="n">
-        <v>43.72434340527661</v>
+        <v>43.72434339764214</v>
       </c>
       <c r="BT47" t="n">
-        <v>29.09170549395553</v>
+        <v>29.09170544600577</v>
       </c>
       <c r="BU47" t="inlineStr"/>
       <c r="BV47" t="n">
-        <v>38.66953860938843</v>
+        <v>38.66953862480322</v>
       </c>
       <c r="BW47" t="n">
-        <v>40.34734863080872</v>
+        <v>40.34734864950283</v>
       </c>
       <c r="BX47" t="n">
-        <v>36.31261376772785</v>
+        <v>36.31261378455255</v>
       </c>
       <c r="BY47" t="n">
         <v>4</v>
@@ -26992,10 +26992,10 @@
         <v>2.7</v>
       </c>
       <c r="CB47" t="n">
-        <v>-6.890733928902937</v>
+        <v>-6.890733885762678</v>
       </c>
       <c r="CC47" t="n">
-        <v>-0.8473368990040364</v>
+        <v>-0.8473368594789088</v>
       </c>
       <c r="CD47" t="inlineStr">
         <is>
@@ -27034,7 +27034,7 @@
         <v>-9.659481922204559</v>
       </c>
       <c r="CP47" t="n">
-        <v>-19.91624499385604</v>
+        <v>-19.91623237135492</v>
       </c>
       <c r="CQ47" t="b">
         <v>1</v>
@@ -27248,10 +27248,10 @@
         <v>13.94999980926514</v>
       </c>
       <c r="BN48" t="n">
-        <v>1.715333650220571</v>
+        <v>1.715333658978063</v>
       </c>
       <c r="BO48" t="n">
-        <v>3.181943921159158</v>
+        <v>3.181943937404306</v>
       </c>
       <c r="BP48" t="n">
         <v>12.01023375391573</v>
@@ -27260,10 +27260,10 @@
         <v>8.698657440543561</v>
       </c>
       <c r="BR48" t="n">
-        <v>15.15689852125179</v>
+        <v>15.15689852921832</v>
       </c>
       <c r="BS48" t="n">
-        <v>4.602811961425198</v>
+        <v>4.602811984924467</v>
       </c>
       <c r="BT48" t="n">
         <v>10.96783610734946</v>
@@ -27530,10 +27530,10 @@
         <v>5.570000171661377</v>
       </c>
       <c r="BN49" t="n">
-        <v>6.611145498583777</v>
+        <v>6.611145418783511</v>
       </c>
       <c r="BO49" t="n">
-        <v>9.625827845937978</v>
+        <v>9.625827729748794</v>
       </c>
       <c r="BP49" t="n">
         <v>4.355488856035963</v>
@@ -27824,37 +27824,37 @@
         <v>43.65000152587891</v>
       </c>
       <c r="BN50" t="n">
-        <v>31.67320334287897</v>
+        <v>31.67320332508118</v>
       </c>
       <c r="BO50" t="n">
-        <v>38.85442818377845</v>
+        <v>38.85442820651731</v>
       </c>
       <c r="BP50" t="n">
-        <v>43.07167831742562</v>
+        <v>43.07167836683539</v>
       </c>
       <c r="BQ50" t="n">
         <v>47.83302112955008</v>
       </c>
       <c r="BR50" t="n">
-        <v>61.35148253200276</v>
+        <v>61.3514825630461</v>
       </c>
       <c r="BS50" t="n">
-        <v>55.87396022701227</v>
+        <v>55.87396023357789</v>
       </c>
       <c r="BT50" t="n">
-        <v>20.30744575455281</v>
+        <v>20.30744579170323</v>
       </c>
       <c r="BU50" t="n">
         <v>76.39578733574842</v>
       </c>
       <c r="BV50" t="n">
-        <v>46.92012585286868</v>
+        <v>46.92012586900745</v>
       </c>
       <c r="BW50" t="n">
-        <v>45.45234972348785</v>
+        <v>45.45234974819273</v>
       </c>
       <c r="BX50" t="n">
-        <v>40.90711475113906</v>
+        <v>40.90711477337346</v>
       </c>
       <c r="BY50" t="n">
         <v>8</v>
@@ -27866,10 +27866,10 @@
         <v>3.8</v>
       </c>
       <c r="CB50" t="n">
-        <v>-6.283818279166975</v>
+        <v>-6.283818228229077</v>
       </c>
       <c r="CC50" t="n">
-        <v>7.491693499829566</v>
+        <v>7.491693536802679</v>
       </c>
       <c r="CD50" t="inlineStr">
         <is>
@@ -28122,10 +28122,10 @@
         <v>10.3100004196167</v>
       </c>
       <c r="BN51" t="n">
-        <v>4.048541581278268</v>
+        <v>4.048541600191035</v>
       </c>
       <c r="BO51" t="n">
-        <v>7.510044633271187</v>
+        <v>7.510044668354368</v>
       </c>
       <c r="BP51" t="n">
         <v>24.39419742141451</v>
@@ -28134,25 +28134,25 @@
         <v>27.3727543950329</v>
       </c>
       <c r="BR51" t="n">
-        <v>23.05525212675452</v>
+        <v>23.0552521471614</v>
       </c>
       <c r="BS51" t="n">
-        <v>15.96194444716485</v>
+        <v>15.96194444498775</v>
       </c>
       <c r="BT51" t="n">
-        <v>13.0481698684521</v>
+        <v>13.04816985155922</v>
       </c>
       <c r="BU51" t="n">
         <v>4.783281030861835</v>
       </c>
       <c r="BV51" t="n">
-        <v>18.55706048201501</v>
+        <v>18.55706048808502</v>
       </c>
       <c r="BW51" t="n">
-        <v>19.50859828695969</v>
+        <v>19.50859829607457</v>
       </c>
       <c r="BX51" t="n">
-        <v>17.55773845826372</v>
+        <v>17.55773846646712</v>
       </c>
       <c r="BY51" t="n">
         <v>6</v>
@@ -28164,10 +28164,10 @@
         <v>6.8</v>
       </c>
       <c r="CB51" t="n">
-        <v>70.29813524407669</v>
+        <v>70.29813532364406</v>
       </c>
       <c r="CC51" t="n">
-        <v>79.99087998781013</v>
+        <v>79.99088004668511</v>
       </c>
       <c r="CD51" t="inlineStr">
         <is>
@@ -28416,10 +28416,10 @@
         <v>30.82999992370605</v>
       </c>
       <c r="BN52" t="n">
-        <v>10.12943436786695</v>
+        <v>10.12943442697306</v>
       </c>
       <c r="BO52" t="n">
-        <v>18.79010075239319</v>
+        <v>18.79010086203503</v>
       </c>
       <c r="BP52" t="n">
         <v>54.9794749648863</v>
@@ -28428,19 +28428,19 @@
         <v>51.86549020659677</v>
       </c>
       <c r="BR52" t="n">
-        <v>58.36213067852821</v>
+        <v>58.36213067090665</v>
       </c>
       <c r="BS52" t="n">
-        <v>25.8725290384045</v>
+        <v>25.872529182595</v>
       </c>
       <c r="BT52" t="n">
-        <v>35.77240180071416</v>
+        <v>35.77240172591892</v>
       </c>
       <c r="BU52" t="n">
         <v>59.1977960724276</v>
       </c>
       <c r="BV52" t="n">
-        <v>43.54856050199296</v>
+        <v>43.5485605264809</v>
       </c>
       <c r="BW52" t="n">
         <v>51.86549020659677</v>
@@ -28461,7 +28461,7 @@
         <v>51.40752935923412</v>
       </c>
       <c r="CC52" t="n">
-        <v>41.25384563659127</v>
+        <v>41.2538457160202</v>
       </c>
       <c r="CD52" t="inlineStr">
         <is>
@@ -28710,37 +28710,37 @@
         <v>31.54999923706055</v>
       </c>
       <c r="BN53" t="n">
-        <v>14.28761665647847</v>
+        <v>14.28761666867111</v>
       </c>
       <c r="BO53" t="n">
-        <v>22.26840044149128</v>
+        <v>22.26840044939432</v>
       </c>
       <c r="BP53" t="n">
-        <v>42.6258781102451</v>
+        <v>42.62587808899728</v>
       </c>
       <c r="BQ53" t="n">
         <v>58.65613740495224</v>
       </c>
       <c r="BR53" t="n">
-        <v>41.90294540458683</v>
+        <v>41.90294540884729</v>
       </c>
       <c r="BS53" t="n">
-        <v>34.87261618466359</v>
+        <v>34.87261621299015</v>
       </c>
       <c r="BT53" t="n">
-        <v>21.30896304234846</v>
+        <v>21.30896303200518</v>
       </c>
       <c r="BU53" t="n">
         <v>76.55851215726285</v>
       </c>
       <c r="BV53" t="n">
-        <v>42.59906467793576</v>
+        <v>42.59906467920705</v>
       </c>
       <c r="BW53" t="n">
-        <v>41.90294540458683</v>
+        <v>41.90294540884729</v>
       </c>
       <c r="BX53" t="n">
-        <v>37.71265086412815</v>
+        <v>37.71265086796257</v>
       </c>
       <c r="BY53" t="n">
         <v>7</v>
@@ -28752,10 +28752,10 @@
         <v>5.4</v>
       </c>
       <c r="CB53" t="n">
-        <v>19.53296917937348</v>
+        <v>19.53296919152694</v>
       </c>
       <c r="CC53" t="n">
-        <v>35.02081048514358</v>
+        <v>35.020810489173</v>
       </c>
       <c r="CD53" t="inlineStr">
         <is>
@@ -29004,10 +29004,10 @@
         <v>25.98999977111816</v>
       </c>
       <c r="BN54" t="n">
-        <v>4.764912414817951</v>
+        <v>4.764912412684581</v>
       </c>
       <c r="BO54" t="n">
-        <v>8.838912529487299</v>
+        <v>8.838912525529899</v>
       </c>
       <c r="BP54" t="n">
         <v>32.12383367232422</v>
@@ -29016,13 +29016,13 @@
         <v>25.73909396655281</v>
       </c>
       <c r="BR54" t="n">
-        <v>41.31716358302893</v>
+        <v>41.31716358620729</v>
       </c>
       <c r="BS54" t="n">
-        <v>12.18233647700617</v>
+        <v>12.18233647726798</v>
       </c>
       <c r="BT54" t="n">
-        <v>28.53601229812676</v>
+        <v>28.53601230187587</v>
       </c>
       <c r="BU54" t="n">
         <v>25.98999977111816</v>
@@ -29292,37 +29292,37 @@
         <v>22.70000076293945</v>
       </c>
       <c r="BN55" t="n">
-        <v>9.68574489568141</v>
+        <v>9.685744928302441</v>
       </c>
       <c r="BO55" t="n">
-        <v>14.38737749143421</v>
+        <v>14.38737747396123</v>
       </c>
       <c r="BP55" t="n">
-        <v>19.31434545536152</v>
+        <v>19.31434536685531</v>
       </c>
       <c r="BQ55" t="n">
         <v>21.34857150335456</v>
       </c>
       <c r="BR55" t="n">
-        <v>18.48506899605968</v>
+        <v>18.48506895783092</v>
       </c>
       <c r="BS55" t="n">
-        <v>22.55167736557078</v>
+        <v>22.55167735666984</v>
       </c>
       <c r="BT55" t="n">
-        <v>9.647003028626367</v>
+        <v>9.647002981576401</v>
       </c>
       <c r="BU55" t="n">
         <v>17.92914232069673</v>
       </c>
       <c r="BV55" t="n">
-        <v>16.66861638209816</v>
+        <v>16.66861636115593</v>
       </c>
       <c r="BW55" t="n">
-        <v>18.20710565837821</v>
+        <v>18.20710563926383</v>
       </c>
       <c r="BX55" t="n">
-        <v>16.38639509254039</v>
+        <v>16.38639507533744</v>
       </c>
       <c r="BY55" t="n">
         <v>8</v>
@@ -29334,10 +29334,10 @@
         <v>2.3</v>
       </c>
       <c r="CB55" t="n">
-        <v>-27.81323990396864</v>
+        <v>-27.81323997975255</v>
       </c>
       <c r="CC55" t="n">
-        <v>-26.56997435298889</v>
+        <v>-26.56997444524541</v>
       </c>
       <c r="CD55" t="inlineStr">
         <is>
@@ -29586,10 +29586,10 @@
         <v>47.36000061035156</v>
       </c>
       <c r="BN56" t="n">
-        <v>7.883046079194521</v>
+        <v>7.883046070219398</v>
       </c>
       <c r="BO56" t="n">
-        <v>14.62305047690583</v>
+        <v>14.62305046025698</v>
       </c>
       <c r="BP56" t="n">
         <v>19.62840187948571</v>
@@ -29598,25 +29598,25 @@
         <v>12.20333989274278</v>
       </c>
       <c r="BR56" t="n">
-        <v>15.97866916371092</v>
+        <v>15.97866920144672</v>
       </c>
       <c r="BS56" t="n">
-        <v>20.76704644318677</v>
+        <v>20.76704644857238</v>
       </c>
       <c r="BT56" t="n">
-        <v>11.83128739825765</v>
+        <v>11.83128742444777</v>
       </c>
       <c r="BU56" t="n">
         <v>12.691038728625</v>
       </c>
       <c r="BV56" t="n">
-        <v>14.45073500776365</v>
+        <v>14.45073501322459</v>
       </c>
       <c r="BW56" t="n">
-        <v>13.65704460276542</v>
+        <v>13.65704459444099</v>
       </c>
       <c r="BX56" t="n">
-        <v>12.29134014248888</v>
+        <v>12.29134013499689</v>
       </c>
       <c r="BY56" t="n">
         <v>8</v>
@@ -29628,10 +29628,10 @@
         <v>2.6</v>
       </c>
       <c r="CB56" t="n">
-        <v>-74.04700172279487</v>
+        <v>-74.0470017386141</v>
       </c>
       <c r="CC56" t="n">
-        <v>-69.48746870453984</v>
+        <v>-69.48746869300912</v>
       </c>
       <c r="CD56" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>-3.681101537516229</v>
       </c>
       <c r="CP56" t="n">
-        <v>-12.75737983983745</v>
+        <v>-12.75737357829422</v>
       </c>
       <c r="CQ56" t="b">
         <v>1</v>
@@ -29882,10 +29882,10 @@
         <v>50.13000106811523</v>
       </c>
       <c r="BN57" t="n">
-        <v>9.795809285794904</v>
+        <v>9.795809280433657</v>
       </c>
       <c r="BO57" t="n">
-        <v>18.17122622514955</v>
+        <v>18.17122621520443</v>
       </c>
       <c r="BP57" t="n">
         <v>57.70829836251319</v>
@@ -29894,23 +29894,23 @@
         <v>43.21887290828121</v>
       </c>
       <c r="BR57" t="n">
-        <v>77.24512128782426</v>
+        <v>77.2451212813032</v>
       </c>
       <c r="BS57" t="n">
-        <v>26.28542158354966</v>
+        <v>26.28542156916364</v>
       </c>
       <c r="BT57" t="n">
         <v>52.69965359897433</v>
       </c>
       <c r="BU57" t="inlineStr"/>
       <c r="BV57" t="n">
-        <v>18.08415236483137</v>
+        <v>18.08415235493391</v>
       </c>
       <c r="BW57" t="n">
-        <v>18.17122622514955</v>
+        <v>18.17122621520443</v>
       </c>
       <c r="BX57" t="n">
-        <v>16.35410360263459</v>
+        <v>16.35410359368399</v>
       </c>
       <c r="BY57" t="n">
         <v>3</v>
@@ -29922,10 +29922,10 @@
         <v>5.9</v>
       </c>
       <c r="CB57" t="n">
-        <v>-67.37661429447587</v>
+        <v>-67.37661431233066</v>
       </c>
       <c r="CC57" t="n">
-        <v>-63.92548976757624</v>
+        <v>-63.92548978731982</v>
       </c>
       <c r="CD57" t="inlineStr">
         <is>
@@ -30174,10 +30174,10 @@
         <v>11.22000026702881</v>
       </c>
       <c r="BN58" t="n">
-        <v>1.930034012003457</v>
+        <v>1.93003401310115</v>
       </c>
       <c r="BO58" t="n">
-        <v>3.580213092266412</v>
+        <v>3.580213094302634</v>
       </c>
       <c r="BP58" t="n">
         <v>24.09481418770368</v>
@@ -30186,13 +30186,13 @@
         <v>20.71331717707942</v>
       </c>
       <c r="BR58" t="n">
-        <v>31.31926061748075</v>
+        <v>31.31926061729749</v>
       </c>
       <c r="BS58" t="n">
-        <v>5.170573449045514</v>
+        <v>5.170573451920021</v>
       </c>
       <c r="BT58" t="n">
-        <v>21.79159984018045</v>
+        <v>21.79159983849966</v>
       </c>
       <c r="BU58" t="n">
         <v>35.73116610615543</v>
@@ -30458,10 +30458,10 @@
         <v>21.15999984741211</v>
       </c>
       <c r="BN59" t="n">
-        <v>5.849808931427029</v>
+        <v>5.849808900047482</v>
       </c>
       <c r="BO59" t="n">
-        <v>10.85139556779714</v>
+        <v>10.85139550958808</v>
       </c>
       <c r="BP59" t="n">
         <v>32.11569278100921</v>
@@ -30470,25 +30470,25 @@
         <v>32.99490367325112</v>
       </c>
       <c r="BR59" t="n">
-        <v>28.79985358925367</v>
+        <v>28.79985359208832</v>
       </c>
       <c r="BS59" t="n">
-        <v>23.13732277729395</v>
+        <v>23.13732278199182</v>
       </c>
       <c r="BT59" t="n">
-        <v>18.68112817936693</v>
+        <v>18.68112821277987</v>
       </c>
       <c r="BU59" t="n">
         <v>14.31401835039106</v>
       </c>
       <c r="BV59" t="n">
-        <v>22.98490213119473</v>
+        <v>22.9849021287285</v>
       </c>
       <c r="BW59" t="n">
-        <v>23.13732277729395</v>
+        <v>23.13732278199182</v>
       </c>
       <c r="BX59" t="n">
-        <v>20.82359049956456</v>
+        <v>20.82359050379264</v>
       </c>
       <c r="BY59" t="n">
         <v>7</v>
@@ -30500,10 +30500,10 @@
         <v>5.6</v>
       </c>
       <c r="CB59" t="n">
-        <v>-1.589836248929333</v>
+        <v>-1.589836228947861</v>
       </c>
       <c r="CC59" t="n">
-        <v>8.62430197042654</v>
+        <v>8.624301958771397</v>
       </c>
       <c r="CD59" t="inlineStr">
         <is>
@@ -30752,37 +30752,37 @@
         <v>38.29999923706055</v>
       </c>
       <c r="BN60" t="n">
-        <v>29.22536348857698</v>
+        <v>29.22536328125286</v>
       </c>
       <c r="BO60" t="n">
-        <v>34.44313637886151</v>
+        <v>34.44313653661566</v>
       </c>
       <c r="BP60" t="n">
-        <v>38.11036748082454</v>
+        <v>38.11036792572925</v>
       </c>
       <c r="BQ60" t="n">
         <v>48.33331772630119</v>
       </c>
       <c r="BR60" t="n">
-        <v>56.94551059663357</v>
+        <v>56.94551082534393</v>
       </c>
       <c r="BS60" t="n">
-        <v>69.48521577932581</v>
+        <v>69.48521537252874</v>
       </c>
       <c r="BT60" t="n">
-        <v>17.48847148405569</v>
+        <v>17.48847184347279</v>
       </c>
       <c r="BU60" t="n">
         <v>27.33708824000841</v>
       </c>
       <c r="BV60" t="n">
-        <v>40.17105889682346</v>
+        <v>40.17105896890661</v>
       </c>
       <c r="BW60" t="n">
-        <v>36.27675192984302</v>
+        <v>36.27675223117245</v>
       </c>
       <c r="BX60" t="n">
-        <v>32.64907673685872</v>
+        <v>32.64907700805521</v>
       </c>
       <c r="BY60" t="n">
         <v>8</v>
@@ -30794,10 +30794,10 @@
         <v>4</v>
       </c>
       <c r="CB60" t="n">
-        <v>-14.75436713516635</v>
+        <v>-14.75436642708152</v>
       </c>
       <c r="CC60" t="n">
-        <v>4.88527336040363</v>
+        <v>4.885273548610281</v>
       </c>
       <c r="CD60" t="inlineStr">
         <is>
@@ -31046,35 +31046,35 @@
         <v>23.48999977111816</v>
       </c>
       <c r="BN61" t="n">
-        <v>22.17988064860755</v>
+        <v>22.17988068119308</v>
       </c>
       <c r="BO61" t="n">
-        <v>27.69794443485965</v>
+        <v>27.69794444356835</v>
       </c>
       <c r="BP61" t="n">
-        <v>36.25062288024533</v>
+        <v>36.2506228383856</v>
       </c>
       <c r="BQ61" t="n">
         <v>59.33971209695032</v>
       </c>
       <c r="BR61" t="n">
-        <v>63.91526263041902</v>
+        <v>63.91526266085211</v>
       </c>
       <c r="BS61" t="n">
-        <v>39.66512977895086</v>
+        <v>39.66512977433361</v>
       </c>
       <c r="BT61" t="n">
-        <v>17.2633541023851</v>
+        <v>17.26335407190329</v>
       </c>
       <c r="BU61" t="inlineStr"/>
       <c r="BV61" t="n">
-        <v>38.04455808177398</v>
+        <v>38.04455808102663</v>
       </c>
       <c r="BW61" t="n">
-        <v>36.25062288024533</v>
+        <v>36.2506228383856</v>
       </c>
       <c r="BX61" t="n">
-        <v>32.6255605922208</v>
+        <v>32.62556055454704</v>
       </c>
       <c r="BY61" t="n">
         <v>7</v>
@@ -31086,10 +31086,10 @@
         <v>3.7</v>
       </c>
       <c r="CB61" t="n">
-        <v>38.89127675656749</v>
+        <v>38.89127659618539</v>
       </c>
       <c r="CC61" t="n">
-        <v>61.96065752436144</v>
+        <v>61.9606575211799</v>
       </c>
       <c r="CD61" t="inlineStr">
         <is>
@@ -31338,10 +31338,10 @@
         <v>17</v>
       </c>
       <c r="BN62" t="n">
-        <v>3.911866922919081</v>
+        <v>3.911866898059126</v>
       </c>
       <c r="BO62" t="n">
-        <v>7.256513142014896</v>
+        <v>7.256513095899678</v>
       </c>
       <c r="BP62" t="n">
         <v>26.9115890083632</v>
@@ -31350,13 +31350,13 @@
         <v>33.31412657095888</v>
       </c>
       <c r="BR62" t="n">
-        <v>18.89988484716407</v>
+        <v>18.89988483457398</v>
       </c>
       <c r="BS62" t="n">
-        <v>21.61167740528777</v>
+        <v>21.61167740819574</v>
       </c>
       <c r="BT62" t="n">
-        <v>13.19293320873089</v>
+        <v>13.19293322695423</v>
       </c>
       <c r="BU62" t="n">
         <v>22.22798951537628</v>
@@ -31408,7 +31408,7 @@
         <v>-3.46060875008245</v>
       </c>
       <c r="CP62" t="n">
-        <v>-41.31434450940703</v>
+        <v>-41.31434850403859</v>
       </c>
       <c r="CQ62" t="b">
         <v>0</v>
@@ -31622,10 +31622,10 @@
         <v>16.31999969482422</v>
       </c>
       <c r="BN63" t="n">
-        <v>4.116375327880321</v>
+        <v>4.116375336048228</v>
       </c>
       <c r="BO63" t="n">
-        <v>7.635876233217995</v>
+        <v>7.635876248369462</v>
       </c>
       <c r="BP63" t="n">
         <v>51.98076825875502</v>
@@ -31634,13 +31634,13 @@
         <v>57.88026518876954</v>
       </c>
       <c r="BR63" t="n">
-        <v>48.62627511622589</v>
+        <v>48.626275131833</v>
       </c>
       <c r="BS63" t="n">
-        <v>40.3445932340031</v>
+        <v>40.34459323288075</v>
       </c>
       <c r="BT63" t="n">
-        <v>32.33758976041154</v>
+        <v>32.33758975294345</v>
       </c>
       <c r="BU63" t="n">
         <v>33.29124944271519</v>
@@ -31902,10 +31902,10 @@
         <v>23.60000038146973</v>
       </c>
       <c r="BN64" t="n">
-        <v>4.133363639119587</v>
+        <v>4.133363617577428</v>
       </c>
       <c r="BO64" t="n">
-        <v>7.667389550566833</v>
+        <v>7.667389510606129</v>
       </c>
       <c r="BP64" t="n">
         <v>27.31004410956103</v>
@@ -31914,25 +31914,25 @@
         <v>27.193785526638</v>
       </c>
       <c r="BR64" t="n">
-        <v>24.22216032649872</v>
+        <v>24.22216033915458</v>
       </c>
       <c r="BS64" t="n">
-        <v>10.54144134154074</v>
+        <v>10.54144128842582</v>
       </c>
       <c r="BT64" t="n">
-        <v>17.55480030209261</v>
+        <v>17.55480032660414</v>
       </c>
       <c r="BU64" t="n">
         <v>16.32128907814843</v>
       </c>
       <c r="BV64" t="n">
-        <v>18.68727289072091</v>
+        <v>18.68727288273402</v>
       </c>
       <c r="BW64" t="n">
-        <v>17.55480030209261</v>
+        <v>17.55480032660414</v>
       </c>
       <c r="BX64" t="n">
-        <v>15.79932027188335</v>
+        <v>15.79932029394373</v>
       </c>
       <c r="BY64" t="n">
         <v>7</v>
@@ -31944,10 +31944,10 @@
         <v>6.6</v>
       </c>
       <c r="CB64" t="n">
-        <v>-33.05372874362884</v>
+        <v>-33.05372865015266</v>
       </c>
       <c r="CC64" t="n">
-        <v>-20.81664157347301</v>
+        <v>-20.81664160731577</v>
       </c>
       <c r="CD64" t="inlineStr">
         <is>
@@ -32196,37 +32196,37 @@
         <v>30.13999938964844</v>
       </c>
       <c r="BN65" t="n">
-        <v>13.85397094329265</v>
+        <v>13.85397106991537</v>
       </c>
       <c r="BO65" t="n">
-        <v>14.30392291287269</v>
+        <v>14.30392293822647</v>
       </c>
       <c r="BP65" t="n">
-        <v>14.87803220816694</v>
+        <v>14.87803209855589</v>
       </c>
       <c r="BQ65" t="n">
         <v>30.20046083334148</v>
       </c>
       <c r="BR65" t="n">
-        <v>13.76466415936448</v>
+        <v>13.76466409986214</v>
       </c>
       <c r="BS65" t="n">
-        <v>29.79376867851225</v>
+        <v>29.79376865230282</v>
       </c>
       <c r="BT65" t="n">
-        <v>5.881118202902866</v>
+        <v>5.881118090917732</v>
       </c>
       <c r="BU65" t="n">
         <v>38.90017075407383</v>
       </c>
       <c r="BV65" t="n">
-        <v>17.52513399120762</v>
+        <v>17.52513396901741</v>
       </c>
       <c r="BW65" t="n">
-        <v>14.30392291287269</v>
+        <v>14.30392293822647</v>
       </c>
       <c r="BX65" t="n">
-        <v>12.87353062158542</v>
+        <v>12.87353064440382</v>
       </c>
       <c r="BY65" t="n">
         <v>7</v>
@@ -32238,10 +32238,10 @@
         <v>6.6</v>
       </c>
       <c r="CB65" t="n">
-        <v>-57.28755513509789</v>
+        <v>-57.28755505938985</v>
       </c>
       <c r="CC65" t="n">
-        <v>-41.85423242833038</v>
+        <v>-41.85423250195417</v>
       </c>
       <c r="CD65" t="inlineStr">
         <is>
@@ -32490,10 +32490,10 @@
         <v>13.9399995803833</v>
       </c>
       <c r="BN66" t="n">
-        <v>9.123776622980419</v>
+        <v>9.12377660539566</v>
       </c>
       <c r="BO66" t="n">
-        <v>16.92460563562868</v>
+        <v>16.92460560300895</v>
       </c>
       <c r="BP66" t="n">
         <v>13.57127071565604</v>
@@ -32514,7 +32514,7 @@
         <v>12.4245083187292</v>
       </c>
       <c r="BV66" t="n">
-        <v>14.60394185756138</v>
+        <v>14.60394185128582</v>
       </c>
       <c r="BW66" t="n">
         <v>12.94835109589414</v>
@@ -32535,7 +32535,7 @@
         <v>-16.40232182859006</v>
       </c>
       <c r="CC66" t="n">
-        <v>4.762857224991568</v>
+        <v>4.762857179973201</v>
       </c>
       <c r="CD66" t="inlineStr">
         <is>
@@ -32784,10 +32784,10 @@
         <v>8.720000267028809</v>
       </c>
       <c r="BN67" t="n">
-        <v>1.668744297970873</v>
+        <v>1.668744295648186</v>
       </c>
       <c r="BO67" t="n">
-        <v>3.09552067273597</v>
+        <v>3.095520668427385</v>
       </c>
       <c r="BP67" t="n">
         <v>22.97017962984726</v>
@@ -32796,13 +32796,13 @@
         <v>22.70135587940091</v>
       </c>
       <c r="BR67" t="n">
-        <v>24.2492799264474</v>
+        <v>24.24927992423272</v>
       </c>
       <c r="BS67" t="n">
-        <v>6.453369682050942</v>
+        <v>6.453369682193078</v>
       </c>
       <c r="BT67" t="n">
-        <v>16.9541158639752</v>
+        <v>16.95411586664666</v>
       </c>
       <c r="BU67" t="n">
         <v>26.03006316116035</v>
@@ -33050,35 +33050,35 @@
         <v>12.30000019073486</v>
       </c>
       <c r="BN68" t="n">
-        <v>10.05632369243019</v>
+        <v>10.05632368334559</v>
       </c>
       <c r="BO68" t="n">
-        <v>10.7547086058028</v>
+        <v>10.75470861182058</v>
       </c>
       <c r="BP68" t="n">
-        <v>11.21224212827102</v>
+        <v>11.21224214467363</v>
       </c>
       <c r="BQ68" t="n">
         <v>15.69034148938449</v>
       </c>
       <c r="BR68" t="n">
-        <v>17.98047494261398</v>
+        <v>17.98047495249218</v>
       </c>
       <c r="BS68" t="n">
-        <v>23.65338612592986</v>
+        <v>23.65338610856754</v>
       </c>
       <c r="BT68" t="n">
-        <v>4.662743542398654</v>
+        <v>4.662743558147716</v>
       </c>
       <c r="BU68" t="inlineStr"/>
       <c r="BV68" t="n">
-        <v>13.91916513810847</v>
+        <v>13.91916513710184</v>
       </c>
       <c r="BW68" t="n">
-        <v>10.98347536703691</v>
+        <v>10.98347537824711</v>
       </c>
       <c r="BX68" t="n">
-        <v>9.88512783033322</v>
+        <v>9.885127840422399</v>
       </c>
       <c r="BY68" t="n">
         <v>4</v>
@@ -33090,10 +33090,10 @@
         <v>2.4</v>
       </c>
       <c r="CB68" t="n">
-        <v>-19.63310831670294</v>
+        <v>-19.63310823467709</v>
       </c>
       <c r="CC68" t="n">
-        <v>13.1639424574421</v>
+        <v>13.16394244925812</v>
       </c>
       <c r="CD68" t="inlineStr">
         <is>
@@ -33342,10 +33342,10 @@
         <v>3.269999980926514</v>
       </c>
       <c r="BN69" t="n">
-        <v>0.7957444718177528</v>
+        <v>0.7957444721106625</v>
       </c>
       <c r="BO69" t="n">
-        <v>1.476105995221931</v>
+        <v>1.476105995765279</v>
       </c>
       <c r="BP69" t="n">
         <v>9.337823221395755</v>
@@ -33354,7 +33354,7 @@
         <v>4.448661621270232</v>
       </c>
       <c r="BR69" t="n">
-        <v>12.97207377572117</v>
+        <v>12.97207377660495</v>
       </c>
       <c r="BS69" t="n">
         <v>6.795306578521528</v>
@@ -33626,10 +33626,10 @@
         <v>15.01000022888184</v>
       </c>
       <c r="BN70" t="n">
-        <v>3.646640788526717</v>
+        <v>3.646640785754632</v>
       </c>
       <c r="BO70" t="n">
-        <v>6.764518662717059</v>
+        <v>6.764518657574841</v>
       </c>
       <c r="BP70" t="n">
         <v>32.49714101841246</v>
@@ -33638,13 +33638,13 @@
         <v>35.16080790586962</v>
       </c>
       <c r="BR70" t="n">
-        <v>29.70492049891628</v>
+        <v>29.70492049684392</v>
       </c>
       <c r="BS70" t="n">
-        <v>11.2005546860463</v>
+        <v>11.20055468622563</v>
       </c>
       <c r="BT70" t="n">
-        <v>19.98011276614524</v>
+        <v>19.98011276882862</v>
       </c>
       <c r="BU70" t="n">
         <v>43.92869987016114</v>
@@ -33910,10 +33910,10 @@
         <v>29.09000015258789</v>
       </c>
       <c r="BN71" t="n">
-        <v>12.61857463123294</v>
+        <v>12.61857464636938</v>
       </c>
       <c r="BO71" t="n">
-        <v>23.40745594093709</v>
+        <v>23.4074559690152</v>
       </c>
       <c r="BP71" t="n">
         <v>36.84918757378484</v>
@@ -33922,19 +33922,19 @@
         <v>25.68115779228379</v>
       </c>
       <c r="BR71" t="n">
-        <v>43.64068775012397</v>
+        <v>43.64068771450234</v>
       </c>
       <c r="BS71" t="n">
-        <v>34.41130752344905</v>
+        <v>34.41130751714145</v>
       </c>
       <c r="BT71" t="n">
-        <v>24.24471208114108</v>
+        <v>24.24471204601605</v>
       </c>
       <c r="BU71" t="n">
         <v>26.21217804663085</v>
       </c>
       <c r="BV71" t="n">
-        <v>28.38315766744795</v>
+        <v>28.38315766321799</v>
       </c>
       <c r="BW71" t="n">
         <v>25.94666791945733</v>
@@ -33955,7 +33955,7 @@
         <v>-19.72498795111156</v>
       </c>
       <c r="CC71" t="n">
-        <v>-2.429846962641058</v>
+        <v>-2.429846977182015</v>
       </c>
       <c r="CD71" t="inlineStr">
         <is>
@@ -34212,37 +34212,37 @@
         <v>18.59000015258789</v>
       </c>
       <c r="BN72" t="n">
-        <v>8.037513557640541</v>
+        <v>8.037513582735578</v>
       </c>
       <c r="BO72" t="n">
-        <v>9.133497110625072</v>
+        <v>9.133497109673302</v>
       </c>
       <c r="BP72" t="n">
-        <v>10.32094258891298</v>
+        <v>10.32094255561303</v>
       </c>
       <c r="BQ72" t="n">
         <v>16.7309332137301</v>
       </c>
       <c r="BR72" t="n">
-        <v>9.598482629513516</v>
+        <v>9.598482607871365</v>
       </c>
       <c r="BS72" t="n">
-        <v>19.39667778541997</v>
+        <v>19.3966777785555</v>
       </c>
       <c r="BT72" t="n">
-        <v>4.592274362850125</v>
+        <v>4.592274334141401</v>
       </c>
       <c r="BU72" t="n">
         <v>17.43118727772496</v>
       </c>
       <c r="BV72" t="n">
-        <v>11.90518856580216</v>
+        <v>11.90518855750565</v>
       </c>
       <c r="BW72" t="n">
-        <v>9.959712609213248</v>
+        <v>9.959712581742195</v>
       </c>
       <c r="BX72" t="n">
-        <v>8.963741348291924</v>
+        <v>8.963741323567977</v>
       </c>
       <c r="BY72" t="n">
         <v>8</v>
@@ -34254,10 +34254,10 @@
         <v>4.2</v>
       </c>
       <c r="CB72" t="n">
-        <v>-51.78191890953754</v>
+        <v>-51.78191904253349</v>
       </c>
       <c r="CC72" t="n">
-        <v>-35.95917983817309</v>
+        <v>-35.95917988280195</v>
       </c>
       <c r="CD72" t="inlineStr">
         <is>
@@ -34510,10 +34510,10 @@
         <v>14.02999973297119</v>
       </c>
       <c r="BN73" t="n">
-        <v>2.263579259975582</v>
+        <v>2.263579260392731</v>
       </c>
       <c r="BO73" t="n">
-        <v>4.198939527254703</v>
+        <v>4.198939528028516</v>
       </c>
       <c r="BP73" t="n">
         <v>24.81942542882086</v>
@@ -34522,7 +34522,7 @@
         <v>18.98830018964925</v>
       </c>
       <c r="BR73" t="n">
-        <v>32.32845202059092</v>
+        <v>32.32845202137064</v>
       </c>
       <c r="BS73" t="n">
         <v>11.58009282301775</v>
@@ -34794,10 +34794,10 @@
         <v>10.68000030517578</v>
       </c>
       <c r="BN74" t="n">
-        <v>6.305613035240026</v>
+        <v>6.305613026207125</v>
       </c>
       <c r="BO74" t="n">
-        <v>11.69691218037025</v>
+        <v>11.69691216361421</v>
       </c>
       <c r="BP74" t="n">
         <v>7.624461424761804</v>
@@ -34818,7 +34818,7 @@
         <v>35.54000257500483</v>
       </c>
       <c r="BV74" t="n">
-        <v>9.873483622261094</v>
+        <v>9.873483618576961</v>
       </c>
       <c r="BW74" t="n">
         <v>7.624461424761804</v>
@@ -34839,7 +34839,7 @@
         <v>-35.74892241379312</v>
       </c>
       <c r="CC74" t="n">
-        <v>-7.551654118622353</v>
+        <v>-7.551654153117992</v>
       </c>
       <c r="CD74" t="inlineStr">
         <is>
@@ -35088,10 +35088,10 @@
         <v>33.16999816894531</v>
       </c>
       <c r="BN75" t="n">
-        <v>9.494426962761574</v>
+        <v>9.494426963696826</v>
       </c>
       <c r="BO75" t="n">
-        <v>17.61216201592272</v>
+        <v>17.61216201765761</v>
       </c>
       <c r="BP75" t="n">
         <v>26.65266681252428</v>
@@ -35100,25 +35100,25 @@
         <v>19.74676755649356</v>
       </c>
       <c r="BR75" t="n">
-        <v>23.99252024317966</v>
+        <v>23.99252024091635</v>
       </c>
       <c r="BS75" t="n">
-        <v>20.91381300398068</v>
+        <v>20.91381300368614</v>
       </c>
       <c r="BT75" t="n">
-        <v>15.38788498325659</v>
+        <v>15.38788498133483</v>
       </c>
       <c r="BU75" t="n">
         <v>26.56395252902917</v>
       </c>
       <c r="BV75" t="n">
-        <v>20.04552426339353</v>
+        <v>20.04552426316734</v>
       </c>
       <c r="BW75" t="n">
-        <v>20.33029028023712</v>
+        <v>20.33029028008985</v>
       </c>
       <c r="BX75" t="n">
-        <v>18.29726125221341</v>
+        <v>18.29726125208087</v>
       </c>
       <c r="BY75" t="n">
         <v>8</v>
@@ -35130,10 +35130,10 @@
         <v>2.8</v>
       </c>
       <c r="CB75" t="n">
-        <v>-44.83791901639651</v>
+        <v>-44.8379190167961</v>
       </c>
       <c r="CC75" t="n">
-        <v>-39.56730367817531</v>
+        <v>-39.56730367885721</v>
       </c>
       <c r="CD75" t="inlineStr">
         <is>
@@ -35382,10 +35382,10 @@
         <v>40.38000106811523</v>
       </c>
       <c r="BN76" t="n">
-        <v>8.83464330698191</v>
+        <v>8.834643310099619</v>
       </c>
       <c r="BO76" t="n">
-        <v>16.38826333445144</v>
+        <v>16.38826334023479</v>
       </c>
       <c r="BP76" t="n">
         <v>116.5653625604633</v>
@@ -35394,7 +35394,7 @@
         <v>85.63237581561071</v>
       </c>
       <c r="BR76" t="n">
-        <v>158.9074122700382</v>
+        <v>158.9074122795475</v>
       </c>
       <c r="BS76" t="n">
         <v>21.83399299607427</v>
@@ -35664,35 +35664,35 @@
         <v>3.289999961853027</v>
       </c>
       <c r="BN77" t="n">
-        <v>2.525405067601556</v>
+        <v>2.525405085572467</v>
       </c>
       <c r="BO77" t="n">
-        <v>3.007784118450875</v>
+        <v>3.007784124692137</v>
       </c>
       <c r="BP77" t="n">
-        <v>3.802819017920141</v>
+        <v>3.802818998750075</v>
       </c>
       <c r="BQ77" t="n">
         <v>6.826829719365466</v>
       </c>
       <c r="BR77" t="n">
-        <v>5.701854068221336</v>
+        <v>5.701854078227071</v>
       </c>
       <c r="BS77" t="n">
-        <v>7.599863477830389</v>
+        <v>7.599863473800712</v>
       </c>
       <c r="BT77" t="n">
-        <v>1.758674092928485</v>
+        <v>1.758674077730844</v>
       </c>
       <c r="BU77" t="inlineStr"/>
       <c r="BV77" t="n">
-        <v>4.460461366045464</v>
+        <v>4.460461365448396</v>
       </c>
       <c r="BW77" t="n">
-        <v>3.802819017920141</v>
+        <v>3.802818998750075</v>
       </c>
       <c r="BX77" t="n">
-        <v>3.422537116128127</v>
+        <v>3.422537098875067</v>
       </c>
       <c r="BY77" t="n">
         <v>7</v>
@@ -35704,10 +35704,10 @@
         <v>4.3</v>
       </c>
       <c r="CB77" t="n">
-        <v>4.028484979083413</v>
+        <v>4.028484454674319</v>
       </c>
       <c r="CC77" t="n">
-        <v>35.57633488643559</v>
+        <v>35.57633486828766</v>
       </c>
       <c r="CD77" t="inlineStr">
         <is>
@@ -35954,10 +35954,10 @@
         <v>57.90000152587891</v>
       </c>
       <c r="BN78" t="n">
-        <v>42.10777042030023</v>
+        <v>42.10777059497064</v>
       </c>
       <c r="BO78" t="n">
-        <v>61.30891373195714</v>
+        <v>61.30891398627725</v>
       </c>
       <c r="BP78" t="n">
         <v>35.44202565445207</v>
@@ -35976,13 +35976,13 @@
         <v>47.85923110896672</v>
       </c>
       <c r="BV78" t="n">
-        <v>43.59743299940729</v>
+        <v>43.59743307090571</v>
       </c>
       <c r="BW78" t="n">
-        <v>41.59695184621908</v>
+        <v>41.59695193355429</v>
       </c>
       <c r="BX78" t="n">
-        <v>37.43725666159717</v>
+        <v>37.43725674019886</v>
       </c>
       <c r="BY78" t="n">
         <v>6</v>
@@ -35994,10 +35994,10 @@
         <v>6.7</v>
       </c>
       <c r="CB78" t="n">
-        <v>-35.34152733162836</v>
+        <v>-35.34152719587416</v>
       </c>
       <c r="CC78" t="n">
-        <v>-24.70219024101228</v>
+        <v>-24.70219011752624</v>
       </c>
       <c r="CD78" t="inlineStr">
         <is>
@@ -36528,10 +36528,10 @@
         <v>30.98999977111816</v>
       </c>
       <c r="BN80" t="n">
-        <v>9.784912721442671</v>
+        <v>9.784912683607681</v>
       </c>
       <c r="BO80" t="n">
-        <v>18.15101309827615</v>
+        <v>18.15101302809225</v>
       </c>
       <c r="BP80" t="n">
         <v>35.58210545643983</v>
@@ -36540,25 +36540,25 @@
         <v>29.86072035143237</v>
       </c>
       <c r="BR80" t="n">
-        <v>35.8007078092272</v>
+        <v>35.80070785967745</v>
       </c>
       <c r="BS80" t="n">
-        <v>19.53056351211559</v>
+        <v>19.5305635185496</v>
       </c>
       <c r="BT80" t="n">
-        <v>22.21563644219314</v>
+        <v>22.21563650275636</v>
       </c>
       <c r="BU80" t="n">
         <v>16.06212703391342</v>
       </c>
       <c r="BV80" t="n">
-        <v>23.37347330313004</v>
+        <v>23.37347330430862</v>
       </c>
       <c r="BW80" t="n">
-        <v>20.87309997715436</v>
+        <v>20.87310001065298</v>
       </c>
       <c r="BX80" t="n">
-        <v>18.78578997943893</v>
+        <v>18.78579000958768</v>
       </c>
       <c r="BY80" t="n">
         <v>8</v>
@@ -36570,10 +36570,10 @@
         <v>3.7</v>
       </c>
       <c r="CB80" t="n">
-        <v>-39.38112256152137</v>
+        <v>-39.38112246423594</v>
       </c>
       <c r="CC80" t="n">
-        <v>-24.5773685841925</v>
+        <v>-24.5773685803894</v>
       </c>
       <c r="CD80" t="inlineStr">
         <is>
@@ -36822,10 +36822,10 @@
         <v>24.15999984741211</v>
       </c>
       <c r="BN81" t="n">
-        <v>11.69546840387669</v>
+        <v>11.69546843022248</v>
       </c>
       <c r="BO81" t="n">
-        <v>21.69509388919126</v>
+        <v>21.6950939380627</v>
       </c>
       <c r="BP81" t="n">
         <v>14.33587093498479</v>
@@ -36846,7 +36846,7 @@
         <v>20.88570664769529</v>
       </c>
       <c r="BV81" t="n">
-        <v>18.8117771150322</v>
+        <v>18.81177712443436</v>
       </c>
       <c r="BW81" t="n">
         <v>17.61078879134004</v>
@@ -36867,7 +36867,7 @@
         <v>-34.39689564441875</v>
       </c>
       <c r="CC81" t="n">
-        <v>-22.13668363475912</v>
+        <v>-22.13668359584292</v>
       </c>
       <c r="CD81" t="inlineStr">
         <is>
@@ -37116,10 +37116,10 @@
         <v>6.010000228881836</v>
       </c>
       <c r="BN82" t="n">
-        <v>1.077283896123123</v>
+        <v>1.077283893799789</v>
       </c>
       <c r="BO82" t="n">
-        <v>1.998361627308394</v>
+        <v>1.998361622998609</v>
       </c>
       <c r="BP82" t="n">
         <v>10.00408329556336</v>
@@ -37128,13 +37128,13 @@
         <v>9.814231118279432</v>
       </c>
       <c r="BR82" t="n">
-        <v>9.918568250839762</v>
+        <v>9.918568251073038</v>
       </c>
       <c r="BS82" t="n">
-        <v>1.795623135730037</v>
+        <v>1.795623135822897</v>
       </c>
       <c r="BT82" t="n">
-        <v>7.060557263035136</v>
+        <v>7.060557265750276</v>
       </c>
       <c r="BU82" t="n">
         <v>9.241541426150913</v>
@@ -37400,25 +37400,25 @@
         <v>26.04999923706055</v>
       </c>
       <c r="BN83" t="n">
-        <v>11.33091885010903</v>
+        <v>11.33091892680614</v>
       </c>
       <c r="BO83" t="n">
-        <v>12.12045518006266</v>
+        <v>12.12045521665131</v>
       </c>
       <c r="BP83" t="n">
-        <v>13.63266064885216</v>
+        <v>13.63266059772857</v>
       </c>
       <c r="BQ83" t="n">
         <v>31.41012129143711</v>
       </c>
       <c r="BR83" t="n">
-        <v>12.3041276679862</v>
+        <v>12.30412766346905</v>
       </c>
       <c r="BS83" t="n">
-        <v>23.32462262412813</v>
+        <v>23.32462261400505</v>
       </c>
       <c r="BT83" t="n">
-        <v>5.670915322482868</v>
+        <v>5.670915273415123</v>
       </c>
       <c r="BU83" t="n">
         <v>51.82639978137158</v>
@@ -37964,10 +37964,10 @@
         <v>5.090000152587891</v>
       </c>
       <c r="BN85" t="n">
-        <v>3.010385661524102</v>
+        <v>3.010385674157753</v>
       </c>
       <c r="BO85" t="n">
-        <v>4.383121523179094</v>
+        <v>4.383121541573688</v>
       </c>
       <c r="BP85" t="n">
         <v>3.927003085082646</v>
@@ -38246,37 +38246,37 @@
         <v>49.43000030517578</v>
       </c>
       <c r="BN86" t="n">
-        <v>15.09930991468122</v>
+        <v>15.09930992193307</v>
       </c>
       <c r="BO86" t="n">
-        <v>23.31094171854089</v>
+        <v>23.31094172285921</v>
       </c>
       <c r="BP86" t="n">
-        <v>43.05579287532063</v>
+        <v>43.05579286261796</v>
       </c>
       <c r="BQ86" t="n">
         <v>58.9399838960196</v>
       </c>
       <c r="BR86" t="n">
-        <v>34.35202648118085</v>
+        <v>34.35202647918983</v>
       </c>
       <c r="BS86" t="n">
-        <v>20.00393888360178</v>
+        <v>20.00393888311108</v>
       </c>
       <c r="BT86" t="n">
-        <v>21.52751972545839</v>
+        <v>21.5275197191661</v>
       </c>
       <c r="BU86" t="n">
         <v>21.42321827789122</v>
       </c>
       <c r="BV86" t="n">
-        <v>25.53896398238214</v>
+        <v>25.53896398096692</v>
       </c>
       <c r="BW86" t="n">
-        <v>21.52751972545839</v>
+        <v>21.5275197191661</v>
       </c>
       <c r="BX86" t="n">
-        <v>19.37476775291255</v>
+        <v>19.37476774724949</v>
       </c>
       <c r="BY86" t="n">
         <v>7</v>
@@ -38288,10 +38288,10 @@
         <v>3.9</v>
       </c>
       <c r="CB86" t="n">
-        <v>-60.8036260706156</v>
+        <v>-60.80362608207233</v>
       </c>
       <c r="CC86" t="n">
-        <v>-48.33306934107387</v>
+        <v>-48.33306934393696</v>
       </c>
       <c r="CD86" t="inlineStr">
         <is>
@@ -38550,10 +38550,10 @@
         <v>74.40000152587891</v>
       </c>
       <c r="BN87" t="n">
-        <v>67.74477295119283</v>
+        <v>67.74477266881908</v>
       </c>
       <c r="BO87" t="n">
-        <v>98.63638941693677</v>
+        <v>98.63638900580059</v>
       </c>
       <c r="BP87" t="n">
         <v>23.80067720298803</v>
@@ -38832,10 +38832,10 @@
         <v>34.70999908447266</v>
       </c>
       <c r="BN88" t="n">
-        <v>8.573258052271054</v>
+        <v>8.573258013423178</v>
       </c>
       <c r="BO88" t="n">
-        <v>15.9033936869628</v>
+        <v>15.9033936149</v>
       </c>
       <c r="BP88" t="n">
         <v>38.58284294205224</v>
@@ -38844,19 +38844,19 @@
         <v>38.8078211315257</v>
       </c>
       <c r="BR88" t="n">
-        <v>31.68748500867603</v>
+        <v>31.68748503174015</v>
       </c>
       <c r="BS88" t="n">
-        <v>46.19482504037982</v>
+        <v>46.19482505052388</v>
       </c>
       <c r="BT88" t="n">
-        <v>21.36756352582433</v>
+        <v>21.36756356900142</v>
       </c>
       <c r="BU88" t="n">
         <v>38.23996334747979</v>
       </c>
       <c r="BV88" t="n">
-        <v>32.96912781184296</v>
+        <v>32.96912781246045</v>
       </c>
       <c r="BW88" t="n">
         <v>38.23996334747979</v>
@@ -38877,7 +38877,7 @@
         <v>-0.8471105718708571</v>
       </c>
       <c r="CC88" t="n">
-        <v>-5.015474844562783</v>
+        <v>-5.015474842783785</v>
       </c>
       <c r="CD88" t="inlineStr">
         <is>
@@ -39134,10 +39134,10 @@
         <v>11</v>
       </c>
       <c r="BN89" t="n">
-        <v>1.815788317870673</v>
+        <v>1.815788320424584</v>
       </c>
       <c r="BO89" t="n">
-        <v>3.368287329650099</v>
+        <v>3.368287334387603</v>
       </c>
       <c r="BP89" t="n">
         <v>11.4763779527559</v>
@@ -39146,19 +39146,19 @@
         <v>10.25101809243598</v>
       </c>
       <c r="BR89" t="n">
-        <v>11.81091623893932</v>
+        <v>11.81091623602316</v>
       </c>
       <c r="BS89" t="n">
-        <v>6.25228616893123</v>
+        <v>6.252286168559588</v>
       </c>
       <c r="BT89" t="n">
-        <v>8.479656232295786</v>
+        <v>8.479656228693139</v>
       </c>
       <c r="BU89" t="n">
         <v>9.119823240596812</v>
       </c>
       <c r="BV89" t="n">
-        <v>9.565012987659172</v>
+        <v>9.565012986510764</v>
       </c>
       <c r="BW89" t="n">
         <v>9.685420666516395</v>
@@ -39179,7 +39179,7 @@
         <v>-20.75564909213859</v>
       </c>
       <c r="CC89" t="n">
-        <v>-13.04533647582571</v>
+        <v>-13.04533648626578</v>
       </c>
       <c r="CD89" t="inlineStr">
         <is>
@@ -39428,10 +39428,10 @@
         <v>18.28000068664551</v>
       </c>
       <c r="BN90" t="n">
-        <v>1.883948384382995</v>
+        <v>1.883948388066104</v>
       </c>
       <c r="BO90" t="n">
-        <v>3.494724253030455</v>
+        <v>3.494724259862622</v>
       </c>
       <c r="BP90" t="n">
         <v>9.5735181461681</v>
@@ -39440,19 +39440,19 @@
         <v>7.985723111152071</v>
       </c>
       <c r="BR90" t="n">
-        <v>9.488583766996632</v>
+        <v>9.488583759541873</v>
       </c>
       <c r="BS90" t="n">
-        <v>6.411779241878547</v>
+        <v>6.411779241124313</v>
       </c>
       <c r="BT90" t="n">
-        <v>7.239152666879412</v>
+        <v>7.239152660912481</v>
       </c>
       <c r="BU90" t="n">
         <v>12.36591560593228</v>
       </c>
       <c r="BV90" t="n">
-        <v>8.079913827433929</v>
+        <v>8.07991382638482</v>
       </c>
       <c r="BW90" t="n">
         <v>7.985723111152071</v>
@@ -39473,7 +39473,7 @@
         <v>-60.68298397117976</v>
       </c>
       <c r="CC90" t="n">
-        <v>-55.79916015355116</v>
+        <v>-55.79916015929027</v>
       </c>
       <c r="CD90" t="inlineStr">
         <is>
@@ -39720,35 +39720,35 @@
         <v>1.990000009536743</v>
       </c>
       <c r="BN91" t="n">
-        <v>0.9124357700774366</v>
+        <v>0.9124357684213066</v>
       </c>
       <c r="BO91" t="n">
-        <v>1.241127160223609</v>
+        <v>1.241127158498317</v>
       </c>
       <c r="BP91" t="n">
-        <v>3.088621474643285</v>
+        <v>3.088621475955837</v>
       </c>
       <c r="BQ91" t="n">
         <v>6.377098847417107</v>
       </c>
       <c r="BR91" t="n">
-        <v>3.109236244518506</v>
+        <v>3.109236242117744</v>
       </c>
       <c r="BS91" t="n">
-        <v>2.200587259929066</v>
+        <v>2.200587256022127</v>
       </c>
       <c r="BT91" t="n">
-        <v>1.520943858069026</v>
+        <v>1.520943858888082</v>
       </c>
       <c r="BU91" t="inlineStr"/>
       <c r="BV91" t="n">
-        <v>2.012158627910155</v>
+        <v>2.012158626650569</v>
       </c>
       <c r="BW91" t="n">
-        <v>1.860765558999046</v>
+        <v>1.860765557455104</v>
       </c>
       <c r="BX91" t="n">
-        <v>1.674689003099141</v>
+        <v>1.674689001709594</v>
       </c>
       <c r="BY91" t="n">
         <v>6</v>
@@ -39760,10 +39760,10 @@
         <v>7</v>
       </c>
       <c r="CB91" t="n">
-        <v>-15.84477411691086</v>
+        <v>-15.84477418673739</v>
       </c>
       <c r="CC91" t="n">
-        <v>1.113498405387947</v>
+        <v>1.113498342092156</v>
       </c>
       <c r="CD91" t="inlineStr">
         <is>
@@ -39998,35 +39998,35 @@
         <v>19.28000068664551</v>
       </c>
       <c r="BN92" t="n">
-        <v>11.48823748485973</v>
+        <v>11.48823744510509</v>
       </c>
       <c r="BO92" t="n">
-        <v>14.44345299318314</v>
+        <v>14.44345296816111</v>
       </c>
       <c r="BP92" t="n">
-        <v>21.69670307589647</v>
+        <v>21.69670311338947</v>
       </c>
       <c r="BQ92" t="n">
         <v>41.11506807497437</v>
       </c>
       <c r="BR92" t="n">
-        <v>26.38206890020495</v>
+        <v>26.38206887337113</v>
       </c>
       <c r="BS92" t="n">
-        <v>17.69598464381247</v>
+        <v>17.69598464687646</v>
       </c>
       <c r="BT92" t="n">
-        <v>10.36856045465285</v>
+        <v>10.36856048162557</v>
       </c>
       <c r="BU92" t="inlineStr"/>
       <c r="BV92" t="n">
-        <v>16.33109454943795</v>
+        <v>16.33109454338303</v>
       </c>
       <c r="BW92" t="n">
-        <v>16.0697188184978</v>
+        <v>16.06971880751879</v>
       </c>
       <c r="BX92" t="n">
-        <v>14.46274693664802</v>
+        <v>14.46274692676691</v>
       </c>
       <c r="BY92" t="n">
         <v>4</v>
@@ -40038,10 +40038,10 @@
         <v>1.9</v>
       </c>
       <c r="CB92" t="n">
-        <v>-24.98575507486472</v>
+        <v>-24.9857551261153</v>
       </c>
       <c r="CC92" t="n">
-        <v>-15.29515576858952</v>
+        <v>-15.29515579999467</v>
       </c>
       <c r="CD92" t="inlineStr">
         <is>
@@ -40300,10 +40300,10 @@
         <v>8.079999923706055</v>
       </c>
       <c r="BN93" t="n">
-        <v>0.479884668914265</v>
+        <v>0.4798846683386274</v>
       </c>
       <c r="BO93" t="n">
-        <v>0.8901860608359615</v>
+        <v>0.8901860597681539</v>
       </c>
       <c r="BP93" t="n">
         <v>9.465959238647676</v>
@@ -40312,13 +40312,13 @@
         <v>8.689746150922641</v>
       </c>
       <c r="BR93" t="n">
-        <v>10.4383620744639</v>
+        <v>10.43836207497712</v>
       </c>
       <c r="BS93" t="n">
-        <v>1.421542439196761</v>
+        <v>1.421542439218198</v>
       </c>
       <c r="BT93" t="n">
-        <v>8.096371772663966</v>
+        <v>8.096371773434445</v>
       </c>
       <c r="BU93" t="inlineStr"/>
       <c r="BV93" t="inlineStr"/>
@@ -40582,10 +40582,10 @@
         <v>6.860000133514404</v>
       </c>
       <c r="BN94" t="n">
-        <v>2.8531394607112</v>
+        <v>2.853139458759279</v>
       </c>
       <c r="BO94" t="n">
-        <v>5.292573699619275</v>
+        <v>5.292573695998461</v>
       </c>
       <c r="BP94" t="n">
         <v>13.11616187143807</v>
@@ -40594,13 +40594,13 @@
         <v>14.08650985127578</v>
       </c>
       <c r="BR94" t="n">
-        <v>12.30620919254138</v>
+        <v>12.30620919162593</v>
       </c>
       <c r="BS94" t="n">
-        <v>12.24172365466801</v>
+        <v>12.24172365501924</v>
       </c>
       <c r="BT94" t="n">
-        <v>6.756741752543419</v>
+        <v>6.756741754446622</v>
       </c>
       <c r="BU94" t="n">
         <v>69.89589803243278</v>
@@ -40866,10 +40866,10 @@
         <v>6.619999885559082</v>
       </c>
       <c r="BN95" t="n">
-        <v>2.937502855944204</v>
+        <v>2.937502855228401</v>
       </c>
       <c r="BO95" t="n">
-        <v>5.449067797776498</v>
+        <v>5.449067796448683</v>
       </c>
       <c r="BP95" t="inlineStr"/>
       <c r="BQ95" t="inlineStr"/>
@@ -40880,13 +40880,13 @@
         <v>8.770765162555669</v>
       </c>
       <c r="BV95" t="n">
-        <v>5.719111938758791</v>
+        <v>5.719111938077584</v>
       </c>
       <c r="BW95" t="n">
-        <v>5.449067797776498</v>
+        <v>5.449067796448683</v>
       </c>
       <c r="BX95" t="n">
-        <v>4.904161017998848</v>
+        <v>4.904161016803815</v>
       </c>
       <c r="BY95" t="n">
         <v>3</v>
@@ -40898,10 +40898,10 @@
         <v>3</v>
       </c>
       <c r="CB95" t="n">
-        <v>-25.91901657435339</v>
+        <v>-25.91901659240524</v>
       </c>
       <c r="CC95" t="n">
-        <v>-13.60857949205551</v>
+        <v>-13.60857950234563</v>
       </c>
       <c r="CD95" t="inlineStr">
         <is>
@@ -41148,10 +41148,10 @@
         <v>7.900000095367432</v>
       </c>
       <c r="BN96" t="n">
-        <v>5.082618185692953</v>
+        <v>5.082618185534834</v>
       </c>
       <c r="BO96" t="n">
-        <v>7.400292078368939</v>
+        <v>7.400292078138719</v>
       </c>
       <c r="BP96" t="n">
         <v>5.753501470015497</v>
@@ -41170,7 +41170,7 @@
         <v>6.990639790663585</v>
       </c>
       <c r="BV96" t="n">
-        <v>6.454531264468423</v>
+        <v>6.454531264403701</v>
       </c>
       <c r="BW96" t="n">
         <v>6.372070630339541</v>
@@ -41191,7 +41191,7 @@
         <v>-27.40679116360369</v>
       </c>
       <c r="CC96" t="n">
-        <v>-18.29707358796912</v>
+        <v>-18.29707358878837</v>
       </c>
       <c r="CD96" t="inlineStr">
         <is>
@@ -41420,10 +41420,10 @@
         <v>49.04999923706055</v>
       </c>
       <c r="BN97" t="n">
-        <v>10.25848665733576</v>
+        <v>10.25848666688068</v>
       </c>
       <c r="BO97" t="n">
-        <v>14.93635657308086</v>
+        <v>14.93635658697828</v>
       </c>
       <c r="BP97" t="inlineStr"/>
       <c r="BQ97" t="inlineStr"/>
@@ -41432,13 +41432,13 @@
       <c r="BT97" t="inlineStr"/>
       <c r="BU97" t="inlineStr"/>
       <c r="BV97" t="n">
-        <v>12.59742161520831</v>
+        <v>12.59742162692948</v>
       </c>
       <c r="BW97" t="n">
-        <v>12.59742161520831</v>
+        <v>12.59742162692948</v>
       </c>
       <c r="BX97" t="n">
-        <v>11.33767945368748</v>
+        <v>11.33767946423653</v>
       </c>
       <c r="BY97" t="n">
         <v>2</v>
@@ -41450,10 +41450,10 @@
         <v>1.5</v>
       </c>
       <c r="CB97" t="n">
-        <v>-76.88546456669238</v>
+        <v>-76.88546454518564</v>
       </c>
       <c r="CC97" t="n">
-        <v>-74.31718285188043</v>
+        <v>-74.31718282798406</v>
       </c>
       <c r="CD97" t="inlineStr">
         <is>
@@ -41500,7 +41500,7 @@
         <v>-13.07815174234251</v>
       </c>
       <c r="CP97" t="n">
-        <v>-24.21663509014712</v>
+        <v>-24.21663039984816</v>
       </c>
       <c r="CQ97" t="b">
         <v>0</v>
@@ -41716,10 +41716,10 @@
         <v>3.769999980926514</v>
       </c>
       <c r="BN98" t="n">
-        <v>34.95537528708254</v>
+        <v>34.95537497010807</v>
       </c>
       <c r="BO98" t="n">
-        <v>64.84222115753811</v>
+        <v>64.84222056955046</v>
       </c>
       <c r="BP98" t="n">
         <v>5.406114691263668</v>
@@ -41996,10 +41996,10 @@
         <v>21.04999923706055</v>
       </c>
       <c r="BN99" t="n">
-        <v>36.28933545596529</v>
+        <v>36.28933506768607</v>
       </c>
       <c r="BO99" t="n">
-        <v>67.31671727081562</v>
+        <v>67.31671655055766</v>
       </c>
       <c r="BP99" t="n">
         <v>25.63533914439818</v>
@@ -42018,7 +42018,7 @@
       </c>
       <c r="BU99" t="inlineStr"/>
       <c r="BV99" t="n">
-        <v>36.4788091163966</v>
+        <v>36.47880895803415</v>
       </c>
       <c r="BW99" t="n">
         <v>28.99450153171436</v>
@@ -42039,7 +42039,7 @@
         <v>23.966994414898</v>
       </c>
       <c r="CC99" t="n">
-        <v>73.29601158451425</v>
+        <v>73.29601083219852</v>
       </c>
       <c r="CD99" t="inlineStr">
         <is>
@@ -42288,10 +42288,10 @@
         <v>2.799999952316284</v>
       </c>
       <c r="BN100" t="n">
-        <v>0.5849893572384276</v>
+        <v>0.5849893577127721</v>
       </c>
       <c r="BO100" t="n">
-        <v>1.085155257677283</v>
+        <v>1.085155258557192</v>
       </c>
       <c r="BP100" t="n">
         <v>3.209342505898855</v>
@@ -42300,13 +42300,13 @@
         <v>3.337413992024261</v>
       </c>
       <c r="BR100" t="n">
-        <v>2.601796800737944</v>
+        <v>2.601796800528128</v>
       </c>
       <c r="BS100" t="n">
-        <v>2.312237281017233</v>
+        <v>2.312237280947792</v>
       </c>
       <c r="BT100" t="n">
-        <v>1.837153326435519</v>
+        <v>1.837153325942542</v>
       </c>
       <c r="BU100" t="n">
         <v>7.034023413406607</v>
@@ -42572,10 +42572,10 @@
         <v>10.88000011444092</v>
       </c>
       <c r="BN101" t="n">
-        <v>0.7363540691624345</v>
+        <v>0.7363540684889903</v>
       </c>
       <c r="BO101" t="n">
-        <v>1.365936798296316</v>
+        <v>1.365936797047077</v>
       </c>
       <c r="BP101" t="n">
         <v>18.22503179726196</v>
@@ -42584,13 +42584,13 @@
         <v>16.89238276609682</v>
       </c>
       <c r="BR101" t="n">
-        <v>20.29998254472227</v>
+        <v>20.29998254493796</v>
       </c>
       <c r="BS101" t="n">
-        <v>2.02044202832603</v>
+        <v>2.020442028344198</v>
       </c>
       <c r="BT101" t="n">
-        <v>15.61526429413316</v>
+        <v>15.61526429501795</v>
       </c>
       <c r="BU101" t="n">
         <v>2.743300088818764</v>
@@ -42854,10 +42854,10 @@
         <v>58.16999816894531</v>
       </c>
       <c r="BN102" t="n">
-        <v>71.06675238287495</v>
+        <v>71.06675227600823</v>
       </c>
       <c r="BO102" t="n">
-        <v>103.4731914694659</v>
+        <v>103.473191313868</v>
       </c>
       <c r="BP102" t="n">
         <v>24.27640373021794</v>
@@ -43136,10 +43136,10 @@
         <v>11.38000011444092</v>
       </c>
       <c r="BN103" t="n">
-        <v>2.021214159507341</v>
+        <v>2.021214149102242</v>
       </c>
       <c r="BO103" t="n">
-        <v>3.749352265886117</v>
+        <v>3.749352246584658</v>
       </c>
       <c r="BP103" t="n">
         <v>11.51909866435005</v>
@@ -43148,25 +43148,25 @@
         <v>12.74686594914816</v>
       </c>
       <c r="BR103" t="n">
-        <v>8.289564099385633</v>
+        <v>8.289564103479844</v>
       </c>
       <c r="BS103" t="n">
-        <v>5.481051626963237</v>
+        <v>5.48105162785978</v>
       </c>
       <c r="BT103" t="n">
-        <v>6.174232716169463</v>
+        <v>6.174232725737991</v>
       </c>
       <c r="BU103" t="n">
         <v>10.87624860734963</v>
       </c>
       <c r="BV103" t="n">
-        <v>8.405201989893184</v>
+        <v>8.40520198921573</v>
       </c>
       <c r="BW103" t="n">
-        <v>8.289564099385633</v>
+        <v>8.289564103479844</v>
       </c>
       <c r="BX103" t="n">
-        <v>7.46060768944707</v>
+        <v>7.46060769313186</v>
       </c>
       <c r="BY103" t="n">
         <v>7</v>
@@ -43178,10 +43178,10 @@
         <v>6.3</v>
       </c>
       <c r="CB103" t="n">
-        <v>-34.44105786976437</v>
+        <v>-34.44105783738485</v>
       </c>
       <c r="CC103" t="n">
-        <v>-26.14058079641664</v>
+        <v>-26.14058080236966</v>
       </c>
       <c r="CD103" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>-8.520896315896199</v>
       </c>
       <c r="CP103" t="n">
-        <v>-30.16381761208197</v>
+        <v>-30.1638259014074</v>
       </c>
       <c r="CQ103" t="b">
         <v>0</v>
@@ -43434,37 +43434,37 @@
         <v>33.22999954223633</v>
       </c>
       <c r="BN104" t="n">
-        <v>14.40022174670126</v>
+        <v>14.4002217408783</v>
       </c>
       <c r="BO104" t="n">
-        <v>18.22494522829895</v>
+        <v>18.22494522899162</v>
       </c>
       <c r="BP104" t="n">
-        <v>22.53560398383716</v>
+        <v>22.5356039938063</v>
       </c>
       <c r="BQ104" t="n">
         <v>31.82713953449119</v>
       </c>
       <c r="BR104" t="n">
-        <v>21.71874062575091</v>
+        <v>21.71874063090968</v>
       </c>
       <c r="BS104" t="n">
-        <v>20.85105072956609</v>
+        <v>20.85105073048481</v>
       </c>
       <c r="BT104" t="n">
-        <v>10.80478948692063</v>
+        <v>10.80478949400741</v>
       </c>
       <c r="BU104" t="n">
         <v>9.730162667946294</v>
       </c>
       <c r="BV104" t="n">
-        <v>18.76158175043906</v>
+        <v>18.76158175268945</v>
       </c>
       <c r="BW104" t="n">
-        <v>19.53799797893252</v>
+        <v>19.53799797973821</v>
       </c>
       <c r="BX104" t="n">
-        <v>17.58419818103927</v>
+        <v>17.58419818176439</v>
       </c>
       <c r="BY104" t="n">
         <v>8</v>
@@ -43476,10 +43476,10 @@
         <v>3.3</v>
       </c>
       <c r="CB104" t="n">
-        <v>-47.08336315596627</v>
+        <v>-47.08336315378413</v>
       </c>
       <c r="CC104" t="n">
-        <v>-43.5402286822408</v>
+        <v>-43.54022867546863</v>
       </c>
       <c r="CD104" t="inlineStr">
         <is>
@@ -43724,10 +43724,10 @@
         <v>13.69999980926514</v>
       </c>
       <c r="BN105" t="n">
-        <v>5.914353264751598</v>
+        <v>5.914353213494441</v>
       </c>
       <c r="BO105" t="n">
-        <v>10.97112530611421</v>
+        <v>10.97112521103219</v>
       </c>
       <c r="BP105" t="n">
         <v>4.690568410148916</v>
@@ -43748,13 +43748,13 @@
         <v>7.282189293389739</v>
       </c>
       <c r="BV105" t="n">
-        <v>7.008328794989263</v>
+        <v>7.008328776696864</v>
       </c>
       <c r="BW105" t="n">
-        <v>6.494690045077785</v>
+        <v>6.494690019449207</v>
       </c>
       <c r="BX105" t="n">
-        <v>5.845221040570007</v>
+        <v>5.845221017504286</v>
       </c>
       <c r="BY105" t="n">
         <v>8</v>
@@ -43766,10 +43766,10 @@
         <v>2.6</v>
       </c>
       <c r="CB105" t="n">
-        <v>-57.33415239453537</v>
+        <v>-57.33415256289831</v>
       </c>
       <c r="CC105" t="n">
-        <v>-48.84431465283949</v>
+        <v>-48.84431478636066</v>
       </c>
       <c r="CD105" t="inlineStr">
         <is>
@@ -44018,37 +44018,37 @@
         <v>20.64999961853027</v>
       </c>
       <c r="BN106" t="n">
-        <v>4.52344714879674</v>
+        <v>4.523447147036063</v>
       </c>
       <c r="BO106" t="n">
-        <v>6.059080981814462</v>
+        <v>6.059080981223047</v>
       </c>
       <c r="BP106" t="n">
-        <v>8.719053517016411</v>
+        <v>8.719053519559111</v>
       </c>
       <c r="BQ106" t="n">
         <v>13.33806641923568</v>
       </c>
       <c r="BR106" t="n">
-        <v>5.722211886071653</v>
+        <v>5.722211887579446</v>
       </c>
       <c r="BS106" t="n">
-        <v>7.646329530910441</v>
+        <v>7.646329531121448</v>
       </c>
       <c r="BT106" t="n">
-        <v>4.2746063698747</v>
+        <v>4.274606371506215</v>
       </c>
       <c r="BU106" t="n">
         <v>9.542354752362813</v>
       </c>
       <c r="BV106" t="n">
-        <v>7.478143825760362</v>
+        <v>7.478143826202977</v>
       </c>
       <c r="BW106" t="n">
-        <v>6.852705256362452</v>
+        <v>6.852705256172247</v>
       </c>
       <c r="BX106" t="n">
-        <v>6.167434730726207</v>
+        <v>6.167434730555023</v>
       </c>
       <c r="BY106" t="n">
         <v>8</v>
@@ -44060,10 +44060,10 @@
         <v>3.1</v>
       </c>
       <c r="CB106" t="n">
-        <v>-70.13348743507065</v>
+        <v>-70.13348743589962</v>
       </c>
       <c r="CC106" t="n">
-        <v>-63.78622777770004</v>
+        <v>-63.78622777555663</v>
       </c>
       <c r="CD106" t="inlineStr">
         <is>
@@ -44316,10 +44316,10 @@
         <v>11.10000038146973</v>
       </c>
       <c r="BN107" t="n">
-        <v>2.412775871555975</v>
+        <v>2.41277587443652</v>
       </c>
       <c r="BO107" t="n">
-        <v>4.475699241736334</v>
+        <v>4.475699247079744</v>
       </c>
       <c r="BP107" t="n">
         <v>12.17508319987366</v>
@@ -44328,19 +44328,19 @@
         <v>12.66813745138942</v>
       </c>
       <c r="BR107" t="n">
-        <v>9.658884147722754</v>
+        <v>9.65888414629844</v>
       </c>
       <c r="BS107" t="n">
-        <v>6.050273289071381</v>
+        <v>6.050273296002826</v>
       </c>
       <c r="BT107" t="n">
-        <v>6.768354111463999</v>
+        <v>6.768354108470306</v>
       </c>
       <c r="BU107" t="n">
         <v>6.969597281386505</v>
       </c>
       <c r="BV107" t="n">
-        <v>8.395146960377721</v>
+        <v>8.395146961500128</v>
       </c>
       <c r="BW107" t="n">
         <v>6.969597281386505</v>
@@ -44361,7 +44361,7 @@
         <v>-43.48975371460926</v>
       </c>
       <c r="CC107" t="n">
-        <v>-24.36804800121874</v>
+        <v>-24.36804799110696</v>
       </c>
       <c r="CD107" t="inlineStr">
         <is>
@@ -44610,10 +44610,10 @@
         <v>3.279999971389771</v>
       </c>
       <c r="BN108" t="n">
-        <v>1.613230661360241</v>
+        <v>1.613230660042015</v>
       </c>
       <c r="BO108" t="n">
-        <v>2.249836299266244</v>
+        <v>2.249836297427826</v>
       </c>
       <c r="BP108" t="n">
         <v>0.6472631907457261</v>
@@ -44622,7 +44622,7 @@
         <v>3.871064759123143</v>
       </c>
       <c r="BR108" t="n">
-        <v>0.6813238739311916</v>
+        <v>0.6813238735655982</v>
       </c>
       <c r="BS108" t="n">
         <v>0.4994766813694884</v>
@@ -44892,10 +44892,10 @@
         <v>92.48000335693359</v>
       </c>
       <c r="BN109" t="n">
-        <v>4.734842736601601</v>
+        <v>4.734842734262458</v>
       </c>
       <c r="BO109" t="n">
-        <v>8.78313327639597</v>
+        <v>8.78313327205686</v>
       </c>
       <c r="BP109" t="n">
         <v>40.72316532001894</v>
@@ -44904,13 +44904,13 @@
         <v>40.44265171170704</v>
       </c>
       <c r="BR109" t="n">
-        <v>33.564479938262</v>
+        <v>33.56447994143418</v>
       </c>
       <c r="BS109" t="n">
-        <v>12.17530260612563</v>
+        <v>12.17530260026385</v>
       </c>
       <c r="BT109" t="n">
-        <v>27.92343273088418</v>
+        <v>27.92343273356223</v>
       </c>
       <c r="BU109" t="n">
         <v>40.83466718250591</v>
@@ -45176,25 +45176,25 @@
         <v>45.63999938964844</v>
       </c>
       <c r="BN110" t="n">
-        <v>17.92408490346122</v>
+        <v>17.9240848341346</v>
       </c>
       <c r="BO110" t="n">
-        <v>19.84158815588889</v>
+        <v>19.84158812358237</v>
       </c>
       <c r="BP110" t="n">
-        <v>23.46392691684247</v>
+        <v>23.46392696939155</v>
       </c>
       <c r="BQ110" t="n">
         <v>50.39275454877635</v>
       </c>
       <c r="BR110" t="n">
-        <v>19.87997254239073</v>
+        <v>19.87997255479513</v>
       </c>
       <c r="BS110" t="n">
-        <v>42.32518624420604</v>
+        <v>42.32518609114327</v>
       </c>
       <c r="BT110" t="n">
-        <v>10.16776760562772</v>
+        <v>10.1677676530915</v>
       </c>
       <c r="BU110" t="n">
         <v>125.2323153640256</v>
@@ -45458,25 +45458,25 @@
         <v>1.490000009536743</v>
       </c>
       <c r="BN111" t="n">
-        <v>0.1327367700281518</v>
+        <v>0.1327367703555731</v>
       </c>
       <c r="BO111" t="n">
-        <v>0.1412162774270382</v>
+        <v>0.1412162777626765</v>
       </c>
       <c r="BP111" t="n">
-        <v>0.3868379085369736</v>
+        <v>0.3868379085021857</v>
       </c>
       <c r="BQ111" t="n">
         <v>2.240405914537407</v>
       </c>
       <c r="BR111" t="n">
-        <v>0.1013057113144217</v>
+        <v>0.1013057114173975</v>
       </c>
       <c r="BS111" t="n">
-        <v>0.3907382805539008</v>
+        <v>0.3907382805498145</v>
       </c>
       <c r="BT111" t="n">
-        <v>0.1597607257228986</v>
+        <v>0.1597607256891873</v>
       </c>
       <c r="BU111" t="inlineStr"/>
       <c r="BV111" t="inlineStr"/>
@@ -45740,10 +45740,10 @@
         <v>18.72999954223633</v>
       </c>
       <c r="BN112" t="n">
-        <v>11.97114013257455</v>
+        <v>11.97114008111446</v>
       </c>
       <c r="BO112" t="n">
-        <v>14.93790094803867</v>
+        <v>14.93790088382544</v>
       </c>
       <c r="BP112" t="inlineStr"/>
       <c r="BQ112" t="inlineStr"/>
@@ -46284,10 +46284,10 @@
         <v>13.30000019073486</v>
       </c>
       <c r="BN114" t="n">
-        <v>6.697030024350779</v>
+        <v>6.697030035313027</v>
       </c>
       <c r="BO114" t="n">
-        <v>9.750875715454736</v>
+        <v>9.750875731415768</v>
       </c>
       <c r="BP114" t="n">
         <v>6.721088531761059</v>
@@ -46306,7 +46306,7 @@
         <v>8.072404896288001</v>
       </c>
       <c r="BV114" t="n">
-        <v>8.644470931944737</v>
+        <v>8.644470936431949</v>
       </c>
       <c r="BW114" t="n">
         <v>8.129705699135654</v>
@@ -46327,7 +46327,7 @@
         <v>-44.98695470456367</v>
       </c>
       <c r="CC114" t="n">
-        <v>-35.00397888740854</v>
+        <v>-35.00397885367011</v>
       </c>
       <c r="CD114" t="inlineStr">
         <is>
@@ -46574,10 +46574,10 @@
         <v>4.78000020980835</v>
       </c>
       <c r="BN115" t="n">
-        <v>4.731783407151704</v>
+        <v>4.731783411106878</v>
       </c>
       <c r="BO115" t="n">
-        <v>5.792188201472368</v>
+        <v>5.792188206313906</v>
       </c>
       <c r="BP115" t="inlineStr"/>
       <c r="BQ115" t="inlineStr"/>
@@ -46586,13 +46586,13 @@
       <c r="BT115" t="inlineStr"/>
       <c r="BU115" t="inlineStr"/>
       <c r="BV115" t="n">
-        <v>5.261985804312037</v>
+        <v>5.261985808710392</v>
       </c>
       <c r="BW115" t="n">
-        <v>5.261985804312037</v>
+        <v>5.261985808710392</v>
       </c>
       <c r="BX115" t="n">
-        <v>4.735787223880833</v>
+        <v>4.735787227839353</v>
       </c>
       <c r="BY115" t="n">
         <v>2</v>
@@ -46604,10 +46604,10 @@
         <v>1.2</v>
       </c>
       <c r="CB115" t="n">
-        <v>-0.9249578239932554</v>
+        <v>-0.9249577411790444</v>
       </c>
       <c r="CC115" t="n">
-        <v>10.08338019556305</v>
+        <v>10.08338028757885</v>
       </c>
       <c r="CD115" t="inlineStr">
         <is>
@@ -46856,25 +46856,25 @@
         <v>8.840000152587891</v>
       </c>
       <c r="BN116" t="n">
-        <v>3.431346810753888</v>
+        <v>3.431346819333306</v>
       </c>
       <c r="BO116" t="n">
-        <v>3.536412043612622</v>
+        <v>3.536412051081776</v>
       </c>
       <c r="BP116" t="n">
-        <v>4.231225265792554</v>
+        <v>4.231225264149843</v>
       </c>
       <c r="BQ116" t="n">
         <v>18.33689952444415</v>
       </c>
       <c r="BR116" t="n">
-        <v>3.333938707140726</v>
+        <v>3.333938712271845</v>
       </c>
       <c r="BS116" t="n">
-        <v>7.293756886926792</v>
+        <v>7.293756886588135</v>
       </c>
       <c r="BT116" t="n">
-        <v>1.667762767049798</v>
+        <v>1.667762765366174</v>
       </c>
       <c r="BU116" t="n">
         <v>20.33122852208574</v>
@@ -47140,10 +47140,10 @@
         <v>3.180000066757202</v>
       </c>
       <c r="BN117" t="n">
-        <v>1.082154256613477</v>
+        <v>1.082154258027389</v>
       </c>
       <c r="BO117" t="n">
-        <v>1.350340311513338</v>
+        <v>1.350340313277655</v>
       </c>
       <c r="BP117" t="n">
         <v>1.231789606948257</v>
@@ -47152,7 +47152,7 @@
         <v>3.296396031779571</v>
       </c>
       <c r="BR117" t="n">
-        <v>1.003918285940099</v>
+        <v>1.003918286800368</v>
       </c>
       <c r="BS117" t="n">
         <v>1.804822955819676</v>
@@ -47164,13 +47164,13 @@
         <v>3.992690653062959</v>
       </c>
       <c r="BV117" t="n">
-        <v>1.176565267556837</v>
+        <v>1.176565268229919</v>
       </c>
       <c r="BW117" t="n">
-        <v>1.156971931780867</v>
+        <v>1.156971932487823</v>
       </c>
       <c r="BX117" t="n">
-        <v>1.041274738602781</v>
+        <v>1.041274739239041</v>
       </c>
       <c r="BY117" t="n">
         <v>6</v>
@@ -47182,10 +47182,10 @@
         <v>6.8</v>
       </c>
       <c r="CB117" t="n">
-        <v>-67.25551205209193</v>
+        <v>-67.25551203208373</v>
       </c>
       <c r="CC117" t="n">
-        <v>-63.00109299190562</v>
+        <v>-63.00109297073948</v>
       </c>
       <c r="CD117" t="inlineStr">
         <is>
@@ -47434,25 +47434,25 @@
         <v>12.96000003814697</v>
       </c>
       <c r="BN118" t="n">
-        <v>1.2122654176785</v>
+        <v>1.2122654132083</v>
       </c>
       <c r="BO118" t="n">
-        <v>2.02222411270637</v>
+        <v>2.022224107370945</v>
       </c>
       <c r="BP118" t="n">
-        <v>6.53775501013157</v>
+        <v>6.537755016990216</v>
       </c>
       <c r="BQ118" t="n">
         <v>9.507573293362324</v>
       </c>
       <c r="BR118" t="n">
-        <v>3.557019843446535</v>
+        <v>3.557019845484418</v>
       </c>
       <c r="BS118" t="n">
-        <v>6.343693811408976</v>
+        <v>6.343693811924265</v>
       </c>
       <c r="BT118" t="n">
-        <v>3.249972234632057</v>
+        <v>3.249972237578455</v>
       </c>
       <c r="BU118" t="n">
         <v>11.90042122154035</v>
@@ -47718,10 +47718,10 @@
         <v>4.980000019073486</v>
       </c>
       <c r="BN119" t="n">
-        <v>1.366636233946992</v>
+        <v>1.366636236977667</v>
       </c>
       <c r="BO119" t="n">
-        <v>2.53511021397167</v>
+        <v>2.535110219593572</v>
       </c>
       <c r="BP119" t="n">
         <v>2.179881078715681</v>
@@ -47998,10 +47998,10 @@
         <v>17.54000091552734</v>
       </c>
       <c r="BN120" t="n">
-        <v>3.291278837407485</v>
+        <v>3.291278829152236</v>
       </c>
       <c r="BO120" t="n">
-        <v>6.105322243390885</v>
+        <v>6.105322228077399</v>
       </c>
       <c r="BP120" t="n">
         <v>14.45304801808068</v>
@@ -48010,23 +48010,23 @@
         <v>15.37949780888101</v>
       </c>
       <c r="BR120" t="n">
-        <v>9.984733823821097</v>
+        <v>9.984733829693496</v>
       </c>
       <c r="BS120" t="n">
-        <v>12.88735514338696</v>
+        <v>12.88735514483539</v>
       </c>
       <c r="BT120" t="n">
-        <v>7.388904835101728</v>
+        <v>7.388904843310748</v>
       </c>
       <c r="BU120" t="inlineStr"/>
       <c r="BV120" t="n">
-        <v>11.03314364544372</v>
+        <v>11.03314364547979</v>
       </c>
       <c r="BW120" t="n">
-        <v>11.43604448360403</v>
+        <v>11.43604448726444</v>
       </c>
       <c r="BX120" t="n">
-        <v>10.29244003524362</v>
+        <v>10.292440038538</v>
       </c>
       <c r="BY120" t="n">
         <v>6</v>
@@ -48038,10 +48038,10 @@
         <v>4.7</v>
       </c>
       <c r="CB120" t="n">
-        <v>-41.32018530208737</v>
+        <v>-41.3201852833053</v>
       </c>
       <c r="CC120" t="n">
-        <v>-37.09724589765217</v>
+        <v>-37.09724589744655</v>
       </c>
       <c r="CD120" t="inlineStr">
         <is>
@@ -48566,25 +48566,25 @@
         <v>18.60000038146973</v>
       </c>
       <c r="BN122" t="n">
-        <v>0.5796472208527133</v>
+        <v>0.5796472206859743</v>
       </c>
       <c r="BO122" t="n">
-        <v>0.8145998497491269</v>
+        <v>0.8145998495314645</v>
       </c>
       <c r="BP122" t="n">
-        <v>5.293708529578077</v>
+        <v>5.293708529686355</v>
       </c>
       <c r="BQ122" t="n">
         <v>12.01035285796767</v>
       </c>
       <c r="BR122" t="n">
-        <v>2.166634325573787</v>
+        <v>2.166634325608912</v>
       </c>
       <c r="BS122" t="n">
-        <v>0.7437994164783981</v>
+        <v>0.7437994164797763</v>
       </c>
       <c r="BT122" t="n">
-        <v>2.626065802770876</v>
+        <v>2.626065802834557</v>
       </c>
       <c r="BU122" t="n">
         <v>18.60000038146973</v>
@@ -49112,10 +49112,10 @@
         <v>4.670000076293945</v>
       </c>
       <c r="BN124" t="n">
-        <v>1.435643399993935</v>
+        <v>1.435643400681037</v>
       </c>
       <c r="BO124" t="n">
-        <v>2.09029679039117</v>
+        <v>2.090296791391591</v>
       </c>
       <c r="BP124" t="inlineStr"/>
       <c r="BQ124" t="inlineStr"/>
@@ -49126,13 +49126,13 @@
         <v>8.935570481567899</v>
       </c>
       <c r="BV124" t="n">
-        <v>1.762970095192553</v>
+        <v>1.762970096036314</v>
       </c>
       <c r="BW124" t="n">
-        <v>1.762970095192553</v>
+        <v>1.762970096036314</v>
       </c>
       <c r="BX124" t="n">
-        <v>1.586673085673297</v>
+        <v>1.586673086432683</v>
       </c>
       <c r="BY124" t="n">
         <v>2</v>
@@ -49144,10 +49144,10 @@
         <v>6.2</v>
       </c>
       <c r="CB124" t="n">
-        <v>-66.02413148283155</v>
+        <v>-66.02413146657062</v>
       </c>
       <c r="CC124" t="n">
-        <v>-62.24903498092394</v>
+        <v>-62.24903496285624</v>
       </c>
       <c r="CD124" t="inlineStr">
         <is>
@@ -49396,10 +49396,10 @@
         <v>5.110000133514404</v>
       </c>
       <c r="BN125" t="n">
-        <v>1.246509809223501</v>
+        <v>1.246509801644789</v>
       </c>
       <c r="BO125" t="n">
-        <v>1.814918282229417</v>
+        <v>1.814918271194813</v>
       </c>
       <c r="BP125" t="inlineStr"/>
       <c r="BQ125" t="inlineStr"/>
@@ -49410,13 +49410,13 @@
         <v>5.110000133514404</v>
       </c>
       <c r="BV125" t="n">
-        <v>1.530714045726459</v>
+        <v>1.530714036419801</v>
       </c>
       <c r="BW125" t="n">
-        <v>1.530714045726459</v>
+        <v>1.530714036419801</v>
       </c>
       <c r="BX125" t="n">
-        <v>1.377642641153813</v>
+        <v>1.377642632777821</v>
       </c>
       <c r="BY125" t="n">
         <v>2</v>
@@ -49428,10 +49428,10 @@
         <v>4.1</v>
       </c>
       <c r="CB125" t="n">
-        <v>-73.04026212996713</v>
+        <v>-73.04026229388087</v>
       </c>
       <c r="CC125" t="n">
-        <v>-70.04473569996348</v>
+        <v>-70.04473588208985</v>
       </c>
       <c r="CD125" t="inlineStr">
         <is>
@@ -49678,10 +49678,10 @@
         <v>4.28000020980835</v>
       </c>
       <c r="BN126" t="n">
-        <v>0.814213874650578</v>
+        <v>0.8142138751323587</v>
       </c>
       <c r="BO126" t="n">
-        <v>1.510366737476822</v>
+        <v>1.510366738370525</v>
       </c>
       <c r="BP126" t="inlineStr"/>
       <c r="BQ126" t="inlineStr"/>
@@ -49692,13 +49692,13 @@
         <v>2.641155783568356</v>
       </c>
       <c r="BV126" t="n">
-        <v>1.655245465231919</v>
+        <v>1.655245465690413</v>
       </c>
       <c r="BW126" t="n">
-        <v>1.510366737476822</v>
+        <v>1.510366738370525</v>
       </c>
       <c r="BX126" t="n">
-        <v>1.35933006372914</v>
+        <v>1.359330064533473</v>
       </c>
       <c r="BY126" t="n">
         <v>3</v>
@@ -49710,10 +49710,10 @@
         <v>3.2</v>
       </c>
       <c r="CB126" t="n">
-        <v>-68.23995333892734</v>
+        <v>-68.2399533201345</v>
       </c>
       <c r="CC126" t="n">
-        <v>-61.32604242778677</v>
+        <v>-61.32604241707427</v>
       </c>
       <c r="CD126" t="inlineStr">
         <is>
@@ -49962,10 +49962,10 @@
         <v>6.150000095367432</v>
       </c>
       <c r="BN127" t="n">
-        <v>0.9823296708930745</v>
+        <v>0.9823296678779233</v>
       </c>
       <c r="BO127" t="n">
-        <v>1.822221539506653</v>
+        <v>1.822221533913548</v>
       </c>
       <c r="BP127" t="inlineStr"/>
       <c r="BQ127" t="inlineStr"/>
@@ -50232,10 +50232,10 @@
         <v>1.029999971389771</v>
       </c>
       <c r="BN128" t="n">
-        <v>0.3006580848837518</v>
+        <v>0.3006580854485645</v>
       </c>
       <c r="BO128" t="n">
-        <v>0.4237819491594474</v>
+        <v>0.4237819499555591</v>
       </c>
       <c r="BP128" t="inlineStr"/>
       <c r="BQ128" t="inlineStr"/>
@@ -50244,13 +50244,13 @@
       <c r="BT128" t="inlineStr"/>
       <c r="BU128" t="inlineStr"/>
       <c r="BV128" t="n">
-        <v>0.3622200170215996</v>
+        <v>0.3622200177020618</v>
       </c>
       <c r="BW128" t="n">
-        <v>0.3622200170215996</v>
+        <v>0.3622200177020618</v>
       </c>
       <c r="BX128" t="n">
-        <v>0.3259980153194397</v>
+        <v>0.3259980159318556</v>
       </c>
       <c r="BY128" t="n">
         <v>2</v>
@@ -50262,10 +50262,10 @@
         <v>1.4</v>
       </c>
       <c r="CB128" t="n">
-        <v>-68.3497063713921</v>
+        <v>-68.34970631193424</v>
       </c>
       <c r="CC128" t="n">
-        <v>-64.83300707932456</v>
+        <v>-64.83300701326027</v>
       </c>
       <c r="CD128" t="inlineStr">
         <is>
@@ -50514,25 +50514,25 @@
         <v>7.519999980926514</v>
       </c>
       <c r="BN129" t="n">
-        <v>1.933891672770167</v>
+        <v>1.933891672656562</v>
       </c>
       <c r="BO129" t="n">
-        <v>2.193509933775043</v>
+        <v>2.193509933674907</v>
       </c>
       <c r="BP129" t="n">
-        <v>3.495424121180071</v>
+        <v>3.495424121225839</v>
       </c>
       <c r="BQ129" t="n">
         <v>10.2857475189034</v>
       </c>
       <c r="BR129" t="n">
-        <v>2.189679678833737</v>
+        <v>2.18967967880547</v>
       </c>
       <c r="BS129" t="n">
-        <v>6.102049350329532</v>
+        <v>6.10204935033831</v>
       </c>
       <c r="BT129" t="n">
-        <v>1.552554598228018</v>
+        <v>1.552554598267607</v>
       </c>
       <c r="BU129" t="n">
         <v>17.47579512860355</v>
@@ -51064,10 +51064,10 @@
         <v>3.599999904632568</v>
       </c>
       <c r="BN131" t="n">
-        <v>0.6792706432446347</v>
+        <v>0.6792706431331945</v>
       </c>
       <c r="BO131" t="n">
-        <v>1.260047043218798</v>
+        <v>1.260047043012076</v>
       </c>
       <c r="BP131" t="inlineStr"/>
       <c r="BQ131" t="inlineStr"/>
@@ -51076,13 +51076,13 @@
       <c r="BT131" t="inlineStr"/>
       <c r="BU131" t="inlineStr"/>
       <c r="BV131" t="n">
-        <v>0.9696588432317161</v>
+        <v>0.9696588430726352</v>
       </c>
       <c r="BW131" t="n">
-        <v>0.9696588432317161</v>
+        <v>0.9696588430726352</v>
       </c>
       <c r="BX131" t="n">
-        <v>0.8726929589085446</v>
+        <v>0.8726929587653717</v>
       </c>
       <c r="BY131" t="n">
         <v>2</v>
@@ -51094,10 +51094,10 @@
         <v>1.9</v>
       </c>
       <c r="CB131" t="n">
-        <v>-75.75852827702741</v>
+        <v>-75.75852828100442</v>
       </c>
       <c r="CC131" t="n">
-        <v>-73.06503141891933</v>
+        <v>-73.06503142333824</v>
       </c>
       <c r="CD131" t="inlineStr">
         <is>
@@ -51344,10 +51344,10 @@
         <v>4.28000020980835</v>
       </c>
       <c r="BN132" t="n">
-        <v>4.711356986085154</v>
+        <v>4.711356982837303</v>
       </c>
       <c r="BO132" t="n">
-        <v>6.859735771739985</v>
+        <v>6.859735767011112</v>
       </c>
       <c r="BP132" t="inlineStr"/>
       <c r="BQ132" t="inlineStr"/>
@@ -51356,13 +51356,13 @@
       <c r="BT132" t="inlineStr"/>
       <c r="BU132" t="inlineStr"/>
       <c r="BV132" t="n">
-        <v>5.78554637891257</v>
+        <v>5.785546374924207</v>
       </c>
       <c r="BW132" t="n">
-        <v>5.78554637891257</v>
+        <v>5.785546374924207</v>
       </c>
       <c r="BX132" t="n">
-        <v>5.206991741021313</v>
+        <v>5.206991737431787</v>
       </c>
       <c r="BY132" t="n">
         <v>2</v>
@@ -51374,10 +51374,10 @@
         <v>1.5</v>
       </c>
       <c r="CB132" t="n">
-        <v>21.65867957409451</v>
+        <v>21.65867949022708</v>
       </c>
       <c r="CC132" t="n">
-        <v>35.17631063788278</v>
+        <v>35.17631054469676</v>
       </c>
       <c r="CD132" t="inlineStr">
         <is>
@@ -51626,25 +51626,25 @@
         <v>35.81000137329102</v>
       </c>
       <c r="BN133" t="n">
-        <v>8.065634755123021</v>
+        <v>8.065634756969228</v>
       </c>
       <c r="BO133" t="n">
-        <v>8.292129796888529</v>
+        <v>8.292129797889556</v>
       </c>
       <c r="BP133" t="n">
-        <v>8.783185315621413</v>
+        <v>8.783185314671268</v>
       </c>
       <c r="BQ133" t="n">
         <v>23.1384064783354</v>
       </c>
       <c r="BR133" t="n">
-        <v>4.174063083122938</v>
+        <v>4.174063082430246</v>
       </c>
       <c r="BS133" t="n">
-        <v>13.43033402917563</v>
+        <v>13.43033402900149</v>
       </c>
       <c r="BT133" t="n">
-        <v>3.448221677083917</v>
+        <v>3.448221676105871</v>
       </c>
       <c r="BU133" t="n">
         <v>47.75065260804188</v>
@@ -52190,10 +52190,10 @@
         <v>1.899999976158142</v>
       </c>
       <c r="BN135" t="n">
-        <v>0.5330663192925285</v>
+        <v>0.5330663169671634</v>
       </c>
       <c r="BO135" t="n">
-        <v>0.7761445608899216</v>
+        <v>0.7761445575041901</v>
       </c>
       <c r="BP135" t="n">
         <v>0.4389160318090776</v>
@@ -52256,7 +52256,7 @@
         <v>-5.472637553583393</v>
       </c>
       <c r="CP135" t="n">
-        <v>-55.3406984212687</v>
+        <v>-55.34070345013065</v>
       </c>
       <c r="CQ135" t="b">
         <v>0</v>
@@ -53244,37 +53244,37 @@
         <v>17.29999923706055</v>
       </c>
       <c r="BN139" t="n">
-        <v>2.082354463823603</v>
+        <v>2.082354473035511</v>
       </c>
       <c r="BO139" t="n">
-        <v>3.27284746500776</v>
+        <v>3.272847473898642</v>
       </c>
       <c r="BP139" t="n">
-        <v>7.904674634413487</v>
+        <v>7.904674620918341</v>
       </c>
       <c r="BQ139" t="n">
         <v>11.82515192553242</v>
       </c>
       <c r="BR139" t="n">
-        <v>4.478923524040838</v>
+        <v>4.478923518998244</v>
       </c>
       <c r="BS139" t="n">
-        <v>5.046513525974235</v>
+        <v>5.046513525269567</v>
       </c>
       <c r="BT139" t="n">
-        <v>3.950487906846359</v>
+        <v>3.950487900377388</v>
       </c>
       <c r="BU139" t="n">
         <v>12.81759973415833</v>
       </c>
       <c r="BV139" t="n">
-        <v>5.508707635091244</v>
+        <v>5.508707634004303</v>
       </c>
       <c r="BW139" t="n">
-        <v>4.478923524040838</v>
+        <v>4.478923518998244</v>
       </c>
       <c r="BX139" t="n">
-        <v>4.031031171636754</v>
+        <v>4.03103116709842</v>
       </c>
       <c r="BY139" t="n">
         <v>7</v>
@@ -53286,10 +53286,10 @@
         <v>6.2</v>
       </c>
       <c r="CB139" t="n">
-        <v>-76.69924075487029</v>
+        <v>-76.69924078110344</v>
       </c>
       <c r="CC139" t="n">
-        <v>-68.15775793047241</v>
+        <v>-68.15775793675532</v>
       </c>
       <c r="CD139" t="inlineStr">
         <is>
@@ -53538,25 +53538,25 @@
         <v>4.460000038146973</v>
       </c>
       <c r="BN140" t="n">
-        <v>1.382638828876659</v>
+        <v>1.382638829410539</v>
       </c>
       <c r="BO140" t="n">
-        <v>1.558197246476937</v>
+        <v>1.558197246955805</v>
       </c>
       <c r="BP140" t="n">
-        <v>2.514156470154307</v>
+        <v>2.514156469956167</v>
       </c>
       <c r="BQ140" t="n">
         <v>7.689960038519025</v>
       </c>
       <c r="BR140" t="n">
-        <v>1.79373604606083</v>
+        <v>1.79373604630844</v>
       </c>
       <c r="BS140" t="n">
-        <v>1.859346784874691</v>
+        <v>1.859346784858499</v>
       </c>
       <c r="BT140" t="n">
-        <v>1.109798640462588</v>
+        <v>1.109798640289226</v>
       </c>
       <c r="BU140" t="n">
         <v>0.03409797823786088</v>
@@ -54628,10 +54628,10 @@
         <v>5.639999866485596</v>
       </c>
       <c r="BN144" t="n">
-        <v>3.947371396441933</v>
+        <v>3.947371420385105</v>
       </c>
       <c r="BO144" t="n">
-        <v>7.322373940399785</v>
+        <v>7.32237398481437</v>
       </c>
       <c r="BP144" t="inlineStr"/>
       <c r="BQ144" t="inlineStr"/>
@@ -54640,13 +54640,13 @@
       <c r="BT144" t="inlineStr"/>
       <c r="BU144" t="inlineStr"/>
       <c r="BV144" t="n">
-        <v>5.634872668420859</v>
+        <v>5.634872702599738</v>
       </c>
       <c r="BW144" t="n">
-        <v>5.634872668420859</v>
+        <v>5.634872702599738</v>
       </c>
       <c r="BX144" t="n">
-        <v>5.071385401578773</v>
+        <v>5.071385432339764</v>
       </c>
       <c r="BY144" t="n">
         <v>2</v>
@@ -54658,10 +54658,10 @@
         <v>1.9</v>
       </c>
       <c r="CB144" t="n">
-        <v>-10.08181699233157</v>
+        <v>-10.08181644692391</v>
       </c>
       <c r="CC144" t="n">
-        <v>-0.09090776925729793</v>
+        <v>-0.09090716324878789</v>
       </c>
       <c r="CD144" t="inlineStr">
         <is>
@@ -54910,10 +54910,10 @@
         <v>3.279999971389771</v>
       </c>
       <c r="BN145" t="n">
-        <v>0.5928288445127856</v>
+        <v>0.5928288456513082</v>
       </c>
       <c r="BO145" t="n">
-        <v>1.099697506571217</v>
+        <v>1.099697508683177</v>
       </c>
       <c r="BP145" t="inlineStr"/>
       <c r="BQ145" t="inlineStr"/>
@@ -54924,13 +54924,13 @@
         <v>3.043030546037059</v>
       </c>
       <c r="BV145" t="n">
-        <v>0.8462631755420015</v>
+        <v>0.8462631771672425</v>
       </c>
       <c r="BW145" t="n">
-        <v>0.8462631755420015</v>
+        <v>0.8462631771672425</v>
       </c>
       <c r="BX145" t="n">
-        <v>0.7616368579878013</v>
+        <v>0.7616368594505183</v>
       </c>
       <c r="BY145" t="n">
         <v>2</v>
@@ -54942,10 +54942,10 @@
         <v>5.1</v>
       </c>
       <c r="CB145" t="n">
-        <v>-76.77936388319273</v>
+        <v>-76.77936383859769</v>
       </c>
       <c r="CC145" t="n">
-        <v>-74.19929320354748</v>
+        <v>-74.19929315399744</v>
       </c>
       <c r="CD145" t="inlineStr">
         <is>
@@ -55476,10 +55476,10 @@
         <v>17.54999923706055</v>
       </c>
       <c r="BN147" t="n">
-        <v>8.89376814819359</v>
+        <v>8.893768125940374</v>
       </c>
       <c r="BO147" t="n">
-        <v>12.94932642376987</v>
+        <v>12.94932639136919</v>
       </c>
       <c r="BP147" t="n">
         <v>4.596323144432881</v>
@@ -56314,10 +56314,10 @@
         <v>10.53999996185303</v>
       </c>
       <c r="BN150" t="n">
-        <v>5.631539581907866</v>
+        <v>5.631539580868287</v>
       </c>
       <c r="BO150" t="n">
-        <v>10.3078031902921</v>
+        <v>10.30780318838928</v>
       </c>
       <c r="BP150" t="inlineStr"/>
       <c r="BQ150" t="inlineStr"/>
@@ -56328,13 +56328,13 @@
         <v>3.619100702685365</v>
       </c>
       <c r="BV150" t="n">
-        <v>6.51948115829511</v>
+        <v>6.519481157314313</v>
       </c>
       <c r="BW150" t="n">
-        <v>5.631539581907866</v>
+        <v>5.631539580868287</v>
       </c>
       <c r="BX150" t="n">
-        <v>5.06838562371708</v>
+        <v>5.068385622781459</v>
       </c>
       <c r="BY150" t="n">
         <v>3</v>
@@ -56346,10 +56346,10 @@
         <v>2.8</v>
       </c>
       <c r="CB150" t="n">
-        <v>-51.91284969581715</v>
+        <v>-51.91284970469402</v>
       </c>
       <c r="CC150" t="n">
-        <v>-38.14533983025815</v>
+        <v>-38.14533983956363</v>
       </c>
       <c r="CD150" t="inlineStr">
         <is>
@@ -56598,10 +56598,10 @@
         <v>14.69999980926514</v>
       </c>
       <c r="BN151" t="n">
-        <v>3.918118775451294</v>
+        <v>3.918118771191979</v>
       </c>
       <c r="BO151" t="n">
-        <v>5.704780937057084</v>
+        <v>5.704780930855522</v>
       </c>
       <c r="BP151" t="inlineStr"/>
       <c r="BQ151" t="inlineStr"/>
@@ -56612,7 +56612,7 @@
         <v>4.70041613027538</v>
       </c>
       <c r="BV151" t="n">
-        <v>4.774438614261252</v>
+        <v>4.774438610774293</v>
       </c>
       <c r="BW151" t="n">
         <v>4.70041613027538</v>
@@ -56633,7 +56633,7 @@
         <v>-71.22194168613856</v>
       </c>
       <c r="CC151" t="n">
-        <v>-67.5208253319023</v>
+        <v>-67.52082535562312</v>
       </c>
       <c r="CD151" t="inlineStr">
         <is>
@@ -56884,10 +56884,10 @@
         <v>16.15999984741211</v>
       </c>
       <c r="BN152" t="n">
-        <v>24.72829521754444</v>
+        <v>24.72829517834871</v>
       </c>
       <c r="BO152" t="n">
-        <v>33.56088967067035</v>
+        <v>33.56088961747447</v>
       </c>
       <c r="BP152" t="n">
         <v>2.716455865750314</v>
@@ -56896,7 +56896,7 @@
         <v>7.265725417124772</v>
       </c>
       <c r="BR152" t="n">
-        <v>6.93897229991293</v>
+        <v>6.938972290397754</v>
       </c>
       <c r="BS152" t="n">
         <v>3.053166357475611</v>
